--- a/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Reels Master" sheetId="1" r:id="rId1"/>
-    <sheet name="Reels Variants" sheetId="2" r:id="rId2"/>
+    <sheet name="reel" sheetId="1" r:id="rId1"/>
+    <sheet name="baitcasting_reel_detail" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -452,7 +452,7 @@
         <v>SRE5000</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="str">
         <v>TIAGRA</v>
@@ -476,10 +476,10 @@
         <v>images/shimano_reels/TIAGRA_main.jpg</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -499,7 +499,7 @@
         <v>SRE5001</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="str">
         <v>TALICA</v>
@@ -523,10 +523,10 @@
         <v>images/shimano_reels/TALICA_main.jpg</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v>SRE5002</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="str">
         <v>EXSENCE DC</v>
@@ -570,10 +570,10 @@
         <v>images/shimano_reels/EXSENCE DC_main.jpg</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -593,7 +593,7 @@
         <v>SRE5003</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="str">
         <v>ANTARES DC</v>
@@ -617,10 +617,10 @@
         <v>images/shimano_reels/ANTARES DC_main.jpg</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -640,7 +640,7 @@
         <v>SRE5004</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="str">
         <v>ANTARES DC MD</v>
@@ -664,10 +664,10 @@
         <v>images/shimano_reels/ANTARES DC MD_main.png</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -687,7 +687,7 @@
         <v>SRE5005</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="str">
         <v>OCEA JIGGER 4000/4000HG</v>
@@ -711,10 +711,10 @@
         <v>images/shimano_reels/OCEA JIGGER 4000_4000HG_main.jpg</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -734,7 +734,7 @@
         <v>SRE5006</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="str">
         <v>CALCUTTA CONQUEST DC</v>
@@ -758,10 +758,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST DC_main.jpg</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>SRE5007</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="str">
         <v>OCEA JIGGER LD</v>
@@ -805,10 +805,10 @@
         <v>images/shimano_reels/OCEA JIGGER LD_main.jpg</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -828,7 +828,7 @@
         <v>SRE5008</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="str">
         <v>OCEA JIGGER F CUSTOM</v>
@@ -852,10 +852,10 @@
         <v>images/shimano_reels/OCEA JIGGER F CUSTOM_main.jpg</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -875,7 +875,7 @@
         <v>SRE5009</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="str">
         <v>OCEA CONQUEST CT</v>
@@ -899,10 +899,10 @@
         <v>images/shimano_reels/OCEA CONQUEST CT_main.jpg</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -922,7 +922,7 @@
         <v>SRE5010</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="str">
         <v>KAIKON</v>
@@ -946,10 +946,10 @@
         <v>images/shimano_reels/KAIKON_main.jpg</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -969,7 +969,7 @@
         <v>SRE5011</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="str">
         <v>ANTARES</v>
@@ -993,10 +993,10 @@
         <v>images/shimano_reels/ANTARES_main.jpg</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -1016,7 +1016,7 @@
         <v>SRE5012</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="str">
         <v>OCEA JIGGER</v>
@@ -1040,10 +1040,10 @@
         <v>images/shimano_reels/OCEA JIGGER_main.jpg</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1063,7 +1063,7 @@
         <v>SRE5013</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="str">
         <v>CALCUTTA CONQUEST MD</v>
@@ -1087,10 +1087,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST MD_main.jpg</v>
       </c>
       <c r="J15" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -1110,7 +1110,7 @@
         <v>SRE5014</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="str">
         <v>CALCUTTA CONQUEST BFS LIMITED</v>
@@ -1134,10 +1134,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST BFS LIMITED_main.jpg</v>
       </c>
       <c r="J16" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -1157,7 +1157,7 @@
         <v>SRE5015</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="str">
         <v>Metanium DC</v>
@@ -1181,10 +1181,10 @@
         <v>images/shimano_reels/Metanium DC_main.jpg</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1204,7 +1204,7 @@
         <v>SRE5016</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="str">
         <v>CALCUTTA CONQUEST</v>
@@ -1228,10 +1228,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST_main.jpg</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1251,7 +1251,7 @@
         <v>SRE5017</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="str">
         <v>OCEA CONQUEST</v>
@@ -1275,10 +1275,10 @@
         <v>images/shimano_reels/OCEA CONQUEST_main.jpg</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1298,7 +1298,7 @@
         <v>SRE5018</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="str">
         <v>CALCUTTA CONQUEST SHALLOW EDITION</v>
@@ -1322,10 +1322,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST SHALLOW EDITION_main.jpg</v>
       </c>
       <c r="J20" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K20" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -1345,7 +1345,7 @@
         <v>SRE5019</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="str">
         <v>CALCUTTA CONQUEST BFS</v>
@@ -1369,10 +1369,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST BFS_main.jpg</v>
       </c>
       <c r="J21" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K21" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1392,7 +1392,7 @@
         <v>SRE5020</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="str">
         <v>OCEA CONQUEST FT</v>
@@ -1416,10 +1416,10 @@
         <v>images/shimano_reels/OCEA CONQUEST FT_main.jpg</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K22" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1439,7 +1439,7 @@
         <v>SRE5021</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="str">
         <v>ALDEBARAN DC</v>
@@ -1463,10 +1463,10 @@
         <v>images/shimano_reels/ALDEBARAN DC_main.jpg</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K23" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1486,7 +1486,7 @@
         <v>SRE5022</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="str">
         <v>STILE</v>
@@ -1510,10 +1510,10 @@
         <v>images/shimano_reels/STILE_main.jpg</v>
       </c>
       <c r="J24" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K24" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1533,7 +1533,7 @@
         <v>SRE5023</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="str">
         <v>BARCHETTA PREMIUM</v>
@@ -1557,10 +1557,10 @@
         <v>images/shimano_reels/BARCHETTA PREMIUM_main.jpg</v>
       </c>
       <c r="J25" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K25" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1580,7 +1580,7 @@
         <v>SRE5024</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="str">
         <v>GRAPPLER PREMIUM</v>
@@ -1604,10 +1604,10 @@
         <v>images/shimano_reels/GRAPPLER PREMIUM_main.jpg</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K26" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1627,7 +1627,7 @@
         <v>SRE5025</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="str">
         <v>ALDEBARAN BFS</v>
@@ -1651,10 +1651,10 @@
         <v>images/shimano_reels/ALDEBARAN BFS_main.jpg</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K27" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1674,7 +1674,7 @@
         <v>SRE5026</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="str">
         <v>ALDEBARAN MGL</v>
@@ -1698,10 +1698,10 @@
         <v>images/shimano_reels/ALDEBARAN MGL_main.jpg</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K28" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1721,7 +1721,7 @@
         <v>SRE5027</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="str">
         <v>Metanium SHALLOW EDITION</v>
@@ -1745,10 +1745,10 @@
         <v>images/shimano_reels/Metanium SHALLOW EDITION_main.jpg</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K29" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -1768,7 +1768,7 @@
         <v>SRE5028</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="str">
         <v>Metanium</v>
@@ -1792,10 +1792,10 @@
         <v>images/shimano_reels/Metanium_main.jpg</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K30" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L30" t="str">
         <v/>
@@ -1815,7 +1815,7 @@
         <v>SRE5029</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="str">
         <v>SPEEDMASTER 石鲷</v>
@@ -1839,10 +1839,10 @@
         <v>images/shimano_reels/SPEEDMASTER 石鲷_main.jpg</v>
       </c>
       <c r="J31" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K31" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L31" t="str">
         <v/>
@@ -1862,7 +1862,7 @@
         <v>SRE5030</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="str">
         <v>TYRNOS</v>
@@ -1886,10 +1886,10 @@
         <v>images/shimano_reels/TYRNOS_main.jpg</v>
       </c>
       <c r="J32" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K32" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -1909,7 +1909,7 @@
         <v>SRE5031</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="str">
         <v>EXSENCE DC SS</v>
@@ -1933,10 +1933,10 @@
         <v>images/shimano_reels/EXSENCE DC SS_main.jpg</v>
       </c>
       <c r="J33" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K33" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -1956,7 +1956,7 @@
         <v>SRE5032</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" t="str">
         <v>TRANX 400</v>
@@ -1980,10 +1980,10 @@
         <v>images/shimano_reels/TRANX 400_main.jpg</v>
       </c>
       <c r="J34" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K34" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>SRE5033</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="str">
         <v>Bantam</v>
@@ -2027,10 +2027,10 @@
         <v>images/shimano_reels/Bantam_main.jpg</v>
       </c>
       <c r="J35" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K35" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -2050,7 +2050,7 @@
         <v>SRE5034</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="str">
         <v>TRANX 300</v>
@@ -2074,10 +2074,10 @@
         <v>images/shimano_reels/TRANX 300_main.jpg</v>
       </c>
       <c r="J36" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K36" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -2097,7 +2097,7 @@
         <v>SRE5035</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="str">
         <v>BAYGAME</v>
@@ -2121,10 +2121,10 @@
         <v>images/shimano_reels/BAYGAME_main.jpg</v>
       </c>
       <c r="J37" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K37" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -2144,7 +2144,7 @@
         <v>SRE5036</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="str">
         <v>GRAPPLER</v>
@@ -2168,10 +2168,10 @@
         <v>images/shimano_reels/GRAPPLER_main.jpg</v>
       </c>
       <c r="J38" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K38" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -2191,7 +2191,7 @@
         <v>SRE5037</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="str">
         <v>BARCHETTA F CUSTOM</v>
@@ -2215,10 +2215,10 @@
         <v>images/shimano_reels/BARCHETTA F CUSTOM_main.jpg</v>
       </c>
       <c r="J39" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K39" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -2238,7 +2238,7 @@
         <v>SRE5038</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="str">
         <v>Scorpion DC MD</v>
@@ -2262,10 +2262,10 @@
         <v>images/shimano_reels/Scorpion DC MD_main.jpg</v>
       </c>
       <c r="J40" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K40" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -2285,7 +2285,7 @@
         <v>SRE5039</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="str">
         <v>SLX DC XT</v>
@@ -2309,10 +2309,10 @@
         <v>images/shimano_reels/SLX DC XT_main.jpg</v>
       </c>
       <c r="J41" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K41" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -2332,7 +2332,7 @@
         <v>SRE5040</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="str">
         <v>Scorpion DC</v>
@@ -2356,10 +2356,10 @@
         <v>images/shimano_reels/Scorpion DC_main.jpg</v>
       </c>
       <c r="J42" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K42" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -2379,7 +2379,7 @@
         <v>SRE5041</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="str">
         <v>Scorpion MD 300</v>
@@ -2403,10 +2403,10 @@
         <v>images/shimano_reels/Scorpion MD 300_main.jpg</v>
       </c>
       <c r="J43" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K43" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -2426,7 +2426,7 @@
         <v>SRE5042</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="str">
         <v>GRAPPLER CT</v>
@@ -2450,10 +2450,10 @@
         <v>images/shimano_reels/GRAPPLER CT_main.jpg</v>
       </c>
       <c r="J44" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K44" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2473,7 +2473,7 @@
         <v>SRE5043</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" t="str">
         <v>CURADO DC</v>
@@ -2497,10 +2497,10 @@
         <v>images/shimano_reels/CURADO DC_main.jpg</v>
       </c>
       <c r="J45" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K45" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2520,7 +2520,7 @@
         <v>SRE5044</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="str">
         <v>CHINUMATIC</v>
@@ -2544,10 +2544,10 @@
         <v>images/shimano_reels/CHINUMATIC_main.jpg</v>
       </c>
       <c r="J46" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K46" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>SRE5045</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="str">
         <v>Stephano SS</v>
@@ -2591,10 +2591,10 @@
         <v>images/shimano_reels/Stephano SS_main.jpg</v>
       </c>
       <c r="J47" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K47" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2614,7 +2614,7 @@
         <v>SRE5046</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" t="str">
         <v>STILE SS</v>
@@ -2638,10 +2638,10 @@
         <v>images/shimano_reels/STILE SS_main.jpg</v>
       </c>
       <c r="J48" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K48" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2661,7 +2661,7 @@
         <v>SRE5047</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="str">
         <v>Scorpion MD 200</v>
@@ -2685,10 +2685,10 @@
         <v>images/shimano_reels/Scorpion MD 200_main.jpg</v>
       </c>
       <c r="J49" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K49" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2708,7 +2708,7 @@
         <v>SRE5048</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="str">
         <v>TORIUM</v>
@@ -2732,10 +2732,10 @@
         <v>images/shimano_reels/TORIUM_main.jpg</v>
       </c>
       <c r="J50" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K50" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2755,7 +2755,7 @@
         <v>SRE5049</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="str">
         <v>TRANX 200</v>
@@ -2779,10 +2779,10 @@
         <v>images/shimano_reels/TRANX 200_main.jpg</v>
       </c>
       <c r="J51" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K51" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2802,7 +2802,7 @@
         <v>SRE5050</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="str">
         <v>TRANX</v>
@@ -2826,10 +2826,10 @@
         <v>images/shimano_reels/TRANX_main.jpg</v>
       </c>
       <c r="J52" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K52" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2849,7 +2849,7 @@
         <v>SRE5051</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" t="str">
         <v>BARCHETTA</v>
@@ -2873,10 +2873,10 @@
         <v>images/shimano_reels/BARCHETTA_main.jpg</v>
       </c>
       <c r="J53" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K53" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2896,7 +2896,7 @@
         <v>SRE5052</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="str">
         <v>BARCHETTA SC</v>
@@ -2920,10 +2920,10 @@
         <v>images/shimano_reels/BARCHETTA SC_main.jpg</v>
       </c>
       <c r="J54" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K54" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2943,7 +2943,7 @@
         <v>SRE5053</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="str">
         <v>SLX DC</v>
@@ -2967,10 +2967,10 @@
         <v>images/shimano_reels/SLX DC_main.jpg</v>
       </c>
       <c r="J55" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K55" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -2990,7 +2990,7 @@
         <v>SRE5054</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="str">
         <v>CURADO</v>
@@ -3014,10 +3014,10 @@
         <v>images/shimano_reels/CURADO_main.jpg</v>
       </c>
       <c r="J56" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K56" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -3037,7 +3037,7 @@
         <v>SRE5055</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="str">
         <v>CURADO 150</v>
@@ -3061,10 +3061,10 @@
         <v>images/shimano_reels/CURADO 150_main.jpg</v>
       </c>
       <c r="J57" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K57" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -3084,7 +3084,7 @@
         <v>SRE5056</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="str">
         <v>CURADO MGL</v>
@@ -3108,10 +3108,10 @@
         <v>images/shimano_reels/CURADO MGL_main.jpg</v>
       </c>
       <c r="J58" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K58" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -3131,7 +3131,7 @@
         <v>SRE5057</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="str">
         <v>CURADO BFS</v>
@@ -3155,10 +3155,10 @@
         <v>images/shimano_reels/CURADO BFS_main.jpg</v>
       </c>
       <c r="J59" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K59" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -3178,7 +3178,7 @@
         <v>SRE5058</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="str">
         <v>SLX</v>
@@ -3202,10 +3202,10 @@
         <v>images/shimano_reels/SLX_main.jpg</v>
       </c>
       <c r="J60" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K60" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -3225,7 +3225,7 @@
         <v>SRE5059</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="str">
         <v>BARCHETTA BB</v>
@@ -3249,10 +3249,10 @@
         <v>images/shimano_reels/BARCHETTA BB_main.jpg</v>
       </c>
       <c r="J61" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K61" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -3272,7 +3272,7 @@
         <v>SRE5060</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="str">
         <v>SLX BFS</v>
@@ -3296,10 +3296,10 @@
         <v>images/shimano_reels/SLX BFS_main.jpg</v>
       </c>
       <c r="J62" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K62" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -3319,7 +3319,7 @@
         <v>SRE5061</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" t="str">
         <v>GRAPPLER BB</v>
@@ -3343,10 +3343,10 @@
         <v>images/shimano_reels/GRAPPLER BB_main.jpg</v>
       </c>
       <c r="J63" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K63" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -3366,7 +3366,7 @@
         <v>SRE5062</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64" t="str">
         <v>SLX XT</v>
@@ -3390,10 +3390,10 @@
         <v>images/shimano_reels/SLX XT_main.jpg</v>
       </c>
       <c r="J64" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K64" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -3413,7 +3413,7 @@
         <v>SRE5063</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="str">
         <v>小船</v>
@@ -3437,10 +3437,10 @@
         <v>images/shimano_reels/小船_main.jpg</v>
       </c>
       <c r="J65" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K65" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -3460,7 +3460,7 @@
         <v>SRE5064</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" t="str">
         <v>CARDIFF</v>
@@ -3484,10 +3484,10 @@
         <v>images/shimano_reels/CARDIFF_main.jpg</v>
       </c>
       <c r="J66" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K66" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -3507,7 +3507,7 @@
         <v>SRE5065</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67" t="str">
         <v>幻风 XT</v>
@@ -3531,10 +3531,10 @@
         <v>images/shimano_reels/幻风 XT_main.jpg</v>
       </c>
       <c r="J67" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K67" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -3554,7 +3554,7 @@
         <v>SRE5066</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" t="str">
         <v>TITANOS FUNE GT</v>
@@ -3578,10 +3578,10 @@
         <v>images/shimano_reels/TITANOS FUNE GT_main.jpg</v>
       </c>
       <c r="J68" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K68" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -3601,7 +3601,7 @@
         <v>SRE5067</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="str">
         <v>BASS ONE XT</v>
@@ -3625,10 +3625,10 @@
         <v>images/shimano_reels/BASS ONE XT_main.jpg</v>
       </c>
       <c r="J69" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K69" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L69" t="str">
         <v/>
@@ -3648,7 +3648,7 @@
         <v>SRE5068</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" t="str">
         <v>CAIUS</v>
@@ -3672,10 +3672,10 @@
         <v>images/shimano_reels/CAIUS_main.jpg</v>
       </c>
       <c r="J70" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K70" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L70" t="str">
         <v/>
@@ -3695,7 +3695,7 @@
         <v>SRE5069</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71" t="str">
         <v>BASS RISE</v>
@@ -3719,10 +3719,10 @@
         <v>images/shimano_reels/BASS RISE_main.jpg</v>
       </c>
       <c r="J71" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K71" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L71" t="str">
         <v/>
@@ -3742,7 +3742,7 @@
         <v>SRE5070</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" t="str">
         <v>幻风</v>
@@ -3766,10 +3766,10 @@
         <v>images/shimano_reels/幻风_main.jpg</v>
       </c>
       <c r="J72" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K72" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L72" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>SRE5071</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" t="str">
         <v>CHINU SPECIAL</v>
@@ -3813,10 +3813,10 @@
         <v>images/shimano_reels/CHINU SPECIAL_main.jpg</v>
       </c>
       <c r="J73" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="K73" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="L73" t="str">
         <v/>
@@ -3958,7 +3958,7 @@
         <v>handle_style</v>
       </c>
       <c r="AM1" t="str">
-        <v>MAX DURABILITY</v>
+        <v>MAX_DURABILITY</v>
       </c>
     </row>
     <row r="2">
@@ -4008,10 +4008,10 @@
         <v>017383</v>
       </c>
       <c r="P2" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB2" t="str">
         <v/>
@@ -4097,10 +4097,10 @@
         <v>020307</v>
       </c>
       <c r="P3" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q3" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB3" t="str">
         <v/>
@@ -4186,10 +4186,10 @@
         <v>020314</v>
       </c>
       <c r="P4" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q4" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB4" t="str">
         <v/>
@@ -4275,10 +4275,10 @@
         <v>020321</v>
       </c>
       <c r="P5" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q5" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB5" t="str">
         <v/>
@@ -4364,10 +4364,10 @@
         <v>020338</v>
       </c>
       <c r="P6" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q6" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB6" t="str">
         <v/>
@@ -4453,10 +4453,10 @@
         <v>020345</v>
       </c>
       <c r="P7" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q7" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB7" t="str">
         <v/>
@@ -4542,10 +4542,10 @@
         <v>020352</v>
       </c>
       <c r="P8" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q8" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB8" t="str">
         <v/>
@@ -4631,10 +4631,10 @@
         <v>020369</v>
       </c>
       <c r="P9" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q9" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB9" t="str">
         <v/>
@@ -4720,10 +4720,10 @@
         <v>020376</v>
       </c>
       <c r="P10" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q10" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB10" t="str">
         <v/>
@@ -4809,10 +4809,10 @@
         <v>032218</v>
       </c>
       <c r="P11" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q11" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB11" t="str">
         <v/>
@@ -4898,10 +4898,10 @@
         <v>032225</v>
       </c>
       <c r="P12" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q12" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB12" t="str">
         <v/>
@@ -4987,10 +4987,10 @@
         <v>032881</v>
       </c>
       <c r="P13" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q13" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB13" t="str">
         <v/>
@@ -5076,10 +5076,10 @@
         <v>044969</v>
       </c>
       <c r="P14" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q14" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB14" t="str">
         <v/>
@@ -5165,10 +5165,10 @@
         <v>044976</v>
       </c>
       <c r="P15" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q15" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB15" t="str">
         <v/>
@@ -5254,10 +5254,10 @@
         <v>042606</v>
       </c>
       <c r="P16" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q16" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB16" t="str">
         <v/>
@@ -5343,10 +5343,10 @@
         <v>042613</v>
       </c>
       <c r="P17" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q17" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB17" t="str">
         <v/>
@@ -5432,10 +5432,10 @@
         <v>042620</v>
       </c>
       <c r="P18" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q18" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB18" t="str">
         <v/>
@@ -5521,10 +5521,10 @@
         <v>042637</v>
       </c>
       <c r="P19" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q19" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB19" t="str">
         <v/>
@@ -5610,10 +5610,10 @@
         <v>042644</v>
       </c>
       <c r="P20" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q20" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB20" t="str">
         <v/>
@@ -5699,10 +5699,10 @@
         <v>042651</v>
       </c>
       <c r="P21" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q21" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB21" t="str">
         <v/>
@@ -5788,10 +5788,10 @@
         <v>046000</v>
       </c>
       <c r="P22" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q22" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB22" t="str">
         <v/>
@@ -5877,10 +5877,10 @@
         <v>046017</v>
       </c>
       <c r="P23" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q23" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB23" t="str">
         <v/>
@@ -5966,10 +5966,10 @@
         <v>046024</v>
       </c>
       <c r="P24" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q24" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB24" t="str">
         <v/>
@@ -6055,10 +6055,10 @@
         <v>046031</v>
       </c>
       <c r="P25" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q25" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB25" t="str">
         <v/>
@@ -6144,10 +6144,10 @@
         <v/>
       </c>
       <c r="P26" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q26" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB26" t="str">
         <v/>
@@ -6233,10 +6233,10 @@
         <v/>
       </c>
       <c r="P27" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q27" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB27" t="str">
         <v/>
@@ -6322,10 +6322,10 @@
         <v/>
       </c>
       <c r="P28" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q28" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB28" t="str">
         <v/>
@@ -6411,10 +6411,10 @@
         <v/>
       </c>
       <c r="P29" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q29" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB29" t="str">
         <v/>
@@ -6500,10 +6500,10 @@
         <v/>
       </c>
       <c r="P30" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q30" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB30" t="str">
         <v/>
@@ -6589,10 +6589,10 @@
         <v/>
       </c>
       <c r="P31" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q31" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB31" t="str">
         <v/>
@@ -6678,10 +6678,10 @@
         <v>040664</v>
       </c>
       <c r="P32" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q32" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB32" t="str">
         <v/>
@@ -6767,10 +6767,10 @@
         <v>040671</v>
       </c>
       <c r="P33" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q33" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB33" t="str">
         <v/>
@@ -6856,10 +6856,10 @@
         <v>039781</v>
       </c>
       <c r="P34" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q34" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB34" t="str">
         <v/>
@@ -6945,10 +6945,10 @@
         <v>039798</v>
       </c>
       <c r="P35" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q35" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB35" t="str">
         <v/>
@@ -7034,10 +7034,10 @@
         <v>040831</v>
       </c>
       <c r="P36" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q36" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB36" t="str">
         <v/>
@@ -7123,10 +7123,10 @@
         <v>040848</v>
       </c>
       <c r="P37" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q37" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB37" t="str">
         <v/>
@@ -7212,10 +7212,10 @@
         <v>040855</v>
       </c>
       <c r="P38" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q38" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB38" t="str">
         <v/>
@@ -7301,10 +7301,10 @@
         <v>040862</v>
       </c>
       <c r="P39" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q39" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB39" t="str">
         <v/>
@@ -7390,10 +7390,10 @@
         <v>040398</v>
       </c>
       <c r="P40" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q40" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB40" t="str">
         <v/>
@@ -7479,10 +7479,10 @@
         <v>040404</v>
       </c>
       <c r="P41" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q41" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB41" t="str">
         <v/>
@@ -7568,10 +7568,10 @@
         <v>046581</v>
       </c>
       <c r="P42" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q42" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB42" t="str">
         <v/>
@@ -7657,10 +7657,10 @@
         <v>046598</v>
       </c>
       <c r="P43" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q43" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB43" t="str">
         <v/>
@@ -7746,10 +7746,10 @@
         <v>048653</v>
       </c>
       <c r="P44" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q44" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB44" t="str">
         <v/>
@@ -7835,10 +7835,10 @@
         <v>048660</v>
       </c>
       <c r="P45" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q45" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB45" t="str">
         <v/>
@@ -7924,10 +7924,10 @@
         <v>040008</v>
       </c>
       <c r="P46" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q46" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB46" t="str">
         <v/>
@@ -8013,10 +8013,10 @@
         <v>040015</v>
       </c>
       <c r="P47" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q47" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB47" t="str">
         <v/>
@@ -8102,10 +8102,10 @@
         <v>040022</v>
       </c>
       <c r="P48" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q48" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB48" t="str">
         <v/>
@@ -8191,10 +8191,10 @@
         <v>040039</v>
       </c>
       <c r="P49" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q49" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB49" t="str">
         <v/>
@@ -8280,10 +8280,10 @@
         <v>040046</v>
       </c>
       <c r="P50" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q50" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB50" t="str">
         <v/>
@@ -8369,10 +8369,10 @@
         <v>040053</v>
       </c>
       <c r="P51" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q51" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB51" t="str">
         <v/>
@@ -8458,10 +8458,10 @@
         <v>040060</v>
       </c>
       <c r="P52" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q52" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB52" t="str">
         <v/>
@@ -8547,10 +8547,10 @@
         <v>048677</v>
       </c>
       <c r="P53" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q53" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB53" t="str">
         <v/>
@@ -8636,10 +8636,10 @@
         <v>048684</v>
       </c>
       <c r="P54" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q54" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB54" t="str">
         <v/>
@@ -8725,10 +8725,10 @@
         <v>048714</v>
       </c>
       <c r="P55" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q55" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB55" t="str">
         <v/>
@@ -8814,10 +8814,10 @@
         <v>048752</v>
       </c>
       <c r="P56" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q56" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB56" t="str">
         <v/>
@@ -8903,10 +8903,10 @@
         <v>049223</v>
       </c>
       <c r="P57" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q57" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB57" t="str">
         <v/>
@@ -8992,10 +8992,10 @@
         <v>049230</v>
       </c>
       <c r="P58" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q58" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB58" t="str">
         <v/>
@@ -9081,10 +9081,10 @@
         <v>046680</v>
       </c>
       <c r="P59" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q59" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB59" t="str">
         <v/>
@@ -9170,10 +9170,10 @@
         <v>046697</v>
       </c>
       <c r="P60" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q60" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB60" t="str">
         <v/>
@@ -9259,10 +9259,10 @@
         <v>046703</v>
       </c>
       <c r="P61" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q61" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB61" t="str">
         <v/>
@@ -9348,10 +9348,10 @@
         <v>046710</v>
       </c>
       <c r="P62" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q62" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB62" t="str">
         <v/>
@@ -9437,10 +9437,10 @@
         <v>046727</v>
       </c>
       <c r="P63" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q63" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB63" t="str">
         <v/>
@@ -9526,10 +9526,10 @@
         <v>047663</v>
       </c>
       <c r="P64" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q64" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB64" t="str">
         <v/>
@@ -9615,10 +9615,10 @@
         <v>047670</v>
       </c>
       <c r="P65" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q65" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB65" t="str">
         <v/>
@@ -9704,10 +9704,10 @@
         <v>047687</v>
       </c>
       <c r="P66" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q66" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB66" t="str">
         <v/>
@@ -9793,10 +9793,10 @@
         <v>047694</v>
       </c>
       <c r="P67" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q67" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB67" t="str">
         <v/>
@@ -9882,10 +9882,10 @@
         <v>047700</v>
       </c>
       <c r="P68" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q68" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB68" t="str">
         <v/>
@@ -9971,10 +9971,10 @@
         <v>047717</v>
       </c>
       <c r="P69" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q69" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB69" t="str">
         <v/>
@@ -10060,10 +10060,10 @@
         <v>033567</v>
       </c>
       <c r="P70" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q70" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB70" t="str">
         <v/>
@@ -10149,10 +10149,10 @@
         <v>033574</v>
       </c>
       <c r="P71" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q71" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB71" t="str">
         <v/>
@@ -10238,10 +10238,10 @@
         <v>033581</v>
       </c>
       <c r="P72" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q72" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB72" t="str">
         <v/>
@@ -10327,10 +10327,10 @@
         <v>047724</v>
       </c>
       <c r="P73" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q73" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB73" t="str">
         <v/>
@@ -10416,10 +10416,10 @@
         <v>047731</v>
       </c>
       <c r="P74" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q74" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB74" t="str">
         <v/>
@@ -10505,10 +10505,10 @@
         <v>047748</v>
       </c>
       <c r="P75" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q75" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB75" t="str">
         <v/>
@@ -10594,10 +10594,10 @@
         <v>047755</v>
       </c>
       <c r="P76" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q76" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB76" t="str">
         <v/>
@@ -10683,10 +10683,10 @@
         <v>047762</v>
       </c>
       <c r="P77" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q77" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB77" t="str">
         <v/>
@@ -10772,10 +10772,10 @@
         <v>047779</v>
       </c>
       <c r="P78" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q78" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB78" t="str">
         <v/>
@@ -10861,10 +10861,10 @@
         <v>043764</v>
       </c>
       <c r="P79" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q79" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB79" t="str">
         <v/>
@@ -10950,10 +10950,10 @@
         <v>043771</v>
       </c>
       <c r="P80" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q80" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB80" t="str">
         <v/>
@@ -11039,10 +11039,10 @@
         <v>043788</v>
       </c>
       <c r="P81" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q81" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB81" t="str">
         <v/>
@@ -11128,10 +11128,10 @@
         <v>043795</v>
       </c>
       <c r="P82" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q82" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB82" t="str">
         <v/>
@@ -11217,10 +11217,10 @@
         <v>043801</v>
       </c>
       <c r="P83" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q83" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB83" t="str">
         <v/>
@@ -11306,10 +11306,10 @@
         <v>043818</v>
       </c>
       <c r="P84" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q84" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB84" t="str">
         <v/>
@@ -11395,10 +11395,10 @@
         <v>036650</v>
       </c>
       <c r="P85" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q85" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB85" t="str">
         <v/>
@@ -11484,10 +11484,10 @@
         <v>036667</v>
       </c>
       <c r="P86" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q86" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB86" t="str">
         <v/>
@@ -11573,10 +11573,10 @@
         <v>036674</v>
       </c>
       <c r="P87" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q87" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB87" t="str">
         <v/>
@@ -11662,10 +11662,10 @@
         <v>036698</v>
       </c>
       <c r="P88" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q88" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB88" t="str">
         <v/>
@@ -11751,10 +11751,10 @@
         <v>036681</v>
       </c>
       <c r="P89" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q89" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB89" t="str">
         <v/>
@@ -11840,10 +11840,10 @@
         <v>036704</v>
       </c>
       <c r="P90" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q90" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB90" t="str">
         <v/>
@@ -11929,10 +11929,10 @@
         <v>036711</v>
       </c>
       <c r="P91" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q91" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB91" t="str">
         <v/>
@@ -12018,10 +12018,10 @@
         <v>036735</v>
       </c>
       <c r="P92" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q92" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB92" t="str">
         <v/>
@@ -12107,10 +12107,10 @@
         <v>036728</v>
       </c>
       <c r="P93" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q93" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB93" t="str">
         <v/>
@@ -12196,10 +12196,10 @@
         <v>036742</v>
       </c>
       <c r="P94" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q94" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB94" t="str">
         <v/>
@@ -12285,10 +12285,10 @@
         <v>045928</v>
       </c>
       <c r="P95" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q95" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB95" t="str">
         <v/>
@@ -12374,10 +12374,10 @@
         <v>045935</v>
       </c>
       <c r="P96" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q96" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB96" t="str">
         <v/>
@@ -12463,10 +12463,10 @@
         <v>045942</v>
       </c>
       <c r="P97" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q97" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB97" t="str">
         <v/>
@@ -12552,10 +12552,10 @@
         <v>045959</v>
       </c>
       <c r="P98" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q98" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB98" t="str">
         <v/>
@@ -12641,10 +12641,10 @@
         <v>045966</v>
       </c>
       <c r="P99" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q99" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB99" t="str">
         <v/>
@@ -12730,10 +12730,10 @@
         <v>045973</v>
       </c>
       <c r="P100" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q100" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB100" t="str">
         <v/>
@@ -12819,10 +12819,10 @@
         <v>049322</v>
       </c>
       <c r="P101" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q101" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB101" t="str">
         <v/>
@@ -12908,10 +12908,10 @@
         <v>049339</v>
       </c>
       <c r="P102" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q102" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB102" t="str">
         <v/>
@@ -12997,10 +12997,10 @@
         <v>049346</v>
       </c>
       <c r="P103" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q103" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB103" t="str">
         <v/>
@@ -13086,10 +13086,10 @@
         <v>049353</v>
       </c>
       <c r="P104" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q104" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB104" t="str">
         <v/>
@@ -13175,10 +13175,10 @@
         <v>046604</v>
       </c>
       <c r="P105" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q105" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB105" t="str">
         <v/>
@@ -13264,10 +13264,10 @@
         <v>046611</v>
       </c>
       <c r="P106" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q106" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB106" t="str">
         <v/>
@@ -13353,10 +13353,10 @@
         <v>046628</v>
       </c>
       <c r="P107" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q107" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB107" t="str">
         <v/>
@@ -13442,10 +13442,10 @@
         <v>046635</v>
       </c>
       <c r="P108" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q108" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB108" t="str">
         <v/>
@@ -13531,10 +13531,10 @@
         <v>046642</v>
       </c>
       <c r="P109" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q109" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB109" t="str">
         <v/>
@@ -13620,10 +13620,10 @@
         <v>046659</v>
       </c>
       <c r="P110" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q110" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB110" t="str">
         <v/>
@@ -13709,10 +13709,10 @@
         <v>042323</v>
       </c>
       <c r="P111" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q111" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB111" t="str">
         <v/>
@@ -13798,10 +13798,10 @@
         <v>042330</v>
       </c>
       <c r="P112" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q112" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB112" t="str">
         <v/>
@@ -13887,10 +13887,10 @@
         <v>042347</v>
       </c>
       <c r="P113" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q113" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB113" t="str">
         <v/>
@@ -13976,10 +13976,10 @@
         <v>042354</v>
       </c>
       <c r="P114" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q114" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB114" t="str">
         <v/>
@@ -14065,10 +14065,10 @@
         <v>042361</v>
       </c>
       <c r="P115" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q115" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB115" t="str">
         <v/>
@@ -14154,10 +14154,10 @@
         <v>042378</v>
       </c>
       <c r="P116" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q116" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB116" t="str">
         <v/>
@@ -14243,10 +14243,10 @@
         <v>042385</v>
       </c>
       <c r="P117" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q117" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB117" t="str">
         <v/>
@@ -14332,10 +14332,10 @@
         <v>042392</v>
       </c>
       <c r="P118" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q118" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB118" t="str">
         <v/>
@@ -14421,10 +14421,10 @@
         <v>044402</v>
       </c>
       <c r="P119" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q119" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB119" t="str">
         <v/>
@@ -14510,10 +14510,10 @@
         <v>044419</v>
       </c>
       <c r="P120" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q120" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB120" t="str">
         <v/>
@@ -14599,10 +14599,10 @@
         <v>044426</v>
       </c>
       <c r="P121" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q121" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB121" t="str">
         <v/>
@@ -14688,10 +14688,10 @@
         <v>044433</v>
       </c>
       <c r="P122" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q122" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB122" t="str">
         <v/>
@@ -14777,10 +14777,10 @@
         <v>044440</v>
       </c>
       <c r="P123" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q123" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB123" t="str">
         <v/>
@@ -14866,10 +14866,10 @@
         <v>044457</v>
       </c>
       <c r="P124" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q124" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB124" t="str">
         <v/>
@@ -14955,10 +14955,10 @@
         <v>044464</v>
       </c>
       <c r="P125" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q125" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB125" t="str">
         <v/>
@@ -15044,10 +15044,10 @@
         <v>044471</v>
       </c>
       <c r="P126" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q126" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB126" t="str">
         <v/>
@@ -15133,10 +15133,10 @@
         <v>046260</v>
       </c>
       <c r="P127" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q127" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB127" t="str">
         <v/>
@@ -15222,10 +15222,10 @@
         <v>046277</v>
       </c>
       <c r="P128" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q128" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB128" t="str">
         <v/>
@@ -15311,10 +15311,10 @@
         <v>046284</v>
       </c>
       <c r="P129" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q129" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB129" t="str">
         <v/>
@@ -15400,10 +15400,10 @@
         <v>046291</v>
       </c>
       <c r="P130" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q130" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB130" t="str">
         <v/>
@@ -15489,10 +15489,10 @@
         <v>046734</v>
       </c>
       <c r="P131" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q131" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB131" t="str">
         <v/>
@@ -15578,10 +15578,10 @@
         <v>046741</v>
       </c>
       <c r="P132" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q132" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB132" t="str">
         <v/>
@@ -15667,10 +15667,10 @@
         <v>045683</v>
       </c>
       <c r="P133" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q133" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB133" t="str">
         <v/>
@@ -15756,10 +15756,10 @@
         <v>045690</v>
       </c>
       <c r="P134" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q134" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB134" t="str">
         <v/>
@@ -15845,10 +15845,10 @@
         <v>045706</v>
       </c>
       <c r="P135" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q135" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB135" t="str">
         <v/>
@@ -15934,10 +15934,10 @@
         <v>045713</v>
       </c>
       <c r="P136" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q136" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB136" t="str">
         <v/>
@@ -16023,10 +16023,10 @@
         <v>049179</v>
       </c>
       <c r="P137" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q137" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB137" t="str">
         <v/>
@@ -16112,10 +16112,10 @@
         <v>049186</v>
       </c>
       <c r="P138" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q138" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB138" t="str">
         <v/>
@@ -16201,10 +16201,10 @@
         <v>049193</v>
       </c>
       <c r="P139" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q139" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB139" t="str">
         <v/>
@@ -16290,10 +16290,10 @@
         <v>049209</v>
       </c>
       <c r="P140" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q140" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB140" t="str">
         <v/>
@@ -16379,10 +16379,10 @@
         <v>047830</v>
       </c>
       <c r="P141" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q141" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB141" t="str">
         <v/>
@@ -16468,10 +16468,10 @@
         <v>047847</v>
       </c>
       <c r="P142" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q142" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB142" t="str">
         <v/>
@@ -16557,10 +16557,10 @@
         <v>047854</v>
       </c>
       <c r="P143" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q143" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB143" t="str">
         <v/>
@@ -16646,10 +16646,10 @@
         <v>047861</v>
       </c>
       <c r="P144" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q144" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB144" t="str">
         <v/>
@@ -16735,10 +16735,10 @@
         <v>048462</v>
       </c>
       <c r="P145" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q145" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB145" t="str">
         <v/>
@@ -16824,10 +16824,10 @@
         <v>048479</v>
       </c>
       <c r="P146" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q146" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB146" t="str">
         <v/>
@@ -16913,10 +16913,10 @@
         <v>048486</v>
       </c>
       <c r="P147" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q147" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB147" t="str">
         <v/>
@@ -17002,10 +17002,10 @@
         <v>048493</v>
       </c>
       <c r="P148" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q148" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB148" t="str">
         <v/>
@@ -17091,10 +17091,10 @@
         <v>047274</v>
       </c>
       <c r="P149" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q149" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB149" t="str">
         <v/>
@@ -17180,10 +17180,10 @@
         <v>047281</v>
       </c>
       <c r="P150" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q150" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB150" t="str">
         <v/>
@@ -17269,10 +17269,10 @@
         <v>047298</v>
       </c>
       <c r="P151" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q151" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB151" t="str">
         <v/>
@@ -17358,10 +17358,10 @@
         <v>047304</v>
       </c>
       <c r="P152" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q152" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB152" t="str">
         <v/>
@@ -17447,10 +17447,10 @@
         <v>047311</v>
       </c>
       <c r="P153" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q153" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB153" t="str">
         <v/>
@@ -17536,10 +17536,10 @@
         <v>047328</v>
       </c>
       <c r="P154" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q154" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB154" t="str">
         <v/>
@@ -17625,10 +17625,10 @@
         <v>047182</v>
       </c>
       <c r="P155" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q155" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB155" t="str">
         <v/>
@@ -17714,10 +17714,10 @@
         <v>047199</v>
       </c>
       <c r="P156" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q156" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB156" t="str">
         <v/>
@@ -17803,10 +17803,10 @@
         <v>043986</v>
       </c>
       <c r="P157" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q157" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB157" t="str">
         <v/>
@@ -17892,10 +17892,10 @@
         <v>043993</v>
       </c>
       <c r="P158" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q158" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB158" t="str">
         <v/>
@@ -17981,10 +17981,10 @@
         <v>044006</v>
       </c>
       <c r="P159" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q159" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB159" t="str">
         <v/>
@@ -18070,10 +18070,10 @@
         <v>044013</v>
       </c>
       <c r="P160" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q160" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB160" t="str">
         <v/>
@@ -18159,10 +18159,10 @@
         <v>038777</v>
       </c>
       <c r="P161" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q161" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB161" t="str">
         <v/>
@@ -18248,10 +18248,10 @@
         <v>038784</v>
       </c>
       <c r="P162" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q162" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB162" t="str">
         <v/>
@@ -18337,10 +18337,10 @@
         <v>038791</v>
       </c>
       <c r="P163" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q163" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB163" t="str">
         <v/>
@@ -18426,10 +18426,10 @@
         <v>038807</v>
       </c>
       <c r="P164" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q164" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB164" t="str">
         <v/>
@@ -18515,10 +18515,10 @@
         <v>044778</v>
       </c>
       <c r="P165" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q165" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB165" t="str">
         <v/>
@@ -18604,10 +18604,10 @@
         <v>044785</v>
       </c>
       <c r="P166" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q166" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB166" t="str">
         <v/>
@@ -18693,10 +18693,10 @@
         <v>044792</v>
       </c>
       <c r="P167" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q167" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB167" t="str">
         <v/>
@@ -18782,10 +18782,10 @@
         <v>044808</v>
       </c>
       <c r="P168" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q168" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB168" t="str">
         <v/>
@@ -18871,10 +18871,10 @@
         <v>044815</v>
       </c>
       <c r="P169" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q169" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB169" t="str">
         <v/>
@@ -18960,10 +18960,10 @@
         <v>044822</v>
       </c>
       <c r="P170" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q170" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB170" t="str">
         <v/>
@@ -19049,10 +19049,10 @@
         <v>-</v>
       </c>
       <c r="P171" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q171" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB171" t="str">
         <v/>
@@ -19138,10 +19138,10 @@
         <v>-</v>
       </c>
       <c r="P172" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q172" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB172" t="str">
         <v/>
@@ -19227,10 +19227,10 @@
         <v>-</v>
       </c>
       <c r="P173" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q173" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB173" t="str">
         <v/>
@@ -19316,10 +19316,10 @@
         <v>-</v>
       </c>
       <c r="P174" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q174" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB174" t="str">
         <v/>
@@ -19405,10 +19405,10 @@
         <v>-</v>
       </c>
       <c r="P175" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q175" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB175" t="str">
         <v/>
@@ -19494,10 +19494,10 @@
         <v>-</v>
       </c>
       <c r="P176" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q176" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB176" t="str">
         <v/>
@@ -19583,10 +19583,10 @@
         <v>041128</v>
       </c>
       <c r="P177" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q177" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB177" t="str">
         <v/>
@@ -19672,10 +19672,10 @@
         <v>041135</v>
       </c>
       <c r="P178" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q178" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB178" t="str">
         <v/>
@@ -19761,10 +19761,10 @@
         <v>041142</v>
       </c>
       <c r="P179" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q179" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB179" t="str">
         <v/>
@@ -19850,10 +19850,10 @@
         <v>041159</v>
       </c>
       <c r="P180" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q180" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB180" t="str">
         <v/>
@@ -19939,10 +19939,10 @@
         <v>041166</v>
       </c>
       <c r="P181" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q181" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB181" t="str">
         <v/>
@@ -20028,10 +20028,10 @@
         <v>041173</v>
       </c>
       <c r="P182" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q182" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB182" t="str">
         <v/>
@@ -20117,10 +20117,10 @@
         <v>046116</v>
       </c>
       <c r="P183" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q183" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB183" t="str">
         <v/>
@@ -20206,10 +20206,10 @@
         <v>046123</v>
       </c>
       <c r="P184" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q184" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB184" t="str">
         <v/>
@@ -20295,10 +20295,10 @@
         <v>046130</v>
       </c>
       <c r="P185" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q185" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB185" t="str">
         <v/>
@@ -20384,10 +20384,10 @@
         <v>046147</v>
       </c>
       <c r="P186" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q186" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB186" t="str">
         <v/>
@@ -20473,10 +20473,10 @@
         <v>044365</v>
       </c>
       <c r="P187" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q187" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB187" t="str">
         <v/>
@@ -20562,10 +20562,10 @@
         <v>044372</v>
       </c>
       <c r="P188" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q188" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB188" t="str">
         <v/>
@@ -20651,10 +20651,10 @@
         <v>044389</v>
       </c>
       <c r="P189" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q189" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB189" t="str">
         <v/>
@@ -20740,10 +20740,10 @@
         <v>023742</v>
       </c>
       <c r="P190" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q190" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB190" t="str">
         <v/>
@@ -20829,10 +20829,10 @@
         <v>022523</v>
       </c>
       <c r="P191" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q191" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB191" t="str">
         <v/>
@@ -20918,10 +20918,10 @@
         <v>022530</v>
       </c>
       <c r="P192" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q192" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB192" t="str">
         <v/>
@@ -21007,10 +21007,10 @@
         <v>041876</v>
       </c>
       <c r="P193" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q193" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB193" t="str">
         <v/>
@@ -21096,10 +21096,10 @@
         <v>041883</v>
       </c>
       <c r="P194" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q194" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB194" t="str">
         <v/>
@@ -21185,10 +21185,10 @@
         <v>041890</v>
       </c>
       <c r="P195" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q195" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB195" t="str">
         <v/>
@@ -21274,10 +21274,10 @@
         <v>041906</v>
       </c>
       <c r="P196" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q196" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB196" t="str">
         <v/>
@@ -21363,10 +21363,10 @@
         <v/>
       </c>
       <c r="P197" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q197" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB197" t="str">
         <v/>
@@ -21452,10 +21452,10 @@
         <v/>
       </c>
       <c r="P198" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q198" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB198" t="str">
         <v/>
@@ -21541,10 +21541,10 @@
         <v/>
       </c>
       <c r="P199" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q199" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB199" t="str">
         <v/>
@@ -21630,10 +21630,10 @@
         <v/>
       </c>
       <c r="P200" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q200" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB200" t="str">
         <v/>
@@ -21719,10 +21719,10 @@
         <v>044617</v>
       </c>
       <c r="P201" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q201" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB201" t="str">
         <v/>
@@ -21808,10 +21808,10 @@
         <v>044624</v>
       </c>
       <c r="P202" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q202" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB202" t="str">
         <v/>
@@ -21897,10 +21897,10 @@
         <v>044631</v>
       </c>
       <c r="P203" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q203" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB203" t="str">
         <v/>
@@ -21986,10 +21986,10 @@
         <v>044648</v>
       </c>
       <c r="P204" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q204" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB204" t="str">
         <v/>
@@ -22075,10 +22075,10 @@
         <v>044655</v>
       </c>
       <c r="P205" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q205" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB205" t="str">
         <v/>
@@ -22164,10 +22164,10 @@
         <v>044662</v>
       </c>
       <c r="P206" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q206" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB206" t="str">
         <v/>
@@ -22253,10 +22253,10 @@
         <v/>
       </c>
       <c r="P207" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q207" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB207" t="str">
         <v/>
@@ -22342,10 +22342,10 @@
         <v/>
       </c>
       <c r="P208" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q208" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB208" t="str">
         <v/>
@@ -22431,10 +22431,10 @@
         <v/>
       </c>
       <c r="P209" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q209" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB209" t="str">
         <v/>
@@ -22520,10 +22520,10 @@
         <v/>
       </c>
       <c r="P210" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q210" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB210" t="str">
         <v/>
@@ -22609,10 +22609,10 @@
         <v>038685</v>
       </c>
       <c r="P211" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q211" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB211" t="str">
         <v/>
@@ -22698,10 +22698,10 @@
         <v>038692</v>
       </c>
       <c r="P212" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q212" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB212" t="str">
         <v/>
@@ -22787,10 +22787,10 @@
         <v>038708</v>
       </c>
       <c r="P213" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q213" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB213" t="str">
         <v/>
@@ -22876,10 +22876,10 @@
         <v>038715</v>
       </c>
       <c r="P214" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q214" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB214" t="str">
         <v/>
@@ -22965,10 +22965,10 @@
         <v>041913</v>
       </c>
       <c r="P215" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q215" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB215" t="str">
         <v/>
@@ -23054,10 +23054,10 @@
         <v>041920</v>
       </c>
       <c r="P216" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q216" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB216" t="str">
         <v/>
@@ -23143,10 +23143,10 @@
         <v>049735</v>
       </c>
       <c r="P217" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q217" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB217" t="str">
         <v/>
@@ -23232,10 +23232,10 @@
         <v>049742</v>
       </c>
       <c r="P218" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q218" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB218" t="str">
         <v/>
@@ -23321,10 +23321,10 @@
         <v>049759</v>
       </c>
       <c r="P219" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q219" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB219" t="str">
         <v/>
@@ -23410,10 +23410,10 @@
         <v>049766</v>
       </c>
       <c r="P220" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q220" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB220" t="str">
         <v/>
@@ -23499,10 +23499,10 @@
         <v>048318</v>
       </c>
       <c r="P221" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q221" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB221" t="str">
         <v/>
@@ -23588,10 +23588,10 @@
         <v>048325</v>
       </c>
       <c r="P222" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q222" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB222" t="str">
         <v/>
@@ -23677,10 +23677,10 @@
         <v>048332</v>
       </c>
       <c r="P223" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q223" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB223" t="str">
         <v/>
@@ -23766,10 +23766,10 @@
         <v>048349</v>
       </c>
       <c r="P224" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q224" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB224" t="str">
         <v/>
@@ -23855,10 +23855,10 @@
         <v>048356</v>
       </c>
       <c r="P225" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q225" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB225" t="str">
         <v/>
@@ -23944,10 +23944,10 @@
         <v>048363</v>
       </c>
       <c r="P226" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q226" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB226" t="str">
         <v/>
@@ -24033,10 +24033,10 @@
         <v>049124</v>
       </c>
       <c r="P227" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q227" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB227" t="str">
         <v/>
@@ -24122,10 +24122,10 @@
         <v>049148</v>
       </c>
       <c r="P228" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q228" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB228" t="str">
         <v/>
@@ -24211,10 +24211,10 @@
         <v>044686</v>
       </c>
       <c r="P229" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q229" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB229" t="str">
         <v/>
@@ -24300,10 +24300,10 @@
         <v>044693</v>
       </c>
       <c r="P230" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q230" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB230" t="str">
         <v/>
@@ -24389,10 +24389,10 @@
         <v>044709</v>
       </c>
       <c r="P231" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q231" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB231" t="str">
         <v/>
@@ -24478,10 +24478,10 @@
         <v>044716</v>
       </c>
       <c r="P232" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q232" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB232" t="str">
         <v/>
@@ -24567,10 +24567,10 @@
         <v>044723</v>
       </c>
       <c r="P233" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q233" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB233" t="str">
         <v/>
@@ -24656,10 +24656,10 @@
         <v>044730</v>
       </c>
       <c r="P234" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q234" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB234" t="str">
         <v/>
@@ -24745,10 +24745,10 @@
         <v>043061</v>
       </c>
       <c r="P235" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q235" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB235" t="str">
         <v/>
@@ -24834,10 +24834,10 @@
         <v>043078</v>
       </c>
       <c r="P236" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q236" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB236" t="str">
         <v/>
@@ -24923,10 +24923,10 @@
         <v>043085</v>
       </c>
       <c r="P237" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q237" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB237" t="str">
         <v/>
@@ -25012,10 +25012,10 @@
         <v>043092</v>
       </c>
       <c r="P238" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q238" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB238" t="str">
         <v/>
@@ -25101,10 +25101,10 @@
         <v>043108</v>
       </c>
       <c r="P239" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q239" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB239" t="str">
         <v/>
@@ -25190,10 +25190,10 @@
         <v>043115</v>
       </c>
       <c r="P240" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q240" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB240" t="str">
         <v/>
@@ -25279,10 +25279,10 @@
         <v>047144</v>
       </c>
       <c r="P241" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q241" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB241" t="str">
         <v/>
@@ -25368,10 +25368,10 @@
         <v>047151</v>
       </c>
       <c r="P242" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q242" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB242" t="str">
         <v/>
@@ -25457,10 +25457,10 @@
         <v>047168</v>
       </c>
       <c r="P243" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q243" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB243" t="str">
         <v/>
@@ -25546,10 +25546,10 @@
         <v>047175</v>
       </c>
       <c r="P244" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q244" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB244" t="str">
         <v/>
@@ -25635,10 +25635,10 @@
         <v>043498</v>
       </c>
       <c r="P245" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q245" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB245" t="str">
         <v/>
@@ -25724,10 +25724,10 @@
         <v>043504</v>
       </c>
       <c r="P246" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q246" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB246" t="str">
         <v/>
@@ -25813,10 +25813,10 @@
         <v>048837</v>
       </c>
       <c r="P247" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q247" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB247" t="str">
         <v/>
@@ -25902,10 +25902,10 @@
         <v>048844</v>
       </c>
       <c r="P248" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q248" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB248" t="str">
         <v/>
@@ -25991,10 +25991,10 @@
         <v/>
       </c>
       <c r="P249" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q249" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB249" t="str">
         <v/>
@@ -26080,10 +26080,10 @@
         <v/>
       </c>
       <c r="P250" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q250" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB250" t="str">
         <v/>
@@ -26169,10 +26169,10 @@
         <v/>
       </c>
       <c r="P251" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q251" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB251" t="str">
         <v/>
@@ -26258,10 +26258,10 @@
         <v/>
       </c>
       <c r="P252" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q252" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB252" t="str">
         <v/>
@@ -26347,10 +26347,10 @@
         <v>021922</v>
       </c>
       <c r="P253" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q253" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB253" t="str">
         <v/>
@@ -26436,10 +26436,10 @@
         <v>021939</v>
       </c>
       <c r="P254" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q254" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB254" t="str">
         <v/>
@@ -26525,10 +26525,10 @@
         <v>021946</v>
       </c>
       <c r="P255" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q255" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB255" t="str">
         <v/>
@@ -26614,10 +26614,10 @@
         <v>021953</v>
       </c>
       <c r="P256" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q256" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB256" t="str">
         <v/>
@@ -26703,10 +26703,10 @@
         <v>021960</v>
       </c>
       <c r="P257" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q257" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB257" t="str">
         <v/>
@@ -26792,10 +26792,10 @@
         <v>021977</v>
       </c>
       <c r="P258" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q258" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB258" t="str">
         <v/>
@@ -26881,10 +26881,10 @@
         <v/>
       </c>
       <c r="P259" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q259" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB259" t="str">
         <v/>
@@ -26970,10 +26970,10 @@
         <v/>
       </c>
       <c r="P260" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q260" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB260" t="str">
         <v/>
@@ -27059,10 +27059,10 @@
         <v/>
       </c>
       <c r="P261" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q261" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB261" t="str">
         <v/>
@@ -27148,10 +27148,10 @@
         <v/>
       </c>
       <c r="P262" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q262" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB262" t="str">
         <v/>
@@ -27237,10 +27237,10 @@
         <v/>
       </c>
       <c r="P263" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q263" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB263" t="str">
         <v/>
@@ -27326,10 +27326,10 @@
         <v/>
       </c>
       <c r="P264" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q264" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB264" t="str">
         <v/>
@@ -27415,10 +27415,10 @@
         <v>037718</v>
       </c>
       <c r="P265" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q265" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB265" t="str">
         <v/>
@@ -27504,10 +27504,10 @@
         <v>037725</v>
       </c>
       <c r="P266" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q266" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB266" t="str">
         <v/>
@@ -27593,10 +27593,10 @@
         <v>036902</v>
       </c>
       <c r="P267" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q267" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB267" t="str">
         <v/>
@@ -27682,10 +27682,10 @@
         <v>036919</v>
       </c>
       <c r="P268" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q268" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB268" t="str">
         <v/>
@@ -27771,10 +27771,10 @@
         <v>036926</v>
       </c>
       <c r="P269" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q269" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB269" t="str">
         <v/>
@@ -27860,10 +27860,10 @@
         <v>036933</v>
       </c>
       <c r="P270" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q270" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB270" t="str">
         <v/>
@@ -27949,10 +27949,10 @@
         <v>046895</v>
       </c>
       <c r="P271" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q271" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB271" t="str">
         <v/>
@@ -28038,10 +28038,10 @@
         <v>046901</v>
       </c>
       <c r="P272" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q272" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB272" t="str">
         <v/>
@@ -28127,10 +28127,10 @@
         <v>046918</v>
       </c>
       <c r="P273" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q273" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB273" t="str">
         <v/>
@@ -28216,10 +28216,10 @@
         <v>046925</v>
       </c>
       <c r="P274" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q274" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB274" t="str">
         <v/>
@@ -28305,10 +28305,10 @@
         <v>042187</v>
       </c>
       <c r="P275" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q275" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB275" t="str">
         <v/>
@@ -28394,10 +28394,10 @@
         <v>042194</v>
       </c>
       <c r="P276" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q276" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB276" t="str">
         <v/>
@@ -28483,10 +28483,10 @@
         <v>042200</v>
       </c>
       <c r="P277" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q277" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB277" t="str">
         <v/>
@@ -28572,10 +28572,10 @@
         <v/>
       </c>
       <c r="P278" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q278" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB278" t="str">
         <v/>
@@ -28661,10 +28661,10 @@
         <v/>
       </c>
       <c r="P279" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q279" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB279" t="str">
         <v/>
@@ -28750,10 +28750,10 @@
         <v/>
       </c>
       <c r="P280" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q280" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB280" t="str">
         <v/>
@@ -28839,10 +28839,10 @@
         <v/>
       </c>
       <c r="P281" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q281" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB281" t="str">
         <v/>
@@ -28928,10 +28928,10 @@
         <v/>
       </c>
       <c r="P282" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q282" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB282" t="str">
         <v/>
@@ -29017,10 +29017,10 @@
         <v/>
       </c>
       <c r="P283" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q283" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB283" t="str">
         <v/>
@@ -29106,10 +29106,10 @@
         <v/>
       </c>
       <c r="P284" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q284" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB284" t="str">
         <v/>
@@ -29195,10 +29195,10 @@
         <v/>
       </c>
       <c r="P285" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q285" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB285" t="str">
         <v/>
@@ -29284,10 +29284,10 @@
         <v>042682</v>
       </c>
       <c r="P286" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q286" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB286" t="str">
         <v/>
@@ -29373,10 +29373,10 @@
         <v>042699</v>
       </c>
       <c r="P287" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q287" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB287" t="str">
         <v/>
@@ -29462,10 +29462,10 @@
         <v>042705</v>
       </c>
       <c r="P288" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q288" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB288" t="str">
         <v/>
@@ -29551,10 +29551,10 @@
         <v>042712</v>
       </c>
       <c r="P289" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q289" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB289" t="str">
         <v/>
@@ -29640,10 +29640,10 @@
         <v>042729</v>
       </c>
       <c r="P290" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q290" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB290" t="str">
         <v/>
@@ -29729,10 +29729,10 @@
         <v>042736</v>
       </c>
       <c r="P291" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q291" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB291" t="str">
         <v/>
@@ -29818,10 +29818,10 @@
         <v>042743</v>
       </c>
       <c r="P292" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q292" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB292" t="str">
         <v/>
@@ -29907,10 +29907,10 @@
         <v>042750</v>
       </c>
       <c r="P293" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q293" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB293" t="str">
         <v/>
@@ -29996,10 +29996,10 @@
         <v>042767</v>
       </c>
       <c r="P294" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q294" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB294" t="str">
         <v/>
@@ -30085,10 +30085,10 @@
         <v>042774</v>
       </c>
       <c r="P295" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q295" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB295" t="str">
         <v/>
@@ -30174,10 +30174,10 @@
         <v>039255</v>
       </c>
       <c r="P296" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q296" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB296" t="str">
         <v/>
@@ -30263,10 +30263,10 @@
         <v>039262</v>
       </c>
       <c r="P297" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q297" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB297" t="str">
         <v/>
@@ -30352,10 +30352,10 @@
         <v>039279</v>
       </c>
       <c r="P298" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q298" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB298" t="str">
         <v/>
@@ -30441,10 +30441,10 @@
         <v>039286</v>
       </c>
       <c r="P299" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q299" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB299" t="str">
         <v/>
@@ -30530,10 +30530,10 @@
         <v>045607</v>
       </c>
       <c r="P300" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q300" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB300" t="str">
         <v/>
@@ -30619,10 +30619,10 @@
         <v>045614</v>
       </c>
       <c r="P301" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q301" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB301" t="str">
         <v/>
@@ -30708,10 +30708,10 @@
         <v>045621</v>
       </c>
       <c r="P302" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q302" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB302" t="str">
         <v/>
@@ -30797,10 +30797,10 @@
         <v>045638</v>
       </c>
       <c r="P303" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q303" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB303" t="str">
         <v/>
@@ -30886,10 +30886,10 @@
         <v>045645</v>
       </c>
       <c r="P304" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q304" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB304" t="str">
         <v/>
@@ -30975,10 +30975,10 @@
         <v>045652</v>
       </c>
       <c r="P305" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q305" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB305" t="str">
         <v/>
@@ -31064,10 +31064,10 @@
         <v/>
       </c>
       <c r="P306" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q306" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB306" t="str">
         <v/>
@@ -31153,10 +31153,10 @@
         <v/>
       </c>
       <c r="P307" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q307" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB307" t="str">
         <v/>
@@ -31242,10 +31242,10 @@
         <v/>
       </c>
       <c r="P308" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q308" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB308" t="str">
         <v/>
@@ -31331,10 +31331,10 @@
         <v/>
       </c>
       <c r="P309" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q309" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB309" t="str">
         <v/>
@@ -31420,10 +31420,10 @@
         <v/>
       </c>
       <c r="P310" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q310" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB310" t="str">
         <v/>
@@ -31509,10 +31509,10 @@
         <v/>
       </c>
       <c r="P311" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q311" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB311" t="str">
         <v/>
@@ -31598,10 +31598,10 @@
         <v/>
       </c>
       <c r="P312" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q312" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB312" t="str">
         <v/>
@@ -31687,10 +31687,10 @@
         <v/>
       </c>
       <c r="P313" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q313" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB313" t="str">
         <v/>
@@ -31776,10 +31776,10 @@
         <v/>
       </c>
       <c r="P314" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q314" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB314" t="str">
         <v/>
@@ -31865,10 +31865,10 @@
         <v/>
       </c>
       <c r="P315" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q315" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB315" t="str">
         <v/>
@@ -31954,10 +31954,10 @@
         <v/>
       </c>
       <c r="P316" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q316" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB316" t="str">
         <v/>
@@ -32043,10 +32043,10 @@
         <v/>
       </c>
       <c r="P317" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q317" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB317" t="str">
         <v/>
@@ -32132,10 +32132,10 @@
         <v/>
       </c>
       <c r="P318" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q318" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB318" t="str">
         <v/>
@@ -32221,10 +32221,10 @@
         <v/>
       </c>
       <c r="P319" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q319" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB319" t="str">
         <v/>
@@ -32310,10 +32310,10 @@
         <v/>
       </c>
       <c r="P320" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q320" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB320" t="str">
         <v/>
@@ -32399,10 +32399,10 @@
         <v/>
       </c>
       <c r="P321" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q321" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB321" t="str">
         <v/>
@@ -32488,10 +32488,10 @@
         <v/>
       </c>
       <c r="P322" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q322" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB322" t="str">
         <v/>
@@ -32577,10 +32577,10 @@
         <v/>
       </c>
       <c r="P323" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q323" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB323" t="str">
         <v/>
@@ -32666,10 +32666,10 @@
         <v/>
       </c>
       <c r="P324" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q324" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB324" t="str">
         <v/>
@@ -32755,10 +32755,10 @@
         <v/>
       </c>
       <c r="P325" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q325" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB325" t="str">
         <v/>
@@ -32844,10 +32844,10 @@
         <v/>
       </c>
       <c r="P326" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q326" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB326" t="str">
         <v/>
@@ -32933,10 +32933,10 @@
         <v/>
       </c>
       <c r="P327" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q327" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB327" t="str">
         <v/>
@@ -33022,10 +33022,10 @@
         <v/>
       </c>
       <c r="P328" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q328" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB328" t="str">
         <v/>
@@ -33111,10 +33111,10 @@
         <v/>
       </c>
       <c r="P329" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q329" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB329" t="str">
         <v/>
@@ -33200,10 +33200,10 @@
         <v/>
       </c>
       <c r="P330" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q330" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB330" t="str">
         <v/>
@@ -33289,10 +33289,10 @@
         <v/>
       </c>
       <c r="P331" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q331" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB331" t="str">
         <v/>
@@ -33378,10 +33378,10 @@
         <v/>
       </c>
       <c r="P332" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q332" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB332" t="str">
         <v/>
@@ -33467,10 +33467,10 @@
         <v/>
       </c>
       <c r="P333" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q333" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB333" t="str">
         <v/>
@@ -33556,10 +33556,10 @@
         <v>046956</v>
       </c>
       <c r="P334" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q334" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB334" t="str">
         <v/>
@@ -33645,10 +33645,10 @@
         <v>046963</v>
       </c>
       <c r="P335" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q335" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB335" t="str">
         <v/>
@@ -33734,10 +33734,10 @@
         <v>046970</v>
       </c>
       <c r="P336" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q336" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB336" t="str">
         <v/>
@@ -33823,10 +33823,10 @@
         <v>046987</v>
       </c>
       <c r="P337" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q337" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB337" t="str">
         <v/>
@@ -33912,10 +33912,10 @@
         <v>046994</v>
       </c>
       <c r="P338" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q338" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB338" t="str">
         <v/>
@@ -34001,10 +34001,10 @@
         <v>047007</v>
       </c>
       <c r="P339" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q339" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB339" t="str">
         <v/>
@@ -34090,10 +34090,10 @@
         <v>044037</v>
       </c>
       <c r="P340" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q340" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB340" t="str">
         <v/>
@@ -34179,10 +34179,10 @@
         <v>044044</v>
       </c>
       <c r="P341" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q341" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB341" t="str">
         <v/>
@@ -34268,10 +34268,10 @@
         <v>044051</v>
       </c>
       <c r="P342" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q342" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB342" t="str">
         <v/>
@@ -34357,10 +34357,10 @@
         <v>044068</v>
       </c>
       <c r="P343" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q343" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB343" t="str">
         <v/>
@@ -34446,10 +34446,10 @@
         <v>044075</v>
       </c>
       <c r="P344" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q344" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB344" t="str">
         <v/>
@@ -34535,10 +34535,10 @@
         <v>044082</v>
       </c>
       <c r="P345" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q345" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB345" t="str">
         <v/>
@@ -34624,10 +34624,10 @@
         <v>044099</v>
       </c>
       <c r="P346" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q346" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB346" t="str">
         <v/>
@@ -34713,10 +34713,10 @@
         <v>044105</v>
       </c>
       <c r="P347" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q347" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB347" t="str">
         <v/>
@@ -34802,10 +34802,10 @@
         <v>048189</v>
       </c>
       <c r="P348" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q348" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB348" t="str">
         <v/>
@@ -34891,10 +34891,10 @@
         <v>048196</v>
       </c>
       <c r="P349" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q349" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB349" t="str">
         <v/>
@@ -34980,10 +34980,10 @@
         <v>044983</v>
       </c>
       <c r="P350" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q350" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB350" t="str">
         <v/>
@@ -35069,10 +35069,10 @@
         <v>044990</v>
       </c>
       <c r="P351" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q351" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB351" t="str">
         <v/>
@@ -35158,10 +35158,10 @@
         <v/>
       </c>
       <c r="P352" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q352" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB352" t="str">
         <v/>
@@ -35247,10 +35247,10 @@
         <v/>
       </c>
       <c r="P353" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q353" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB353" t="str">
         <v/>
@@ -35336,10 +35336,10 @@
         <v/>
       </c>
       <c r="P354" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q354" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB354" t="str">
         <v/>
@@ -35425,10 +35425,10 @@
         <v/>
       </c>
       <c r="P355" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q355" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB355" t="str">
         <v/>
@@ -35514,10 +35514,10 @@
         <v/>
       </c>
       <c r="P356" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q356" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB356" t="str">
         <v/>
@@ -35603,10 +35603,10 @@
         <v/>
       </c>
       <c r="P357" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q357" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB357" t="str">
         <v/>
@@ -35692,10 +35692,10 @@
         <v>039293</v>
       </c>
       <c r="P358" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q358" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB358" t="str">
         <v/>
@@ -35781,10 +35781,10 @@
         <v>039309</v>
       </c>
       <c r="P359" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q359" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB359" t="str">
         <v/>
@@ -35870,10 +35870,10 @@
         <v>039316</v>
       </c>
       <c r="P360" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q360" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB360" t="str">
         <v/>
@@ -35959,10 +35959,10 @@
         <v>039323</v>
       </c>
       <c r="P361" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q361" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB361" t="str">
         <v/>
@@ -36048,10 +36048,10 @@
         <v/>
       </c>
       <c r="P362" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q362" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB362" t="str">
         <v/>
@@ -36137,10 +36137,10 @@
         <v/>
       </c>
       <c r="P363" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q363" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB363" t="str">
         <v/>
@@ -36226,10 +36226,10 @@
         <v/>
       </c>
       <c r="P364" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q364" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB364" t="str">
         <v/>
@@ -36315,10 +36315,10 @@
         <v/>
       </c>
       <c r="P365" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q365" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB365" t="str">
         <v/>
@@ -36404,10 +36404,10 @@
         <v/>
       </c>
       <c r="P366" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q366" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB366" t="str">
         <v/>
@@ -36493,10 +36493,10 @@
         <v/>
       </c>
       <c r="P367" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q367" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB367" t="str">
         <v/>
@@ -36582,10 +36582,10 @@
         <v>041937</v>
       </c>
       <c r="P368" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q368" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB368" t="str">
         <v/>
@@ -36671,10 +36671,10 @@
         <v>041944</v>
       </c>
       <c r="P369" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q369" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB369" t="str">
         <v/>
@@ -36760,10 +36760,10 @@
         <v>041951</v>
       </c>
       <c r="P370" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q370" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB370" t="str">
         <v/>
@@ -36849,10 +36849,10 @@
         <v>041968</v>
       </c>
       <c r="P371" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q371" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB371" t="str">
         <v/>
@@ -36938,10 +36938,10 @@
         <v/>
       </c>
       <c r="P372" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q372" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB372" t="str">
         <v/>
@@ -37027,10 +37027,10 @@
         <v/>
       </c>
       <c r="P373" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q373" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB373" t="str">
         <v/>
@@ -37116,10 +37116,10 @@
         <v/>
       </c>
       <c r="P374" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q374" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB374" t="str">
         <v/>
@@ -37205,10 +37205,10 @@
         <v/>
       </c>
       <c r="P375" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q375" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB375" t="str">
         <v/>
@@ -37294,10 +37294,10 @@
         <v/>
       </c>
       <c r="P376" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q376" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB376" t="str">
         <v/>
@@ -37383,10 +37383,10 @@
         <v/>
       </c>
       <c r="P377" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q377" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB377" t="str">
         <v/>
@@ -37472,10 +37472,10 @@
         <v>016454</v>
       </c>
       <c r="P378" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q378" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB378" t="str">
         <v/>
@@ -37561,10 +37561,10 @@
         <v>016461</v>
       </c>
       <c r="P379" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q379" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB379" t="str">
         <v/>
@@ -37650,10 +37650,10 @@
         <v>037312</v>
       </c>
       <c r="P380" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q380" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB380" t="str">
         <v/>
@@ -37739,10 +37739,10 @@
         <v>037329</v>
       </c>
       <c r="P381" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q381" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB381" t="str">
         <v/>
@@ -37828,10 +37828,10 @@
         <v/>
       </c>
       <c r="P382" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q382" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB382" t="str">
         <v/>
@@ -37917,10 +37917,10 @@
         <v/>
       </c>
       <c r="P383" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q383" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB383" t="str">
         <v/>
@@ -38006,10 +38006,10 @@
         <v>038869</v>
       </c>
       <c r="P384" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q384" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB384" t="str">
         <v/>
@@ -38095,10 +38095,10 @@
         <v>038876</v>
       </c>
       <c r="P385" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q385" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB385" t="str">
         <v/>
@@ -38184,10 +38184,10 @@
         <v>042163</v>
       </c>
       <c r="P386" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q386" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB386" t="str">
         <v/>
@@ -38273,10 +38273,10 @@
         <v>042170</v>
       </c>
       <c r="P387" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q387" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB387" t="str">
         <v/>
@@ -38362,10 +38362,10 @@
         <v>011657</v>
       </c>
       <c r="P388" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q388" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB388" t="str">
         <v/>
@@ -38451,10 +38451,10 @@
         <v>011664</v>
       </c>
       <c r="P389" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="Q389" t="str">
-        <v>2026-04-09 00:35:43</v>
+        <v>2026-04-09 12:52:05</v>
       </c>
       <c r="AB389" t="str">
         <v/>

--- a/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
@@ -476,10 +476,10 @@
         <v>images/shimano_reels/TIAGRA_main.jpg</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -523,10 +523,10 @@
         <v>images/shimano_reels/TALICA_main.jpg</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -570,10 +570,10 @@
         <v>images/shimano_reels/EXSENCE DC_main.jpg</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -617,10 +617,10 @@
         <v>images/shimano_reels/ANTARES DC_main.jpg</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -664,10 +664,10 @@
         <v>images/shimano_reels/ANTARES DC MD_main.png</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -711,10 +711,10 @@
         <v>images/shimano_reels/OCEA JIGGER 4000_4000HG_main.jpg</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -758,10 +758,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST DC_main.jpg</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -805,10 +805,10 @@
         <v>images/shimano_reels/OCEA JIGGER LD_main.jpg</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -852,10 +852,10 @@
         <v>images/shimano_reels/OCEA JIGGER F CUSTOM_main.jpg</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -899,10 +899,10 @@
         <v>images/shimano_reels/OCEA CONQUEST CT_main.jpg</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -946,10 +946,10 @@
         <v>images/shimano_reels/KAIKON_main.jpg</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -993,10 +993,10 @@
         <v>images/shimano_reels/ANTARES_main.jpg</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -1040,10 +1040,10 @@
         <v>images/shimano_reels/OCEA JIGGER_main.jpg</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1087,10 +1087,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST MD_main.jpg</v>
       </c>
       <c r="J15" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -1134,10 +1134,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST BFS LIMITED_main.jpg</v>
       </c>
       <c r="J16" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -1181,10 +1181,10 @@
         <v>images/shimano_reels/Metanium DC_main.jpg</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1228,10 +1228,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST_main.jpg</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1275,10 +1275,10 @@
         <v>images/shimano_reels/OCEA CONQUEST_main.jpg</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1322,10 +1322,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST SHALLOW EDITION_main.jpg</v>
       </c>
       <c r="J20" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K20" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -1369,10 +1369,10 @@
         <v>images/shimano_reels/CALCUTTA CONQUEST BFS_main.jpg</v>
       </c>
       <c r="J21" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K21" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1416,10 +1416,10 @@
         <v>images/shimano_reels/OCEA CONQUEST FT_main.jpg</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K22" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1463,10 +1463,10 @@
         <v>images/shimano_reels/ALDEBARAN DC_main.jpg</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K23" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1510,10 +1510,10 @@
         <v>images/shimano_reels/STILE_main.jpg</v>
       </c>
       <c r="J24" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K24" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1557,10 +1557,10 @@
         <v>images/shimano_reels/BARCHETTA PREMIUM_main.jpg</v>
       </c>
       <c r="J25" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K25" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1604,10 +1604,10 @@
         <v>images/shimano_reels/GRAPPLER PREMIUM_main.jpg</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K26" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1651,10 +1651,10 @@
         <v>images/shimano_reels/ALDEBARAN BFS_main.jpg</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K27" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1698,10 +1698,10 @@
         <v>images/shimano_reels/ALDEBARAN MGL_main.jpg</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K28" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1745,10 +1745,10 @@
         <v>images/shimano_reels/Metanium SHALLOW EDITION_main.jpg</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K29" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -1792,10 +1792,10 @@
         <v>images/shimano_reels/Metanium_main.jpg</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K30" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L30" t="str">
         <v/>
@@ -1839,10 +1839,10 @@
         <v>images/shimano_reels/SPEEDMASTER 石鲷_main.jpg</v>
       </c>
       <c r="J31" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K31" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L31" t="str">
         <v/>
@@ -1886,10 +1886,10 @@
         <v>images/shimano_reels/TYRNOS_main.jpg</v>
       </c>
       <c r="J32" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K32" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -1933,10 +1933,10 @@
         <v>images/shimano_reels/EXSENCE DC SS_main.jpg</v>
       </c>
       <c r="J33" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K33" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -1980,10 +1980,10 @@
         <v>images/shimano_reels/TRANX 400_main.jpg</v>
       </c>
       <c r="J34" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K34" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -2027,10 +2027,10 @@
         <v>images/shimano_reels/Bantam_main.jpg</v>
       </c>
       <c r="J35" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K35" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -2074,10 +2074,10 @@
         <v>images/shimano_reels/TRANX 300_main.jpg</v>
       </c>
       <c r="J36" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K36" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -2121,10 +2121,10 @@
         <v>images/shimano_reels/BAYGAME_main.jpg</v>
       </c>
       <c r="J37" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K37" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -2168,10 +2168,10 @@
         <v>images/shimano_reels/GRAPPLER_main.jpg</v>
       </c>
       <c r="J38" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K38" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -2215,10 +2215,10 @@
         <v>images/shimano_reels/BARCHETTA F CUSTOM_main.jpg</v>
       </c>
       <c r="J39" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K39" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -2262,10 +2262,10 @@
         <v>images/shimano_reels/Scorpion DC MD_main.jpg</v>
       </c>
       <c r="J40" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K40" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -2309,10 +2309,10 @@
         <v>images/shimano_reels/SLX DC XT_main.jpg</v>
       </c>
       <c r="J41" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K41" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -2356,10 +2356,10 @@
         <v>images/shimano_reels/Scorpion DC_main.jpg</v>
       </c>
       <c r="J42" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K42" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -2403,10 +2403,10 @@
         <v>images/shimano_reels/Scorpion MD 300_main.jpg</v>
       </c>
       <c r="J43" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K43" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -2450,10 +2450,10 @@
         <v>images/shimano_reels/GRAPPLER CT_main.jpg</v>
       </c>
       <c r="J44" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K44" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2497,10 +2497,10 @@
         <v>images/shimano_reels/CURADO DC_main.jpg</v>
       </c>
       <c r="J45" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K45" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2544,10 +2544,10 @@
         <v>images/shimano_reels/CHINUMATIC_main.jpg</v>
       </c>
       <c r="J46" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K46" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2591,10 +2591,10 @@
         <v>images/shimano_reels/Stephano SS_main.jpg</v>
       </c>
       <c r="J47" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K47" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2638,10 +2638,10 @@
         <v>images/shimano_reels/STILE SS_main.jpg</v>
       </c>
       <c r="J48" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K48" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2685,10 +2685,10 @@
         <v>images/shimano_reels/Scorpion MD 200_main.jpg</v>
       </c>
       <c r="J49" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K49" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2732,10 +2732,10 @@
         <v>images/shimano_reels/TORIUM_main.jpg</v>
       </c>
       <c r="J50" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K50" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2779,10 +2779,10 @@
         <v>images/shimano_reels/TRANX 200_main.jpg</v>
       </c>
       <c r="J51" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K51" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2826,10 +2826,10 @@
         <v>images/shimano_reels/TRANX_main.jpg</v>
       </c>
       <c r="J52" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K52" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2873,10 +2873,10 @@
         <v>images/shimano_reels/BARCHETTA_main.jpg</v>
       </c>
       <c r="J53" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K53" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2920,10 +2920,10 @@
         <v>images/shimano_reels/BARCHETTA SC_main.jpg</v>
       </c>
       <c r="J54" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K54" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2967,10 +2967,10 @@
         <v>images/shimano_reels/SLX DC_main.jpg</v>
       </c>
       <c r="J55" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K55" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -3014,10 +3014,10 @@
         <v>images/shimano_reels/CURADO_main.jpg</v>
       </c>
       <c r="J56" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K56" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -3061,10 +3061,10 @@
         <v>images/shimano_reels/CURADO 150_main.jpg</v>
       </c>
       <c r="J57" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K57" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -3108,10 +3108,10 @@
         <v>images/shimano_reels/CURADO MGL_main.jpg</v>
       </c>
       <c r="J58" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K58" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -3155,10 +3155,10 @@
         <v>images/shimano_reels/CURADO BFS_main.jpg</v>
       </c>
       <c r="J59" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K59" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -3202,10 +3202,10 @@
         <v>images/shimano_reels/SLX_main.jpg</v>
       </c>
       <c r="J60" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K60" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -3249,10 +3249,10 @@
         <v>images/shimano_reels/BARCHETTA BB_main.jpg</v>
       </c>
       <c r="J61" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K61" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -3296,10 +3296,10 @@
         <v>images/shimano_reels/SLX BFS_main.jpg</v>
       </c>
       <c r="J62" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K62" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -3343,10 +3343,10 @@
         <v>images/shimano_reels/GRAPPLER BB_main.jpg</v>
       </c>
       <c r="J63" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K63" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -3390,10 +3390,10 @@
         <v>images/shimano_reels/SLX XT_main.jpg</v>
       </c>
       <c r="J64" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K64" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -3437,10 +3437,10 @@
         <v>images/shimano_reels/小船_main.jpg</v>
       </c>
       <c r="J65" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K65" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -3484,10 +3484,10 @@
         <v>images/shimano_reels/CARDIFF_main.jpg</v>
       </c>
       <c r="J66" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K66" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -3531,10 +3531,10 @@
         <v>images/shimano_reels/幻风 XT_main.jpg</v>
       </c>
       <c r="J67" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K67" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -3578,10 +3578,10 @@
         <v>images/shimano_reels/TITANOS FUNE GT_main.jpg</v>
       </c>
       <c r="J68" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K68" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -3625,10 +3625,10 @@
         <v>images/shimano_reels/BASS ONE XT_main.jpg</v>
       </c>
       <c r="J69" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K69" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L69" t="str">
         <v/>
@@ -3672,10 +3672,10 @@
         <v>images/shimano_reels/CAIUS_main.jpg</v>
       </c>
       <c r="J70" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K70" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L70" t="str">
         <v/>
@@ -3719,10 +3719,10 @@
         <v>images/shimano_reels/BASS RISE_main.jpg</v>
       </c>
       <c r="J71" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K71" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L71" t="str">
         <v/>
@@ -3766,10 +3766,10 @@
         <v>images/shimano_reels/幻风_main.jpg</v>
       </c>
       <c r="J72" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K72" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L72" t="str">
         <v/>
@@ -3813,10 +3813,10 @@
         <v>images/shimano_reels/CHINU SPECIAL_main.jpg</v>
       </c>
       <c r="J73" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="K73" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="L73" t="str">
         <v/>
@@ -3840,7 +3840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM389"/>
+  <dimension ref="A1:AN389"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3960,6 +3960,9 @@
       <c r="AM1" t="str">
         <v>MAX_DURABILITY</v>
       </c>
+      <c r="AN1" t="str">
+        <v>type</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -4008,10 +4011,10 @@
         <v>017383</v>
       </c>
       <c r="P2" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB2" t="str">
         <v/>
@@ -4048,6 +4051,9 @@
       </c>
       <c r="AM2" t="str">
         <v/>
+      </c>
+      <c r="AN2" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="3">
@@ -4097,10 +4103,10 @@
         <v>020307</v>
       </c>
       <c r="P3" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q3" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB3" t="str">
         <v/>
@@ -4137,6 +4143,9 @@
       </c>
       <c r="AM3" t="str">
         <v/>
+      </c>
+      <c r="AN3" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="4">
@@ -4186,10 +4195,10 @@
         <v>020314</v>
       </c>
       <c r="P4" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q4" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB4" t="str">
         <v/>
@@ -4226,6 +4235,9 @@
       </c>
       <c r="AM4" t="str">
         <v/>
+      </c>
+      <c r="AN4" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="5">
@@ -4275,10 +4287,10 @@
         <v>020321</v>
       </c>
       <c r="P5" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q5" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB5" t="str">
         <v/>
@@ -4315,6 +4327,9 @@
       </c>
       <c r="AM5" t="str">
         <v/>
+      </c>
+      <c r="AN5" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="6">
@@ -4364,10 +4379,10 @@
         <v>020338</v>
       </c>
       <c r="P6" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q6" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB6" t="str">
         <v/>
@@ -4404,6 +4419,9 @@
       </c>
       <c r="AM6" t="str">
         <v/>
+      </c>
+      <c r="AN6" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="7">
@@ -4453,10 +4471,10 @@
         <v>020345</v>
       </c>
       <c r="P7" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q7" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB7" t="str">
         <v/>
@@ -4493,6 +4511,9 @@
       </c>
       <c r="AM7" t="str">
         <v/>
+      </c>
+      <c r="AN7" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="8">
@@ -4542,10 +4563,10 @@
         <v>020352</v>
       </c>
       <c r="P8" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q8" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB8" t="str">
         <v/>
@@ -4582,6 +4603,9 @@
       </c>
       <c r="AM8" t="str">
         <v/>
+      </c>
+      <c r="AN8" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="9">
@@ -4631,10 +4655,10 @@
         <v>020369</v>
       </c>
       <c r="P9" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q9" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB9" t="str">
         <v/>
@@ -4671,6 +4695,9 @@
       </c>
       <c r="AM9" t="str">
         <v/>
+      </c>
+      <c r="AN9" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="10">
@@ -4720,10 +4747,10 @@
         <v>020376</v>
       </c>
       <c r="P10" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q10" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB10" t="str">
         <v/>
@@ -4760,6 +4787,9 @@
       </c>
       <c r="AM10" t="str">
         <v/>
+      </c>
+      <c r="AN10" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="11">
@@ -4809,10 +4839,10 @@
         <v>032218</v>
       </c>
       <c r="P11" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q11" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB11" t="str">
         <v/>
@@ -4849,6 +4879,9 @@
       </c>
       <c r="AM11" t="str">
         <v/>
+      </c>
+      <c r="AN11" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="12">
@@ -4898,10 +4931,10 @@
         <v>032225</v>
       </c>
       <c r="P12" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q12" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB12" t="str">
         <v/>
@@ -4938,6 +4971,9 @@
       </c>
       <c r="AM12" t="str">
         <v/>
+      </c>
+      <c r="AN12" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="13">
@@ -4987,10 +5023,10 @@
         <v>032881</v>
       </c>
       <c r="P13" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q13" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB13" t="str">
         <v/>
@@ -5027,6 +5063,9 @@
       </c>
       <c r="AM13" t="str">
         <v/>
+      </c>
+      <c r="AN13" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="14">
@@ -5076,10 +5115,10 @@
         <v>044969</v>
       </c>
       <c r="P14" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q14" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB14" t="str">
         <v/>
@@ -5116,6 +5155,9 @@
       </c>
       <c r="AM14" t="str">
         <v/>
+      </c>
+      <c r="AN14" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="15">
@@ -5165,10 +5207,10 @@
         <v>044976</v>
       </c>
       <c r="P15" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q15" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB15" t="str">
         <v/>
@@ -5205,6 +5247,9 @@
       </c>
       <c r="AM15" t="str">
         <v/>
+      </c>
+      <c r="AN15" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="16">
@@ -5254,10 +5299,10 @@
         <v>042606</v>
       </c>
       <c r="P16" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q16" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB16" t="str">
         <v/>
@@ -5294,6 +5339,9 @@
       </c>
       <c r="AM16" t="str">
         <v/>
+      </c>
+      <c r="AN16" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="17">
@@ -5343,10 +5391,10 @@
         <v>042613</v>
       </c>
       <c r="P17" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q17" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB17" t="str">
         <v/>
@@ -5383,6 +5431,9 @@
       </c>
       <c r="AM17" t="str">
         <v/>
+      </c>
+      <c r="AN17" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="18">
@@ -5432,10 +5483,10 @@
         <v>042620</v>
       </c>
       <c r="P18" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q18" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB18" t="str">
         <v/>
@@ -5472,6 +5523,9 @@
       </c>
       <c r="AM18" t="str">
         <v/>
+      </c>
+      <c r="AN18" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="19">
@@ -5521,10 +5575,10 @@
         <v>042637</v>
       </c>
       <c r="P19" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q19" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB19" t="str">
         <v/>
@@ -5561,6 +5615,9 @@
       </c>
       <c r="AM19" t="str">
         <v/>
+      </c>
+      <c r="AN19" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="20">
@@ -5610,10 +5667,10 @@
         <v>042644</v>
       </c>
       <c r="P20" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q20" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB20" t="str">
         <v/>
@@ -5650,6 +5707,9 @@
       </c>
       <c r="AM20" t="str">
         <v/>
+      </c>
+      <c r="AN20" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="21">
@@ -5699,10 +5759,10 @@
         <v>042651</v>
       </c>
       <c r="P21" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q21" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB21" t="str">
         <v/>
@@ -5739,6 +5799,9 @@
       </c>
       <c r="AM21" t="str">
         <v/>
+      </c>
+      <c r="AN21" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="22">
@@ -5788,10 +5851,10 @@
         <v>046000</v>
       </c>
       <c r="P22" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q22" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB22" t="str">
         <v/>
@@ -5828,6 +5891,9 @@
       </c>
       <c r="AM22" t="str">
         <v/>
+      </c>
+      <c r="AN22" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="23">
@@ -5877,10 +5943,10 @@
         <v>046017</v>
       </c>
       <c r="P23" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q23" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB23" t="str">
         <v/>
@@ -5917,6 +5983,9 @@
       </c>
       <c r="AM23" t="str">
         <v/>
+      </c>
+      <c r="AN23" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="24">
@@ -5966,10 +6035,10 @@
         <v>046024</v>
       </c>
       <c r="P24" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q24" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB24" t="str">
         <v/>
@@ -6006,6 +6075,9 @@
       </c>
       <c r="AM24" t="str">
         <v/>
+      </c>
+      <c r="AN24" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="25">
@@ -6055,10 +6127,10 @@
         <v>046031</v>
       </c>
       <c r="P25" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q25" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB25" t="str">
         <v/>
@@ -6095,6 +6167,9 @@
       </c>
       <c r="AM25" t="str">
         <v/>
+      </c>
+      <c r="AN25" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="26">
@@ -6144,10 +6219,10 @@
         <v/>
       </c>
       <c r="P26" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q26" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB26" t="str">
         <v/>
@@ -6184,6 +6259,9 @@
       </c>
       <c r="AM26" t="str">
         <v/>
+      </c>
+      <c r="AN26" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="27">
@@ -6233,10 +6311,10 @@
         <v/>
       </c>
       <c r="P27" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q27" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB27" t="str">
         <v/>
@@ -6273,6 +6351,9 @@
       </c>
       <c r="AM27" t="str">
         <v/>
+      </c>
+      <c r="AN27" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="28">
@@ -6322,10 +6403,10 @@
         <v/>
       </c>
       <c r="P28" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q28" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB28" t="str">
         <v/>
@@ -6362,6 +6443,9 @@
       </c>
       <c r="AM28" t="str">
         <v/>
+      </c>
+      <c r="AN28" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="29">
@@ -6411,10 +6495,10 @@
         <v/>
       </c>
       <c r="P29" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q29" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB29" t="str">
         <v/>
@@ -6451,6 +6535,9 @@
       </c>
       <c r="AM29" t="str">
         <v/>
+      </c>
+      <c r="AN29" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="30">
@@ -6500,10 +6587,10 @@
         <v/>
       </c>
       <c r="P30" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q30" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB30" t="str">
         <v/>
@@ -6540,6 +6627,9 @@
       </c>
       <c r="AM30" t="str">
         <v/>
+      </c>
+      <c r="AN30" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="31">
@@ -6589,10 +6679,10 @@
         <v/>
       </c>
       <c r="P31" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q31" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB31" t="str">
         <v/>
@@ -6629,6 +6719,9 @@
       </c>
       <c r="AM31" t="str">
         <v/>
+      </c>
+      <c r="AN31" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="32">
@@ -6678,10 +6771,10 @@
         <v>040664</v>
       </c>
       <c r="P32" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q32" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB32" t="str">
         <v/>
@@ -6718,6 +6811,9 @@
       </c>
       <c r="AM32" t="str">
         <v/>
+      </c>
+      <c r="AN32" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="33">
@@ -6767,10 +6863,10 @@
         <v>040671</v>
       </c>
       <c r="P33" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q33" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB33" t="str">
         <v/>
@@ -6807,6 +6903,9 @@
       </c>
       <c r="AM33" t="str">
         <v/>
+      </c>
+      <c r="AN33" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="34">
@@ -6856,10 +6955,10 @@
         <v>039781</v>
       </c>
       <c r="P34" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q34" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB34" t="str">
         <v/>
@@ -6896,6 +6995,9 @@
       </c>
       <c r="AM34" t="str">
         <v/>
+      </c>
+      <c r="AN34" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="35">
@@ -6945,10 +7047,10 @@
         <v>039798</v>
       </c>
       <c r="P35" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q35" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB35" t="str">
         <v/>
@@ -6985,6 +7087,9 @@
       </c>
       <c r="AM35" t="str">
         <v/>
+      </c>
+      <c r="AN35" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="36">
@@ -7034,10 +7139,10 @@
         <v>040831</v>
       </c>
       <c r="P36" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q36" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB36" t="str">
         <v/>
@@ -7074,6 +7179,9 @@
       </c>
       <c r="AM36" t="str">
         <v/>
+      </c>
+      <c r="AN36" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="37">
@@ -7123,10 +7231,10 @@
         <v>040848</v>
       </c>
       <c r="P37" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q37" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB37" t="str">
         <v/>
@@ -7163,6 +7271,9 @@
       </c>
       <c r="AM37" t="str">
         <v/>
+      </c>
+      <c r="AN37" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="38">
@@ -7212,10 +7323,10 @@
         <v>040855</v>
       </c>
       <c r="P38" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q38" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB38" t="str">
         <v/>
@@ -7252,6 +7363,9 @@
       </c>
       <c r="AM38" t="str">
         <v/>
+      </c>
+      <c r="AN38" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="39">
@@ -7301,10 +7415,10 @@
         <v>040862</v>
       </c>
       <c r="P39" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q39" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB39" t="str">
         <v/>
@@ -7341,6 +7455,9 @@
       </c>
       <c r="AM39" t="str">
         <v/>
+      </c>
+      <c r="AN39" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="40">
@@ -7390,10 +7507,10 @@
         <v>040398</v>
       </c>
       <c r="P40" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q40" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB40" t="str">
         <v/>
@@ -7430,6 +7547,9 @@
       </c>
       <c r="AM40" t="str">
         <v/>
+      </c>
+      <c r="AN40" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="41">
@@ -7479,10 +7599,10 @@
         <v>040404</v>
       </c>
       <c r="P41" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q41" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB41" t="str">
         <v/>
@@ -7519,6 +7639,9 @@
       </c>
       <c r="AM41" t="str">
         <v/>
+      </c>
+      <c r="AN41" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="42">
@@ -7568,10 +7691,10 @@
         <v>046581</v>
       </c>
       <c r="P42" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q42" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB42" t="str">
         <v/>
@@ -7608,6 +7731,9 @@
       </c>
       <c r="AM42" t="str">
         <v/>
+      </c>
+      <c r="AN42" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="43">
@@ -7657,10 +7783,10 @@
         <v>046598</v>
       </c>
       <c r="P43" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q43" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB43" t="str">
         <v/>
@@ -7697,6 +7823,9 @@
       </c>
       <c r="AM43" t="str">
         <v/>
+      </c>
+      <c r="AN43" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="44">
@@ -7746,10 +7875,10 @@
         <v>048653</v>
       </c>
       <c r="P44" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q44" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB44" t="str">
         <v/>
@@ -7786,6 +7915,9 @@
       </c>
       <c r="AM44" t="str">
         <v/>
+      </c>
+      <c r="AN44" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="45">
@@ -7835,10 +7967,10 @@
         <v>048660</v>
       </c>
       <c r="P45" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q45" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB45" t="str">
         <v/>
@@ -7875,6 +8007,9 @@
       </c>
       <c r="AM45" t="str">
         <v/>
+      </c>
+      <c r="AN45" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="46">
@@ -7924,10 +8059,10 @@
         <v>040008</v>
       </c>
       <c r="P46" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q46" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB46" t="str">
         <v/>
@@ -7964,6 +8099,9 @@
       </c>
       <c r="AM46" t="str">
         <v/>
+      </c>
+      <c r="AN46" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="47">
@@ -8013,10 +8151,10 @@
         <v>040015</v>
       </c>
       <c r="P47" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q47" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB47" t="str">
         <v/>
@@ -8053,6 +8191,9 @@
       </c>
       <c r="AM47" t="str">
         <v/>
+      </c>
+      <c r="AN47" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="48">
@@ -8102,10 +8243,10 @@
         <v>040022</v>
       </c>
       <c r="P48" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q48" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB48" t="str">
         <v/>
@@ -8142,6 +8283,9 @@
       </c>
       <c r="AM48" t="str">
         <v/>
+      </c>
+      <c r="AN48" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="49">
@@ -8191,10 +8335,10 @@
         <v>040039</v>
       </c>
       <c r="P49" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q49" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB49" t="str">
         <v/>
@@ -8231,6 +8375,9 @@
       </c>
       <c r="AM49" t="str">
         <v/>
+      </c>
+      <c r="AN49" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="50">
@@ -8280,10 +8427,10 @@
         <v>040046</v>
       </c>
       <c r="P50" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q50" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB50" t="str">
         <v/>
@@ -8320,6 +8467,9 @@
       </c>
       <c r="AM50" t="str">
         <v/>
+      </c>
+      <c r="AN50" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="51">
@@ -8369,10 +8519,10 @@
         <v>040053</v>
       </c>
       <c r="P51" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q51" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB51" t="str">
         <v/>
@@ -8409,6 +8559,9 @@
       </c>
       <c r="AM51" t="str">
         <v/>
+      </c>
+      <c r="AN51" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="52">
@@ -8458,10 +8611,10 @@
         <v>040060</v>
       </c>
       <c r="P52" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q52" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB52" t="str">
         <v/>
@@ -8498,6 +8651,9 @@
       </c>
       <c r="AM52" t="str">
         <v/>
+      </c>
+      <c r="AN52" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="53">
@@ -8547,10 +8703,10 @@
         <v>048677</v>
       </c>
       <c r="P53" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q53" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB53" t="str">
         <v/>
@@ -8587,6 +8743,9 @@
       </c>
       <c r="AM53" t="str">
         <v/>
+      </c>
+      <c r="AN53" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="54">
@@ -8636,10 +8795,10 @@
         <v>048684</v>
       </c>
       <c r="P54" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q54" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB54" t="str">
         <v/>
@@ -8676,6 +8835,9 @@
       </c>
       <c r="AM54" t="str">
         <v/>
+      </c>
+      <c r="AN54" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="55">
@@ -8725,10 +8887,10 @@
         <v>048714</v>
       </c>
       <c r="P55" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q55" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB55" t="str">
         <v/>
@@ -8765,6 +8927,9 @@
       </c>
       <c r="AM55" t="str">
         <v/>
+      </c>
+      <c r="AN55" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="56">
@@ -8814,10 +8979,10 @@
         <v>048752</v>
       </c>
       <c r="P56" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q56" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB56" t="str">
         <v/>
@@ -8854,6 +9019,9 @@
       </c>
       <c r="AM56" t="str">
         <v/>
+      </c>
+      <c r="AN56" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="57">
@@ -8903,10 +9071,10 @@
         <v>049223</v>
       </c>
       <c r="P57" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q57" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB57" t="str">
         <v/>
@@ -8943,6 +9111,9 @@
       </c>
       <c r="AM57" t="str">
         <v/>
+      </c>
+      <c r="AN57" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="58">
@@ -8992,10 +9163,10 @@
         <v>049230</v>
       </c>
       <c r="P58" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q58" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB58" t="str">
         <v/>
@@ -9032,6 +9203,9 @@
       </c>
       <c r="AM58" t="str">
         <v/>
+      </c>
+      <c r="AN58" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="59">
@@ -9081,10 +9255,10 @@
         <v>046680</v>
       </c>
       <c r="P59" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q59" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB59" t="str">
         <v/>
@@ -9121,6 +9295,9 @@
       </c>
       <c r="AM59" t="str">
         <v/>
+      </c>
+      <c r="AN59" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="60">
@@ -9170,10 +9347,10 @@
         <v>046697</v>
       </c>
       <c r="P60" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q60" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB60" t="str">
         <v/>
@@ -9210,6 +9387,9 @@
       </c>
       <c r="AM60" t="str">
         <v/>
+      </c>
+      <c r="AN60" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="61">
@@ -9259,10 +9439,10 @@
         <v>046703</v>
       </c>
       <c r="P61" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q61" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB61" t="str">
         <v/>
@@ -9299,6 +9479,9 @@
       </c>
       <c r="AM61" t="str">
         <v/>
+      </c>
+      <c r="AN61" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="62">
@@ -9348,10 +9531,10 @@
         <v>046710</v>
       </c>
       <c r="P62" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q62" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB62" t="str">
         <v/>
@@ -9388,6 +9571,9 @@
       </c>
       <c r="AM62" t="str">
         <v/>
+      </c>
+      <c r="AN62" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="63">
@@ -9437,10 +9623,10 @@
         <v>046727</v>
       </c>
       <c r="P63" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q63" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB63" t="str">
         <v/>
@@ -9477,6 +9663,9 @@
       </c>
       <c r="AM63" t="str">
         <v/>
+      </c>
+      <c r="AN63" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="64">
@@ -9526,10 +9715,10 @@
         <v>047663</v>
       </c>
       <c r="P64" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q64" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB64" t="str">
         <v/>
@@ -9566,6 +9755,9 @@
       </c>
       <c r="AM64" t="str">
         <v/>
+      </c>
+      <c r="AN64" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="65">
@@ -9615,10 +9807,10 @@
         <v>047670</v>
       </c>
       <c r="P65" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q65" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB65" t="str">
         <v/>
@@ -9655,6 +9847,9 @@
       </c>
       <c r="AM65" t="str">
         <v/>
+      </c>
+      <c r="AN65" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="66">
@@ -9704,10 +9899,10 @@
         <v>047687</v>
       </c>
       <c r="P66" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q66" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB66" t="str">
         <v/>
@@ -9744,6 +9939,9 @@
       </c>
       <c r="AM66" t="str">
         <v/>
+      </c>
+      <c r="AN66" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="67">
@@ -9793,10 +9991,10 @@
         <v>047694</v>
       </c>
       <c r="P67" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q67" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB67" t="str">
         <v/>
@@ -9833,6 +10031,9 @@
       </c>
       <c r="AM67" t="str">
         <v/>
+      </c>
+      <c r="AN67" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="68">
@@ -9882,10 +10083,10 @@
         <v>047700</v>
       </c>
       <c r="P68" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q68" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB68" t="str">
         <v/>
@@ -9922,6 +10123,9 @@
       </c>
       <c r="AM68" t="str">
         <v/>
+      </c>
+      <c r="AN68" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="69">
@@ -9971,10 +10175,10 @@
         <v>047717</v>
       </c>
       <c r="P69" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q69" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB69" t="str">
         <v/>
@@ -10011,6 +10215,9 @@
       </c>
       <c r="AM69" t="str">
         <v/>
+      </c>
+      <c r="AN69" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="70">
@@ -10060,10 +10267,10 @@
         <v>033567</v>
       </c>
       <c r="P70" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q70" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB70" t="str">
         <v/>
@@ -10100,6 +10307,9 @@
       </c>
       <c r="AM70" t="str">
         <v/>
+      </c>
+      <c r="AN70" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="71">
@@ -10149,10 +10359,10 @@
         <v>033574</v>
       </c>
       <c r="P71" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q71" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB71" t="str">
         <v/>
@@ -10189,6 +10399,9 @@
       </c>
       <c r="AM71" t="str">
         <v/>
+      </c>
+      <c r="AN71" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="72">
@@ -10238,10 +10451,10 @@
         <v>033581</v>
       </c>
       <c r="P72" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q72" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB72" t="str">
         <v/>
@@ -10278,6 +10491,9 @@
       </c>
       <c r="AM72" t="str">
         <v/>
+      </c>
+      <c r="AN72" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="73">
@@ -10327,10 +10543,10 @@
         <v>047724</v>
       </c>
       <c r="P73" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q73" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB73" t="str">
         <v/>
@@ -10367,6 +10583,9 @@
       </c>
       <c r="AM73" t="str">
         <v/>
+      </c>
+      <c r="AN73" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="74">
@@ -10416,10 +10635,10 @@
         <v>047731</v>
       </c>
       <c r="P74" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q74" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB74" t="str">
         <v/>
@@ -10456,6 +10675,9 @@
       </c>
       <c r="AM74" t="str">
         <v/>
+      </c>
+      <c r="AN74" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="75">
@@ -10505,10 +10727,10 @@
         <v>047748</v>
       </c>
       <c r="P75" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q75" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB75" t="str">
         <v/>
@@ -10545,6 +10767,9 @@
       </c>
       <c r="AM75" t="str">
         <v/>
+      </c>
+      <c r="AN75" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="76">
@@ -10594,10 +10819,10 @@
         <v>047755</v>
       </c>
       <c r="P76" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q76" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB76" t="str">
         <v/>
@@ -10634,6 +10859,9 @@
       </c>
       <c r="AM76" t="str">
         <v/>
+      </c>
+      <c r="AN76" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="77">
@@ -10683,10 +10911,10 @@
         <v>047762</v>
       </c>
       <c r="P77" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q77" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB77" t="str">
         <v/>
@@ -10723,6 +10951,9 @@
       </c>
       <c r="AM77" t="str">
         <v/>
+      </c>
+      <c r="AN77" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="78">
@@ -10772,10 +11003,10 @@
         <v>047779</v>
       </c>
       <c r="P78" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q78" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB78" t="str">
         <v/>
@@ -10812,6 +11043,9 @@
       </c>
       <c r="AM78" t="str">
         <v/>
+      </c>
+      <c r="AN78" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="79">
@@ -10861,10 +11095,10 @@
         <v>043764</v>
       </c>
       <c r="P79" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q79" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB79" t="str">
         <v/>
@@ -10901,6 +11135,9 @@
       </c>
       <c r="AM79" t="str">
         <v/>
+      </c>
+      <c r="AN79" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="80">
@@ -10950,10 +11187,10 @@
         <v>043771</v>
       </c>
       <c r="P80" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q80" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB80" t="str">
         <v/>
@@ -10990,6 +11227,9 @@
       </c>
       <c r="AM80" t="str">
         <v/>
+      </c>
+      <c r="AN80" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="81">
@@ -11039,10 +11279,10 @@
         <v>043788</v>
       </c>
       <c r="P81" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q81" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB81" t="str">
         <v/>
@@ -11079,6 +11319,9 @@
       </c>
       <c r="AM81" t="str">
         <v/>
+      </c>
+      <c r="AN81" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="82">
@@ -11128,10 +11371,10 @@
         <v>043795</v>
       </c>
       <c r="P82" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q82" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB82" t="str">
         <v/>
@@ -11168,6 +11411,9 @@
       </c>
       <c r="AM82" t="str">
         <v/>
+      </c>
+      <c r="AN82" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="83">
@@ -11217,10 +11463,10 @@
         <v>043801</v>
       </c>
       <c r="P83" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q83" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB83" t="str">
         <v/>
@@ -11257,6 +11503,9 @@
       </c>
       <c r="AM83" t="str">
         <v/>
+      </c>
+      <c r="AN83" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="84">
@@ -11306,10 +11555,10 @@
         <v>043818</v>
       </c>
       <c r="P84" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q84" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB84" t="str">
         <v/>
@@ -11346,6 +11595,9 @@
       </c>
       <c r="AM84" t="str">
         <v/>
+      </c>
+      <c r="AN84" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="85">
@@ -11395,10 +11647,10 @@
         <v>036650</v>
       </c>
       <c r="P85" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q85" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB85" t="str">
         <v/>
@@ -11435,6 +11687,9 @@
       </c>
       <c r="AM85" t="str">
         <v/>
+      </c>
+      <c r="AN85" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="86">
@@ -11484,10 +11739,10 @@
         <v>036667</v>
       </c>
       <c r="P86" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q86" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB86" t="str">
         <v/>
@@ -11524,6 +11779,9 @@
       </c>
       <c r="AM86" t="str">
         <v/>
+      </c>
+      <c r="AN86" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="87">
@@ -11573,10 +11831,10 @@
         <v>036674</v>
       </c>
       <c r="P87" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q87" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB87" t="str">
         <v/>
@@ -11613,6 +11871,9 @@
       </c>
       <c r="AM87" t="str">
         <v/>
+      </c>
+      <c r="AN87" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="88">
@@ -11662,10 +11923,10 @@
         <v>036698</v>
       </c>
       <c r="P88" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q88" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB88" t="str">
         <v/>
@@ -11702,6 +11963,9 @@
       </c>
       <c r="AM88" t="str">
         <v/>
+      </c>
+      <c r="AN88" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="89">
@@ -11751,10 +12015,10 @@
         <v>036681</v>
       </c>
       <c r="P89" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q89" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB89" t="str">
         <v/>
@@ -11791,6 +12055,9 @@
       </c>
       <c r="AM89" t="str">
         <v/>
+      </c>
+      <c r="AN89" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="90">
@@ -11840,10 +12107,10 @@
         <v>036704</v>
       </c>
       <c r="P90" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q90" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB90" t="str">
         <v/>
@@ -11880,6 +12147,9 @@
       </c>
       <c r="AM90" t="str">
         <v/>
+      </c>
+      <c r="AN90" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="91">
@@ -11929,10 +12199,10 @@
         <v>036711</v>
       </c>
       <c r="P91" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q91" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB91" t="str">
         <v/>
@@ -11969,6 +12239,9 @@
       </c>
       <c r="AM91" t="str">
         <v/>
+      </c>
+      <c r="AN91" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="92">
@@ -12018,10 +12291,10 @@
         <v>036735</v>
       </c>
       <c r="P92" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q92" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB92" t="str">
         <v/>
@@ -12058,6 +12331,9 @@
       </c>
       <c r="AM92" t="str">
         <v/>
+      </c>
+      <c r="AN92" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="93">
@@ -12107,10 +12383,10 @@
         <v>036728</v>
       </c>
       <c r="P93" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q93" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB93" t="str">
         <v/>
@@ -12147,6 +12423,9 @@
       </c>
       <c r="AM93" t="str">
         <v/>
+      </c>
+      <c r="AN93" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="94">
@@ -12196,10 +12475,10 @@
         <v>036742</v>
       </c>
       <c r="P94" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q94" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB94" t="str">
         <v/>
@@ -12236,6 +12515,9 @@
       </c>
       <c r="AM94" t="str">
         <v/>
+      </c>
+      <c r="AN94" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="95">
@@ -12285,10 +12567,10 @@
         <v>045928</v>
       </c>
       <c r="P95" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q95" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB95" t="str">
         <v/>
@@ -12325,6 +12607,9 @@
       </c>
       <c r="AM95" t="str">
         <v/>
+      </c>
+      <c r="AN95" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="96">
@@ -12374,10 +12659,10 @@
         <v>045935</v>
       </c>
       <c r="P96" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q96" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB96" t="str">
         <v/>
@@ -12414,6 +12699,9 @@
       </c>
       <c r="AM96" t="str">
         <v/>
+      </c>
+      <c r="AN96" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="97">
@@ -12463,10 +12751,10 @@
         <v>045942</v>
       </c>
       <c r="P97" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q97" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB97" t="str">
         <v/>
@@ -12503,6 +12791,9 @@
       </c>
       <c r="AM97" t="str">
         <v/>
+      </c>
+      <c r="AN97" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="98">
@@ -12552,10 +12843,10 @@
         <v>045959</v>
       </c>
       <c r="P98" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q98" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB98" t="str">
         <v/>
@@ -12592,6 +12883,9 @@
       </c>
       <c r="AM98" t="str">
         <v/>
+      </c>
+      <c r="AN98" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="99">
@@ -12641,10 +12935,10 @@
         <v>045966</v>
       </c>
       <c r="P99" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q99" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB99" t="str">
         <v/>
@@ -12681,6 +12975,9 @@
       </c>
       <c r="AM99" t="str">
         <v/>
+      </c>
+      <c r="AN99" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="100">
@@ -12730,10 +13027,10 @@
         <v>045973</v>
       </c>
       <c r="P100" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q100" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB100" t="str">
         <v/>
@@ -12770,6 +13067,9 @@
       </c>
       <c r="AM100" t="str">
         <v/>
+      </c>
+      <c r="AN100" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="101">
@@ -12819,10 +13119,10 @@
         <v>049322</v>
       </c>
       <c r="P101" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q101" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB101" t="str">
         <v/>
@@ -12859,6 +13159,9 @@
       </c>
       <c r="AM101" t="str">
         <v/>
+      </c>
+      <c r="AN101" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="102">
@@ -12908,10 +13211,10 @@
         <v>049339</v>
       </c>
       <c r="P102" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q102" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB102" t="str">
         <v/>
@@ -12948,6 +13251,9 @@
       </c>
       <c r="AM102" t="str">
         <v/>
+      </c>
+      <c r="AN102" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="103">
@@ -12997,10 +13303,10 @@
         <v>049346</v>
       </c>
       <c r="P103" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q103" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB103" t="str">
         <v/>
@@ -13037,6 +13343,9 @@
       </c>
       <c r="AM103" t="str">
         <v/>
+      </c>
+      <c r="AN103" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="104">
@@ -13086,10 +13395,10 @@
         <v>049353</v>
       </c>
       <c r="P104" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q104" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB104" t="str">
         <v/>
@@ -13126,6 +13435,9 @@
       </c>
       <c r="AM104" t="str">
         <v/>
+      </c>
+      <c r="AN104" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="105">
@@ -13175,10 +13487,10 @@
         <v>046604</v>
       </c>
       <c r="P105" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q105" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB105" t="str">
         <v/>
@@ -13215,6 +13527,9 @@
       </c>
       <c r="AM105" t="str">
         <v/>
+      </c>
+      <c r="AN105" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="106">
@@ -13264,10 +13579,10 @@
         <v>046611</v>
       </c>
       <c r="P106" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q106" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB106" t="str">
         <v/>
@@ -13304,6 +13619,9 @@
       </c>
       <c r="AM106" t="str">
         <v/>
+      </c>
+      <c r="AN106" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="107">
@@ -13353,10 +13671,10 @@
         <v>046628</v>
       </c>
       <c r="P107" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q107" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB107" t="str">
         <v/>
@@ -13393,6 +13711,9 @@
       </c>
       <c r="AM107" t="str">
         <v/>
+      </c>
+      <c r="AN107" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="108">
@@ -13442,10 +13763,10 @@
         <v>046635</v>
       </c>
       <c r="P108" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q108" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB108" t="str">
         <v/>
@@ -13482,6 +13803,9 @@
       </c>
       <c r="AM108" t="str">
         <v/>
+      </c>
+      <c r="AN108" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="109">
@@ -13531,10 +13855,10 @@
         <v>046642</v>
       </c>
       <c r="P109" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q109" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB109" t="str">
         <v/>
@@ -13571,6 +13895,9 @@
       </c>
       <c r="AM109" t="str">
         <v/>
+      </c>
+      <c r="AN109" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="110">
@@ -13620,10 +13947,10 @@
         <v>046659</v>
       </c>
       <c r="P110" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q110" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB110" t="str">
         <v/>
@@ -13660,6 +13987,9 @@
       </c>
       <c r="AM110" t="str">
         <v/>
+      </c>
+      <c r="AN110" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="111">
@@ -13709,10 +14039,10 @@
         <v>042323</v>
       </c>
       <c r="P111" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q111" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB111" t="str">
         <v/>
@@ -13749,6 +14079,9 @@
       </c>
       <c r="AM111" t="str">
         <v/>
+      </c>
+      <c r="AN111" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="112">
@@ -13798,10 +14131,10 @@
         <v>042330</v>
       </c>
       <c r="P112" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q112" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB112" t="str">
         <v/>
@@ -13838,6 +14171,9 @@
       </c>
       <c r="AM112" t="str">
         <v/>
+      </c>
+      <c r="AN112" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="113">
@@ -13887,10 +14223,10 @@
         <v>042347</v>
       </c>
       <c r="P113" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q113" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB113" t="str">
         <v/>
@@ -13927,6 +14263,9 @@
       </c>
       <c r="AM113" t="str">
         <v/>
+      </c>
+      <c r="AN113" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="114">
@@ -13976,10 +14315,10 @@
         <v>042354</v>
       </c>
       <c r="P114" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q114" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB114" t="str">
         <v/>
@@ -14016,6 +14355,9 @@
       </c>
       <c r="AM114" t="str">
         <v/>
+      </c>
+      <c r="AN114" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="115">
@@ -14065,10 +14407,10 @@
         <v>042361</v>
       </c>
       <c r="P115" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q115" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB115" t="str">
         <v/>
@@ -14105,6 +14447,9 @@
       </c>
       <c r="AM115" t="str">
         <v/>
+      </c>
+      <c r="AN115" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="116">
@@ -14154,10 +14499,10 @@
         <v>042378</v>
       </c>
       <c r="P116" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q116" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB116" t="str">
         <v/>
@@ -14194,6 +14539,9 @@
       </c>
       <c r="AM116" t="str">
         <v/>
+      </c>
+      <c r="AN116" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="117">
@@ -14243,10 +14591,10 @@
         <v>042385</v>
       </c>
       <c r="P117" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q117" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB117" t="str">
         <v/>
@@ -14283,6 +14631,9 @@
       </c>
       <c r="AM117" t="str">
         <v/>
+      </c>
+      <c r="AN117" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="118">
@@ -14332,10 +14683,10 @@
         <v>042392</v>
       </c>
       <c r="P118" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q118" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB118" t="str">
         <v/>
@@ -14372,6 +14723,9 @@
       </c>
       <c r="AM118" t="str">
         <v/>
+      </c>
+      <c r="AN118" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="119">
@@ -14421,10 +14775,10 @@
         <v>044402</v>
       </c>
       <c r="P119" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q119" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB119" t="str">
         <v/>
@@ -14461,6 +14815,9 @@
       </c>
       <c r="AM119" t="str">
         <v/>
+      </c>
+      <c r="AN119" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="120">
@@ -14510,10 +14867,10 @@
         <v>044419</v>
       </c>
       <c r="P120" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q120" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB120" t="str">
         <v/>
@@ -14550,6 +14907,9 @@
       </c>
       <c r="AM120" t="str">
         <v/>
+      </c>
+      <c r="AN120" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="121">
@@ -14599,10 +14959,10 @@
         <v>044426</v>
       </c>
       <c r="P121" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q121" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB121" t="str">
         <v/>
@@ -14639,6 +14999,9 @@
       </c>
       <c r="AM121" t="str">
         <v/>
+      </c>
+      <c r="AN121" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="122">
@@ -14688,10 +15051,10 @@
         <v>044433</v>
       </c>
       <c r="P122" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q122" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB122" t="str">
         <v/>
@@ -14728,6 +15091,9 @@
       </c>
       <c r="AM122" t="str">
         <v/>
+      </c>
+      <c r="AN122" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="123">
@@ -14777,10 +15143,10 @@
         <v>044440</v>
       </c>
       <c r="P123" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q123" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB123" t="str">
         <v/>
@@ -14817,6 +15183,9 @@
       </c>
       <c r="AM123" t="str">
         <v/>
+      </c>
+      <c r="AN123" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="124">
@@ -14866,10 +15235,10 @@
         <v>044457</v>
       </c>
       <c r="P124" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q124" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB124" t="str">
         <v/>
@@ -14906,6 +15275,9 @@
       </c>
       <c r="AM124" t="str">
         <v/>
+      </c>
+      <c r="AN124" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="125">
@@ -14955,10 +15327,10 @@
         <v>044464</v>
       </c>
       <c r="P125" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q125" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB125" t="str">
         <v/>
@@ -14995,6 +15367,9 @@
       </c>
       <c r="AM125" t="str">
         <v/>
+      </c>
+      <c r="AN125" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="126">
@@ -15044,10 +15419,10 @@
         <v>044471</v>
       </c>
       <c r="P126" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q126" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB126" t="str">
         <v/>
@@ -15084,6 +15459,9 @@
       </c>
       <c r="AM126" t="str">
         <v/>
+      </c>
+      <c r="AN126" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="127">
@@ -15133,10 +15511,10 @@
         <v>046260</v>
       </c>
       <c r="P127" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q127" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB127" t="str">
         <v/>
@@ -15173,6 +15551,9 @@
       </c>
       <c r="AM127" t="str">
         <v/>
+      </c>
+      <c r="AN127" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="128">
@@ -15222,10 +15603,10 @@
         <v>046277</v>
       </c>
       <c r="P128" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q128" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB128" t="str">
         <v/>
@@ -15262,6 +15643,9 @@
       </c>
       <c r="AM128" t="str">
         <v/>
+      </c>
+      <c r="AN128" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="129">
@@ -15311,10 +15695,10 @@
         <v>046284</v>
       </c>
       <c r="P129" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q129" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB129" t="str">
         <v/>
@@ -15351,6 +15735,9 @@
       </c>
       <c r="AM129" t="str">
         <v/>
+      </c>
+      <c r="AN129" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="130">
@@ -15400,10 +15787,10 @@
         <v>046291</v>
       </c>
       <c r="P130" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q130" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB130" t="str">
         <v/>
@@ -15440,6 +15827,9 @@
       </c>
       <c r="AM130" t="str">
         <v/>
+      </c>
+      <c r="AN130" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="131">
@@ -15489,10 +15879,10 @@
         <v>046734</v>
       </c>
       <c r="P131" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q131" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB131" t="str">
         <v/>
@@ -15529,6 +15919,9 @@
       </c>
       <c r="AM131" t="str">
         <v/>
+      </c>
+      <c r="AN131" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="132">
@@ -15578,10 +15971,10 @@
         <v>046741</v>
       </c>
       <c r="P132" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q132" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB132" t="str">
         <v/>
@@ -15618,6 +16011,9 @@
       </c>
       <c r="AM132" t="str">
         <v/>
+      </c>
+      <c r="AN132" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="133">
@@ -15667,10 +16063,10 @@
         <v>045683</v>
       </c>
       <c r="P133" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q133" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB133" t="str">
         <v/>
@@ -15707,6 +16103,9 @@
       </c>
       <c r="AM133" t="str">
         <v/>
+      </c>
+      <c r="AN133" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="134">
@@ -15756,10 +16155,10 @@
         <v>045690</v>
       </c>
       <c r="P134" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q134" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB134" t="str">
         <v/>
@@ -15796,6 +16195,9 @@
       </c>
       <c r="AM134" t="str">
         <v/>
+      </c>
+      <c r="AN134" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="135">
@@ -15845,10 +16247,10 @@
         <v>045706</v>
       </c>
       <c r="P135" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q135" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB135" t="str">
         <v/>
@@ -15885,6 +16287,9 @@
       </c>
       <c r="AM135" t="str">
         <v/>
+      </c>
+      <c r="AN135" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="136">
@@ -15934,10 +16339,10 @@
         <v>045713</v>
       </c>
       <c r="P136" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q136" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB136" t="str">
         <v/>
@@ -15974,6 +16379,9 @@
       </c>
       <c r="AM136" t="str">
         <v/>
+      </c>
+      <c r="AN136" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="137">
@@ -16023,10 +16431,10 @@
         <v>049179</v>
       </c>
       <c r="P137" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q137" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB137" t="str">
         <v/>
@@ -16063,6 +16471,9 @@
       </c>
       <c r="AM137" t="str">
         <v/>
+      </c>
+      <c r="AN137" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="138">
@@ -16112,10 +16523,10 @@
         <v>049186</v>
       </c>
       <c r="P138" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q138" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB138" t="str">
         <v/>
@@ -16152,6 +16563,9 @@
       </c>
       <c r="AM138" t="str">
         <v/>
+      </c>
+      <c r="AN138" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="139">
@@ -16201,10 +16615,10 @@
         <v>049193</v>
       </c>
       <c r="P139" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q139" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB139" t="str">
         <v/>
@@ -16241,6 +16655,9 @@
       </c>
       <c r="AM139" t="str">
         <v/>
+      </c>
+      <c r="AN139" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="140">
@@ -16290,10 +16707,10 @@
         <v>049209</v>
       </c>
       <c r="P140" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q140" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB140" t="str">
         <v/>
@@ -16330,6 +16747,9 @@
       </c>
       <c r="AM140" t="str">
         <v/>
+      </c>
+      <c r="AN140" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="141">
@@ -16379,10 +16799,10 @@
         <v>047830</v>
       </c>
       <c r="P141" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q141" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB141" t="str">
         <v/>
@@ -16419,6 +16839,9 @@
       </c>
       <c r="AM141" t="str">
         <v/>
+      </c>
+      <c r="AN141" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="142">
@@ -16468,10 +16891,10 @@
         <v>047847</v>
       </c>
       <c r="P142" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q142" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB142" t="str">
         <v/>
@@ -16508,6 +16931,9 @@
       </c>
       <c r="AM142" t="str">
         <v/>
+      </c>
+      <c r="AN142" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="143">
@@ -16557,10 +16983,10 @@
         <v>047854</v>
       </c>
       <c r="P143" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q143" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB143" t="str">
         <v/>
@@ -16597,6 +17023,9 @@
       </c>
       <c r="AM143" t="str">
         <v/>
+      </c>
+      <c r="AN143" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="144">
@@ -16646,10 +17075,10 @@
         <v>047861</v>
       </c>
       <c r="P144" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q144" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB144" t="str">
         <v/>
@@ -16686,6 +17115,9 @@
       </c>
       <c r="AM144" t="str">
         <v/>
+      </c>
+      <c r="AN144" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="145">
@@ -16735,10 +17167,10 @@
         <v>048462</v>
       </c>
       <c r="P145" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q145" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB145" t="str">
         <v/>
@@ -16775,6 +17207,9 @@
       </c>
       <c r="AM145" t="str">
         <v/>
+      </c>
+      <c r="AN145" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="146">
@@ -16824,10 +17259,10 @@
         <v>048479</v>
       </c>
       <c r="P146" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q146" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB146" t="str">
         <v/>
@@ -16864,6 +17299,9 @@
       </c>
       <c r="AM146" t="str">
         <v/>
+      </c>
+      <c r="AN146" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="147">
@@ -16913,10 +17351,10 @@
         <v>048486</v>
       </c>
       <c r="P147" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q147" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB147" t="str">
         <v/>
@@ -16953,6 +17391,9 @@
       </c>
       <c r="AM147" t="str">
         <v/>
+      </c>
+      <c r="AN147" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="148">
@@ -17002,10 +17443,10 @@
         <v>048493</v>
       </c>
       <c r="P148" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q148" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB148" t="str">
         <v/>
@@ -17042,6 +17483,9 @@
       </c>
       <c r="AM148" t="str">
         <v/>
+      </c>
+      <c r="AN148" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="149">
@@ -17091,10 +17535,10 @@
         <v>047274</v>
       </c>
       <c r="P149" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q149" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB149" t="str">
         <v/>
@@ -17131,6 +17575,9 @@
       </c>
       <c r="AM149" t="str">
         <v/>
+      </c>
+      <c r="AN149" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="150">
@@ -17180,10 +17627,10 @@
         <v>047281</v>
       </c>
       <c r="P150" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q150" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB150" t="str">
         <v/>
@@ -17220,6 +17667,9 @@
       </c>
       <c r="AM150" t="str">
         <v/>
+      </c>
+      <c r="AN150" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="151">
@@ -17269,10 +17719,10 @@
         <v>047298</v>
       </c>
       <c r="P151" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q151" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB151" t="str">
         <v/>
@@ -17309,6 +17759,9 @@
       </c>
       <c r="AM151" t="str">
         <v/>
+      </c>
+      <c r="AN151" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="152">
@@ -17358,10 +17811,10 @@
         <v>047304</v>
       </c>
       <c r="P152" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q152" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB152" t="str">
         <v/>
@@ -17398,6 +17851,9 @@
       </c>
       <c r="AM152" t="str">
         <v/>
+      </c>
+      <c r="AN152" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="153">
@@ -17447,10 +17903,10 @@
         <v>047311</v>
       </c>
       <c r="P153" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q153" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB153" t="str">
         <v/>
@@ -17487,6 +17943,9 @@
       </c>
       <c r="AM153" t="str">
         <v/>
+      </c>
+      <c r="AN153" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="154">
@@ -17536,10 +17995,10 @@
         <v>047328</v>
       </c>
       <c r="P154" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q154" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB154" t="str">
         <v/>
@@ -17576,6 +18035,9 @@
       </c>
       <c r="AM154" t="str">
         <v/>
+      </c>
+      <c r="AN154" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="155">
@@ -17625,10 +18087,10 @@
         <v>047182</v>
       </c>
       <c r="P155" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q155" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB155" t="str">
         <v/>
@@ -17665,6 +18127,9 @@
       </c>
       <c r="AM155" t="str">
         <v/>
+      </c>
+      <c r="AN155" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="156">
@@ -17714,10 +18179,10 @@
         <v>047199</v>
       </c>
       <c r="P156" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q156" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB156" t="str">
         <v/>
@@ -17754,6 +18219,9 @@
       </c>
       <c r="AM156" t="str">
         <v/>
+      </c>
+      <c r="AN156" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="157">
@@ -17803,10 +18271,10 @@
         <v>043986</v>
       </c>
       <c r="P157" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q157" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB157" t="str">
         <v/>
@@ -17843,6 +18311,9 @@
       </c>
       <c r="AM157" t="str">
         <v/>
+      </c>
+      <c r="AN157" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="158">
@@ -17892,10 +18363,10 @@
         <v>043993</v>
       </c>
       <c r="P158" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q158" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB158" t="str">
         <v/>
@@ -17932,6 +18403,9 @@
       </c>
       <c r="AM158" t="str">
         <v/>
+      </c>
+      <c r="AN158" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="159">
@@ -17981,10 +18455,10 @@
         <v>044006</v>
       </c>
       <c r="P159" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q159" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB159" t="str">
         <v/>
@@ -18021,6 +18495,9 @@
       </c>
       <c r="AM159" t="str">
         <v/>
+      </c>
+      <c r="AN159" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="160">
@@ -18070,10 +18547,10 @@
         <v>044013</v>
       </c>
       <c r="P160" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q160" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB160" t="str">
         <v/>
@@ -18110,6 +18587,9 @@
       </c>
       <c r="AM160" t="str">
         <v/>
+      </c>
+      <c r="AN160" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="161">
@@ -18159,10 +18639,10 @@
         <v>038777</v>
       </c>
       <c r="P161" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q161" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB161" t="str">
         <v/>
@@ -18199,6 +18679,9 @@
       </c>
       <c r="AM161" t="str">
         <v/>
+      </c>
+      <c r="AN161" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="162">
@@ -18248,10 +18731,10 @@
         <v>038784</v>
       </c>
       <c r="P162" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q162" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB162" t="str">
         <v/>
@@ -18288,6 +18771,9 @@
       </c>
       <c r="AM162" t="str">
         <v/>
+      </c>
+      <c r="AN162" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="163">
@@ -18337,10 +18823,10 @@
         <v>038791</v>
       </c>
       <c r="P163" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q163" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB163" t="str">
         <v/>
@@ -18377,6 +18863,9 @@
       </c>
       <c r="AM163" t="str">
         <v/>
+      </c>
+      <c r="AN163" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="164">
@@ -18426,10 +18915,10 @@
         <v>038807</v>
       </c>
       <c r="P164" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q164" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB164" t="str">
         <v/>
@@ -18466,6 +18955,9 @@
       </c>
       <c r="AM164" t="str">
         <v/>
+      </c>
+      <c r="AN164" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="165">
@@ -18515,10 +19007,10 @@
         <v>044778</v>
       </c>
       <c r="P165" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q165" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB165" t="str">
         <v/>
@@ -18555,6 +19047,9 @@
       </c>
       <c r="AM165" t="str">
         <v/>
+      </c>
+      <c r="AN165" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="166">
@@ -18604,10 +19099,10 @@
         <v>044785</v>
       </c>
       <c r="P166" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q166" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB166" t="str">
         <v/>
@@ -18644,6 +19139,9 @@
       </c>
       <c r="AM166" t="str">
         <v/>
+      </c>
+      <c r="AN166" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="167">
@@ -18693,10 +19191,10 @@
         <v>044792</v>
       </c>
       <c r="P167" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q167" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB167" t="str">
         <v/>
@@ -18733,6 +19231,9 @@
       </c>
       <c r="AM167" t="str">
         <v/>
+      </c>
+      <c r="AN167" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="168">
@@ -18782,10 +19283,10 @@
         <v>044808</v>
       </c>
       <c r="P168" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q168" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB168" t="str">
         <v/>
@@ -18822,6 +19323,9 @@
       </c>
       <c r="AM168" t="str">
         <v/>
+      </c>
+      <c r="AN168" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="169">
@@ -18871,10 +19375,10 @@
         <v>044815</v>
       </c>
       <c r="P169" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q169" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB169" t="str">
         <v/>
@@ -18911,6 +19415,9 @@
       </c>
       <c r="AM169" t="str">
         <v/>
+      </c>
+      <c r="AN169" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="170">
@@ -18960,10 +19467,10 @@
         <v>044822</v>
       </c>
       <c r="P170" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q170" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB170" t="str">
         <v/>
@@ -19000,6 +19507,9 @@
       </c>
       <c r="AM170" t="str">
         <v/>
+      </c>
+      <c r="AN170" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="171">
@@ -19049,10 +19559,10 @@
         <v>-</v>
       </c>
       <c r="P171" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q171" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB171" t="str">
         <v/>
@@ -19089,6 +19599,9 @@
       </c>
       <c r="AM171" t="str">
         <v/>
+      </c>
+      <c r="AN171" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="172">
@@ -19138,10 +19651,10 @@
         <v>-</v>
       </c>
       <c r="P172" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q172" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB172" t="str">
         <v/>
@@ -19178,6 +19691,9 @@
       </c>
       <c r="AM172" t="str">
         <v/>
+      </c>
+      <c r="AN172" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="173">
@@ -19227,10 +19743,10 @@
         <v>-</v>
       </c>
       <c r="P173" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q173" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB173" t="str">
         <v/>
@@ -19267,6 +19783,9 @@
       </c>
       <c r="AM173" t="str">
         <v/>
+      </c>
+      <c r="AN173" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="174">
@@ -19316,10 +19835,10 @@
         <v>-</v>
       </c>
       <c r="P174" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q174" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB174" t="str">
         <v/>
@@ -19356,6 +19875,9 @@
       </c>
       <c r="AM174" t="str">
         <v/>
+      </c>
+      <c r="AN174" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="175">
@@ -19405,10 +19927,10 @@
         <v>-</v>
       </c>
       <c r="P175" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q175" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB175" t="str">
         <v/>
@@ -19445,6 +19967,9 @@
       </c>
       <c r="AM175" t="str">
         <v/>
+      </c>
+      <c r="AN175" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="176">
@@ -19494,10 +20019,10 @@
         <v>-</v>
       </c>
       <c r="P176" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q176" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB176" t="str">
         <v/>
@@ -19534,6 +20059,9 @@
       </c>
       <c r="AM176" t="str">
         <v/>
+      </c>
+      <c r="AN176" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="177">
@@ -19583,10 +20111,10 @@
         <v>041128</v>
       </c>
       <c r="P177" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q177" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB177" t="str">
         <v/>
@@ -19623,6 +20151,9 @@
       </c>
       <c r="AM177" t="str">
         <v/>
+      </c>
+      <c r="AN177" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="178">
@@ -19672,10 +20203,10 @@
         <v>041135</v>
       </c>
       <c r="P178" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q178" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB178" t="str">
         <v/>
@@ -19712,6 +20243,9 @@
       </c>
       <c r="AM178" t="str">
         <v/>
+      </c>
+      <c r="AN178" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="179">
@@ -19761,10 +20295,10 @@
         <v>041142</v>
       </c>
       <c r="P179" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q179" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB179" t="str">
         <v/>
@@ -19801,6 +20335,9 @@
       </c>
       <c r="AM179" t="str">
         <v/>
+      </c>
+      <c r="AN179" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="180">
@@ -19850,10 +20387,10 @@
         <v>041159</v>
       </c>
       <c r="P180" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q180" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB180" t="str">
         <v/>
@@ -19890,6 +20427,9 @@
       </c>
       <c r="AM180" t="str">
         <v/>
+      </c>
+      <c r="AN180" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="181">
@@ -19939,10 +20479,10 @@
         <v>041166</v>
       </c>
       <c r="P181" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q181" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB181" t="str">
         <v/>
@@ -19979,6 +20519,9 @@
       </c>
       <c r="AM181" t="str">
         <v/>
+      </c>
+      <c r="AN181" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="182">
@@ -20028,10 +20571,10 @@
         <v>041173</v>
       </c>
       <c r="P182" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q182" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB182" t="str">
         <v/>
@@ -20068,6 +20611,9 @@
       </c>
       <c r="AM182" t="str">
         <v/>
+      </c>
+      <c r="AN182" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="183">
@@ -20117,10 +20663,10 @@
         <v>046116</v>
       </c>
       <c r="P183" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q183" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB183" t="str">
         <v/>
@@ -20157,6 +20703,9 @@
       </c>
       <c r="AM183" t="str">
         <v/>
+      </c>
+      <c r="AN183" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="184">
@@ -20206,10 +20755,10 @@
         <v>046123</v>
       </c>
       <c r="P184" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q184" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB184" t="str">
         <v/>
@@ -20246,6 +20795,9 @@
       </c>
       <c r="AM184" t="str">
         <v/>
+      </c>
+      <c r="AN184" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="185">
@@ -20295,10 +20847,10 @@
         <v>046130</v>
       </c>
       <c r="P185" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q185" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB185" t="str">
         <v/>
@@ -20335,6 +20887,9 @@
       </c>
       <c r="AM185" t="str">
         <v/>
+      </c>
+      <c r="AN185" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="186">
@@ -20384,10 +20939,10 @@
         <v>046147</v>
       </c>
       <c r="P186" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q186" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB186" t="str">
         <v/>
@@ -20424,6 +20979,9 @@
       </c>
       <c r="AM186" t="str">
         <v/>
+      </c>
+      <c r="AN186" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="187">
@@ -20473,10 +21031,10 @@
         <v>044365</v>
       </c>
       <c r="P187" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q187" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB187" t="str">
         <v/>
@@ -20513,6 +21071,9 @@
       </c>
       <c r="AM187" t="str">
         <v/>
+      </c>
+      <c r="AN187" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="188">
@@ -20562,10 +21123,10 @@
         <v>044372</v>
       </c>
       <c r="P188" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q188" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB188" t="str">
         <v/>
@@ -20602,6 +21163,9 @@
       </c>
       <c r="AM188" t="str">
         <v/>
+      </c>
+      <c r="AN188" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="189">
@@ -20651,10 +21215,10 @@
         <v>044389</v>
       </c>
       <c r="P189" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q189" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB189" t="str">
         <v/>
@@ -20691,6 +21255,9 @@
       </c>
       <c r="AM189" t="str">
         <v/>
+      </c>
+      <c r="AN189" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="190">
@@ -20740,10 +21307,10 @@
         <v>023742</v>
       </c>
       <c r="P190" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q190" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB190" t="str">
         <v/>
@@ -20780,6 +21347,9 @@
       </c>
       <c r="AM190" t="str">
         <v/>
+      </c>
+      <c r="AN190" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="191">
@@ -20829,10 +21399,10 @@
         <v>022523</v>
       </c>
       <c r="P191" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q191" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB191" t="str">
         <v/>
@@ -20869,6 +21439,9 @@
       </c>
       <c r="AM191" t="str">
         <v/>
+      </c>
+      <c r="AN191" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="192">
@@ -20918,10 +21491,10 @@
         <v>022530</v>
       </c>
       <c r="P192" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q192" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB192" t="str">
         <v/>
@@ -20958,6 +21531,9 @@
       </c>
       <c r="AM192" t="str">
         <v/>
+      </c>
+      <c r="AN192" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="193">
@@ -21007,10 +21583,10 @@
         <v>041876</v>
       </c>
       <c r="P193" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q193" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB193" t="str">
         <v/>
@@ -21047,6 +21623,9 @@
       </c>
       <c r="AM193" t="str">
         <v/>
+      </c>
+      <c r="AN193" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="194">
@@ -21096,10 +21675,10 @@
         <v>041883</v>
       </c>
       <c r="P194" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q194" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB194" t="str">
         <v/>
@@ -21136,6 +21715,9 @@
       </c>
       <c r="AM194" t="str">
         <v/>
+      </c>
+      <c r="AN194" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="195">
@@ -21185,10 +21767,10 @@
         <v>041890</v>
       </c>
       <c r="P195" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q195" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB195" t="str">
         <v/>
@@ -21225,6 +21807,9 @@
       </c>
       <c r="AM195" t="str">
         <v/>
+      </c>
+      <c r="AN195" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="196">
@@ -21274,10 +21859,10 @@
         <v>041906</v>
       </c>
       <c r="P196" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q196" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB196" t="str">
         <v/>
@@ -21314,6 +21899,9 @@
       </c>
       <c r="AM196" t="str">
         <v/>
+      </c>
+      <c r="AN196" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="197">
@@ -21363,10 +21951,10 @@
         <v/>
       </c>
       <c r="P197" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q197" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB197" t="str">
         <v/>
@@ -21403,6 +21991,9 @@
       </c>
       <c r="AM197" t="str">
         <v/>
+      </c>
+      <c r="AN197" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="198">
@@ -21452,10 +22043,10 @@
         <v/>
       </c>
       <c r="P198" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q198" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB198" t="str">
         <v/>
@@ -21492,6 +22083,9 @@
       </c>
       <c r="AM198" t="str">
         <v/>
+      </c>
+      <c r="AN198" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="199">
@@ -21541,10 +22135,10 @@
         <v/>
       </c>
       <c r="P199" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q199" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB199" t="str">
         <v/>
@@ -21581,6 +22175,9 @@
       </c>
       <c r="AM199" t="str">
         <v/>
+      </c>
+      <c r="AN199" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="200">
@@ -21630,10 +22227,10 @@
         <v/>
       </c>
       <c r="P200" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q200" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB200" t="str">
         <v/>
@@ -21670,6 +22267,9 @@
       </c>
       <c r="AM200" t="str">
         <v/>
+      </c>
+      <c r="AN200" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="201">
@@ -21719,10 +22319,10 @@
         <v>044617</v>
       </c>
       <c r="P201" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q201" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB201" t="str">
         <v/>
@@ -21759,6 +22359,9 @@
       </c>
       <c r="AM201" t="str">
         <v/>
+      </c>
+      <c r="AN201" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="202">
@@ -21808,10 +22411,10 @@
         <v>044624</v>
       </c>
       <c r="P202" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q202" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB202" t="str">
         <v/>
@@ -21848,6 +22451,9 @@
       </c>
       <c r="AM202" t="str">
         <v/>
+      </c>
+      <c r="AN202" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="203">
@@ -21897,10 +22503,10 @@
         <v>044631</v>
       </c>
       <c r="P203" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q203" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB203" t="str">
         <v/>
@@ -21937,6 +22543,9 @@
       </c>
       <c r="AM203" t="str">
         <v/>
+      </c>
+      <c r="AN203" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="204">
@@ -21986,10 +22595,10 @@
         <v>044648</v>
       </c>
       <c r="P204" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q204" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB204" t="str">
         <v/>
@@ -22026,6 +22635,9 @@
       </c>
       <c r="AM204" t="str">
         <v/>
+      </c>
+      <c r="AN204" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="205">
@@ -22075,10 +22687,10 @@
         <v>044655</v>
       </c>
       <c r="P205" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q205" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB205" t="str">
         <v/>
@@ -22115,6 +22727,9 @@
       </c>
       <c r="AM205" t="str">
         <v/>
+      </c>
+      <c r="AN205" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="206">
@@ -22164,10 +22779,10 @@
         <v>044662</v>
       </c>
       <c r="P206" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q206" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB206" t="str">
         <v/>
@@ -22204,6 +22819,9 @@
       </c>
       <c r="AM206" t="str">
         <v/>
+      </c>
+      <c r="AN206" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="207">
@@ -22253,10 +22871,10 @@
         <v/>
       </c>
       <c r="P207" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q207" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB207" t="str">
         <v/>
@@ -22293,6 +22911,9 @@
       </c>
       <c r="AM207" t="str">
         <v/>
+      </c>
+      <c r="AN207" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="208">
@@ -22342,10 +22963,10 @@
         <v/>
       </c>
       <c r="P208" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q208" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB208" t="str">
         <v/>
@@ -22382,6 +23003,9 @@
       </c>
       <c r="AM208" t="str">
         <v/>
+      </c>
+      <c r="AN208" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="209">
@@ -22431,10 +23055,10 @@
         <v/>
       </c>
       <c r="P209" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q209" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB209" t="str">
         <v/>
@@ -22471,6 +23095,9 @@
       </c>
       <c r="AM209" t="str">
         <v/>
+      </c>
+      <c r="AN209" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="210">
@@ -22520,10 +23147,10 @@
         <v/>
       </c>
       <c r="P210" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q210" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB210" t="str">
         <v/>
@@ -22560,6 +23187,9 @@
       </c>
       <c r="AM210" t="str">
         <v/>
+      </c>
+      <c r="AN210" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="211">
@@ -22609,10 +23239,10 @@
         <v>038685</v>
       </c>
       <c r="P211" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q211" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB211" t="str">
         <v/>
@@ -22649,6 +23279,9 @@
       </c>
       <c r="AM211" t="str">
         <v/>
+      </c>
+      <c r="AN211" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="212">
@@ -22698,10 +23331,10 @@
         <v>038692</v>
       </c>
       <c r="P212" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q212" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB212" t="str">
         <v/>
@@ -22738,6 +23371,9 @@
       </c>
       <c r="AM212" t="str">
         <v/>
+      </c>
+      <c r="AN212" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="213">
@@ -22787,10 +23423,10 @@
         <v>038708</v>
       </c>
       <c r="P213" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q213" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB213" t="str">
         <v/>
@@ -22827,6 +23463,9 @@
       </c>
       <c r="AM213" t="str">
         <v/>
+      </c>
+      <c r="AN213" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="214">
@@ -22876,10 +23515,10 @@
         <v>038715</v>
       </c>
       <c r="P214" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q214" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB214" t="str">
         <v/>
@@ -22916,6 +23555,9 @@
       </c>
       <c r="AM214" t="str">
         <v/>
+      </c>
+      <c r="AN214" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="215">
@@ -22965,10 +23607,10 @@
         <v>041913</v>
       </c>
       <c r="P215" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q215" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB215" t="str">
         <v/>
@@ -23005,6 +23647,9 @@
       </c>
       <c r="AM215" t="str">
         <v/>
+      </c>
+      <c r="AN215" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="216">
@@ -23054,10 +23699,10 @@
         <v>041920</v>
       </c>
       <c r="P216" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q216" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB216" t="str">
         <v/>
@@ -23094,6 +23739,9 @@
       </c>
       <c r="AM216" t="str">
         <v/>
+      </c>
+      <c r="AN216" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="217">
@@ -23143,10 +23791,10 @@
         <v>049735</v>
       </c>
       <c r="P217" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q217" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB217" t="str">
         <v/>
@@ -23183,6 +23831,9 @@
       </c>
       <c r="AM217" t="str">
         <v/>
+      </c>
+      <c r="AN217" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="218">
@@ -23232,10 +23883,10 @@
         <v>049742</v>
       </c>
       <c r="P218" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q218" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB218" t="str">
         <v/>
@@ -23272,6 +23923,9 @@
       </c>
       <c r="AM218" t="str">
         <v/>
+      </c>
+      <c r="AN218" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="219">
@@ -23321,10 +23975,10 @@
         <v>049759</v>
       </c>
       <c r="P219" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q219" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB219" t="str">
         <v/>
@@ -23361,6 +24015,9 @@
       </c>
       <c r="AM219" t="str">
         <v/>
+      </c>
+      <c r="AN219" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="220">
@@ -23410,10 +24067,10 @@
         <v>049766</v>
       </c>
       <c r="P220" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q220" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB220" t="str">
         <v/>
@@ -23450,6 +24107,9 @@
       </c>
       <c r="AM220" t="str">
         <v/>
+      </c>
+      <c r="AN220" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="221">
@@ -23499,10 +24159,10 @@
         <v>048318</v>
       </c>
       <c r="P221" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q221" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB221" t="str">
         <v/>
@@ -23539,6 +24199,9 @@
       </c>
       <c r="AM221" t="str">
         <v/>
+      </c>
+      <c r="AN221" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="222">
@@ -23588,10 +24251,10 @@
         <v>048325</v>
       </c>
       <c r="P222" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q222" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB222" t="str">
         <v/>
@@ -23628,6 +24291,9 @@
       </c>
       <c r="AM222" t="str">
         <v/>
+      </c>
+      <c r="AN222" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="223">
@@ -23677,10 +24343,10 @@
         <v>048332</v>
       </c>
       <c r="P223" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q223" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB223" t="str">
         <v/>
@@ -23717,6 +24383,9 @@
       </c>
       <c r="AM223" t="str">
         <v/>
+      </c>
+      <c r="AN223" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="224">
@@ -23766,10 +24435,10 @@
         <v>048349</v>
       </c>
       <c r="P224" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q224" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB224" t="str">
         <v/>
@@ -23806,6 +24475,9 @@
       </c>
       <c r="AM224" t="str">
         <v/>
+      </c>
+      <c r="AN224" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="225">
@@ -23855,10 +24527,10 @@
         <v>048356</v>
       </c>
       <c r="P225" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q225" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB225" t="str">
         <v/>
@@ -23895,6 +24567,9 @@
       </c>
       <c r="AM225" t="str">
         <v/>
+      </c>
+      <c r="AN225" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="226">
@@ -23944,10 +24619,10 @@
         <v>048363</v>
       </c>
       <c r="P226" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q226" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB226" t="str">
         <v/>
@@ -23984,6 +24659,9 @@
       </c>
       <c r="AM226" t="str">
         <v/>
+      </c>
+      <c r="AN226" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="227">
@@ -24033,10 +24711,10 @@
         <v>049124</v>
       </c>
       <c r="P227" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q227" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB227" t="str">
         <v/>
@@ -24073,6 +24751,9 @@
       </c>
       <c r="AM227" t="str">
         <v/>
+      </c>
+      <c r="AN227" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="228">
@@ -24122,10 +24803,10 @@
         <v>049148</v>
       </c>
       <c r="P228" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q228" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB228" t="str">
         <v/>
@@ -24162,6 +24843,9 @@
       </c>
       <c r="AM228" t="str">
         <v/>
+      </c>
+      <c r="AN228" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="229">
@@ -24211,10 +24895,10 @@
         <v>044686</v>
       </c>
       <c r="P229" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q229" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB229" t="str">
         <v/>
@@ -24251,6 +24935,9 @@
       </c>
       <c r="AM229" t="str">
         <v/>
+      </c>
+      <c r="AN229" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="230">
@@ -24300,10 +24987,10 @@
         <v>044693</v>
       </c>
       <c r="P230" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q230" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB230" t="str">
         <v/>
@@ -24340,6 +25027,9 @@
       </c>
       <c r="AM230" t="str">
         <v/>
+      </c>
+      <c r="AN230" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="231">
@@ -24389,10 +25079,10 @@
         <v>044709</v>
       </c>
       <c r="P231" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q231" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB231" t="str">
         <v/>
@@ -24429,6 +25119,9 @@
       </c>
       <c r="AM231" t="str">
         <v/>
+      </c>
+      <c r="AN231" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="232">
@@ -24478,10 +25171,10 @@
         <v>044716</v>
       </c>
       <c r="P232" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q232" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB232" t="str">
         <v/>
@@ -24518,6 +25211,9 @@
       </c>
       <c r="AM232" t="str">
         <v/>
+      </c>
+      <c r="AN232" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="233">
@@ -24567,10 +25263,10 @@
         <v>044723</v>
       </c>
       <c r="P233" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q233" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB233" t="str">
         <v/>
@@ -24607,6 +25303,9 @@
       </c>
       <c r="AM233" t="str">
         <v/>
+      </c>
+      <c r="AN233" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="234">
@@ -24656,10 +25355,10 @@
         <v>044730</v>
       </c>
       <c r="P234" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q234" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB234" t="str">
         <v/>
@@ -24696,6 +25395,9 @@
       </c>
       <c r="AM234" t="str">
         <v/>
+      </c>
+      <c r="AN234" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="235">
@@ -24745,10 +25447,10 @@
         <v>043061</v>
       </c>
       <c r="P235" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q235" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB235" t="str">
         <v/>
@@ -24785,6 +25487,9 @@
       </c>
       <c r="AM235" t="str">
         <v/>
+      </c>
+      <c r="AN235" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="236">
@@ -24834,10 +25539,10 @@
         <v>043078</v>
       </c>
       <c r="P236" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q236" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB236" t="str">
         <v/>
@@ -24874,6 +25579,9 @@
       </c>
       <c r="AM236" t="str">
         <v/>
+      </c>
+      <c r="AN236" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="237">
@@ -24923,10 +25631,10 @@
         <v>043085</v>
       </c>
       <c r="P237" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q237" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB237" t="str">
         <v/>
@@ -24963,6 +25671,9 @@
       </c>
       <c r="AM237" t="str">
         <v/>
+      </c>
+      <c r="AN237" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="238">
@@ -25012,10 +25723,10 @@
         <v>043092</v>
       </c>
       <c r="P238" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q238" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB238" t="str">
         <v/>
@@ -25052,6 +25763,9 @@
       </c>
       <c r="AM238" t="str">
         <v/>
+      </c>
+      <c r="AN238" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="239">
@@ -25101,10 +25815,10 @@
         <v>043108</v>
       </c>
       <c r="P239" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q239" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB239" t="str">
         <v/>
@@ -25141,6 +25855,9 @@
       </c>
       <c r="AM239" t="str">
         <v/>
+      </c>
+      <c r="AN239" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="240">
@@ -25190,10 +25907,10 @@
         <v>043115</v>
       </c>
       <c r="P240" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q240" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB240" t="str">
         <v/>
@@ -25230,6 +25947,9 @@
       </c>
       <c r="AM240" t="str">
         <v/>
+      </c>
+      <c r="AN240" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="241">
@@ -25279,10 +25999,10 @@
         <v>047144</v>
       </c>
       <c r="P241" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q241" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB241" t="str">
         <v/>
@@ -25319,6 +26039,9 @@
       </c>
       <c r="AM241" t="str">
         <v/>
+      </c>
+      <c r="AN241" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="242">
@@ -25368,10 +26091,10 @@
         <v>047151</v>
       </c>
       <c r="P242" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q242" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB242" t="str">
         <v/>
@@ -25408,6 +26131,9 @@
       </c>
       <c r="AM242" t="str">
         <v/>
+      </c>
+      <c r="AN242" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="243">
@@ -25457,10 +26183,10 @@
         <v>047168</v>
       </c>
       <c r="P243" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q243" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB243" t="str">
         <v/>
@@ -25497,6 +26223,9 @@
       </c>
       <c r="AM243" t="str">
         <v/>
+      </c>
+      <c r="AN243" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="244">
@@ -25546,10 +26275,10 @@
         <v>047175</v>
       </c>
       <c r="P244" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q244" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB244" t="str">
         <v/>
@@ -25586,6 +26315,9 @@
       </c>
       <c r="AM244" t="str">
         <v/>
+      </c>
+      <c r="AN244" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="245">
@@ -25635,10 +26367,10 @@
         <v>043498</v>
       </c>
       <c r="P245" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q245" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB245" t="str">
         <v/>
@@ -25675,6 +26407,9 @@
       </c>
       <c r="AM245" t="str">
         <v/>
+      </c>
+      <c r="AN245" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="246">
@@ -25724,10 +26459,10 @@
         <v>043504</v>
       </c>
       <c r="P246" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q246" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB246" t="str">
         <v/>
@@ -25764,6 +26499,9 @@
       </c>
       <c r="AM246" t="str">
         <v/>
+      </c>
+      <c r="AN246" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="247">
@@ -25813,10 +26551,10 @@
         <v>048837</v>
       </c>
       <c r="P247" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q247" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB247" t="str">
         <v/>
@@ -25853,6 +26591,9 @@
       </c>
       <c r="AM247" t="str">
         <v/>
+      </c>
+      <c r="AN247" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="248">
@@ -25902,10 +26643,10 @@
         <v>048844</v>
       </c>
       <c r="P248" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q248" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB248" t="str">
         <v/>
@@ -25942,6 +26683,9 @@
       </c>
       <c r="AM248" t="str">
         <v/>
+      </c>
+      <c r="AN248" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="249">
@@ -25991,10 +26735,10 @@
         <v/>
       </c>
       <c r="P249" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q249" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB249" t="str">
         <v/>
@@ -26031,6 +26775,9 @@
       </c>
       <c r="AM249" t="str">
         <v/>
+      </c>
+      <c r="AN249" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="250">
@@ -26080,10 +26827,10 @@
         <v/>
       </c>
       <c r="P250" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q250" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB250" t="str">
         <v/>
@@ -26120,6 +26867,9 @@
       </c>
       <c r="AM250" t="str">
         <v/>
+      </c>
+      <c r="AN250" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="251">
@@ -26169,10 +26919,10 @@
         <v/>
       </c>
       <c r="P251" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q251" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB251" t="str">
         <v/>
@@ -26209,6 +26959,9 @@
       </c>
       <c r="AM251" t="str">
         <v/>
+      </c>
+      <c r="AN251" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="252">
@@ -26258,10 +27011,10 @@
         <v/>
       </c>
       <c r="P252" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q252" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB252" t="str">
         <v/>
@@ -26298,6 +27051,9 @@
       </c>
       <c r="AM252" t="str">
         <v/>
+      </c>
+      <c r="AN252" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="253">
@@ -26347,10 +27103,10 @@
         <v>021922</v>
       </c>
       <c r="P253" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q253" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB253" t="str">
         <v/>
@@ -26387,6 +27143,9 @@
       </c>
       <c r="AM253" t="str">
         <v/>
+      </c>
+      <c r="AN253" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="254">
@@ -26436,10 +27195,10 @@
         <v>021939</v>
       </c>
       <c r="P254" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q254" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB254" t="str">
         <v/>
@@ -26476,6 +27235,9 @@
       </c>
       <c r="AM254" t="str">
         <v/>
+      </c>
+      <c r="AN254" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="255">
@@ -26525,10 +27287,10 @@
         <v>021946</v>
       </c>
       <c r="P255" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q255" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB255" t="str">
         <v/>
@@ -26565,6 +27327,9 @@
       </c>
       <c r="AM255" t="str">
         <v/>
+      </c>
+      <c r="AN255" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="256">
@@ -26614,10 +27379,10 @@
         <v>021953</v>
       </c>
       <c r="P256" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q256" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB256" t="str">
         <v/>
@@ -26654,6 +27419,9 @@
       </c>
       <c r="AM256" t="str">
         <v/>
+      </c>
+      <c r="AN256" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="257">
@@ -26703,10 +27471,10 @@
         <v>021960</v>
       </c>
       <c r="P257" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q257" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB257" t="str">
         <v/>
@@ -26743,6 +27511,9 @@
       </c>
       <c r="AM257" t="str">
         <v/>
+      </c>
+      <c r="AN257" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="258">
@@ -26792,10 +27563,10 @@
         <v>021977</v>
       </c>
       <c r="P258" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q258" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB258" t="str">
         <v/>
@@ -26832,6 +27603,9 @@
       </c>
       <c r="AM258" t="str">
         <v/>
+      </c>
+      <c r="AN258" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="259">
@@ -26881,10 +27655,10 @@
         <v/>
       </c>
       <c r="P259" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q259" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB259" t="str">
         <v/>
@@ -26921,6 +27695,9 @@
       </c>
       <c r="AM259" t="str">
         <v/>
+      </c>
+      <c r="AN259" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="260">
@@ -26970,10 +27747,10 @@
         <v/>
       </c>
       <c r="P260" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q260" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB260" t="str">
         <v/>
@@ -27010,6 +27787,9 @@
       </c>
       <c r="AM260" t="str">
         <v/>
+      </c>
+      <c r="AN260" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="261">
@@ -27059,10 +27839,10 @@
         <v/>
       </c>
       <c r="P261" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q261" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB261" t="str">
         <v/>
@@ -27099,6 +27879,9 @@
       </c>
       <c r="AM261" t="str">
         <v/>
+      </c>
+      <c r="AN261" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="262">
@@ -27148,10 +27931,10 @@
         <v/>
       </c>
       <c r="P262" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q262" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB262" t="str">
         <v/>
@@ -27188,6 +27971,9 @@
       </c>
       <c r="AM262" t="str">
         <v/>
+      </c>
+      <c r="AN262" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="263">
@@ -27237,10 +28023,10 @@
         <v/>
       </c>
       <c r="P263" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q263" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB263" t="str">
         <v/>
@@ -27277,6 +28063,9 @@
       </c>
       <c r="AM263" t="str">
         <v/>
+      </c>
+      <c r="AN263" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="264">
@@ -27326,10 +28115,10 @@
         <v/>
       </c>
       <c r="P264" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q264" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB264" t="str">
         <v/>
@@ -27366,6 +28155,9 @@
       </c>
       <c r="AM264" t="str">
         <v/>
+      </c>
+      <c r="AN264" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="265">
@@ -27415,10 +28207,10 @@
         <v>037718</v>
       </c>
       <c r="P265" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q265" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB265" t="str">
         <v/>
@@ -27455,6 +28247,9 @@
       </c>
       <c r="AM265" t="str">
         <v/>
+      </c>
+      <c r="AN265" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="266">
@@ -27504,10 +28299,10 @@
         <v>037725</v>
       </c>
       <c r="P266" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q266" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB266" t="str">
         <v/>
@@ -27544,6 +28339,9 @@
       </c>
       <c r="AM266" t="str">
         <v/>
+      </c>
+      <c r="AN266" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="267">
@@ -27593,10 +28391,10 @@
         <v>036902</v>
       </c>
       <c r="P267" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q267" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB267" t="str">
         <v/>
@@ -27633,6 +28431,9 @@
       </c>
       <c r="AM267" t="str">
         <v/>
+      </c>
+      <c r="AN267" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="268">
@@ -27682,10 +28483,10 @@
         <v>036919</v>
       </c>
       <c r="P268" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q268" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB268" t="str">
         <v/>
@@ -27722,6 +28523,9 @@
       </c>
       <c r="AM268" t="str">
         <v/>
+      </c>
+      <c r="AN268" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="269">
@@ -27771,10 +28575,10 @@
         <v>036926</v>
       </c>
       <c r="P269" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q269" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB269" t="str">
         <v/>
@@ -27811,6 +28615,9 @@
       </c>
       <c r="AM269" t="str">
         <v/>
+      </c>
+      <c r="AN269" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="270">
@@ -27860,10 +28667,10 @@
         <v>036933</v>
       </c>
       <c r="P270" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q270" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB270" t="str">
         <v/>
@@ -27900,6 +28707,9 @@
       </c>
       <c r="AM270" t="str">
         <v/>
+      </c>
+      <c r="AN270" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="271">
@@ -27949,10 +28759,10 @@
         <v>046895</v>
       </c>
       <c r="P271" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q271" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB271" t="str">
         <v/>
@@ -27989,6 +28799,9 @@
       </c>
       <c r="AM271" t="str">
         <v/>
+      </c>
+      <c r="AN271" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="272">
@@ -28038,10 +28851,10 @@
         <v>046901</v>
       </c>
       <c r="P272" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q272" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB272" t="str">
         <v/>
@@ -28078,6 +28891,9 @@
       </c>
       <c r="AM272" t="str">
         <v/>
+      </c>
+      <c r="AN272" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="273">
@@ -28127,10 +28943,10 @@
         <v>046918</v>
       </c>
       <c r="P273" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q273" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB273" t="str">
         <v/>
@@ -28167,6 +28983,9 @@
       </c>
       <c r="AM273" t="str">
         <v/>
+      </c>
+      <c r="AN273" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="274">
@@ -28216,10 +29035,10 @@
         <v>046925</v>
       </c>
       <c r="P274" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q274" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB274" t="str">
         <v/>
@@ -28256,6 +29075,9 @@
       </c>
       <c r="AM274" t="str">
         <v/>
+      </c>
+      <c r="AN274" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="275">
@@ -28305,10 +29127,10 @@
         <v>042187</v>
       </c>
       <c r="P275" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q275" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB275" t="str">
         <v/>
@@ -28345,6 +29167,9 @@
       </c>
       <c r="AM275" t="str">
         <v/>
+      </c>
+      <c r="AN275" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="276">
@@ -28394,10 +29219,10 @@
         <v>042194</v>
       </c>
       <c r="P276" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q276" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB276" t="str">
         <v/>
@@ -28434,6 +29259,9 @@
       </c>
       <c r="AM276" t="str">
         <v/>
+      </c>
+      <c r="AN276" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="277">
@@ -28483,10 +29311,10 @@
         <v>042200</v>
       </c>
       <c r="P277" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q277" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB277" t="str">
         <v/>
@@ -28523,6 +29351,9 @@
       </c>
       <c r="AM277" t="str">
         <v/>
+      </c>
+      <c r="AN277" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="278">
@@ -28572,10 +29403,10 @@
         <v/>
       </c>
       <c r="P278" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q278" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB278" t="str">
         <v/>
@@ -28612,6 +29443,9 @@
       </c>
       <c r="AM278" t="str">
         <v/>
+      </c>
+      <c r="AN278" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="279">
@@ -28661,10 +29495,10 @@
         <v/>
       </c>
       <c r="P279" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q279" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB279" t="str">
         <v/>
@@ -28701,6 +29535,9 @@
       </c>
       <c r="AM279" t="str">
         <v/>
+      </c>
+      <c r="AN279" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="280">
@@ -28750,10 +29587,10 @@
         <v/>
       </c>
       <c r="P280" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q280" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB280" t="str">
         <v/>
@@ -28790,6 +29627,9 @@
       </c>
       <c r="AM280" t="str">
         <v/>
+      </c>
+      <c r="AN280" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="281">
@@ -28839,10 +29679,10 @@
         <v/>
       </c>
       <c r="P281" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q281" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB281" t="str">
         <v/>
@@ -28879,6 +29719,9 @@
       </c>
       <c r="AM281" t="str">
         <v/>
+      </c>
+      <c r="AN281" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="282">
@@ -28928,10 +29771,10 @@
         <v/>
       </c>
       <c r="P282" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q282" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB282" t="str">
         <v/>
@@ -28968,6 +29811,9 @@
       </c>
       <c r="AM282" t="str">
         <v/>
+      </c>
+      <c r="AN282" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="283">
@@ -29017,10 +29863,10 @@
         <v/>
       </c>
       <c r="P283" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q283" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB283" t="str">
         <v/>
@@ -29057,6 +29903,9 @@
       </c>
       <c r="AM283" t="str">
         <v/>
+      </c>
+      <c r="AN283" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="284">
@@ -29106,10 +29955,10 @@
         <v/>
       </c>
       <c r="P284" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q284" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB284" t="str">
         <v/>
@@ -29146,6 +29995,9 @@
       </c>
       <c r="AM284" t="str">
         <v/>
+      </c>
+      <c r="AN284" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="285">
@@ -29195,10 +30047,10 @@
         <v/>
       </c>
       <c r="P285" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q285" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB285" t="str">
         <v/>
@@ -29235,6 +30087,9 @@
       </c>
       <c r="AM285" t="str">
         <v/>
+      </c>
+      <c r="AN285" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="286">
@@ -29284,10 +30139,10 @@
         <v>042682</v>
       </c>
       <c r="P286" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q286" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB286" t="str">
         <v/>
@@ -29324,6 +30179,9 @@
       </c>
       <c r="AM286" t="str">
         <v/>
+      </c>
+      <c r="AN286" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="287">
@@ -29373,10 +30231,10 @@
         <v>042699</v>
       </c>
       <c r="P287" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q287" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB287" t="str">
         <v/>
@@ -29413,6 +30271,9 @@
       </c>
       <c r="AM287" t="str">
         <v/>
+      </c>
+      <c r="AN287" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="288">
@@ -29462,10 +30323,10 @@
         <v>042705</v>
       </c>
       <c r="P288" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q288" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB288" t="str">
         <v/>
@@ -29502,6 +30363,9 @@
       </c>
       <c r="AM288" t="str">
         <v/>
+      </c>
+      <c r="AN288" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="289">
@@ -29551,10 +30415,10 @@
         <v>042712</v>
       </c>
       <c r="P289" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q289" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB289" t="str">
         <v/>
@@ -29591,6 +30455,9 @@
       </c>
       <c r="AM289" t="str">
         <v/>
+      </c>
+      <c r="AN289" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="290">
@@ -29640,10 +30507,10 @@
         <v>042729</v>
       </c>
       <c r="P290" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q290" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB290" t="str">
         <v/>
@@ -29680,6 +30547,9 @@
       </c>
       <c r="AM290" t="str">
         <v/>
+      </c>
+      <c r="AN290" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="291">
@@ -29729,10 +30599,10 @@
         <v>042736</v>
       </c>
       <c r="P291" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q291" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB291" t="str">
         <v/>
@@ -29769,6 +30639,9 @@
       </c>
       <c r="AM291" t="str">
         <v/>
+      </c>
+      <c r="AN291" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="292">
@@ -29818,10 +30691,10 @@
         <v>042743</v>
       </c>
       <c r="P292" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q292" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB292" t="str">
         <v/>
@@ -29858,6 +30731,9 @@
       </c>
       <c r="AM292" t="str">
         <v/>
+      </c>
+      <c r="AN292" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="293">
@@ -29907,10 +30783,10 @@
         <v>042750</v>
       </c>
       <c r="P293" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q293" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB293" t="str">
         <v/>
@@ -29947,6 +30823,9 @@
       </c>
       <c r="AM293" t="str">
         <v/>
+      </c>
+      <c r="AN293" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="294">
@@ -29996,10 +30875,10 @@
         <v>042767</v>
       </c>
       <c r="P294" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q294" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB294" t="str">
         <v/>
@@ -30036,6 +30915,9 @@
       </c>
       <c r="AM294" t="str">
         <v/>
+      </c>
+      <c r="AN294" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="295">
@@ -30085,10 +30967,10 @@
         <v>042774</v>
       </c>
       <c r="P295" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q295" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB295" t="str">
         <v/>
@@ -30125,6 +31007,9 @@
       </c>
       <c r="AM295" t="str">
         <v/>
+      </c>
+      <c r="AN295" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="296">
@@ -30174,10 +31059,10 @@
         <v>039255</v>
       </c>
       <c r="P296" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q296" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB296" t="str">
         <v/>
@@ -30214,6 +31099,9 @@
       </c>
       <c r="AM296" t="str">
         <v/>
+      </c>
+      <c r="AN296" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="297">
@@ -30263,10 +31151,10 @@
         <v>039262</v>
       </c>
       <c r="P297" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q297" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB297" t="str">
         <v/>
@@ -30303,6 +31191,9 @@
       </c>
       <c r="AM297" t="str">
         <v/>
+      </c>
+      <c r="AN297" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="298">
@@ -30352,10 +31243,10 @@
         <v>039279</v>
       </c>
       <c r="P298" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q298" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB298" t="str">
         <v/>
@@ -30392,6 +31283,9 @@
       </c>
       <c r="AM298" t="str">
         <v/>
+      </c>
+      <c r="AN298" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="299">
@@ -30441,10 +31335,10 @@
         <v>039286</v>
       </c>
       <c r="P299" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q299" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB299" t="str">
         <v/>
@@ -30481,6 +31375,9 @@
       </c>
       <c r="AM299" t="str">
         <v/>
+      </c>
+      <c r="AN299" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="300">
@@ -30530,10 +31427,10 @@
         <v>045607</v>
       </c>
       <c r="P300" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q300" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB300" t="str">
         <v/>
@@ -30570,6 +31467,9 @@
       </c>
       <c r="AM300" t="str">
         <v/>
+      </c>
+      <c r="AN300" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="301">
@@ -30619,10 +31519,10 @@
         <v>045614</v>
       </c>
       <c r="P301" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q301" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB301" t="str">
         <v/>
@@ -30659,6 +31559,9 @@
       </c>
       <c r="AM301" t="str">
         <v/>
+      </c>
+      <c r="AN301" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="302">
@@ -30708,10 +31611,10 @@
         <v>045621</v>
       </c>
       <c r="P302" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q302" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB302" t="str">
         <v/>
@@ -30748,6 +31651,9 @@
       </c>
       <c r="AM302" t="str">
         <v/>
+      </c>
+      <c r="AN302" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="303">
@@ -30797,10 +31703,10 @@
         <v>045638</v>
       </c>
       <c r="P303" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q303" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB303" t="str">
         <v/>
@@ -30837,6 +31743,9 @@
       </c>
       <c r="AM303" t="str">
         <v/>
+      </c>
+      <c r="AN303" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="304">
@@ -30886,10 +31795,10 @@
         <v>045645</v>
       </c>
       <c r="P304" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q304" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB304" t="str">
         <v/>
@@ -30926,6 +31835,9 @@
       </c>
       <c r="AM304" t="str">
         <v/>
+      </c>
+      <c r="AN304" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="305">
@@ -30975,10 +31887,10 @@
         <v>045652</v>
       </c>
       <c r="P305" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q305" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB305" t="str">
         <v/>
@@ -31015,6 +31927,9 @@
       </c>
       <c r="AM305" t="str">
         <v/>
+      </c>
+      <c r="AN305" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="306">
@@ -31064,10 +31979,10 @@
         <v/>
       </c>
       <c r="P306" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q306" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB306" t="str">
         <v/>
@@ -31104,6 +32019,9 @@
       </c>
       <c r="AM306" t="str">
         <v/>
+      </c>
+      <c r="AN306" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="307">
@@ -31153,10 +32071,10 @@
         <v/>
       </c>
       <c r="P307" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q307" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB307" t="str">
         <v/>
@@ -31193,6 +32111,9 @@
       </c>
       <c r="AM307" t="str">
         <v/>
+      </c>
+      <c r="AN307" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="308">
@@ -31242,10 +32163,10 @@
         <v/>
       </c>
       <c r="P308" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q308" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB308" t="str">
         <v/>
@@ -31282,6 +32203,9 @@
       </c>
       <c r="AM308" t="str">
         <v/>
+      </c>
+      <c r="AN308" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="309">
@@ -31331,10 +32255,10 @@
         <v/>
       </c>
       <c r="P309" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q309" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB309" t="str">
         <v/>
@@ -31371,6 +32295,9 @@
       </c>
       <c r="AM309" t="str">
         <v/>
+      </c>
+      <c r="AN309" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="310">
@@ -31420,10 +32347,10 @@
         <v/>
       </c>
       <c r="P310" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q310" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB310" t="str">
         <v/>
@@ -31460,6 +32387,9 @@
       </c>
       <c r="AM310" t="str">
         <v/>
+      </c>
+      <c r="AN310" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="311">
@@ -31509,10 +32439,10 @@
         <v/>
       </c>
       <c r="P311" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q311" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB311" t="str">
         <v/>
@@ -31549,6 +32479,9 @@
       </c>
       <c r="AM311" t="str">
         <v/>
+      </c>
+      <c r="AN311" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="312">
@@ -31598,10 +32531,10 @@
         <v/>
       </c>
       <c r="P312" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q312" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB312" t="str">
         <v/>
@@ -31638,6 +32571,9 @@
       </c>
       <c r="AM312" t="str">
         <v/>
+      </c>
+      <c r="AN312" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="313">
@@ -31687,10 +32623,10 @@
         <v/>
       </c>
       <c r="P313" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q313" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB313" t="str">
         <v/>
@@ -31727,6 +32663,9 @@
       </c>
       <c r="AM313" t="str">
         <v/>
+      </c>
+      <c r="AN313" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="314">
@@ -31776,10 +32715,10 @@
         <v/>
       </c>
       <c r="P314" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q314" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB314" t="str">
         <v/>
@@ -31816,6 +32755,9 @@
       </c>
       <c r="AM314" t="str">
         <v/>
+      </c>
+      <c r="AN314" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="315">
@@ -31865,10 +32807,10 @@
         <v/>
       </c>
       <c r="P315" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q315" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB315" t="str">
         <v/>
@@ -31905,6 +32847,9 @@
       </c>
       <c r="AM315" t="str">
         <v/>
+      </c>
+      <c r="AN315" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="316">
@@ -31954,10 +32899,10 @@
         <v/>
       </c>
       <c r="P316" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q316" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB316" t="str">
         <v/>
@@ -31994,6 +32939,9 @@
       </c>
       <c r="AM316" t="str">
         <v/>
+      </c>
+      <c r="AN316" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="317">
@@ -32043,10 +32991,10 @@
         <v/>
       </c>
       <c r="P317" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q317" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB317" t="str">
         <v/>
@@ -32083,6 +33031,9 @@
       </c>
       <c r="AM317" t="str">
         <v/>
+      </c>
+      <c r="AN317" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="318">
@@ -32132,10 +33083,10 @@
         <v/>
       </c>
       <c r="P318" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q318" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB318" t="str">
         <v/>
@@ -32172,6 +33123,9 @@
       </c>
       <c r="AM318" t="str">
         <v/>
+      </c>
+      <c r="AN318" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="319">
@@ -32221,10 +33175,10 @@
         <v/>
       </c>
       <c r="P319" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q319" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB319" t="str">
         <v/>
@@ -32261,6 +33215,9 @@
       </c>
       <c r="AM319" t="str">
         <v/>
+      </c>
+      <c r="AN319" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="320">
@@ -32310,10 +33267,10 @@
         <v/>
       </c>
       <c r="P320" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q320" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB320" t="str">
         <v/>
@@ -32350,6 +33307,9 @@
       </c>
       <c r="AM320" t="str">
         <v/>
+      </c>
+      <c r="AN320" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="321">
@@ -32399,10 +33359,10 @@
         <v/>
       </c>
       <c r="P321" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q321" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB321" t="str">
         <v/>
@@ -32439,6 +33399,9 @@
       </c>
       <c r="AM321" t="str">
         <v/>
+      </c>
+      <c r="AN321" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="322">
@@ -32488,10 +33451,10 @@
         <v/>
       </c>
       <c r="P322" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q322" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB322" t="str">
         <v/>
@@ -32528,6 +33491,9 @@
       </c>
       <c r="AM322" t="str">
         <v/>
+      </c>
+      <c r="AN322" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="323">
@@ -32577,10 +33543,10 @@
         <v/>
       </c>
       <c r="P323" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q323" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB323" t="str">
         <v/>
@@ -32617,6 +33583,9 @@
       </c>
       <c r="AM323" t="str">
         <v/>
+      </c>
+      <c r="AN323" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="324">
@@ -32666,10 +33635,10 @@
         <v/>
       </c>
       <c r="P324" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q324" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB324" t="str">
         <v/>
@@ -32706,6 +33675,9 @@
       </c>
       <c r="AM324" t="str">
         <v/>
+      </c>
+      <c r="AN324" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="325">
@@ -32755,10 +33727,10 @@
         <v/>
       </c>
       <c r="P325" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q325" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB325" t="str">
         <v/>
@@ -32795,6 +33767,9 @@
       </c>
       <c r="AM325" t="str">
         <v/>
+      </c>
+      <c r="AN325" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="326">
@@ -32844,10 +33819,10 @@
         <v/>
       </c>
       <c r="P326" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q326" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB326" t="str">
         <v/>
@@ -32884,6 +33859,9 @@
       </c>
       <c r="AM326" t="str">
         <v/>
+      </c>
+      <c r="AN326" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="327">
@@ -32933,10 +33911,10 @@
         <v/>
       </c>
       <c r="P327" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q327" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB327" t="str">
         <v/>
@@ -32973,6 +33951,9 @@
       </c>
       <c r="AM327" t="str">
         <v/>
+      </c>
+      <c r="AN327" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="328">
@@ -33022,10 +34003,10 @@
         <v/>
       </c>
       <c r="P328" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q328" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB328" t="str">
         <v/>
@@ -33062,6 +34043,9 @@
       </c>
       <c r="AM328" t="str">
         <v/>
+      </c>
+      <c r="AN328" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="329">
@@ -33111,10 +34095,10 @@
         <v/>
       </c>
       <c r="P329" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q329" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB329" t="str">
         <v/>
@@ -33151,6 +34135,9 @@
       </c>
       <c r="AM329" t="str">
         <v/>
+      </c>
+      <c r="AN329" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="330">
@@ -33200,10 +34187,10 @@
         <v/>
       </c>
       <c r="P330" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q330" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB330" t="str">
         <v/>
@@ -33240,6 +34227,9 @@
       </c>
       <c r="AM330" t="str">
         <v/>
+      </c>
+      <c r="AN330" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="331">
@@ -33289,10 +34279,10 @@
         <v/>
       </c>
       <c r="P331" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q331" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB331" t="str">
         <v/>
@@ -33329,6 +34319,9 @@
       </c>
       <c r="AM331" t="str">
         <v/>
+      </c>
+      <c r="AN331" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="332">
@@ -33378,10 +34371,10 @@
         <v/>
       </c>
       <c r="P332" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q332" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB332" t="str">
         <v/>
@@ -33418,6 +34411,9 @@
       </c>
       <c r="AM332" t="str">
         <v/>
+      </c>
+      <c r="AN332" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="333">
@@ -33467,10 +34463,10 @@
         <v/>
       </c>
       <c r="P333" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q333" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB333" t="str">
         <v/>
@@ -33507,6 +34503,9 @@
       </c>
       <c r="AM333" t="str">
         <v/>
+      </c>
+      <c r="AN333" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="334">
@@ -33556,10 +34555,10 @@
         <v>046956</v>
       </c>
       <c r="P334" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q334" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB334" t="str">
         <v/>
@@ -33596,6 +34595,9 @@
       </c>
       <c r="AM334" t="str">
         <v/>
+      </c>
+      <c r="AN334" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="335">
@@ -33645,10 +34647,10 @@
         <v>046963</v>
       </c>
       <c r="P335" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q335" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB335" t="str">
         <v/>
@@ -33685,6 +34687,9 @@
       </c>
       <c r="AM335" t="str">
         <v/>
+      </c>
+      <c r="AN335" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="336">
@@ -33734,10 +34739,10 @@
         <v>046970</v>
       </c>
       <c r="P336" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q336" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB336" t="str">
         <v/>
@@ -33774,6 +34779,9 @@
       </c>
       <c r="AM336" t="str">
         <v/>
+      </c>
+      <c r="AN336" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="337">
@@ -33823,10 +34831,10 @@
         <v>046987</v>
       </c>
       <c r="P337" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q337" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB337" t="str">
         <v/>
@@ -33863,6 +34871,9 @@
       </c>
       <c r="AM337" t="str">
         <v/>
+      </c>
+      <c r="AN337" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="338">
@@ -33912,10 +34923,10 @@
         <v>046994</v>
       </c>
       <c r="P338" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q338" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB338" t="str">
         <v/>
@@ -33952,6 +34963,9 @@
       </c>
       <c r="AM338" t="str">
         <v/>
+      </c>
+      <c r="AN338" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="339">
@@ -34001,10 +35015,10 @@
         <v>047007</v>
       </c>
       <c r="P339" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q339" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB339" t="str">
         <v/>
@@ -34041,6 +35055,9 @@
       </c>
       <c r="AM339" t="str">
         <v/>
+      </c>
+      <c r="AN339" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="340">
@@ -34090,10 +35107,10 @@
         <v>044037</v>
       </c>
       <c r="P340" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q340" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB340" t="str">
         <v/>
@@ -34130,6 +35147,9 @@
       </c>
       <c r="AM340" t="str">
         <v/>
+      </c>
+      <c r="AN340" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="341">
@@ -34179,10 +35199,10 @@
         <v>044044</v>
       </c>
       <c r="P341" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q341" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB341" t="str">
         <v/>
@@ -34219,6 +35239,9 @@
       </c>
       <c r="AM341" t="str">
         <v/>
+      </c>
+      <c r="AN341" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="342">
@@ -34268,10 +35291,10 @@
         <v>044051</v>
       </c>
       <c r="P342" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q342" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB342" t="str">
         <v/>
@@ -34308,6 +35331,9 @@
       </c>
       <c r="AM342" t="str">
         <v/>
+      </c>
+      <c r="AN342" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="343">
@@ -34357,10 +35383,10 @@
         <v>044068</v>
       </c>
       <c r="P343" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q343" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB343" t="str">
         <v/>
@@ -34397,6 +35423,9 @@
       </c>
       <c r="AM343" t="str">
         <v/>
+      </c>
+      <c r="AN343" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="344">
@@ -34446,10 +35475,10 @@
         <v>044075</v>
       </c>
       <c r="P344" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q344" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB344" t="str">
         <v/>
@@ -34486,6 +35515,9 @@
       </c>
       <c r="AM344" t="str">
         <v/>
+      </c>
+      <c r="AN344" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="345">
@@ -34535,10 +35567,10 @@
         <v>044082</v>
       </c>
       <c r="P345" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q345" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB345" t="str">
         <v/>
@@ -34575,6 +35607,9 @@
       </c>
       <c r="AM345" t="str">
         <v/>
+      </c>
+      <c r="AN345" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="346">
@@ -34624,10 +35659,10 @@
         <v>044099</v>
       </c>
       <c r="P346" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q346" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB346" t="str">
         <v/>
@@ -34664,6 +35699,9 @@
       </c>
       <c r="AM346" t="str">
         <v/>
+      </c>
+      <c r="AN346" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="347">
@@ -34713,10 +35751,10 @@
         <v>044105</v>
       </c>
       <c r="P347" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q347" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB347" t="str">
         <v/>
@@ -34753,6 +35791,9 @@
       </c>
       <c r="AM347" t="str">
         <v/>
+      </c>
+      <c r="AN347" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="348">
@@ -34802,10 +35843,10 @@
         <v>048189</v>
       </c>
       <c r="P348" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q348" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB348" t="str">
         <v/>
@@ -34842,6 +35883,9 @@
       </c>
       <c r="AM348" t="str">
         <v/>
+      </c>
+      <c r="AN348" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="349">
@@ -34891,10 +35935,10 @@
         <v>048196</v>
       </c>
       <c r="P349" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q349" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB349" t="str">
         <v/>
@@ -34931,6 +35975,9 @@
       </c>
       <c r="AM349" t="str">
         <v/>
+      </c>
+      <c r="AN349" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="350">
@@ -34980,10 +36027,10 @@
         <v>044983</v>
       </c>
       <c r="P350" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q350" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB350" t="str">
         <v/>
@@ -35020,6 +36067,9 @@
       </c>
       <c r="AM350" t="str">
         <v/>
+      </c>
+      <c r="AN350" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="351">
@@ -35069,10 +36119,10 @@
         <v>044990</v>
       </c>
       <c r="P351" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q351" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB351" t="str">
         <v/>
@@ -35109,6 +36159,9 @@
       </c>
       <c r="AM351" t="str">
         <v/>
+      </c>
+      <c r="AN351" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="352">
@@ -35158,10 +36211,10 @@
         <v/>
       </c>
       <c r="P352" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q352" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB352" t="str">
         <v/>
@@ -35198,6 +36251,9 @@
       </c>
       <c r="AM352" t="str">
         <v/>
+      </c>
+      <c r="AN352" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="353">
@@ -35247,10 +36303,10 @@
         <v/>
       </c>
       <c r="P353" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q353" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB353" t="str">
         <v/>
@@ -35287,6 +36343,9 @@
       </c>
       <c r="AM353" t="str">
         <v/>
+      </c>
+      <c r="AN353" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="354">
@@ -35336,10 +36395,10 @@
         <v/>
       </c>
       <c r="P354" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q354" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB354" t="str">
         <v/>
@@ -35376,6 +36435,9 @@
       </c>
       <c r="AM354" t="str">
         <v/>
+      </c>
+      <c r="AN354" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="355">
@@ -35425,10 +36487,10 @@
         <v/>
       </c>
       <c r="P355" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q355" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB355" t="str">
         <v/>
@@ -35465,6 +36527,9 @@
       </c>
       <c r="AM355" t="str">
         <v/>
+      </c>
+      <c r="AN355" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="356">
@@ -35514,10 +36579,10 @@
         <v/>
       </c>
       <c r="P356" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q356" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB356" t="str">
         <v/>
@@ -35554,6 +36619,9 @@
       </c>
       <c r="AM356" t="str">
         <v/>
+      </c>
+      <c r="AN356" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="357">
@@ -35603,10 +36671,10 @@
         <v/>
       </c>
       <c r="P357" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q357" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB357" t="str">
         <v/>
@@ -35643,6 +36711,9 @@
       </c>
       <c r="AM357" t="str">
         <v/>
+      </c>
+      <c r="AN357" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="358">
@@ -35692,10 +36763,10 @@
         <v>039293</v>
       </c>
       <c r="P358" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q358" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB358" t="str">
         <v/>
@@ -35732,6 +36803,9 @@
       </c>
       <c r="AM358" t="str">
         <v/>
+      </c>
+      <c r="AN358" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="359">
@@ -35781,10 +36855,10 @@
         <v>039309</v>
       </c>
       <c r="P359" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q359" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB359" t="str">
         <v/>
@@ -35821,6 +36895,9 @@
       </c>
       <c r="AM359" t="str">
         <v/>
+      </c>
+      <c r="AN359" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="360">
@@ -35870,10 +36947,10 @@
         <v>039316</v>
       </c>
       <c r="P360" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q360" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB360" t="str">
         <v/>
@@ -35910,6 +36987,9 @@
       </c>
       <c r="AM360" t="str">
         <v/>
+      </c>
+      <c r="AN360" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="361">
@@ -35959,10 +37039,10 @@
         <v>039323</v>
       </c>
       <c r="P361" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q361" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB361" t="str">
         <v/>
@@ -35999,6 +37079,9 @@
       </c>
       <c r="AM361" t="str">
         <v/>
+      </c>
+      <c r="AN361" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="362">
@@ -36048,10 +37131,10 @@
         <v/>
       </c>
       <c r="P362" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q362" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB362" t="str">
         <v/>
@@ -36088,6 +37171,9 @@
       </c>
       <c r="AM362" t="str">
         <v/>
+      </c>
+      <c r="AN362" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="363">
@@ -36137,10 +37223,10 @@
         <v/>
       </c>
       <c r="P363" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q363" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB363" t="str">
         <v/>
@@ -36177,6 +37263,9 @@
       </c>
       <c r="AM363" t="str">
         <v/>
+      </c>
+      <c r="AN363" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="364">
@@ -36226,10 +37315,10 @@
         <v/>
       </c>
       <c r="P364" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q364" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB364" t="str">
         <v/>
@@ -36266,6 +37355,9 @@
       </c>
       <c r="AM364" t="str">
         <v/>
+      </c>
+      <c r="AN364" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="365">
@@ -36315,10 +37407,10 @@
         <v/>
       </c>
       <c r="P365" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q365" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB365" t="str">
         <v/>
@@ -36355,6 +37447,9 @@
       </c>
       <c r="AM365" t="str">
         <v/>
+      </c>
+      <c r="AN365" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="366">
@@ -36404,10 +37499,10 @@
         <v/>
       </c>
       <c r="P366" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q366" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB366" t="str">
         <v/>
@@ -36444,6 +37539,9 @@
       </c>
       <c r="AM366" t="str">
         <v/>
+      </c>
+      <c r="AN366" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="367">
@@ -36493,10 +37591,10 @@
         <v/>
       </c>
       <c r="P367" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q367" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB367" t="str">
         <v/>
@@ -36533,6 +37631,9 @@
       </c>
       <c r="AM367" t="str">
         <v/>
+      </c>
+      <c r="AN367" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="368">
@@ -36582,10 +37683,10 @@
         <v>041937</v>
       </c>
       <c r="P368" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q368" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB368" t="str">
         <v/>
@@ -36622,6 +37723,9 @@
       </c>
       <c r="AM368" t="str">
         <v/>
+      </c>
+      <c r="AN368" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="369">
@@ -36671,10 +37775,10 @@
         <v>041944</v>
       </c>
       <c r="P369" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q369" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB369" t="str">
         <v/>
@@ -36711,6 +37815,9 @@
       </c>
       <c r="AM369" t="str">
         <v/>
+      </c>
+      <c r="AN369" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="370">
@@ -36760,10 +37867,10 @@
         <v>041951</v>
       </c>
       <c r="P370" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q370" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB370" t="str">
         <v/>
@@ -36800,6 +37907,9 @@
       </c>
       <c r="AM370" t="str">
         <v/>
+      </c>
+      <c r="AN370" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="371">
@@ -36849,10 +37959,10 @@
         <v>041968</v>
       </c>
       <c r="P371" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q371" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB371" t="str">
         <v/>
@@ -36889,6 +37999,9 @@
       </c>
       <c r="AM371" t="str">
         <v/>
+      </c>
+      <c r="AN371" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="372">
@@ -36938,10 +38051,10 @@
         <v/>
       </c>
       <c r="P372" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q372" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB372" t="str">
         <v/>
@@ -36978,6 +38091,9 @@
       </c>
       <c r="AM372" t="str">
         <v/>
+      </c>
+      <c r="AN372" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="373">
@@ -37027,10 +38143,10 @@
         <v/>
       </c>
       <c r="P373" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q373" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB373" t="str">
         <v/>
@@ -37067,6 +38183,9 @@
       </c>
       <c r="AM373" t="str">
         <v/>
+      </c>
+      <c r="AN373" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="374">
@@ -37116,10 +38235,10 @@
         <v/>
       </c>
       <c r="P374" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q374" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB374" t="str">
         <v/>
@@ -37156,6 +38275,9 @@
       </c>
       <c r="AM374" t="str">
         <v/>
+      </c>
+      <c r="AN374" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="375">
@@ -37205,10 +38327,10 @@
         <v/>
       </c>
       <c r="P375" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q375" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB375" t="str">
         <v/>
@@ -37245,6 +38367,9 @@
       </c>
       <c r="AM375" t="str">
         <v/>
+      </c>
+      <c r="AN375" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="376">
@@ -37294,10 +38419,10 @@
         <v/>
       </c>
       <c r="P376" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q376" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB376" t="str">
         <v/>
@@ -37334,6 +38459,9 @@
       </c>
       <c r="AM376" t="str">
         <v/>
+      </c>
+      <c r="AN376" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="377">
@@ -37383,10 +38511,10 @@
         <v/>
       </c>
       <c r="P377" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q377" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB377" t="str">
         <v/>
@@ -37423,6 +38551,9 @@
       </c>
       <c r="AM377" t="str">
         <v/>
+      </c>
+      <c r="AN377" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="378">
@@ -37472,10 +38603,10 @@
         <v>016454</v>
       </c>
       <c r="P378" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q378" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB378" t="str">
         <v/>
@@ -37512,6 +38643,9 @@
       </c>
       <c r="AM378" t="str">
         <v/>
+      </c>
+      <c r="AN378" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="379">
@@ -37561,10 +38695,10 @@
         <v>016461</v>
       </c>
       <c r="P379" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q379" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB379" t="str">
         <v/>
@@ -37601,6 +38735,9 @@
       </c>
       <c r="AM379" t="str">
         <v/>
+      </c>
+      <c r="AN379" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="380">
@@ -37650,10 +38787,10 @@
         <v>037312</v>
       </c>
       <c r="P380" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q380" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB380" t="str">
         <v/>
@@ -37690,6 +38827,9 @@
       </c>
       <c r="AM380" t="str">
         <v/>
+      </c>
+      <c r="AN380" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="381">
@@ -37739,10 +38879,10 @@
         <v>037329</v>
       </c>
       <c r="P381" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q381" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB381" t="str">
         <v/>
@@ -37779,6 +38919,9 @@
       </c>
       <c r="AM381" t="str">
         <v/>
+      </c>
+      <c r="AN381" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="382">
@@ -37828,10 +38971,10 @@
         <v/>
       </c>
       <c r="P382" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q382" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB382" t="str">
         <v/>
@@ -37868,6 +39011,9 @@
       </c>
       <c r="AM382" t="str">
         <v/>
+      </c>
+      <c r="AN382" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="383">
@@ -37917,10 +39063,10 @@
         <v/>
       </c>
       <c r="P383" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q383" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB383" t="str">
         <v/>
@@ -37957,6 +39103,9 @@
       </c>
       <c r="AM383" t="str">
         <v/>
+      </c>
+      <c r="AN383" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="384">
@@ -38006,10 +39155,10 @@
         <v>038869</v>
       </c>
       <c r="P384" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q384" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB384" t="str">
         <v/>
@@ -38046,6 +39195,9 @@
       </c>
       <c r="AM384" t="str">
         <v/>
+      </c>
+      <c r="AN384" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="385">
@@ -38095,10 +39247,10 @@
         <v>038876</v>
       </c>
       <c r="P385" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q385" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB385" t="str">
         <v/>
@@ -38135,6 +39287,9 @@
       </c>
       <c r="AM385" t="str">
         <v/>
+      </c>
+      <c r="AN385" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="386">
@@ -38184,10 +39339,10 @@
         <v>042163</v>
       </c>
       <c r="P386" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q386" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB386" t="str">
         <v/>
@@ -38224,6 +39379,9 @@
       </c>
       <c r="AM386" t="str">
         <v/>
+      </c>
+      <c r="AN386" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="387">
@@ -38273,10 +39431,10 @@
         <v>042170</v>
       </c>
       <c r="P387" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q387" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB387" t="str">
         <v/>
@@ -38313,6 +39471,9 @@
       </c>
       <c r="AM387" t="str">
         <v/>
+      </c>
+      <c r="AN387" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="388">
@@ -38362,10 +39523,10 @@
         <v>011657</v>
       </c>
       <c r="P388" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q388" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB388" t="str">
         <v/>
@@ -38402,6 +39563,9 @@
       </c>
       <c r="AM388" t="str">
         <v/>
+      </c>
+      <c r="AN388" t="str">
+        <v>baitcasting</v>
       </c>
     </row>
     <row r="389">
@@ -38451,10 +39615,10 @@
         <v>011664</v>
       </c>
       <c r="P389" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="Q389" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="AB389" t="str">
         <v/>
@@ -38492,10 +39656,13 @@
       <c r="AM389" t="str">
         <v/>
       </c>
+      <c r="AN389" t="str">
+        <v>baitcasting</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AM389"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AN389"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
@@ -473,7 +473,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I2" t="str">
-        <v>images/shimano_reels/TIAGRA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TIAGRA_main.jpg</v>
       </c>
       <c r="J2" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -520,7 +520,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I3" t="str">
-        <v>images/shimano_reels/TALICA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TALICA_main.jpg</v>
       </c>
       <c r="J3" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -567,7 +567,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I4" t="str">
-        <v>images/shimano_reels/EXSENCE DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20DC%20SS_main.jpg</v>
       </c>
       <c r="J4" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -614,7 +614,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I5" t="str">
-        <v>images/shimano_reels/ANTARES DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES%20DC%20MD_main.png</v>
       </c>
       <c r="J5" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -661,7 +661,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I6" t="str">
-        <v>images/shimano_reels/ANTARES DC MD_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES%20DC%20MD_main.png</v>
       </c>
       <c r="J6" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -708,7 +708,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I7" t="str">
-        <v>images/shimano_reels/OCEA JIGGER 4000_4000HG_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20JIGGER%204000_4000HG_main.jpg</v>
       </c>
       <c r="J7" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -755,7 +755,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I8" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20DC_main.jpg</v>
       </c>
       <c r="J8" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -802,7 +802,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I9" t="str">
-        <v>images/shimano_reels/OCEA JIGGER LD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20JIGGER%20LD_main.jpg</v>
       </c>
       <c r="J9" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -849,7 +849,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I10" t="str">
-        <v>images/shimano_reels/OCEA JIGGER F CUSTOM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20JIGGER%20F%20CUSTOM_main.jpg</v>
       </c>
       <c r="J10" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -896,7 +896,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I11" t="str">
-        <v>images/shimano_reels/OCEA CONQUEST CT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20CONQUEST%20CT_main.jpg</v>
       </c>
       <c r="J11" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -943,7 +943,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I12" t="str">
-        <v>images/shimano_reels/KAIKON_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/KAIKON_main.jpg</v>
       </c>
       <c r="J12" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -990,7 +990,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I13" t="str">
-        <v>images/shimano_reels/ANTARES_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES_main.jpg</v>
       </c>
       <c r="J13" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1037,7 +1037,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I14" t="str">
-        <v>images/shimano_reels/OCEA JIGGER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20JIGGER%204000_4000HG_main.jpg</v>
       </c>
       <c r="J14" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1084,7 +1084,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I15" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST MD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20MD_main.jpg</v>
       </c>
       <c r="J15" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1131,7 +1131,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I16" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST BFS LIMITED_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20BFS%20LIMITED_main.jpg</v>
       </c>
       <c r="J16" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1178,7 +1178,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I17" t="str">
-        <v>images/shimano_reels/Metanium DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium%20DC_main.jpg</v>
       </c>
       <c r="J17" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1225,7 +1225,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I18" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20BFS%20LIMITED_main.jpg</v>
       </c>
       <c r="J18" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1272,7 +1272,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I19" t="str">
-        <v>images/shimano_reels/OCEA CONQUEST_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20CONQUEST%20CT_main.jpg</v>
       </c>
       <c r="J19" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1319,7 +1319,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I20" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST SHALLOW EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20SHALLOW%20EDITION_main.jpg</v>
       </c>
       <c r="J20" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1366,7 +1366,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I21" t="str">
-        <v>images/shimano_reels/CALCUTTA CONQUEST BFS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20BFS%20LIMITED_main.jpg</v>
       </c>
       <c r="J21" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1413,7 +1413,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I22" t="str">
-        <v>images/shimano_reels/OCEA CONQUEST FT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20CONQUEST%20FT_main.jpg</v>
       </c>
       <c r="J22" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1460,7 +1460,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I23" t="str">
-        <v>images/shimano_reels/ALDEBARAN DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20DC_main.jpg</v>
       </c>
       <c r="J23" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1507,7 +1507,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I24" t="str">
-        <v>images/shimano_reels/STILE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STILE_main.jpg</v>
       </c>
       <c r="J24" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1554,7 +1554,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I25" t="str">
-        <v>images/shimano_reels/BARCHETTA PREMIUM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA%20PREMIUM_main.jpg</v>
       </c>
       <c r="J25" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1601,7 +1601,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I26" t="str">
-        <v>images/shimano_reels/GRAPPLER PREMIUM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER%20PREMIUM_main.jpg</v>
       </c>
       <c r="J26" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1648,7 +1648,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I27" t="str">
-        <v>images/shimano_reels/ALDEBARAN BFS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20BFS_main.jpg</v>
       </c>
       <c r="J27" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1695,7 +1695,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I28" t="str">
-        <v>images/shimano_reels/ALDEBARAN MGL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20MGL_main.jpg</v>
       </c>
       <c r="J28" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1742,7 +1742,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I29" t="str">
-        <v>images/shimano_reels/Metanium SHALLOW EDITION_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium%20SHALLOW%20EDITION_main.jpg</v>
       </c>
       <c r="J29" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1789,7 +1789,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I30" t="str">
-        <v>images/shimano_reels/Metanium_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium_main.jpg</v>
       </c>
       <c r="J30" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1836,7 +1836,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I31" t="str">
-        <v>images/shimano_reels/SPEEDMASTER 石鲷_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPEEDMASTER%20%E7%9F%B3%E9%B2%B7_main.jpg</v>
       </c>
       <c r="J31" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1883,7 +1883,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I32" t="str">
-        <v>images/shimano_reels/TYRNOS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TYRNOS_main.jpg</v>
       </c>
       <c r="J32" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1930,7 +1930,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I33" t="str">
-        <v>images/shimano_reels/EXSENCE DC SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20DC%20SS_main.jpg</v>
       </c>
       <c r="J33" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1977,7 +1977,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I34" t="str">
-        <v>images/shimano_reels/TRANX 400_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TRANX%20400_main.jpg</v>
       </c>
       <c r="J34" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2024,7 +2024,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I35" t="str">
-        <v>images/shimano_reels/Bantam_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Bantam_main.jpg</v>
       </c>
       <c r="J35" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2071,7 +2071,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I36" t="str">
-        <v>images/shimano_reels/TRANX 300_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TRANX%20300_main.jpg</v>
       </c>
       <c r="J36" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2118,7 +2118,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I37" t="str">
-        <v>images/shimano_reels/BAYGAME_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BAYGAME_main.jpg</v>
       </c>
       <c r="J37" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2165,7 +2165,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I38" t="str">
-        <v>images/shimano_reels/GRAPPLER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER_main.jpg</v>
       </c>
       <c r="J38" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2212,7 +2212,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I39" t="str">
-        <v>images/shimano_reels/BARCHETTA F CUSTOM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA%20F%20CUSTOM_main.jpg</v>
       </c>
       <c r="J39" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2259,7 +2259,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I40" t="str">
-        <v>images/shimano_reels/Scorpion DC MD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20DC%20MD_main.jpg</v>
       </c>
       <c r="J40" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2306,7 +2306,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I41" t="str">
-        <v>images/shimano_reels/SLX DC XT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX%20DC%20XT_main.jpg</v>
       </c>
       <c r="J41" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2353,7 +2353,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I42" t="str">
-        <v>images/shimano_reels/Scorpion DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20DC%20MD_main.jpg</v>
       </c>
       <c r="J42" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2400,7 +2400,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I43" t="str">
-        <v>images/shimano_reels/Scorpion MD 300_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20MD%20300_main.jpg</v>
       </c>
       <c r="J43" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2447,7 +2447,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I44" t="str">
-        <v>images/shimano_reels/GRAPPLER CT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER%20CT_main.jpg</v>
       </c>
       <c r="J44" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2494,7 +2494,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I45" t="str">
-        <v>images/shimano_reels/CURADO DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO%20DC_main.jpg</v>
       </c>
       <c r="J45" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2541,7 +2541,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I46" t="str">
-        <v>images/shimano_reels/CHINUMATIC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CHINUMATIC_main.jpg</v>
       </c>
       <c r="J46" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2588,7 +2588,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I47" t="str">
-        <v>images/shimano_reels/Stephano SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Stephano%20SS_main.jpg</v>
       </c>
       <c r="J47" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2635,7 +2635,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I48" t="str">
-        <v>images/shimano_reels/STILE SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/STILE%20SS_main.jpg</v>
       </c>
       <c r="J48" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2682,7 +2682,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I49" t="str">
-        <v>images/shimano_reels/Scorpion MD 200_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20MD%20200_main.jpg</v>
       </c>
       <c r="J49" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2729,7 +2729,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I50" t="str">
-        <v>images/shimano_reels/TORIUM_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TORIUM_main.jpg</v>
       </c>
       <c r="J50" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2776,7 +2776,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I51" t="str">
-        <v>images/shimano_reels/TRANX 200_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TRANX%20200_main.jpg</v>
       </c>
       <c r="J51" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2823,7 +2823,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I52" t="str">
-        <v>images/shimano_reels/TRANX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TRANX_main.jpg</v>
       </c>
       <c r="J52" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2870,7 +2870,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I53" t="str">
-        <v>images/shimano_reels/BARCHETTA_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA_main.jpg</v>
       </c>
       <c r="J53" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2917,7 +2917,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I54" t="str">
-        <v>images/shimano_reels/BARCHETTA SC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA%20SC_main.jpg</v>
       </c>
       <c r="J54" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2964,7 +2964,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I55" t="str">
-        <v>images/shimano_reels/SLX DC_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX%20DC%20XT_main.jpg</v>
       </c>
       <c r="J55" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3011,7 +3011,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I56" t="str">
-        <v>images/shimano_reels/CURADO_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO_main.jpg</v>
       </c>
       <c r="J56" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3058,7 +3058,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I57" t="str">
-        <v>images/shimano_reels/CURADO 150_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO%20150_main.jpg</v>
       </c>
       <c r="J57" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3105,7 +3105,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I58" t="str">
-        <v>images/shimano_reels/CURADO MGL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO%20MGL_main.jpg</v>
       </c>
       <c r="J58" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3152,7 +3152,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I59" t="str">
-        <v>images/shimano_reels/CURADO BFS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO%20BFS_main.jpg</v>
       </c>
       <c r="J59" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3199,7 +3199,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I60" t="str">
-        <v>images/shimano_reels/SLX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX_main.jpg</v>
       </c>
       <c r="J60" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3246,7 +3246,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I61" t="str">
-        <v>images/shimano_reels/BARCHETTA BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA%20BB_main.jpg</v>
       </c>
       <c r="J61" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3293,7 +3293,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I62" t="str">
-        <v>images/shimano_reels/SLX BFS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX%20BFS_main.jpg</v>
       </c>
       <c r="J62" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3340,7 +3340,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I63" t="str">
-        <v>images/shimano_reels/GRAPPLER BB_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER%20BB_main.jpg</v>
       </c>
       <c r="J63" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3387,7 +3387,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I64" t="str">
-        <v>images/shimano_reels/SLX XT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX%20XT_main.jpg</v>
       </c>
       <c r="J64" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3434,7 +3434,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I65" t="str">
-        <v>images/shimano_reels/小船_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/%E5%B0%8F%E8%88%B9_main.jpg</v>
       </c>
       <c r="J65" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3481,7 +3481,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I66" t="str">
-        <v>images/shimano_reels/CARDIFF_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CARDIFF_main.jpg</v>
       </c>
       <c r="J66" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3528,7 +3528,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I67" t="str">
-        <v>images/shimano_reels/幻风 XT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/%E5%B9%BB%E9%A3%8E%20XT_main.jpg</v>
       </c>
       <c r="J67" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3575,7 +3575,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I68" t="str">
-        <v>images/shimano_reels/TITANOS FUNE GT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TITANOS%20FUNE%20GT_main.jpg</v>
       </c>
       <c r="J68" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3622,7 +3622,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I69" t="str">
-        <v>images/shimano_reels/BASS ONE XT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BASS%20ONE%20XT_main.jpg</v>
       </c>
       <c r="J69" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3669,7 +3669,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I70" t="str">
-        <v>images/shimano_reels/CAIUS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CAIUS_main.jpg</v>
       </c>
       <c r="J70" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3716,7 +3716,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I71" t="str">
-        <v>images/shimano_reels/BASS RISE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BASS%20RISE_main.jpg</v>
       </c>
       <c r="J71" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3763,7 +3763,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I72" t="str">
-        <v>images/shimano_reels/幻风_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/%E5%B9%BB%E9%A3%8E%20XT_main.jpg</v>
       </c>
       <c r="J72" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3810,7 +3810,7 @@
         <v>baitcasting</v>
       </c>
       <c r="I73" t="str">
-        <v>images/shimano_reels/CHINU SPECIAL_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CHINU%20SPECIAL_main.jpg</v>
       </c>
       <c r="J73" t="str">
         <v>2026-04-10 00:51:20</v>

--- a/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
@@ -4282,7 +4282,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AX389"/>
+  <dimension ref="A1:AY389"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4435,6 +4435,9 @@
       <c r="AX1" t="str">
         <v>variant_description</v>
       </c>
+      <c r="AY1" t="str">
+        <v>body_material_tech</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -4587,6 +4590,9 @@
       <c r="AX2" t="str">
         <v/>
       </c>
+      <c r="AY2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -4739,6 +4745,9 @@
       <c r="AX3" t="str">
         <v/>
       </c>
+      <c r="AY3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -4891,6 +4900,9 @@
       <c r="AX4" t="str">
         <v/>
       </c>
+      <c r="AY4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -5043,6 +5055,9 @@
       <c r="AX5" t="str">
         <v/>
       </c>
+      <c r="AY5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -5195,6 +5210,9 @@
       <c r="AX6" t="str">
         <v/>
       </c>
+      <c r="AY6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -5347,6 +5365,9 @@
       <c r="AX7" t="str">
         <v/>
       </c>
+      <c r="AY7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -5499,6 +5520,9 @@
       <c r="AX8" t="str">
         <v/>
       </c>
+      <c r="AY8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -5651,6 +5675,9 @@
       <c r="AX9" t="str">
         <v/>
       </c>
+      <c r="AY9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -5803,6 +5830,9 @@
       <c r="AX10" t="str">
         <v/>
       </c>
+      <c r="AY10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -5955,6 +5985,9 @@
       <c r="AX11" t="str">
         <v/>
       </c>
+      <c r="AY11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -6107,6 +6140,9 @@
       <c r="AX12" t="str">
         <v/>
       </c>
+      <c r="AY12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -6259,6 +6295,9 @@
       <c r="AX13" t="str">
         <v/>
       </c>
+      <c r="AY13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -6411,6 +6450,9 @@
       <c r="AX14" t="str">
         <v/>
       </c>
+      <c r="AY14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -6563,6 +6605,9 @@
       <c r="AX15" t="str">
         <v/>
       </c>
+      <c r="AY15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -6715,6 +6760,9 @@
       <c r="AX16" t="str">
         <v/>
       </c>
+      <c r="AY16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -6867,6 +6915,9 @@
       <c r="AX17" t="str">
         <v/>
       </c>
+      <c r="AY17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -7019,6 +7070,9 @@
       <c r="AX18" t="str">
         <v/>
       </c>
+      <c r="AY18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -7171,6 +7225,9 @@
       <c r="AX19" t="str">
         <v/>
       </c>
+      <c r="AY19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -7323,6 +7380,9 @@
       <c r="AX20" t="str">
         <v/>
       </c>
+      <c r="AY20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -7475,6 +7535,9 @@
       <c r="AX21" t="str">
         <v/>
       </c>
+      <c r="AY21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -7627,6 +7690,9 @@
       <c r="AX22" t="str">
         <v/>
       </c>
+      <c r="AY22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -7779,6 +7845,9 @@
       <c r="AX23" t="str">
         <v/>
       </c>
+      <c r="AY23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -7931,6 +8000,9 @@
       <c r="AX24" t="str">
         <v/>
       </c>
+      <c r="AY24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -8083,6 +8155,9 @@
       <c r="AX25" t="str">
         <v/>
       </c>
+      <c r="AY25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -8235,6 +8310,9 @@
       <c r="AX26" t="str">
         <v/>
       </c>
+      <c r="AY26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -8387,6 +8465,9 @@
       <c r="AX27" t="str">
         <v/>
       </c>
+      <c r="AY27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -8539,6 +8620,9 @@
       <c r="AX28" t="str">
         <v/>
       </c>
+      <c r="AY28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -8691,6 +8775,9 @@
       <c r="AX29" t="str">
         <v/>
       </c>
+      <c r="AY29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -8843,6 +8930,9 @@
       <c r="AX30" t="str">
         <v/>
       </c>
+      <c r="AY30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -8995,6 +9085,9 @@
       <c r="AX31" t="str">
         <v/>
       </c>
+      <c r="AY31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -9147,6 +9240,9 @@
       <c r="AX32" t="str">
         <v/>
       </c>
+      <c r="AY32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -9299,6 +9395,9 @@
       <c r="AX33" t="str">
         <v/>
       </c>
+      <c r="AY33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -9451,6 +9550,9 @@
       <c r="AX34" t="str">
         <v/>
       </c>
+      <c r="AY34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -9603,6 +9705,9 @@
       <c r="AX35" t="str">
         <v/>
       </c>
+      <c r="AY35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -9755,6 +9860,9 @@
       <c r="AX36" t="str">
         <v/>
       </c>
+      <c r="AY36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -9907,6 +10015,9 @@
       <c r="AX37" t="str">
         <v/>
       </c>
+      <c r="AY37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -10059,6 +10170,9 @@
       <c r="AX38" t="str">
         <v/>
       </c>
+      <c r="AY38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -10211,6 +10325,9 @@
       <c r="AX39" t="str">
         <v/>
       </c>
+      <c r="AY39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -10363,6 +10480,9 @@
       <c r="AX40" t="str">
         <v/>
       </c>
+      <c r="AY40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -10515,6 +10635,9 @@
       <c r="AX41" t="str">
         <v/>
       </c>
+      <c r="AY41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -10667,6 +10790,9 @@
       <c r="AX42" t="str">
         <v/>
       </c>
+      <c r="AY42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -10819,6 +10945,9 @@
       <c r="AX43" t="str">
         <v/>
       </c>
+      <c r="AY43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -10971,6 +11100,9 @@
       <c r="AX44" t="str">
         <v/>
       </c>
+      <c r="AY44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -11123,6 +11255,9 @@
       <c r="AX45" t="str">
         <v/>
       </c>
+      <c r="AY45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -11275,6 +11410,9 @@
       <c r="AX46" t="str">
         <v/>
       </c>
+      <c r="AY46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -11427,6 +11565,9 @@
       <c r="AX47" t="str">
         <v/>
       </c>
+      <c r="AY47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -11579,6 +11720,9 @@
       <c r="AX48" t="str">
         <v/>
       </c>
+      <c r="AY48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -11731,6 +11875,9 @@
       <c r="AX49" t="str">
         <v/>
       </c>
+      <c r="AY49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -11883,6 +12030,9 @@
       <c r="AX50" t="str">
         <v/>
       </c>
+      <c r="AY50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -12035,6 +12185,9 @@
       <c r="AX51" t="str">
         <v/>
       </c>
+      <c r="AY51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -12187,6 +12340,9 @@
       <c r="AX52" t="str">
         <v/>
       </c>
+      <c r="AY52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -12339,6 +12495,9 @@
       <c r="AX53" t="str">
         <v/>
       </c>
+      <c r="AY53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -12491,6 +12650,9 @@
       <c r="AX54" t="str">
         <v/>
       </c>
+      <c r="AY54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -12643,6 +12805,9 @@
       <c r="AX55" t="str">
         <v/>
       </c>
+      <c r="AY55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -12795,6 +12960,9 @@
       <c r="AX56" t="str">
         <v/>
       </c>
+      <c r="AY56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -12947,6 +13115,9 @@
       <c r="AX57" t="str">
         <v/>
       </c>
+      <c r="AY57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -13099,6 +13270,9 @@
       <c r="AX58" t="str">
         <v/>
       </c>
+      <c r="AY58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -13251,6 +13425,9 @@
       <c r="AX59" t="str">
         <v/>
       </c>
+      <c r="AY59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -13403,6 +13580,9 @@
       <c r="AX60" t="str">
         <v/>
       </c>
+      <c r="AY60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -13555,6 +13735,9 @@
       <c r="AX61" t="str">
         <v/>
       </c>
+      <c r="AY61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -13707,6 +13890,9 @@
       <c r="AX62" t="str">
         <v/>
       </c>
+      <c r="AY62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -13859,6 +14045,9 @@
       <c r="AX63" t="str">
         <v/>
       </c>
+      <c r="AY63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -14011,6 +14200,9 @@
       <c r="AX64" t="str">
         <v/>
       </c>
+      <c r="AY64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -14163,6 +14355,9 @@
       <c r="AX65" t="str">
         <v/>
       </c>
+      <c r="AY65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -14315,6 +14510,9 @@
       <c r="AX66" t="str">
         <v/>
       </c>
+      <c r="AY66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -14467,6 +14665,9 @@
       <c r="AX67" t="str">
         <v/>
       </c>
+      <c r="AY67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -14619,6 +14820,9 @@
       <c r="AX68" t="str">
         <v/>
       </c>
+      <c r="AY68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -14771,6 +14975,9 @@
       <c r="AX69" t="str">
         <v/>
       </c>
+      <c r="AY69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -14923,6 +15130,9 @@
       <c r="AX70" t="str">
         <v/>
       </c>
+      <c r="AY70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -15075,6 +15285,9 @@
       <c r="AX71" t="str">
         <v/>
       </c>
+      <c r="AY71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -15227,6 +15440,9 @@
       <c r="AX72" t="str">
         <v/>
       </c>
+      <c r="AY72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -15379,6 +15595,9 @@
       <c r="AX73" t="str">
         <v/>
       </c>
+      <c r="AY73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -15531,6 +15750,9 @@
       <c r="AX74" t="str">
         <v/>
       </c>
+      <c r="AY74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -15683,6 +15905,9 @@
       <c r="AX75" t="str">
         <v/>
       </c>
+      <c r="AY75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -15835,6 +16060,9 @@
       <c r="AX76" t="str">
         <v/>
       </c>
+      <c r="AY76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -15987,6 +16215,9 @@
       <c r="AX77" t="str">
         <v/>
       </c>
+      <c r="AY77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -16139,6 +16370,9 @@
       <c r="AX78" t="str">
         <v/>
       </c>
+      <c r="AY78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -16291,6 +16525,9 @@
       <c r="AX79" t="str">
         <v/>
       </c>
+      <c r="AY79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -16443,6 +16680,9 @@
       <c r="AX80" t="str">
         <v/>
       </c>
+      <c r="AY80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -16595,6 +16835,9 @@
       <c r="AX81" t="str">
         <v/>
       </c>
+      <c r="AY81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -16747,6 +16990,9 @@
       <c r="AX82" t="str">
         <v/>
       </c>
+      <c r="AY82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -16899,6 +17145,9 @@
       <c r="AX83" t="str">
         <v/>
       </c>
+      <c r="AY83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -17051,6 +17300,9 @@
       <c r="AX84" t="str">
         <v/>
       </c>
+      <c r="AY84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -17203,6 +17455,9 @@
       <c r="AX85" t="str">
         <v/>
       </c>
+      <c r="AY85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -17355,6 +17610,9 @@
       <c r="AX86" t="str">
         <v/>
       </c>
+      <c r="AY86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -17507,6 +17765,9 @@
       <c r="AX87" t="str">
         <v/>
       </c>
+      <c r="AY87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -17659,6 +17920,9 @@
       <c r="AX88" t="str">
         <v/>
       </c>
+      <c r="AY88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -17811,6 +18075,9 @@
       <c r="AX89" t="str">
         <v/>
       </c>
+      <c r="AY89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -17963,6 +18230,9 @@
       <c r="AX90" t="str">
         <v/>
       </c>
+      <c r="AY90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -18115,6 +18385,9 @@
       <c r="AX91" t="str">
         <v/>
       </c>
+      <c r="AY91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -18267,6 +18540,9 @@
       <c r="AX92" t="str">
         <v/>
       </c>
+      <c r="AY92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -18419,6 +18695,9 @@
       <c r="AX93" t="str">
         <v/>
       </c>
+      <c r="AY93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -18571,6 +18850,9 @@
       <c r="AX94" t="str">
         <v/>
       </c>
+      <c r="AY94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -18723,6 +19005,9 @@
       <c r="AX95" t="str">
         <v/>
       </c>
+      <c r="AY95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -18875,6 +19160,9 @@
       <c r="AX96" t="str">
         <v/>
       </c>
+      <c r="AY96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -19027,6 +19315,9 @@
       <c r="AX97" t="str">
         <v/>
       </c>
+      <c r="AY97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -19179,6 +19470,9 @@
       <c r="AX98" t="str">
         <v/>
       </c>
+      <c r="AY98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -19331,6 +19625,9 @@
       <c r="AX99" t="str">
         <v/>
       </c>
+      <c r="AY99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -19483,6 +19780,9 @@
       <c r="AX100" t="str">
         <v/>
       </c>
+      <c r="AY100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -19635,6 +19935,9 @@
       <c r="AX101" t="str">
         <v/>
       </c>
+      <c r="AY101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -19787,6 +20090,9 @@
       <c r="AX102" t="str">
         <v/>
       </c>
+      <c r="AY102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -19939,6 +20245,9 @@
       <c r="AX103" t="str">
         <v/>
       </c>
+      <c r="AY103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -20091,6 +20400,9 @@
       <c r="AX104" t="str">
         <v/>
       </c>
+      <c r="AY104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -20243,6 +20555,9 @@
       <c r="AX105" t="str">
         <v/>
       </c>
+      <c r="AY105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -20395,6 +20710,9 @@
       <c r="AX106" t="str">
         <v/>
       </c>
+      <c r="AY106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -20547,6 +20865,9 @@
       <c r="AX107" t="str">
         <v/>
       </c>
+      <c r="AY107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -20699,6 +21020,9 @@
       <c r="AX108" t="str">
         <v/>
       </c>
+      <c r="AY108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -20851,6 +21175,9 @@
       <c r="AX109" t="str">
         <v/>
       </c>
+      <c r="AY109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -21003,6 +21330,9 @@
       <c r="AX110" t="str">
         <v/>
       </c>
+      <c r="AY110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -21155,6 +21485,9 @@
       <c r="AX111" t="str">
         <v/>
       </c>
+      <c r="AY111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -21307,6 +21640,9 @@
       <c r="AX112" t="str">
         <v/>
       </c>
+      <c r="AY112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -21459,6 +21795,9 @@
       <c r="AX113" t="str">
         <v/>
       </c>
+      <c r="AY113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -21611,6 +21950,9 @@
       <c r="AX114" t="str">
         <v/>
       </c>
+      <c r="AY114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -21763,6 +22105,9 @@
       <c r="AX115" t="str">
         <v/>
       </c>
+      <c r="AY115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -21915,6 +22260,9 @@
       <c r="AX116" t="str">
         <v/>
       </c>
+      <c r="AY116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -22067,6 +22415,9 @@
       <c r="AX117" t="str">
         <v/>
       </c>
+      <c r="AY117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -22219,6 +22570,9 @@
       <c r="AX118" t="str">
         <v/>
       </c>
+      <c r="AY118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -22371,6 +22725,9 @@
       <c r="AX119" t="str">
         <v/>
       </c>
+      <c r="AY119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -22523,6 +22880,9 @@
       <c r="AX120" t="str">
         <v/>
       </c>
+      <c r="AY120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -22675,6 +23035,9 @@
       <c r="AX121" t="str">
         <v/>
       </c>
+      <c r="AY121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -22827,6 +23190,9 @@
       <c r="AX122" t="str">
         <v/>
       </c>
+      <c r="AY122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -22979,6 +23345,9 @@
       <c r="AX123" t="str">
         <v/>
       </c>
+      <c r="AY123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -23131,6 +23500,9 @@
       <c r="AX124" t="str">
         <v/>
       </c>
+      <c r="AY124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -23283,6 +23655,9 @@
       <c r="AX125" t="str">
         <v/>
       </c>
+      <c r="AY125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -23435,6 +23810,9 @@
       <c r="AX126" t="str">
         <v/>
       </c>
+      <c r="AY126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -23587,6 +23965,9 @@
       <c r="AX127" t="str">
         <v/>
       </c>
+      <c r="AY127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -23739,6 +24120,9 @@
       <c r="AX128" t="str">
         <v/>
       </c>
+      <c r="AY128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -23891,6 +24275,9 @@
       <c r="AX129" t="str">
         <v/>
       </c>
+      <c r="AY129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -24043,6 +24430,9 @@
       <c r="AX130" t="str">
         <v/>
       </c>
+      <c r="AY130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -24195,6 +24585,9 @@
       <c r="AX131" t="str">
         <v/>
       </c>
+      <c r="AY131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -24347,6 +24740,9 @@
       <c r="AX132" t="str">
         <v/>
       </c>
+      <c r="AY132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -24499,6 +24895,9 @@
       <c r="AX133" t="str">
         <v/>
       </c>
+      <c r="AY133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -24651,6 +25050,9 @@
       <c r="AX134" t="str">
         <v/>
       </c>
+      <c r="AY134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -24803,6 +25205,9 @@
       <c r="AX135" t="str">
         <v/>
       </c>
+      <c r="AY135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -24955,6 +25360,9 @@
       <c r="AX136" t="str">
         <v/>
       </c>
+      <c r="AY136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -25107,6 +25515,9 @@
       <c r="AX137" t="str">
         <v/>
       </c>
+      <c r="AY137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -25259,6 +25670,9 @@
       <c r="AX138" t="str">
         <v/>
       </c>
+      <c r="AY138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -25411,6 +25825,9 @@
       <c r="AX139" t="str">
         <v/>
       </c>
+      <c r="AY139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -25563,6 +25980,9 @@
       <c r="AX140" t="str">
         <v/>
       </c>
+      <c r="AY140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -25715,6 +26135,9 @@
       <c r="AX141" t="str">
         <v/>
       </c>
+      <c r="AY141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -25867,6 +26290,9 @@
       <c r="AX142" t="str">
         <v/>
       </c>
+      <c r="AY142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -26019,6 +26445,9 @@
       <c r="AX143" t="str">
         <v/>
       </c>
+      <c r="AY143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -26171,6 +26600,9 @@
       <c r="AX144" t="str">
         <v/>
       </c>
+      <c r="AY144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -26323,6 +26755,9 @@
       <c r="AX145" t="str">
         <v/>
       </c>
+      <c r="AY145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -26475,6 +26910,9 @@
       <c r="AX146" t="str">
         <v/>
       </c>
+      <c r="AY146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -26627,6 +27065,9 @@
       <c r="AX147" t="str">
         <v/>
       </c>
+      <c r="AY147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -26779,6 +27220,9 @@
       <c r="AX148" t="str">
         <v/>
       </c>
+      <c r="AY148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -26931,6 +27375,9 @@
       <c r="AX149" t="str">
         <v/>
       </c>
+      <c r="AY149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -27083,6 +27530,9 @@
       <c r="AX150" t="str">
         <v/>
       </c>
+      <c r="AY150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -27235,6 +27685,9 @@
       <c r="AX151" t="str">
         <v/>
       </c>
+      <c r="AY151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -27387,6 +27840,9 @@
       <c r="AX152" t="str">
         <v/>
       </c>
+      <c r="AY152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -27539,6 +27995,9 @@
       <c r="AX153" t="str">
         <v/>
       </c>
+      <c r="AY153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -27691,6 +28150,9 @@
       <c r="AX154" t="str">
         <v/>
       </c>
+      <c r="AY154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -27843,6 +28305,9 @@
       <c r="AX155" t="str">
         <v/>
       </c>
+      <c r="AY155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -27995,6 +28460,9 @@
       <c r="AX156" t="str">
         <v/>
       </c>
+      <c r="AY156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -28147,6 +28615,9 @@
       <c r="AX157" t="str">
         <v/>
       </c>
+      <c r="AY157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -28299,6 +28770,9 @@
       <c r="AX158" t="str">
         <v/>
       </c>
+      <c r="AY158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -28451,6 +28925,9 @@
       <c r="AX159" t="str">
         <v/>
       </c>
+      <c r="AY159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -28603,6 +29080,9 @@
       <c r="AX160" t="str">
         <v/>
       </c>
+      <c r="AY160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -28755,6 +29235,9 @@
       <c r="AX161" t="str">
         <v/>
       </c>
+      <c r="AY161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -28907,6 +29390,9 @@
       <c r="AX162" t="str">
         <v/>
       </c>
+      <c r="AY162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -29059,6 +29545,9 @@
       <c r="AX163" t="str">
         <v/>
       </c>
+      <c r="AY163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -29211,6 +29700,9 @@
       <c r="AX164" t="str">
         <v/>
       </c>
+      <c r="AY164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -29363,6 +29855,9 @@
       <c r="AX165" t="str">
         <v/>
       </c>
+      <c r="AY165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -29515,6 +30010,9 @@
       <c r="AX166" t="str">
         <v/>
       </c>
+      <c r="AY166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -29667,6 +30165,9 @@
       <c r="AX167" t="str">
         <v/>
       </c>
+      <c r="AY167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -29819,6 +30320,9 @@
       <c r="AX168" t="str">
         <v/>
       </c>
+      <c r="AY168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -29971,6 +30475,9 @@
       <c r="AX169" t="str">
         <v/>
       </c>
+      <c r="AY169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -30123,6 +30630,9 @@
       <c r="AX170" t="str">
         <v/>
       </c>
+      <c r="AY170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -30275,6 +30785,9 @@
       <c r="AX171" t="str">
         <v/>
       </c>
+      <c r="AY171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -30427,6 +30940,9 @@
       <c r="AX172" t="str">
         <v/>
       </c>
+      <c r="AY172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -30579,6 +31095,9 @@
       <c r="AX173" t="str">
         <v/>
       </c>
+      <c r="AY173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -30731,6 +31250,9 @@
       <c r="AX174" t="str">
         <v/>
       </c>
+      <c r="AY174" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -30883,6 +31405,9 @@
       <c r="AX175" t="str">
         <v/>
       </c>
+      <c r="AY175" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -31035,6 +31560,9 @@
       <c r="AX176" t="str">
         <v/>
       </c>
+      <c r="AY176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -31187,6 +31715,9 @@
       <c r="AX177" t="str">
         <v/>
       </c>
+      <c r="AY177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -31339,6 +31870,9 @@
       <c r="AX178" t="str">
         <v/>
       </c>
+      <c r="AY178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -31491,6 +32025,9 @@
       <c r="AX179" t="str">
         <v/>
       </c>
+      <c r="AY179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -31643,6 +32180,9 @@
       <c r="AX180" t="str">
         <v/>
       </c>
+      <c r="AY180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -31795,6 +32335,9 @@
       <c r="AX181" t="str">
         <v/>
       </c>
+      <c r="AY181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -31947,6 +32490,9 @@
       <c r="AX182" t="str">
         <v/>
       </c>
+      <c r="AY182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -32099,6 +32645,9 @@
       <c r="AX183" t="str">
         <v/>
       </c>
+      <c r="AY183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -32251,6 +32800,9 @@
       <c r="AX184" t="str">
         <v/>
       </c>
+      <c r="AY184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -32403,6 +32955,9 @@
       <c r="AX185" t="str">
         <v/>
       </c>
+      <c r="AY185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -32555,6 +33110,9 @@
       <c r="AX186" t="str">
         <v/>
       </c>
+      <c r="AY186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -32707,6 +33265,9 @@
       <c r="AX187" t="str">
         <v/>
       </c>
+      <c r="AY187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -32859,6 +33420,9 @@
       <c r="AX188" t="str">
         <v/>
       </c>
+      <c r="AY188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -33011,6 +33575,9 @@
       <c r="AX189" t="str">
         <v/>
       </c>
+      <c r="AY189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -33163,6 +33730,9 @@
       <c r="AX190" t="str">
         <v/>
       </c>
+      <c r="AY190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -33315,6 +33885,9 @@
       <c r="AX191" t="str">
         <v/>
       </c>
+      <c r="AY191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -33467,6 +34040,9 @@
       <c r="AX192" t="str">
         <v/>
       </c>
+      <c r="AY192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -33619,6 +34195,9 @@
       <c r="AX193" t="str">
         <v/>
       </c>
+      <c r="AY193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -33771,6 +34350,9 @@
       <c r="AX194" t="str">
         <v/>
       </c>
+      <c r="AY194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -33923,6 +34505,9 @@
       <c r="AX195" t="str">
         <v/>
       </c>
+      <c r="AY195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -34075,6 +34660,9 @@
       <c r="AX196" t="str">
         <v/>
       </c>
+      <c r="AY196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -34227,6 +34815,9 @@
       <c r="AX197" t="str">
         <v/>
       </c>
+      <c r="AY197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -34379,6 +34970,9 @@
       <c r="AX198" t="str">
         <v/>
       </c>
+      <c r="AY198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -34531,6 +35125,9 @@
       <c r="AX199" t="str">
         <v/>
       </c>
+      <c r="AY199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -34683,6 +35280,9 @@
       <c r="AX200" t="str">
         <v/>
       </c>
+      <c r="AY200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -34835,6 +35435,9 @@
       <c r="AX201" t="str">
         <v/>
       </c>
+      <c r="AY201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -34987,6 +35590,9 @@
       <c r="AX202" t="str">
         <v/>
       </c>
+      <c r="AY202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -35139,6 +35745,9 @@
       <c r="AX203" t="str">
         <v/>
       </c>
+      <c r="AY203" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -35291,6 +35900,9 @@
       <c r="AX204" t="str">
         <v/>
       </c>
+      <c r="AY204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -35443,6 +36055,9 @@
       <c r="AX205" t="str">
         <v/>
       </c>
+      <c r="AY205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -35595,6 +36210,9 @@
       <c r="AX206" t="str">
         <v/>
       </c>
+      <c r="AY206" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -35747,6 +36365,9 @@
       <c r="AX207" t="str">
         <v/>
       </c>
+      <c r="AY207" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -35899,6 +36520,9 @@
       <c r="AX208" t="str">
         <v/>
       </c>
+      <c r="AY208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -36051,6 +36675,9 @@
       <c r="AX209" t="str">
         <v/>
       </c>
+      <c r="AY209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -36203,6 +36830,9 @@
       <c r="AX210" t="str">
         <v/>
       </c>
+      <c r="AY210" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -36355,6 +36985,9 @@
       <c r="AX211" t="str">
         <v/>
       </c>
+      <c r="AY211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -36507,6 +37140,9 @@
       <c r="AX212" t="str">
         <v/>
       </c>
+      <c r="AY212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -36659,6 +37295,9 @@
       <c r="AX213" t="str">
         <v/>
       </c>
+      <c r="AY213" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -36811,6 +37450,9 @@
       <c r="AX214" t="str">
         <v/>
       </c>
+      <c r="AY214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -36963,6 +37605,9 @@
       <c r="AX215" t="str">
         <v/>
       </c>
+      <c r="AY215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -37115,6 +37760,9 @@
       <c r="AX216" t="str">
         <v/>
       </c>
+      <c r="AY216" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -37267,6 +37915,9 @@
       <c r="AX217" t="str">
         <v/>
       </c>
+      <c r="AY217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -37419,6 +38070,9 @@
       <c r="AX218" t="str">
         <v/>
       </c>
+      <c r="AY218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -37571,6 +38225,9 @@
       <c r="AX219" t="str">
         <v/>
       </c>
+      <c r="AY219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -37723,6 +38380,9 @@
       <c r="AX220" t="str">
         <v/>
       </c>
+      <c r="AY220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -37875,6 +38535,9 @@
       <c r="AX221" t="str">
         <v/>
       </c>
+      <c r="AY221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -38027,6 +38690,9 @@
       <c r="AX222" t="str">
         <v/>
       </c>
+      <c r="AY222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -38179,6 +38845,9 @@
       <c r="AX223" t="str">
         <v/>
       </c>
+      <c r="AY223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -38331,6 +39000,9 @@
       <c r="AX224" t="str">
         <v/>
       </c>
+      <c r="AY224" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -38483,6 +39155,9 @@
       <c r="AX225" t="str">
         <v/>
       </c>
+      <c r="AY225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -38635,6 +39310,9 @@
       <c r="AX226" t="str">
         <v/>
       </c>
+      <c r="AY226" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -38787,6 +39465,9 @@
       <c r="AX227" t="str">
         <v/>
       </c>
+      <c r="AY227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -38939,6 +39620,9 @@
       <c r="AX228" t="str">
         <v/>
       </c>
+      <c r="AY228" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -39091,6 +39775,9 @@
       <c r="AX229" t="str">
         <v/>
       </c>
+      <c r="AY229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -39243,6 +39930,9 @@
       <c r="AX230" t="str">
         <v/>
       </c>
+      <c r="AY230" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -39395,6 +40085,9 @@
       <c r="AX231" t="str">
         <v/>
       </c>
+      <c r="AY231" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -39547,6 +40240,9 @@
       <c r="AX232" t="str">
         <v/>
       </c>
+      <c r="AY232" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -39699,6 +40395,9 @@
       <c r="AX233" t="str">
         <v/>
       </c>
+      <c r="AY233" t="str">
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -39851,6 +40550,9 @@
       <c r="AX234" t="str">
         <v/>
       </c>
+      <c r="AY234" t="str">
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -40003,6 +40705,9 @@
       <c r="AX235" t="str">
         <v/>
       </c>
+      <c r="AY235" t="str">
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -40155,6 +40860,9 @@
       <c r="AX236" t="str">
         <v/>
       </c>
+      <c r="AY236" t="str">
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -40307,6 +41015,9 @@
       <c r="AX237" t="str">
         <v/>
       </c>
+      <c r="AY237" t="str">
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -40459,6 +41170,9 @@
       <c r="AX238" t="str">
         <v/>
       </c>
+      <c r="AY238" t="str">
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -40611,6 +41325,9 @@
       <c r="AX239" t="str">
         <v/>
       </c>
+      <c r="AY239" t="str">
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -40763,6 +41480,9 @@
       <c r="AX240" t="str">
         <v/>
       </c>
+      <c r="AY240" t="str">
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -40915,6 +41635,9 @@
       <c r="AX241" t="str">
         <v/>
       </c>
+      <c r="AY241" t="str">
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -41067,6 +41790,9 @@
       <c r="AX242" t="str">
         <v/>
       </c>
+      <c r="AY242" t="str">
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -41219,6 +41945,9 @@
       <c r="AX243" t="str">
         <v/>
       </c>
+      <c r="AY243" t="str">
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -41371,6 +42100,9 @@
       <c r="AX244" t="str">
         <v/>
       </c>
+      <c r="AY244" t="str">
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -41523,6 +42255,9 @@
       <c r="AX245" t="str">
         <v/>
       </c>
+      <c r="AY245" t="str">
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -41675,6 +42410,9 @@
       <c r="AX246" t="str">
         <v/>
       </c>
+      <c r="AY246" t="str">
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -41827,6 +42565,9 @@
       <c r="AX247" t="str">
         <v/>
       </c>
+      <c r="AY247" t="str">
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -41979,6 +42720,9 @@
       <c r="AX248" t="str">
         <v/>
       </c>
+      <c r="AY248" t="str">
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -42131,6 +42875,9 @@
       <c r="AX249" t="str">
         <v/>
       </c>
+      <c r="AY249" t="str">
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -42283,6 +43030,9 @@
       <c r="AX250" t="str">
         <v/>
       </c>
+      <c r="AY250" t="str">
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -42435,6 +43185,9 @@
       <c r="AX251" t="str">
         <v/>
       </c>
+      <c r="AY251" t="str">
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -42587,6 +43340,9 @@
       <c r="AX252" t="str">
         <v/>
       </c>
+      <c r="AY252" t="str">
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -42739,6 +43495,9 @@
       <c r="AX253" t="str">
         <v/>
       </c>
+      <c r="AY253" t="str">
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -42891,6 +43650,9 @@
       <c r="AX254" t="str">
         <v/>
       </c>
+      <c r="AY254" t="str">
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -43043,6 +43805,9 @@
       <c r="AX255" t="str">
         <v/>
       </c>
+      <c r="AY255" t="str">
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -43195,6 +43960,9 @@
       <c r="AX256" t="str">
         <v/>
       </c>
+      <c r="AY256" t="str">
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -43347,6 +44115,9 @@
       <c r="AX257" t="str">
         <v/>
       </c>
+      <c r="AY257" t="str">
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -43499,6 +44270,9 @@
       <c r="AX258" t="str">
         <v/>
       </c>
+      <c r="AY258" t="str">
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -43651,6 +44425,9 @@
       <c r="AX259" t="str">
         <v/>
       </c>
+      <c r="AY259" t="str">
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -43803,6 +44580,9 @@
       <c r="AX260" t="str">
         <v/>
       </c>
+      <c r="AY260" t="str">
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -43955,6 +44735,9 @@
       <c r="AX261" t="str">
         <v/>
       </c>
+      <c r="AY261" t="str">
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -44107,6 +44890,9 @@
       <c r="AX262" t="str">
         <v/>
       </c>
+      <c r="AY262" t="str">
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -44259,6 +45045,9 @@
       <c r="AX263" t="str">
         <v/>
       </c>
+      <c r="AY263" t="str">
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -44411,6 +45200,9 @@
       <c r="AX264" t="str">
         <v/>
       </c>
+      <c r="AY264" t="str">
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -44563,6 +45355,9 @@
       <c r="AX265" t="str">
         <v/>
       </c>
+      <c r="AY265" t="str">
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -44715,6 +45510,9 @@
       <c r="AX266" t="str">
         <v/>
       </c>
+      <c r="AY266" t="str">
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -44867,6 +45665,9 @@
       <c r="AX267" t="str">
         <v/>
       </c>
+      <c r="AY267" t="str">
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -45019,6 +45820,9 @@
       <c r="AX268" t="str">
         <v/>
       </c>
+      <c r="AY268" t="str">
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -45171,6 +45975,9 @@
       <c r="AX269" t="str">
         <v/>
       </c>
+      <c r="AY269" t="str">
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -45323,6 +46130,9 @@
       <c r="AX270" t="str">
         <v/>
       </c>
+      <c r="AY270" t="str">
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -45475,6 +46285,9 @@
       <c r="AX271" t="str">
         <v/>
       </c>
+      <c r="AY271" t="str">
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -45627,6 +46440,9 @@
       <c r="AX272" t="str">
         <v/>
       </c>
+      <c r="AY272" t="str">
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -45779,6 +46595,9 @@
       <c r="AX273" t="str">
         <v/>
       </c>
+      <c r="AY273" t="str">
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -45931,6 +46750,9 @@
       <c r="AX274" t="str">
         <v/>
       </c>
+      <c r="AY274" t="str">
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -46083,6 +46905,9 @@
       <c r="AX275" t="str">
         <v/>
       </c>
+      <c r="AY275" t="str">
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -46235,6 +47060,9 @@
       <c r="AX276" t="str">
         <v/>
       </c>
+      <c r="AY276" t="str">
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -46387,6 +47215,9 @@
       <c r="AX277" t="str">
         <v/>
       </c>
+      <c r="AY277" t="str">
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -46539,6 +47370,9 @@
       <c r="AX278" t="str">
         <v/>
       </c>
+      <c r="AY278" t="str">
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -46691,6 +47525,9 @@
       <c r="AX279" t="str">
         <v/>
       </c>
+      <c r="AY279" t="str">
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -46843,6 +47680,9 @@
       <c r="AX280" t="str">
         <v/>
       </c>
+      <c r="AY280" t="str">
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -46995,6 +47835,9 @@
       <c r="AX281" t="str">
         <v/>
       </c>
+      <c r="AY281" t="str">
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -47147,6 +47990,9 @@
       <c r="AX282" t="str">
         <v/>
       </c>
+      <c r="AY282" t="str">
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -47299,6 +48145,9 @@
       <c r="AX283" t="str">
         <v/>
       </c>
+      <c r="AY283" t="str">
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -47451,6 +48300,9 @@
       <c r="AX284" t="str">
         <v/>
       </c>
+      <c r="AY284" t="str">
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -47603,6 +48455,9 @@
       <c r="AX285" t="str">
         <v/>
       </c>
+      <c r="AY285" t="str">
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -47755,6 +48610,9 @@
       <c r="AX286" t="str">
         <v/>
       </c>
+      <c r="AY286" t="str">
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -47907,6 +48765,9 @@
       <c r="AX287" t="str">
         <v/>
       </c>
+      <c r="AY287" t="str">
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -48059,6 +48920,9 @@
       <c r="AX288" t="str">
         <v/>
       </c>
+      <c r="AY288" t="str">
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -48211,6 +49075,9 @@
       <c r="AX289" t="str">
         <v/>
       </c>
+      <c r="AY289" t="str">
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -48363,6 +49230,9 @@
       <c r="AX290" t="str">
         <v/>
       </c>
+      <c r="AY290" t="str">
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -48515,6 +49385,9 @@
       <c r="AX291" t="str">
         <v/>
       </c>
+      <c r="AY291" t="str">
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
@@ -48667,6 +49540,9 @@
       <c r="AX292" t="str">
         <v/>
       </c>
+      <c r="AY292" t="str">
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -48819,6 +49695,9 @@
       <c r="AX293" t="str">
         <v/>
       </c>
+      <c r="AY293" t="str">
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -48971,6 +49850,9 @@
       <c r="AX294" t="str">
         <v/>
       </c>
+      <c r="AY294" t="str">
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
@@ -49123,6 +50005,9 @@
       <c r="AX295" t="str">
         <v/>
       </c>
+      <c r="AY295" t="str">
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
@@ -49275,6 +50160,9 @@
       <c r="AX296" t="str">
         <v/>
       </c>
+      <c r="AY296" t="str">
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -49427,6 +50315,9 @@
       <c r="AX297" t="str">
         <v/>
       </c>
+      <c r="AY297" t="str">
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -49579,6 +50470,9 @@
       <c r="AX298" t="str">
         <v/>
       </c>
+      <c r="AY298" t="str">
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -49731,6 +50625,9 @@
       <c r="AX299" t="str">
         <v/>
       </c>
+      <c r="AY299" t="str">
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -49883,6 +50780,9 @@
       <c r="AX300" t="str">
         <v/>
       </c>
+      <c r="AY300" t="str">
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -50035,6 +50935,9 @@
       <c r="AX301" t="str">
         <v/>
       </c>
+      <c r="AY301" t="str">
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -50187,6 +51090,9 @@
       <c r="AX302" t="str">
         <v/>
       </c>
+      <c r="AY302" t="str">
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -50339,6 +51245,9 @@
       <c r="AX303" t="str">
         <v/>
       </c>
+      <c r="AY303" t="str">
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -50491,6 +51400,9 @@
       <c r="AX304" t="str">
         <v/>
       </c>
+      <c r="AY304" t="str">
+        <v/>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -50643,6 +51555,9 @@
       <c r="AX305" t="str">
         <v/>
       </c>
+      <c r="AY305" t="str">
+        <v/>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -50795,6 +51710,9 @@
       <c r="AX306" t="str">
         <v/>
       </c>
+      <c r="AY306" t="str">
+        <v/>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -50947,6 +51865,9 @@
       <c r="AX307" t="str">
         <v/>
       </c>
+      <c r="AY307" t="str">
+        <v/>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -51099,6 +52020,9 @@
       <c r="AX308" t="str">
         <v/>
       </c>
+      <c r="AY308" t="str">
+        <v/>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -51251,6 +52175,9 @@
       <c r="AX309" t="str">
         <v/>
       </c>
+      <c r="AY309" t="str">
+        <v/>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -51403,6 +52330,9 @@
       <c r="AX310" t="str">
         <v/>
       </c>
+      <c r="AY310" t="str">
+        <v/>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -51555,6 +52485,9 @@
       <c r="AX311" t="str">
         <v/>
       </c>
+      <c r="AY311" t="str">
+        <v/>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -51707,6 +52640,9 @@
       <c r="AX312" t="str">
         <v/>
       </c>
+      <c r="AY312" t="str">
+        <v/>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -51859,6 +52795,9 @@
       <c r="AX313" t="str">
         <v/>
       </c>
+      <c r="AY313" t="str">
+        <v/>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -52011,6 +52950,9 @@
       <c r="AX314" t="str">
         <v/>
       </c>
+      <c r="AY314" t="str">
+        <v/>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -52163,6 +53105,9 @@
       <c r="AX315" t="str">
         <v/>
       </c>
+      <c r="AY315" t="str">
+        <v/>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -52315,6 +53260,9 @@
       <c r="AX316" t="str">
         <v/>
       </c>
+      <c r="AY316" t="str">
+        <v/>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -52467,6 +53415,9 @@
       <c r="AX317" t="str">
         <v/>
       </c>
+      <c r="AY317" t="str">
+        <v/>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -52619,6 +53570,9 @@
       <c r="AX318" t="str">
         <v/>
       </c>
+      <c r="AY318" t="str">
+        <v/>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -52771,6 +53725,9 @@
       <c r="AX319" t="str">
         <v/>
       </c>
+      <c r="AY319" t="str">
+        <v/>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -52923,6 +53880,9 @@
       <c r="AX320" t="str">
         <v/>
       </c>
+      <c r="AY320" t="str">
+        <v/>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -53075,6 +54035,9 @@
       <c r="AX321" t="str">
         <v/>
       </c>
+      <c r="AY321" t="str">
+        <v/>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -53227,6 +54190,9 @@
       <c r="AX322" t="str">
         <v/>
       </c>
+      <c r="AY322" t="str">
+        <v/>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -53379,6 +54345,9 @@
       <c r="AX323" t="str">
         <v/>
       </c>
+      <c r="AY323" t="str">
+        <v/>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -53531,6 +54500,9 @@
       <c r="AX324" t="str">
         <v/>
       </c>
+      <c r="AY324" t="str">
+        <v/>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -53683,6 +54655,9 @@
       <c r="AX325" t="str">
         <v/>
       </c>
+      <c r="AY325" t="str">
+        <v/>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -53835,6 +54810,9 @@
       <c r="AX326" t="str">
         <v/>
       </c>
+      <c r="AY326" t="str">
+        <v/>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -53987,6 +54965,9 @@
       <c r="AX327" t="str">
         <v/>
       </c>
+      <c r="AY327" t="str">
+        <v/>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -54139,6 +55120,9 @@
       <c r="AX328" t="str">
         <v/>
       </c>
+      <c r="AY328" t="str">
+        <v/>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -54291,6 +55275,9 @@
       <c r="AX329" t="str">
         <v/>
       </c>
+      <c r="AY329" t="str">
+        <v/>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -54443,6 +55430,9 @@
       <c r="AX330" t="str">
         <v/>
       </c>
+      <c r="AY330" t="str">
+        <v/>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -54595,6 +55585,9 @@
       <c r="AX331" t="str">
         <v/>
       </c>
+      <c r="AY331" t="str">
+        <v/>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -54747,6 +55740,9 @@
       <c r="AX332" t="str">
         <v/>
       </c>
+      <c r="AY332" t="str">
+        <v/>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -54899,6 +55895,9 @@
       <c r="AX333" t="str">
         <v/>
       </c>
+      <c r="AY333" t="str">
+        <v/>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -55051,6 +56050,9 @@
       <c r="AX334" t="str">
         <v/>
       </c>
+      <c r="AY334" t="str">
+        <v/>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -55203,6 +56205,9 @@
       <c r="AX335" t="str">
         <v/>
       </c>
+      <c r="AY335" t="str">
+        <v/>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -55355,6 +56360,9 @@
       <c r="AX336" t="str">
         <v/>
       </c>
+      <c r="AY336" t="str">
+        <v/>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -55507,6 +56515,9 @@
       <c r="AX337" t="str">
         <v/>
       </c>
+      <c r="AY337" t="str">
+        <v/>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -55659,6 +56670,9 @@
       <c r="AX338" t="str">
         <v/>
       </c>
+      <c r="AY338" t="str">
+        <v/>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -55811,6 +56825,9 @@
       <c r="AX339" t="str">
         <v/>
       </c>
+      <c r="AY339" t="str">
+        <v/>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -55963,6 +56980,9 @@
       <c r="AX340" t="str">
         <v/>
       </c>
+      <c r="AY340" t="str">
+        <v/>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -56115,6 +57135,9 @@
       <c r="AX341" t="str">
         <v/>
       </c>
+      <c r="AY341" t="str">
+        <v/>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -56267,6 +57290,9 @@
       <c r="AX342" t="str">
         <v/>
       </c>
+      <c r="AY342" t="str">
+        <v/>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -56419,6 +57445,9 @@
       <c r="AX343" t="str">
         <v/>
       </c>
+      <c r="AY343" t="str">
+        <v/>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -56571,6 +57600,9 @@
       <c r="AX344" t="str">
         <v/>
       </c>
+      <c r="AY344" t="str">
+        <v/>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -56723,6 +57755,9 @@
       <c r="AX345" t="str">
         <v/>
       </c>
+      <c r="AY345" t="str">
+        <v/>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -56875,6 +57910,9 @@
       <c r="AX346" t="str">
         <v/>
       </c>
+      <c r="AY346" t="str">
+        <v/>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -57027,6 +58065,9 @@
       <c r="AX347" t="str">
         <v/>
       </c>
+      <c r="AY347" t="str">
+        <v/>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -57179,6 +58220,9 @@
       <c r="AX348" t="str">
         <v/>
       </c>
+      <c r="AY348" t="str">
+        <v/>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -57331,6 +58375,9 @@
       <c r="AX349" t="str">
         <v/>
       </c>
+      <c r="AY349" t="str">
+        <v/>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -57483,6 +58530,9 @@
       <c r="AX350" t="str">
         <v/>
       </c>
+      <c r="AY350" t="str">
+        <v/>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -57635,6 +58685,9 @@
       <c r="AX351" t="str">
         <v/>
       </c>
+      <c r="AY351" t="str">
+        <v/>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -57787,6 +58840,9 @@
       <c r="AX352" t="str">
         <v/>
       </c>
+      <c r="AY352" t="str">
+        <v/>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
@@ -57939,6 +58995,9 @@
       <c r="AX353" t="str">
         <v/>
       </c>
+      <c r="AY353" t="str">
+        <v/>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -58091,6 +59150,9 @@
       <c r="AX354" t="str">
         <v/>
       </c>
+      <c r="AY354" t="str">
+        <v/>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -58243,6 +59305,9 @@
       <c r="AX355" t="str">
         <v/>
       </c>
+      <c r="AY355" t="str">
+        <v/>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -58395,6 +59460,9 @@
       <c r="AX356" t="str">
         <v/>
       </c>
+      <c r="AY356" t="str">
+        <v/>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
@@ -58547,6 +59615,9 @@
       <c r="AX357" t="str">
         <v/>
       </c>
+      <c r="AY357" t="str">
+        <v/>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
@@ -58699,6 +59770,9 @@
       <c r="AX358" t="str">
         <v/>
       </c>
+      <c r="AY358" t="str">
+        <v/>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -58851,6 +59925,9 @@
       <c r="AX359" t="str">
         <v/>
       </c>
+      <c r="AY359" t="str">
+        <v/>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -59003,6 +60080,9 @@
       <c r="AX360" t="str">
         <v/>
       </c>
+      <c r="AY360" t="str">
+        <v/>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -59155,6 +60235,9 @@
       <c r="AX361" t="str">
         <v/>
       </c>
+      <c r="AY361" t="str">
+        <v/>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
@@ -59307,6 +60390,9 @@
       <c r="AX362" t="str">
         <v/>
       </c>
+      <c r="AY362" t="str">
+        <v/>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
@@ -59459,6 +60545,9 @@
       <c r="AX363" t="str">
         <v/>
       </c>
+      <c r="AY363" t="str">
+        <v/>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
@@ -59611,6 +60700,9 @@
       <c r="AX364" t="str">
         <v/>
       </c>
+      <c r="AY364" t="str">
+        <v/>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
@@ -59763,6 +60855,9 @@
       <c r="AX365" t="str">
         <v/>
       </c>
+      <c r="AY365" t="str">
+        <v/>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
@@ -59915,6 +61010,9 @@
       <c r="AX366" t="str">
         <v/>
       </c>
+      <c r="AY366" t="str">
+        <v/>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
@@ -60067,6 +61165,9 @@
       <c r="AX367" t="str">
         <v/>
       </c>
+      <c r="AY367" t="str">
+        <v/>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
@@ -60219,6 +61320,9 @@
       <c r="AX368" t="str">
         <v/>
       </c>
+      <c r="AY368" t="str">
+        <v/>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
@@ -60371,6 +61475,9 @@
       <c r="AX369" t="str">
         <v/>
       </c>
+      <c r="AY369" t="str">
+        <v/>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
@@ -60523,6 +61630,9 @@
       <c r="AX370" t="str">
         <v/>
       </c>
+      <c r="AY370" t="str">
+        <v/>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
@@ -60675,6 +61785,9 @@
       <c r="AX371" t="str">
         <v/>
       </c>
+      <c r="AY371" t="str">
+        <v/>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
@@ -60827,6 +61940,9 @@
       <c r="AX372" t="str">
         <v/>
       </c>
+      <c r="AY372" t="str">
+        <v/>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
@@ -60979,6 +62095,9 @@
       <c r="AX373" t="str">
         <v/>
       </c>
+      <c r="AY373" t="str">
+        <v/>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
@@ -61131,6 +62250,9 @@
       <c r="AX374" t="str">
         <v/>
       </c>
+      <c r="AY374" t="str">
+        <v/>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
@@ -61283,6 +62405,9 @@
       <c r="AX375" t="str">
         <v/>
       </c>
+      <c r="AY375" t="str">
+        <v/>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
@@ -61435,6 +62560,9 @@
       <c r="AX376" t="str">
         <v/>
       </c>
+      <c r="AY376" t="str">
+        <v/>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
@@ -61587,6 +62715,9 @@
       <c r="AX377" t="str">
         <v/>
       </c>
+      <c r="AY377" t="str">
+        <v/>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
@@ -61739,6 +62870,9 @@
       <c r="AX378" t="str">
         <v/>
       </c>
+      <c r="AY378" t="str">
+        <v/>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
@@ -61891,6 +63025,9 @@
       <c r="AX379" t="str">
         <v/>
       </c>
+      <c r="AY379" t="str">
+        <v/>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
@@ -62043,6 +63180,9 @@
       <c r="AX380" t="str">
         <v/>
       </c>
+      <c r="AY380" t="str">
+        <v/>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
@@ -62195,6 +63335,9 @@
       <c r="AX381" t="str">
         <v/>
       </c>
+      <c r="AY381" t="str">
+        <v/>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
@@ -62347,6 +63490,9 @@
       <c r="AX382" t="str">
         <v/>
       </c>
+      <c r="AY382" t="str">
+        <v/>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
@@ -62499,6 +63645,9 @@
       <c r="AX383" t="str">
         <v/>
       </c>
+      <c r="AY383" t="str">
+        <v/>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
@@ -62651,6 +63800,9 @@
       <c r="AX384" t="str">
         <v/>
       </c>
+      <c r="AY384" t="str">
+        <v/>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
@@ -62803,6 +63955,9 @@
       <c r="AX385" t="str">
         <v/>
       </c>
+      <c r="AY385" t="str">
+        <v/>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
@@ -62955,6 +64110,9 @@
       <c r="AX386" t="str">
         <v/>
       </c>
+      <c r="AY386" t="str">
+        <v/>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
@@ -63107,6 +64265,9 @@
       <c r="AX387" t="str">
         <v/>
       </c>
+      <c r="AY387" t="str">
+        <v/>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
@@ -63259,6 +64420,9 @@
       <c r="AX388" t="str">
         <v/>
       </c>
+      <c r="AY388" t="str">
+        <v/>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
@@ -63411,10 +64575,13 @@
       <c r="AX389" t="str">
         <v/>
       </c>
+      <c r="AY389" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AX389"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AY389"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
@@ -633,10 +633,10 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>2021</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>21 Antares DC</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -689,7 +689,7 @@
         <v>2023</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>23 Antares DC MD Monster Drive</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -1269,10 +1269,10 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>2024</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>24 Metanium DC</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -1481,10 +1481,10 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>2023</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>23 Calcutta Conquest BFS</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -1799,10 +1799,10 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>2022</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>22 Aldebaran BFS</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -7628,10 +7628,10 @@
         <v/>
       </c>
       <c r="AD22" t="str">
-        <v>Hagane aluminum alloy body</v>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE22" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="AF22" t="str">
         <v/>
@@ -7691,7 +7691,7 @@
         <v/>
       </c>
       <c r="AY22" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="23">
@@ -7783,10 +7783,10 @@
         <v/>
       </c>
       <c r="AD23" t="str">
-        <v>Hagane aluminum alloy body</v>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE23" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="AF23" t="str">
         <v/>
@@ -7846,7 +7846,7 @@
         <v/>
       </c>
       <c r="AY23" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="24">
@@ -7938,10 +7938,10 @@
         <v/>
       </c>
       <c r="AD24" t="str">
-        <v>Hagane aluminum alloy body</v>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE24" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="AF24" t="str">
         <v/>
@@ -8001,7 +8001,7 @@
         <v/>
       </c>
       <c r="AY24" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="25">
@@ -8093,10 +8093,10 @@
         <v/>
       </c>
       <c r="AD25" t="str">
-        <v>Hagane aluminum alloy body</v>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE25" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="AF25" t="str">
         <v/>
@@ -8156,7 +8156,7 @@
         <v/>
       </c>
       <c r="AY25" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="26">
@@ -8248,10 +8248,10 @@
         <v/>
       </c>
       <c r="AD26" t="str">
-        <v>Hagane aluminum alloy body</v>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE26" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="AF26" t="str">
         <v/>
@@ -8311,7 +8311,7 @@
         <v/>
       </c>
       <c r="AY26" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="27">
@@ -8403,10 +8403,10 @@
         <v/>
       </c>
       <c r="AD27" t="str">
-        <v>Hagane aluminum alloy body</v>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE27" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="AF27" t="str">
         <v/>
@@ -8466,7 +8466,7 @@
         <v/>
       </c>
       <c r="AY27" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="28">
@@ -8558,10 +8558,10 @@
         <v/>
       </c>
       <c r="AD28" t="str">
-        <v>metal frames</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE28" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="AF28" t="str">
         <v/>
@@ -8621,7 +8621,7 @@
         <v/>
       </c>
       <c r="AY28" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="29">
@@ -8713,10 +8713,10 @@
         <v/>
       </c>
       <c r="AD29" t="str">
-        <v>metal frames</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE29" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="AF29" t="str">
         <v/>
@@ -8776,7 +8776,7 @@
         <v/>
       </c>
       <c r="AY29" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="30">
@@ -8868,10 +8868,10 @@
         <v/>
       </c>
       <c r="AD30" t="str">
-        <v>metal frames</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE30" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="AF30" t="str">
         <v/>
@@ -8931,7 +8931,7 @@
         <v/>
       </c>
       <c r="AY30" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="31">
@@ -9023,10 +9023,10 @@
         <v/>
       </c>
       <c r="AD31" t="str">
-        <v>metal frames</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE31" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="AF31" t="str">
         <v/>
@@ -9086,7 +9086,7 @@
         <v/>
       </c>
       <c r="AY31" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="32">
@@ -20493,7 +20493,7 @@
         <v/>
       </c>
       <c r="AD105" t="str">
-        <v>Core solid metal body</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE105" t="str">
         <v>Duralumin drive gear</v>
@@ -20556,7 +20556,7 @@
         <v/>
       </c>
       <c r="AY105" t="str">
-        <v/>
+        <v>CORESOLID BODY / 一体成型</v>
       </c>
     </row>
     <row r="106">
@@ -20648,7 +20648,7 @@
         <v/>
       </c>
       <c r="AD106" t="str">
-        <v>Core solid metal body</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE106" t="str">
         <v>Duralumin drive gear</v>
@@ -20711,7 +20711,7 @@
         <v/>
       </c>
       <c r="AY106" t="str">
-        <v/>
+        <v>CORESOLID BODY / 一体成型</v>
       </c>
     </row>
     <row r="107">
@@ -20803,7 +20803,7 @@
         <v/>
       </c>
       <c r="AD107" t="str">
-        <v>Core solid metal body</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE107" t="str">
         <v>Duralumin drive gear</v>
@@ -20866,7 +20866,7 @@
         <v/>
       </c>
       <c r="AY107" t="str">
-        <v/>
+        <v>CORESOLID BODY / 一体成型</v>
       </c>
     </row>
     <row r="108">
@@ -20958,7 +20958,7 @@
         <v/>
       </c>
       <c r="AD108" t="str">
-        <v>Core solid metal body</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE108" t="str">
         <v>Duralumin drive gear</v>
@@ -21021,7 +21021,7 @@
         <v/>
       </c>
       <c r="AY108" t="str">
-        <v/>
+        <v>CORESOLID BODY / 一体成型</v>
       </c>
     </row>
     <row r="109">
@@ -21113,7 +21113,7 @@
         <v/>
       </c>
       <c r="AD109" t="str">
-        <v>Core solid metal body</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE109" t="str">
         <v>Duralumin drive gear</v>
@@ -21176,7 +21176,7 @@
         <v/>
       </c>
       <c r="AY109" t="str">
-        <v/>
+        <v>CORESOLID BODY / 一体成型</v>
       </c>
     </row>
     <row r="110">
@@ -21268,7 +21268,7 @@
         <v/>
       </c>
       <c r="AD110" t="str">
-        <v>Core solid metal body</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE110" t="str">
         <v>Duralumin drive gear</v>
@@ -21331,7 +21331,7 @@
         <v/>
       </c>
       <c r="AY110" t="str">
-        <v/>
+        <v>CORESOLID BODY / 一体成型</v>
       </c>
     </row>
     <row r="111">
@@ -24833,7 +24833,7 @@
         <v/>
       </c>
       <c r="AD133" t="str">
-        <v>Fully machined aluminum body and side plates</v>
+        <v>Aluminum</v>
       </c>
       <c r="AE133" t="str">
         <v/>
@@ -24896,7 +24896,7 @@
         <v/>
       </c>
       <c r="AY133" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
     </row>
     <row r="134">
@@ -24988,7 +24988,7 @@
         <v/>
       </c>
       <c r="AD134" t="str">
-        <v>Fully machined aluminum body and side plates</v>
+        <v>Aluminum</v>
       </c>
       <c r="AE134" t="str">
         <v/>
@@ -25051,7 +25051,7 @@
         <v/>
       </c>
       <c r="AY134" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
     </row>
     <row r="135">
@@ -25143,7 +25143,7 @@
         <v/>
       </c>
       <c r="AD135" t="str">
-        <v>Fully machined aluminum body and side plates</v>
+        <v>Aluminum</v>
       </c>
       <c r="AE135" t="str">
         <v/>
@@ -25206,7 +25206,7 @@
         <v/>
       </c>
       <c r="AY135" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
     </row>
     <row r="136">
@@ -25298,7 +25298,7 @@
         <v/>
       </c>
       <c r="AD136" t="str">
-        <v>Fully machined aluminum body and side plates</v>
+        <v>Aluminum</v>
       </c>
       <c r="AE136" t="str">
         <v/>
@@ -25361,7 +25361,7 @@
         <v/>
       </c>
       <c r="AY136" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
     </row>
     <row r="137">
@@ -28553,10 +28553,10 @@
         <v/>
       </c>
       <c r="AD157" t="str">
-        <v>Hagane body system</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE157" t="str">
-        <v/>
+        <v>Aluminum main gear</v>
       </c>
       <c r="AF157" t="str">
         <v/>
@@ -28616,7 +28616,7 @@
         <v/>
       </c>
       <c r="AY157" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="158">
@@ -28708,10 +28708,10 @@
         <v/>
       </c>
       <c r="AD158" t="str">
-        <v>Hagane body system</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE158" t="str">
-        <v/>
+        <v>Aluminum main gear</v>
       </c>
       <c r="AF158" t="str">
         <v/>
@@ -28771,7 +28771,7 @@
         <v/>
       </c>
       <c r="AY158" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="159">
@@ -28863,10 +28863,10 @@
         <v/>
       </c>
       <c r="AD159" t="str">
-        <v>Hagane body system</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE159" t="str">
-        <v/>
+        <v>Aluminum main gear</v>
       </c>
       <c r="AF159" t="str">
         <v/>
@@ -28926,7 +28926,7 @@
         <v/>
       </c>
       <c r="AY159" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="160">
@@ -29018,10 +29018,10 @@
         <v/>
       </c>
       <c r="AD160" t="str">
-        <v>Hagane body system</v>
+        <v>Magnesium</v>
       </c>
       <c r="AE160" t="str">
-        <v/>
+        <v>Aluminum main gear</v>
       </c>
       <c r="AF160" t="str">
         <v/>
@@ -29081,7 +29081,7 @@
         <v/>
       </c>
       <c r="AY160" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
     </row>
     <row r="161">

--- a/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
@@ -492,7 +492,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J2" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TIAGRA_main.jpeg</v>
@@ -554,7 +554,7 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J3" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TALICA_main.jpeg</v>
@@ -619,7 +619,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J4" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/EXSENCE%20DC%20SS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20Exsence%20DC_main.jpg</v>
       </c>
       <c r="K4" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -681,7 +681,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J5" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/21%20Antares%20DC_main.jpg</v>
       </c>
       <c r="K5" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -740,7 +740,7 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J6" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA JIGGER 4000_4000HG_main.jpeg</v>
@@ -802,10 +802,10 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J7" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA CONQUEST DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/19%20CALCUTTA%20CONQUEST%20DC_main.jpg</v>
       </c>
       <c r="K7" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -864,7 +864,7 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J8" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA JIGGER LD_main.jpeg</v>
@@ -926,7 +926,7 @@
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J9" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA JIGGER F CUSTOM_main.jpeg</v>
@@ -988,7 +988,7 @@
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J10" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA CONQUEST CT_main.jpeg</v>
@@ -1050,7 +1050,7 @@
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J11" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/KAIKON_main.jpeg</v>
@@ -1115,7 +1115,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J12" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ANTARES_main.jpg</v>
       </c>
       <c r="K12" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J13" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA JIGGER_main.jpeg</v>
@@ -1236,10 +1236,10 @@
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J14" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA CONQUEST MD_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20MD_main.jpg</v>
       </c>
       <c r="K14" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1298,10 +1298,10 @@
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J15" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA CONQUEST BFS LIMITED_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/26%20CALCUTTA%20CONQUEST%20BFS%20LIMITED_main.jpg</v>
       </c>
       <c r="K15" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1363,7 +1363,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J16" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/24%20Metanium%20DC_main.jpg</v>
       </c>
       <c r="K16" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1422,10 +1422,10 @@
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J17" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA CONQUEST_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/21%20CALCUTTA%20CONQUEST_main.jpg</v>
       </c>
       <c r="K17" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1484,10 +1484,10 @@
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J18" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA CONQUEST_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA%20CONQUEST_main.jpg</v>
       </c>
       <c r="K18" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1546,10 +1546,10 @@
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J19" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA CONQUEST SHALLOW EDITION_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA%20CONQUEST%20SHALLOW%20EDITION_main.jpg</v>
       </c>
       <c r="K19" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1608,10 +1608,10 @@
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J20" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CALCUTTA CONQUEST BFS_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/23%20Calcutta%20Conquest%20BFS_main.jpg</v>
       </c>
       <c r="K20" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1670,10 +1670,10 @@
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J21" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/OCEA CONQUEST FT_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/26%20OCEA%20CONQUEST%20FT_main.jpg</v>
       </c>
       <c r="K21" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1735,7 +1735,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J22" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/25%20ALDEBARAN%20DC_main.jpg</v>
       </c>
       <c r="K22" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -1856,7 +1856,7 @@
         <v/>
       </c>
       <c r="I24" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J24" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA PREMIUM_main.jpeg</v>
@@ -1918,7 +1918,7 @@
         <v/>
       </c>
       <c r="I25" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J25" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER PREMIUM_main.jpeg</v>
@@ -1983,7 +1983,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J26" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/ALDEBARAN%20BFS_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20Aldebaran%20BFS_main.jpg</v>
       </c>
       <c r="K26" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2107,7 +2107,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J28" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium SHALLOW EDITION_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20Metanium%20SHALLOW%20EDITION_main.jpeg</v>
       </c>
       <c r="K28" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2169,7 +2169,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J29" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Metanium_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/20%20Metanium_main.jpg</v>
       </c>
       <c r="K29" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2228,7 +2228,7 @@
         <v/>
       </c>
       <c r="I30" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J30" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SPEEDMASTER 石鲷_main.jpeg</v>
@@ -2290,7 +2290,7 @@
         <v/>
       </c>
       <c r="I31" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J31" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TYRNOS_main.jpeg</v>
@@ -2479,7 +2479,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J34" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Bantam_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20Bantam_main.jpg</v>
       </c>
       <c r="K34" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2600,7 +2600,7 @@
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J36" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BAYGAME_main.jpeg</v>
@@ -2662,10 +2662,10 @@
         <v/>
       </c>
       <c r="I37" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J37" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER_main.jpg</v>
       </c>
       <c r="K37" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2724,7 +2724,7 @@
         <v/>
       </c>
       <c r="I38" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J38" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA F CUSTOM_main.jpeg</v>
@@ -2786,10 +2786,10 @@
         <v/>
       </c>
       <c r="I39" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J39" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER%EF%BC%88300%E7%BA%BF%E6%9D%AF%EF%BC%89_main.jpg</v>
       </c>
       <c r="K39" t="str">
         <v>2026-04-16 22:59:05</v>
@@ -2851,7 +2851,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J40" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion DC MD_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion%20DC%20MD_main.jpg</v>
       </c>
       <c r="K40" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -2910,7 +2910,7 @@
         <v/>
       </c>
       <c r="I41" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J41" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/SLX DC XT_main.jpeg</v>
@@ -2975,7 +2975,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J42" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/21%20Scorpion%20DC_main.jpg</v>
       </c>
       <c r="K42" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3025,10 +3025,10 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>2025</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>25 Scorpion MD 300</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -3037,7 +3037,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J43" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion MD 300_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/25%20Scorpion%20MD%20300_main.jpg</v>
       </c>
       <c r="K43" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3096,10 +3096,10 @@
         <v/>
       </c>
       <c r="I44" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J44" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER%EF%BC%88150%E7%BA%BF%E6%9D%AF%EF%BC%89_main.jpg</v>
       </c>
       <c r="K44" t="str">
         <v>2026-04-16 22:59:19</v>
@@ -3158,7 +3158,7 @@
         <v/>
       </c>
       <c r="I45" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J45" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER CT_main.jpeg</v>
@@ -3211,10 +3211,10 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v/>
+        <v>2022</v>
       </c>
       <c r="G46" t="str">
-        <v/>
+        <v>22 CURADO DC 200</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -3223,7 +3223,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J46" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20CURADO%20DC%20200_main.jpg</v>
       </c>
       <c r="K46" t="str">
         <v>2026-04-16 22:59:23</v>
@@ -3282,7 +3282,7 @@
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J47" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CHINUMATIC_main.jpeg</v>
@@ -3347,7 +3347,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J48" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO DC_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CURADO%20DC%EF%BC%88150%E7%BA%BF%E6%9D%AF%EF%BC%89_main.jpg</v>
       </c>
       <c r="K48" t="str">
         <v>2026-04-16 22:59:32</v>
@@ -3406,7 +3406,7 @@
         <v/>
       </c>
       <c r="I49" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J49" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Stephano SS_main.jpeg</v>
@@ -3533,7 +3533,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J51" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/Scorpion MD 200_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/24%20Scorpion%20MD%20200_main.jpg</v>
       </c>
       <c r="K51" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -3592,7 +3592,7 @@
         <v/>
       </c>
       <c r="I52" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J52" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TORIUM_main.jpeg</v>
@@ -3778,7 +3778,7 @@
         <v/>
       </c>
       <c r="I55" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J55" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA_main.jpeg</v>
@@ -3840,7 +3840,7 @@
         <v/>
       </c>
       <c r="I56" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J56" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA SC_main.jpeg</v>
@@ -3967,7 +3967,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J58" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22 CURADO 200_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20CURADO%20200_main.jpg</v>
       </c>
       <c r="K58" t="str">
         <v>2026-04-16 23:00:03</v>
@@ -4091,7 +4091,7 @@
         <v>baitcasting</v>
       </c>
       <c r="J60" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20CURADO%20300_main.jpeg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/22%20CURADO%20300_main.jpg</v>
       </c>
       <c r="K60" t="str">
         <v>2026-04-10 00:51:20</v>
@@ -4398,7 +4398,7 @@
         <v/>
       </c>
       <c r="I65" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J65" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/BARCHETTA BB_main.jpeg</v>
@@ -4522,7 +4522,7 @@
         <v/>
       </c>
       <c r="I67" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J67" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/GRAPPLER BB_main.jpeg</v>
@@ -4646,7 +4646,7 @@
         <v/>
       </c>
       <c r="I69" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J69" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/小船_main.jpeg</v>
@@ -4708,7 +4708,7 @@
         <v/>
       </c>
       <c r="I70" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J70" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CARDIFF_main.jpeg</v>
@@ -4770,7 +4770,7 @@
         <v/>
       </c>
       <c r="I71" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J71" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/幻风 XT_main.jpeg</v>
@@ -4832,7 +4832,7 @@
         <v/>
       </c>
       <c r="I72" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J72" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/TITANOS FUNE GT_main.jpeg</v>
@@ -5080,7 +5080,7 @@
         <v/>
       </c>
       <c r="I76" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J76" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/幻风_main.jpeg</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="I77" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="J77" t="str">
         <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_reels/CHINU SPECIAL_main.jpeg</v>
@@ -5517,7 +5517,7 @@
         <v/>
       </c>
       <c r="AV2" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW2" t="str">
         <v/>
@@ -5532,10 +5532,10 @@
         <v/>
       </c>
       <c r="BA2" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=017383</v>
       </c>
       <c r="BB2" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_03_tiagra.pdf</v>
       </c>
       <c r="BC2" t="str">
         <v/>
@@ -5702,7 +5702,7 @@
         <v/>
       </c>
       <c r="AV3" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW3" t="str">
         <v/>
@@ -5717,10 +5717,10 @@
         <v/>
       </c>
       <c r="BA3" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=020307</v>
       </c>
       <c r="BB3" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_05_tiagra.pdf</v>
       </c>
       <c r="BC3" t="str">
         <v/>
@@ -5887,7 +5887,7 @@
         <v/>
       </c>
       <c r="AV4" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW4" t="str">
         <v/>
@@ -5902,10 +5902,10 @@
         <v/>
       </c>
       <c r="BA4" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=020314</v>
       </c>
       <c r="BB4" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_05_tiagra.pdf</v>
       </c>
       <c r="BC4" t="str">
         <v/>
@@ -6072,7 +6072,7 @@
         <v/>
       </c>
       <c r="AV5" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW5" t="str">
         <v/>
@@ -6087,10 +6087,10 @@
         <v/>
       </c>
       <c r="BA5" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=020321</v>
       </c>
       <c r="BB5" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_05_tiagra.pdf</v>
       </c>
       <c r="BC5" t="str">
         <v/>
@@ -6257,7 +6257,7 @@
         <v/>
       </c>
       <c r="AV6" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW6" t="str">
         <v/>
@@ -6272,10 +6272,10 @@
         <v/>
       </c>
       <c r="BA6" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=020338</v>
       </c>
       <c r="BB6" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_05_tiagra.pdf</v>
       </c>
       <c r="BC6" t="str">
         <v/>
@@ -6442,7 +6442,7 @@
         <v/>
       </c>
       <c r="AV7" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW7" t="str">
         <v/>
@@ -6457,10 +6457,10 @@
         <v/>
       </c>
       <c r="BA7" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=020345</v>
       </c>
       <c r="BB7" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_05_tiagra.pdf</v>
       </c>
       <c r="BC7" t="str">
         <v/>
@@ -6627,7 +6627,7 @@
         <v/>
       </c>
       <c r="AV8" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW8" t="str">
         <v/>
@@ -6642,10 +6642,10 @@
         <v/>
       </c>
       <c r="BA8" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=020352</v>
       </c>
       <c r="BB8" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_05_tiagra.pdf</v>
       </c>
       <c r="BC8" t="str">
         <v/>
@@ -6812,7 +6812,7 @@
         <v/>
       </c>
       <c r="AV9" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW9" t="str">
         <v/>
@@ -6827,10 +6827,10 @@
         <v/>
       </c>
       <c r="BA9" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=020369</v>
       </c>
       <c r="BB9" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_05_tiagra.pdf</v>
       </c>
       <c r="BC9" t="str">
         <v/>
@@ -6997,7 +6997,7 @@
         <v/>
       </c>
       <c r="AV10" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW10" t="str">
         <v/>
@@ -7012,10 +7012,10 @@
         <v/>
       </c>
       <c r="BA10" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=020376</v>
       </c>
       <c r="BB10" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_05_tiagra.pdf</v>
       </c>
       <c r="BC10" t="str">
         <v/>
@@ -7182,7 +7182,7 @@
         <v/>
       </c>
       <c r="AV11" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW11" t="str">
         <v/>
@@ -7197,10 +7197,10 @@
         <v/>
       </c>
       <c r="BA11" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=032218</v>
       </c>
       <c r="BB11" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_13_talica.pdf</v>
       </c>
       <c r="BC11" t="str">
         <v/>
@@ -7367,7 +7367,7 @@
         <v/>
       </c>
       <c r="AV12" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW12" t="str">
         <v/>
@@ -7382,10 +7382,10 @@
         <v/>
       </c>
       <c r="BA12" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=032225</v>
       </c>
       <c r="BB12" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_13_talica.pdf</v>
       </c>
       <c r="BC12" t="str">
         <v/>
@@ -7552,7 +7552,7 @@
         <v/>
       </c>
       <c r="AV13" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW13" t="str">
         <v/>
@@ -7567,10 +7567,10 @@
         <v/>
       </c>
       <c r="BA13" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=032881</v>
       </c>
       <c r="BB13" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_13_talica.pdf</v>
       </c>
       <c r="BC13" t="str">
         <v/>
@@ -7737,7 +7737,7 @@
         <v/>
       </c>
       <c r="AV14" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW14" t="str">
         <v/>
@@ -7922,7 +7922,7 @@
         <v/>
       </c>
       <c r="AV15" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW15" t="str">
         <v/>
@@ -8107,7 +8107,7 @@
         <v/>
       </c>
       <c r="AV16" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW16" t="str">
         <v/>
@@ -8292,7 +8292,7 @@
         <v/>
       </c>
       <c r="AV17" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW17" t="str">
         <v/>
@@ -8477,7 +8477,7 @@
         <v/>
       </c>
       <c r="AV18" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW18" t="str">
         <v/>
@@ -8662,7 +8662,7 @@
         <v/>
       </c>
       <c r="AV19" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW19" t="str">
         <v/>
@@ -9232,10 +9232,10 @@
         <v/>
       </c>
       <c r="BA22" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042606</v>
       </c>
       <c r="BB22" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_antares_dc.pdf</v>
       </c>
       <c r="BC22" t="str">
         <v/>
@@ -9417,10 +9417,10 @@
         <v/>
       </c>
       <c r="BA23" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042613</v>
       </c>
       <c r="BB23" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_antares_dc.pdf</v>
       </c>
       <c r="BC23" t="str">
         <v/>
@@ -9602,10 +9602,10 @@
         <v/>
       </c>
       <c r="BA24" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042620</v>
       </c>
       <c r="BB24" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_antares_dc.pdf</v>
       </c>
       <c r="BC24" t="str">
         <v/>
@@ -9787,10 +9787,10 @@
         <v/>
       </c>
       <c r="BA25" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042637</v>
       </c>
       <c r="BB25" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_antares_dc.pdf</v>
       </c>
       <c r="BC25" t="str">
         <v/>
@@ -9972,10 +9972,10 @@
         <v/>
       </c>
       <c r="BA26" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042644</v>
       </c>
       <c r="BB26" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_antares_dc.pdf</v>
       </c>
       <c r="BC26" t="str">
         <v/>
@@ -10157,10 +10157,10 @@
         <v/>
       </c>
       <c r="BA27" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042651</v>
       </c>
       <c r="BB27" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_antares_dc.pdf</v>
       </c>
       <c r="BC27" t="str">
         <v/>
@@ -10327,7 +10327,7 @@
         <v/>
       </c>
       <c r="AV28" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW28" t="str">
         <v/>
@@ -10342,10 +10342,10 @@
         <v/>
       </c>
       <c r="BA28" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040664</v>
       </c>
       <c r="BB28" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20OCEA%20JIGEER_.pdf</v>
       </c>
       <c r="BC28" t="str">
         <v/>
@@ -10512,7 +10512,7 @@
         <v/>
       </c>
       <c r="AV29" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW29" t="str">
         <v/>
@@ -10527,10 +10527,10 @@
         <v/>
       </c>
       <c r="BA29" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040671</v>
       </c>
       <c r="BB29" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20OCEA%20JIGEER_.pdf</v>
       </c>
       <c r="BC29" t="str">
         <v/>
@@ -10643,7 +10643,7 @@
         <v/>
       </c>
       <c r="AD30" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE30" t="str">
         <v/>
@@ -10697,7 +10697,7 @@
         <v/>
       </c>
       <c r="AV30" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW30" t="str">
         <v/>
@@ -10706,16 +10706,16 @@
         <v/>
       </c>
       <c r="AY30" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ30" t="str">
         <v/>
       </c>
       <c r="BA30" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=039781</v>
       </c>
       <c r="BB30" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19CALCUTTA_CQE_DC.pdf</v>
       </c>
       <c r="BC30" t="str">
         <v/>
@@ -10828,7 +10828,7 @@
         <v/>
       </c>
       <c r="AD31" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE31" t="str">
         <v/>
@@ -10882,7 +10882,7 @@
         <v/>
       </c>
       <c r="AV31" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW31" t="str">
         <v/>
@@ -10891,16 +10891,16 @@
         <v/>
       </c>
       <c r="AY31" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ31" t="str">
         <v/>
       </c>
       <c r="BA31" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=039798</v>
       </c>
       <c r="BB31" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19CALCUTTA_CQE_DC.pdf</v>
       </c>
       <c r="BC31" t="str">
         <v/>
@@ -11013,7 +11013,7 @@
         <v/>
       </c>
       <c r="AD32" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE32" t="str">
         <v/>
@@ -11067,7 +11067,7 @@
         <v/>
       </c>
       <c r="AV32" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW32" t="str">
         <v/>
@@ -11076,16 +11076,16 @@
         <v/>
       </c>
       <c r="AY32" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ32" t="str">
         <v/>
       </c>
       <c r="BA32" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040831</v>
       </c>
       <c r="BB32" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19CALCUTTA_CQE_DC.pdf</v>
       </c>
       <c r="BC32" t="str">
         <v/>
@@ -11198,7 +11198,7 @@
         <v/>
       </c>
       <c r="AD33" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE33" t="str">
         <v/>
@@ -11252,7 +11252,7 @@
         <v/>
       </c>
       <c r="AV33" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW33" t="str">
         <v/>
@@ -11261,16 +11261,16 @@
         <v/>
       </c>
       <c r="AY33" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ33" t="str">
         <v/>
       </c>
       <c r="BA33" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040848</v>
       </c>
       <c r="BB33" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20_calcutta_cqe_dc.pdf</v>
       </c>
       <c r="BC33" t="str">
         <v/>
@@ -11383,7 +11383,7 @@
         <v/>
       </c>
       <c r="AD34" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE34" t="str">
         <v/>
@@ -11437,7 +11437,7 @@
         <v/>
       </c>
       <c r="AV34" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW34" t="str">
         <v/>
@@ -11446,16 +11446,16 @@
         <v/>
       </c>
       <c r="AY34" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ34" t="str">
         <v/>
       </c>
       <c r="BA34" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040855</v>
       </c>
       <c r="BB34" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19CALCUTTA_CQE_DC.pdf</v>
       </c>
       <c r="BC34" t="str">
         <v/>
@@ -11568,7 +11568,7 @@
         <v/>
       </c>
       <c r="AD35" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE35" t="str">
         <v/>
@@ -11622,7 +11622,7 @@
         <v/>
       </c>
       <c r="AV35" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW35" t="str">
         <v/>
@@ -11631,16 +11631,16 @@
         <v/>
       </c>
       <c r="AY35" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ35" t="str">
         <v/>
       </c>
       <c r="BA35" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040862</v>
       </c>
       <c r="BB35" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20_calcutta_cqe_dc.pdf</v>
       </c>
       <c r="BC35" t="str">
         <v/>
@@ -11753,7 +11753,7 @@
         <v/>
       </c>
       <c r="AD36" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE36" t="str">
         <v/>
@@ -11807,7 +11807,7 @@
         <v/>
       </c>
       <c r="AV36" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW36" t="str">
         <v/>
@@ -11816,16 +11816,16 @@
         <v/>
       </c>
       <c r="AY36" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ36" t="str">
         <v/>
       </c>
       <c r="BA36" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040398</v>
       </c>
       <c r="BB36" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19CALCUTTA_CQE_DC.pdf</v>
       </c>
       <c r="BC36" t="str">
         <v/>
@@ -11938,7 +11938,7 @@
         <v/>
       </c>
       <c r="AD37" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE37" t="str">
         <v/>
@@ -11992,7 +11992,7 @@
         <v/>
       </c>
       <c r="AV37" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW37" t="str">
         <v/>
@@ -12001,16 +12001,16 @@
         <v/>
       </c>
       <c r="AY37" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ37" t="str">
         <v/>
       </c>
       <c r="BA37" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040404</v>
       </c>
       <c r="BB37" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19CALCUTTA_CQE_DC.pdf</v>
       </c>
       <c r="BC37" t="str">
         <v/>
@@ -12123,7 +12123,7 @@
         <v/>
       </c>
       <c r="AD38" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE38" t="str">
         <v/>
@@ -12177,7 +12177,7 @@
         <v/>
       </c>
       <c r="AV38" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW38" t="str">
         <v/>
@@ -12186,16 +12186,16 @@
         <v/>
       </c>
       <c r="AY38" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ38" t="str">
         <v/>
       </c>
       <c r="BA38" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048677</v>
       </c>
       <c r="BB38" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19CALCUTTA_CQE_DC.pdf</v>
       </c>
       <c r="BC38" t="str">
         <v/>
@@ -12308,7 +12308,7 @@
         <v/>
       </c>
       <c r="AD39" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE39" t="str">
         <v/>
@@ -12362,7 +12362,7 @@
         <v/>
       </c>
       <c r="AV39" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW39" t="str">
         <v/>
@@ -12371,16 +12371,16 @@
         <v/>
       </c>
       <c r="AY39" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ39" t="str">
         <v/>
       </c>
       <c r="BA39" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048684</v>
       </c>
       <c r="BB39" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20_calcutta_cqe_dc.pdf</v>
       </c>
       <c r="BC39" t="str">
         <v/>
@@ -12493,7 +12493,7 @@
         <v/>
       </c>
       <c r="AD40" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE40" t="str">
         <v/>
@@ -12547,7 +12547,7 @@
         <v/>
       </c>
       <c r="AV40" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW40" t="str">
         <v/>
@@ -12556,16 +12556,16 @@
         <v/>
       </c>
       <c r="AY40" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ40" t="str">
         <v/>
       </c>
       <c r="BA40" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048714</v>
       </c>
       <c r="BB40" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19CALCUTTA_CQE_DC.pdf</v>
       </c>
       <c r="BC40" t="str">
         <v/>
@@ -12678,7 +12678,7 @@
         <v/>
       </c>
       <c r="AD41" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE41" t="str">
         <v/>
@@ -12732,7 +12732,7 @@
         <v/>
       </c>
       <c r="AV41" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW41" t="str">
         <v/>
@@ -12741,16 +12741,16 @@
         <v/>
       </c>
       <c r="AY41" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ41" t="str">
         <v/>
       </c>
       <c r="BA41" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048752</v>
       </c>
       <c r="BB41" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19CALCUTTA_CQE_DC.pdf</v>
       </c>
       <c r="BC41" t="str">
         <v/>
@@ -12917,7 +12917,7 @@
         <v/>
       </c>
       <c r="AV42" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW42" t="str">
         <v/>
@@ -12932,10 +12932,10 @@
         <v/>
       </c>
       <c r="BA42" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046581</v>
       </c>
       <c r="BB42" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24oceajigger_ld_2500_q2.pdf</v>
       </c>
       <c r="BC42" t="str">
         <v/>
@@ -13102,7 +13102,7 @@
         <v/>
       </c>
       <c r="AV43" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW43" t="str">
         <v/>
@@ -13117,10 +13117,10 @@
         <v/>
       </c>
       <c r="BA43" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046598</v>
       </c>
       <c r="BB43" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24oceajigger_ld_2500_q2.pdf</v>
       </c>
       <c r="BC43" t="str">
         <v/>
@@ -13287,7 +13287,7 @@
         <v/>
       </c>
       <c r="AV44" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW44" t="str">
         <v/>
@@ -13302,10 +13302,10 @@
         <v/>
       </c>
       <c r="BA44" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048653</v>
       </c>
       <c r="BB44" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_26ocea_jigger_ld_2501_q.pdf</v>
       </c>
       <c r="BC44" t="str">
         <v/>
@@ -13472,7 +13472,7 @@
         <v/>
       </c>
       <c r="AV45" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW45" t="str">
         <v/>
@@ -13487,10 +13487,10 @@
         <v/>
       </c>
       <c r="BA45" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048660</v>
       </c>
       <c r="BB45" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_26ocea_jigger_ld_2501_q.pdf</v>
       </c>
       <c r="BC45" t="str">
         <v/>
@@ -13657,7 +13657,7 @@
         <v/>
       </c>
       <c r="AV46" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW46" t="str">
         <v/>
@@ -13672,10 +13672,10 @@
         <v/>
       </c>
       <c r="BA46" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040008</v>
       </c>
       <c r="BB46" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19OCEA%20JIGGER_FC_.pdf</v>
       </c>
       <c r="BC46" t="str">
         <v/>
@@ -13842,7 +13842,7 @@
         <v/>
       </c>
       <c r="AV47" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW47" t="str">
         <v/>
@@ -13857,10 +13857,10 @@
         <v/>
       </c>
       <c r="BA47" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040015</v>
       </c>
       <c r="BB47" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19OCEA%20JIGGER_FC_.pdf</v>
       </c>
       <c r="BC47" t="str">
         <v/>
@@ -14027,7 +14027,7 @@
         <v/>
       </c>
       <c r="AV48" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW48" t="str">
         <v/>
@@ -14042,10 +14042,10 @@
         <v/>
       </c>
       <c r="BA48" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040022</v>
       </c>
       <c r="BB48" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19OCEA%20JIGGER_FC_.pdf</v>
       </c>
       <c r="BC48" t="str">
         <v/>
@@ -14212,7 +14212,7 @@
         <v/>
       </c>
       <c r="AV49" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW49" t="str">
         <v/>
@@ -14227,10 +14227,10 @@
         <v/>
       </c>
       <c r="BA49" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040039</v>
       </c>
       <c r="BB49" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19OCEA%20JIGGER_FC_.pdf</v>
       </c>
       <c r="BC49" t="str">
         <v/>
@@ -14397,7 +14397,7 @@
         <v/>
       </c>
       <c r="AV50" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW50" t="str">
         <v/>
@@ -14412,10 +14412,10 @@
         <v/>
       </c>
       <c r="BA50" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040046</v>
       </c>
       <c r="BB50" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19OCEA%20JIGGER_FC_.pdf</v>
       </c>
       <c r="BC50" t="str">
         <v/>
@@ -14582,7 +14582,7 @@
         <v/>
       </c>
       <c r="AV51" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW51" t="str">
         <v/>
@@ -14597,10 +14597,10 @@
         <v/>
       </c>
       <c r="BA51" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040053</v>
       </c>
       <c r="BB51" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19OCEA%20JIGGER_FC_.pdf</v>
       </c>
       <c r="BC51" t="str">
         <v/>
@@ -14767,7 +14767,7 @@
         <v/>
       </c>
       <c r="AV52" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW52" t="str">
         <v/>
@@ -14782,10 +14782,10 @@
         <v/>
       </c>
       <c r="BA52" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=040060</v>
       </c>
       <c r="BB52" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_19OCEA%20JIGGER_FC_.pdf</v>
       </c>
       <c r="BC52" t="str">
         <v/>
@@ -14952,7 +14952,7 @@
         <v/>
       </c>
       <c r="AV53" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW53" t="str">
         <v/>
@@ -14967,10 +14967,10 @@
         <v/>
       </c>
       <c r="BA53" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=049223</v>
       </c>
       <c r="BB53" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24_26ocea_conquest_ct_300_q2.pdf</v>
       </c>
       <c r="BC53" t="str">
         <v/>
@@ -15137,7 +15137,7 @@
         <v/>
       </c>
       <c r="AV54" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW54" t="str">
         <v/>
@@ -15152,10 +15152,10 @@
         <v/>
       </c>
       <c r="BA54" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=049230</v>
       </c>
       <c r="BB54" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24_26ocea_conquest_ct_300_q2.pdf</v>
       </c>
       <c r="BC54" t="str">
         <v/>
@@ -15322,7 +15322,7 @@
         <v/>
       </c>
       <c r="AV55" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW55" t="str">
         <v/>
@@ -15337,10 +15337,10 @@
         <v/>
       </c>
       <c r="BA55" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046680</v>
       </c>
       <c r="BB55" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24_26ocea_conquest_ct_300_q2.pdf</v>
       </c>
       <c r="BC55" t="str">
         <v/>
@@ -15507,7 +15507,7 @@
         <v/>
       </c>
       <c r="AV56" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW56" t="str">
         <v/>
@@ -15522,10 +15522,10 @@
         <v/>
       </c>
       <c r="BA56" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046697</v>
       </c>
       <c r="BB56" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24_26ocea_conquest_ct_300_q2.pdf</v>
       </c>
       <c r="BC56" t="str">
         <v/>
@@ -15692,7 +15692,7 @@
         <v/>
       </c>
       <c r="AV57" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW57" t="str">
         <v/>
@@ -15707,10 +15707,10 @@
         <v/>
       </c>
       <c r="BA57" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046703</v>
       </c>
       <c r="BB57" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24_26ocea_conquest_ct_300_q2.pdf</v>
       </c>
       <c r="BC57" t="str">
         <v/>
@@ -15877,7 +15877,7 @@
         <v/>
       </c>
       <c r="AV58" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW58" t="str">
         <v/>
@@ -15892,10 +15892,10 @@
         <v/>
       </c>
       <c r="BA58" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046710</v>
       </c>
       <c r="BB58" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24_26ocea_conquest_ct_300_q2.pdf</v>
       </c>
       <c r="BC58" t="str">
         <v/>
@@ -16062,7 +16062,7 @@
         <v/>
       </c>
       <c r="AV59" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW59" t="str">
         <v/>
@@ -16077,10 +16077,10 @@
         <v/>
       </c>
       <c r="BA59" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046727</v>
       </c>
       <c r="BB59" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24_26ocea_conquest_ct_300_q2.pdf</v>
       </c>
       <c r="BC59" t="str">
         <v/>
@@ -16247,7 +16247,7 @@
         <v/>
       </c>
       <c r="AV60" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW60" t="str">
         <v/>
@@ -16262,10 +16262,10 @@
         <v/>
       </c>
       <c r="BA60" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047663</v>
       </c>
       <c r="BB60" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25ocea_conquest_ct_200_q3.pdf</v>
       </c>
       <c r="BC60" t="str">
         <v/>
@@ -16432,7 +16432,7 @@
         <v/>
       </c>
       <c r="AV61" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW61" t="str">
         <v/>
@@ -16447,10 +16447,10 @@
         <v/>
       </c>
       <c r="BA61" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047670</v>
       </c>
       <c r="BB61" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25ocea_conquest_ct_200_q3.pdf</v>
       </c>
       <c r="BC61" t="str">
         <v/>
@@ -16617,7 +16617,7 @@
         <v/>
       </c>
       <c r="AV62" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW62" t="str">
         <v/>
@@ -16632,10 +16632,10 @@
         <v/>
       </c>
       <c r="BA62" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047687</v>
       </c>
       <c r="BB62" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25ocea_conquest_ct_200_q3.pdf</v>
       </c>
       <c r="BC62" t="str">
         <v/>
@@ -16802,7 +16802,7 @@
         <v/>
       </c>
       <c r="AV63" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW63" t="str">
         <v/>
@@ -16817,10 +16817,10 @@
         <v/>
       </c>
       <c r="BA63" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047694</v>
       </c>
       <c r="BB63" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25ocea_conquest_ct_200_q3.pdf</v>
       </c>
       <c r="BC63" t="str">
         <v/>
@@ -16987,7 +16987,7 @@
         <v/>
       </c>
       <c r="AV64" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW64" t="str">
         <v/>
@@ -17002,10 +17002,10 @@
         <v/>
       </c>
       <c r="BA64" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047700</v>
       </c>
       <c r="BB64" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25ocea_conquest_ct_200_q3.pdf</v>
       </c>
       <c r="BC64" t="str">
         <v/>
@@ -17172,7 +17172,7 @@
         <v/>
       </c>
       <c r="AV65" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW65" t="str">
         <v/>
@@ -17187,10 +17187,10 @@
         <v/>
       </c>
       <c r="BA65" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047717</v>
       </c>
       <c r="BB65" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25ocea_conquest_ct_200_q3.pdf</v>
       </c>
       <c r="BC65" t="str">
         <v/>
@@ -17357,7 +17357,7 @@
         <v/>
       </c>
       <c r="AV66" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW66" t="str">
         <v/>
@@ -17372,10 +17372,10 @@
         <v/>
       </c>
       <c r="BA66" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=033567</v>
       </c>
       <c r="BB66" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_15_kaikon_2000T_3000T_4000T.pdf</v>
       </c>
       <c r="BC66" t="str">
         <v/>
@@ -17542,7 +17542,7 @@
         <v/>
       </c>
       <c r="AV67" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW67" t="str">
         <v/>
@@ -17557,10 +17557,10 @@
         <v/>
       </c>
       <c r="BA67" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=033574</v>
       </c>
       <c r="BB67" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_15_kaikon_2000T_3000T_4000T.pdf</v>
       </c>
       <c r="BC67" t="str">
         <v/>
@@ -17727,7 +17727,7 @@
         <v/>
       </c>
       <c r="AV68" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW68" t="str">
         <v/>
@@ -17742,10 +17742,10 @@
         <v/>
       </c>
       <c r="BA68" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=033581</v>
       </c>
       <c r="BB68" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_15_kaikon_2000T_3000T_4000T.pdf</v>
       </c>
       <c r="BC68" t="str">
         <v/>
@@ -17921,16 +17921,16 @@
         <v/>
       </c>
       <c r="AY69" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
       <c r="AZ69" t="str">
         <v/>
       </c>
       <c r="BA69" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047724</v>
       </c>
       <c r="BB69" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25antares_q.pdf</v>
       </c>
       <c r="BC69" t="str">
         <v/>
@@ -18106,16 +18106,16 @@
         <v/>
       </c>
       <c r="AY70" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
       <c r="AZ70" t="str">
         <v/>
       </c>
       <c r="BA70" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047731</v>
       </c>
       <c r="BB70" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25antares_q.pdf</v>
       </c>
       <c r="BC70" t="str">
         <v/>
@@ -18291,16 +18291,16 @@
         <v/>
       </c>
       <c r="AY71" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
       <c r="AZ71" t="str">
         <v/>
       </c>
       <c r="BA71" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047748</v>
       </c>
       <c r="BB71" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25antares_q.pdf</v>
       </c>
       <c r="BC71" t="str">
         <v/>
@@ -18476,16 +18476,16 @@
         <v/>
       </c>
       <c r="AY72" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
       <c r="AZ72" t="str">
         <v/>
       </c>
       <c r="BA72" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047755</v>
       </c>
       <c r="BB72" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25antares_q.pdf</v>
       </c>
       <c r="BC72" t="str">
         <v/>
@@ -18661,16 +18661,16 @@
         <v/>
       </c>
       <c r="AY73" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
       <c r="AZ73" t="str">
         <v/>
       </c>
       <c r="BA73" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047762</v>
       </c>
       <c r="BB73" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25antares_q.pdf</v>
       </c>
       <c r="BC73" t="str">
         <v/>
@@ -18846,16 +18846,16 @@
         <v/>
       </c>
       <c r="AY74" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
       <c r="AZ74" t="str">
         <v/>
       </c>
       <c r="BA74" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047779</v>
       </c>
       <c r="BB74" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25antares_q.pdf</v>
       </c>
       <c r="BC74" t="str">
         <v/>
@@ -19022,7 +19022,7 @@
         <v/>
       </c>
       <c r="AV75" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW75" t="str">
         <v/>
@@ -19037,10 +19037,10 @@
         <v/>
       </c>
       <c r="BA75" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043764</v>
       </c>
       <c r="BB75" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC75" t="str">
         <v/>
@@ -19207,7 +19207,7 @@
         <v/>
       </c>
       <c r="AV76" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW76" t="str">
         <v/>
@@ -19222,10 +19222,10 @@
         <v/>
       </c>
       <c r="BA76" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043771</v>
       </c>
       <c r="BB76" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC76" t="str">
         <v/>
@@ -19392,7 +19392,7 @@
         <v/>
       </c>
       <c r="AV77" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW77" t="str">
         <v/>
@@ -19407,10 +19407,10 @@
         <v/>
       </c>
       <c r="BA77" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043788</v>
       </c>
       <c r="BB77" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC77" t="str">
         <v/>
@@ -19577,7 +19577,7 @@
         <v/>
       </c>
       <c r="AV78" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW78" t="str">
         <v/>
@@ -19592,10 +19592,10 @@
         <v/>
       </c>
       <c r="BA78" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043795</v>
       </c>
       <c r="BB78" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC78" t="str">
         <v/>
@@ -19762,7 +19762,7 @@
         <v/>
       </c>
       <c r="AV79" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW79" t="str">
         <v/>
@@ -19777,10 +19777,10 @@
         <v/>
       </c>
       <c r="BA79" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043801</v>
       </c>
       <c r="BB79" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC79" t="str">
         <v/>
@@ -19947,7 +19947,7 @@
         <v/>
       </c>
       <c r="AV80" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW80" t="str">
         <v/>
@@ -19962,10 +19962,10 @@
         <v/>
       </c>
       <c r="BA80" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043818</v>
       </c>
       <c r="BB80" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC80" t="str">
         <v/>
@@ -20132,7 +20132,7 @@
         <v/>
       </c>
       <c r="AV81" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW81" t="str">
         <v/>
@@ -20147,10 +20147,10 @@
         <v/>
       </c>
       <c r="BA81" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036650</v>
       </c>
       <c r="BB81" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_17OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC81" t="str">
         <v/>
@@ -20317,7 +20317,7 @@
         <v/>
       </c>
       <c r="AV82" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW82" t="str">
         <v/>
@@ -20332,10 +20332,10 @@
         <v/>
       </c>
       <c r="BA82" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036667</v>
       </c>
       <c r="BB82" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_17OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC82" t="str">
         <v/>
@@ -20502,7 +20502,7 @@
         <v/>
       </c>
       <c r="AV83" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW83" t="str">
         <v/>
@@ -20517,10 +20517,10 @@
         <v/>
       </c>
       <c r="BA83" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036674</v>
       </c>
       <c r="BB83" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_17OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC83" t="str">
         <v/>
@@ -20687,7 +20687,7 @@
         <v/>
       </c>
       <c r="AV84" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW84" t="str">
         <v/>
@@ -20702,10 +20702,10 @@
         <v/>
       </c>
       <c r="BA84" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036698</v>
       </c>
       <c r="BB84" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_17OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC84" t="str">
         <v/>
@@ -20872,7 +20872,7 @@
         <v/>
       </c>
       <c r="AV85" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW85" t="str">
         <v/>
@@ -20887,10 +20887,10 @@
         <v/>
       </c>
       <c r="BA85" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036681</v>
       </c>
       <c r="BB85" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_17OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC85" t="str">
         <v/>
@@ -21057,7 +21057,7 @@
         <v/>
       </c>
       <c r="AV86" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW86" t="str">
         <v/>
@@ -21072,10 +21072,10 @@
         <v/>
       </c>
       <c r="BA86" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036704</v>
       </c>
       <c r="BB86" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_17OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC86" t="str">
         <v/>
@@ -21242,7 +21242,7 @@
         <v/>
       </c>
       <c r="AV87" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW87" t="str">
         <v/>
@@ -21257,10 +21257,10 @@
         <v/>
       </c>
       <c r="BA87" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036711</v>
       </c>
       <c r="BB87" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_17OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC87" t="str">
         <v/>
@@ -21427,7 +21427,7 @@
         <v/>
       </c>
       <c r="AV88" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW88" t="str">
         <v/>
@@ -21442,10 +21442,10 @@
         <v/>
       </c>
       <c r="BA88" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036735</v>
       </c>
       <c r="BB88" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_17OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC88" t="str">
         <v/>
@@ -21612,7 +21612,7 @@
         <v/>
       </c>
       <c r="AV89" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW89" t="str">
         <v/>
@@ -21627,10 +21627,10 @@
         <v/>
       </c>
       <c r="BA89" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036728</v>
       </c>
       <c r="BB89" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_17OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC89" t="str">
         <v/>
@@ -21797,7 +21797,7 @@
         <v/>
       </c>
       <c r="AV90" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW90" t="str">
         <v/>
@@ -21812,10 +21812,10 @@
         <v/>
       </c>
       <c r="BA90" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036742</v>
       </c>
       <c r="BB90" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_17OCEA%20JIGGER_.pdf</v>
       </c>
       <c r="BC90" t="str">
         <v/>
@@ -21928,7 +21928,7 @@
         <v/>
       </c>
       <c r="AD91" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE91" t="str">
         <v/>
@@ -21982,7 +21982,7 @@
         <v/>
       </c>
       <c r="AV91" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW91" t="str">
         <v/>
@@ -21991,16 +21991,16 @@
         <v/>
       </c>
       <c r="AY91" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ91" t="str">
         <v/>
       </c>
       <c r="BA91" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045928</v>
       </c>
       <c r="BB91" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23conquest%20md.pdf</v>
       </c>
       <c r="BC91" t="str">
         <v/>
@@ -22113,7 +22113,7 @@
         <v/>
       </c>
       <c r="AD92" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE92" t="str">
         <v/>
@@ -22167,7 +22167,7 @@
         <v/>
       </c>
       <c r="AV92" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW92" t="str">
         <v/>
@@ -22176,16 +22176,16 @@
         <v/>
       </c>
       <c r="AY92" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ92" t="str">
         <v/>
       </c>
       <c r="BA92" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045935</v>
       </c>
       <c r="BB92" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23conquest%20md.pdf</v>
       </c>
       <c r="BC92" t="str">
         <v/>
@@ -22298,7 +22298,7 @@
         <v/>
       </c>
       <c r="AD93" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE93" t="str">
         <v/>
@@ -22352,7 +22352,7 @@
         <v/>
       </c>
       <c r="AV93" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW93" t="str">
         <v/>
@@ -22361,16 +22361,16 @@
         <v/>
       </c>
       <c r="AY93" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ93" t="str">
         <v/>
       </c>
       <c r="BA93" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045942</v>
       </c>
       <c r="BB93" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23conquest%20md.pdf</v>
       </c>
       <c r="BC93" t="str">
         <v/>
@@ -22483,7 +22483,7 @@
         <v/>
       </c>
       <c r="AD94" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE94" t="str">
         <v/>
@@ -22537,7 +22537,7 @@
         <v/>
       </c>
       <c r="AV94" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW94" t="str">
         <v/>
@@ -22546,16 +22546,16 @@
         <v/>
       </c>
       <c r="AY94" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ94" t="str">
         <v/>
       </c>
       <c r="BA94" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045959</v>
       </c>
       <c r="BB94" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23conquest%20md.pdf</v>
       </c>
       <c r="BC94" t="str">
         <v/>
@@ -22668,7 +22668,7 @@
         <v/>
       </c>
       <c r="AD95" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE95" t="str">
         <v/>
@@ -22722,7 +22722,7 @@
         <v/>
       </c>
       <c r="AV95" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW95" t="str">
         <v/>
@@ -22731,16 +22731,16 @@
         <v/>
       </c>
       <c r="AY95" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ95" t="str">
         <v/>
       </c>
       <c r="BA95" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045966</v>
       </c>
       <c r="BB95" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23conquest%20md.pdf</v>
       </c>
       <c r="BC95" t="str">
         <v/>
@@ -22853,7 +22853,7 @@
         <v/>
       </c>
       <c r="AD96" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE96" t="str">
         <v/>
@@ -22907,7 +22907,7 @@
         <v/>
       </c>
       <c r="AV96" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW96" t="str">
         <v/>
@@ -22916,16 +22916,16 @@
         <v/>
       </c>
       <c r="AY96" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ96" t="str">
         <v/>
       </c>
       <c r="BA96" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045973</v>
       </c>
       <c r="BB96" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23conquest%20md.pdf</v>
       </c>
       <c r="BC96" t="str">
         <v/>
@@ -23038,7 +23038,7 @@
         <v/>
       </c>
       <c r="AD97" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE97" t="str">
         <v/>
@@ -23092,7 +23092,7 @@
         <v/>
       </c>
       <c r="AV97" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW97" t="str">
         <v/>
@@ -23101,16 +23101,16 @@
         <v/>
       </c>
       <c r="AY97" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ97" t="str">
         <v/>
       </c>
       <c r="BA97" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=049322</v>
       </c>
       <c r="BB97" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_26ct_conquest_bfs_ltd_q.pdf</v>
       </c>
       <c r="BC97" t="str">
         <v/>
@@ -23223,7 +23223,7 @@
         <v/>
       </c>
       <c r="AD98" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE98" t="str">
         <v/>
@@ -23277,7 +23277,7 @@
         <v/>
       </c>
       <c r="AV98" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW98" t="str">
         <v/>
@@ -23286,16 +23286,16 @@
         <v/>
       </c>
       <c r="AY98" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ98" t="str">
         <v/>
       </c>
       <c r="BA98" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=049339</v>
       </c>
       <c r="BB98" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_26ct_conquest_bfs_ltd_q.pdf</v>
       </c>
       <c r="BC98" t="str">
         <v/>
@@ -23408,7 +23408,7 @@
         <v/>
       </c>
       <c r="AD99" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE99" t="str">
         <v/>
@@ -23462,7 +23462,7 @@
         <v/>
       </c>
       <c r="AV99" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW99" t="str">
         <v/>
@@ -23471,16 +23471,16 @@
         <v/>
       </c>
       <c r="AY99" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ99" t="str">
         <v/>
       </c>
       <c r="BA99" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=049346</v>
       </c>
       <c r="BB99" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_26ct_conquest_bfs_ltd_q.pdf</v>
       </c>
       <c r="BC99" t="str">
         <v/>
@@ -23593,7 +23593,7 @@
         <v/>
       </c>
       <c r="AD100" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE100" t="str">
         <v/>
@@ -23647,7 +23647,7 @@
         <v/>
       </c>
       <c r="AV100" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW100" t="str">
         <v/>
@@ -23656,16 +23656,16 @@
         <v/>
       </c>
       <c r="AY100" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ100" t="str">
         <v/>
       </c>
       <c r="BA100" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=049353</v>
       </c>
       <c r="BB100" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_26ct_conquest_bfs_ltd_q.pdf</v>
       </c>
       <c r="BC100" t="str">
         <v/>
@@ -23847,10 +23847,10 @@
         <v/>
       </c>
       <c r="BA101" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046604</v>
       </c>
       <c r="BB101" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24metanium_dc_70_q.pdf</v>
       </c>
       <c r="BC101" t="str">
         <v/>
@@ -24032,10 +24032,10 @@
         <v/>
       </c>
       <c r="BA102" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046611</v>
       </c>
       <c r="BB102" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24metanium_dc_71_q.pdf</v>
       </c>
       <c r="BC102" t="str">
         <v/>
@@ -24217,10 +24217,10 @@
         <v/>
       </c>
       <c r="BA103" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046628</v>
       </c>
       <c r="BB103" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24metanium_dc_70_q.pdf</v>
       </c>
       <c r="BC103" t="str">
         <v/>
@@ -24402,10 +24402,10 @@
         <v/>
       </c>
       <c r="BA104" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046635</v>
       </c>
       <c r="BB104" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24metanium_dc_71_q.pdf</v>
       </c>
       <c r="BC104" t="str">
         <v/>
@@ -24587,10 +24587,10 @@
         <v/>
       </c>
       <c r="BA105" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046642</v>
       </c>
       <c r="BB105" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24metanium_dc_70_q.pdf</v>
       </c>
       <c r="BC105" t="str">
         <v/>
@@ -24772,10 +24772,10 @@
         <v/>
       </c>
       <c r="BA106" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046659</v>
       </c>
       <c r="BB106" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24metanium_dc_71_q.pdf</v>
       </c>
       <c r="BC106" t="str">
         <v/>
@@ -24888,7 +24888,7 @@
         <v/>
       </c>
       <c r="AD107" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE107" t="str">
         <v/>
@@ -24942,7 +24942,7 @@
         <v/>
       </c>
       <c r="AV107" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW107" t="str">
         <v/>
@@ -24951,16 +24951,16 @@
         <v/>
       </c>
       <c r="AY107" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ107" t="str">
         <v/>
       </c>
       <c r="BA107" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042323</v>
       </c>
       <c r="BB107" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_calcutta_cqe.pdf</v>
       </c>
       <c r="BC107" t="str">
         <v/>
@@ -25073,7 +25073,7 @@
         <v/>
       </c>
       <c r="AD108" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE108" t="str">
         <v/>
@@ -25127,7 +25127,7 @@
         <v/>
       </c>
       <c r="AV108" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW108" t="str">
         <v/>
@@ -25136,16 +25136,16 @@
         <v/>
       </c>
       <c r="AY108" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ108" t="str">
         <v/>
       </c>
       <c r="BA108" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042330</v>
       </c>
       <c r="BB108" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_calcutta_cqe.pdf</v>
       </c>
       <c r="BC108" t="str">
         <v/>
@@ -25258,7 +25258,7 @@
         <v/>
       </c>
       <c r="AD109" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE109" t="str">
         <v/>
@@ -25312,7 +25312,7 @@
         <v/>
       </c>
       <c r="AV109" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW109" t="str">
         <v/>
@@ -25321,16 +25321,16 @@
         <v/>
       </c>
       <c r="AY109" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ109" t="str">
         <v/>
       </c>
       <c r="BA109" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042347</v>
       </c>
       <c r="BB109" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_calcutta_cqe.pdf</v>
       </c>
       <c r="BC109" t="str">
         <v/>
@@ -25443,7 +25443,7 @@
         <v/>
       </c>
       <c r="AD110" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE110" t="str">
         <v/>
@@ -25497,7 +25497,7 @@
         <v/>
       </c>
       <c r="AV110" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW110" t="str">
         <v/>
@@ -25506,16 +25506,16 @@
         <v/>
       </c>
       <c r="AY110" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ110" t="str">
         <v/>
       </c>
       <c r="BA110" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042354</v>
       </c>
       <c r="BB110" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_calcutta_cqe.pdf</v>
       </c>
       <c r="BC110" t="str">
         <v/>
@@ -25628,7 +25628,7 @@
         <v/>
       </c>
       <c r="AD111" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE111" t="str">
         <v/>
@@ -25682,7 +25682,7 @@
         <v/>
       </c>
       <c r="AV111" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW111" t="str">
         <v/>
@@ -25691,16 +25691,16 @@
         <v/>
       </c>
       <c r="AY111" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ111" t="str">
         <v/>
       </c>
       <c r="BA111" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042361</v>
       </c>
       <c r="BB111" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_calcutta_cqe.pdf</v>
       </c>
       <c r="BC111" t="str">
         <v/>
@@ -25813,7 +25813,7 @@
         <v/>
       </c>
       <c r="AD112" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE112" t="str">
         <v/>
@@ -25867,7 +25867,7 @@
         <v/>
       </c>
       <c r="AV112" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW112" t="str">
         <v/>
@@ -25876,16 +25876,16 @@
         <v/>
       </c>
       <c r="AY112" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ112" t="str">
         <v/>
       </c>
       <c r="BA112" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042378</v>
       </c>
       <c r="BB112" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_calcutta_cqe.pdf</v>
       </c>
       <c r="BC112" t="str">
         <v/>
@@ -25998,7 +25998,7 @@
         <v/>
       </c>
       <c r="AD113" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE113" t="str">
         <v/>
@@ -26052,7 +26052,7 @@
         <v/>
       </c>
       <c r="AV113" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW113" t="str">
         <v/>
@@ -26061,16 +26061,16 @@
         <v/>
       </c>
       <c r="AY113" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ113" t="str">
         <v/>
       </c>
       <c r="BA113" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042385</v>
       </c>
       <c r="BB113" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_calcutta_cqe.pdf</v>
       </c>
       <c r="BC113" t="str">
         <v/>
@@ -26183,7 +26183,7 @@
         <v/>
       </c>
       <c r="AD114" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE114" t="str">
         <v/>
@@ -26237,7 +26237,7 @@
         <v/>
       </c>
       <c r="AV114" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW114" t="str">
         <v/>
@@ -26246,16 +26246,16 @@
         <v/>
       </c>
       <c r="AY114" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ114" t="str">
         <v/>
       </c>
       <c r="BA114" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042392</v>
       </c>
       <c r="BB114" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_calcutta_cqe.pdf</v>
       </c>
       <c r="BC114" t="str">
         <v/>
@@ -26368,7 +26368,7 @@
         <v/>
       </c>
       <c r="AD115" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE115" t="str">
         <v/>
@@ -26422,7 +26422,7 @@
         <v/>
       </c>
       <c r="AV115" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW115" t="str">
         <v/>
@@ -26431,16 +26431,16 @@
         <v/>
       </c>
       <c r="AY115" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ115" t="str">
         <v/>
       </c>
       <c r="BA115" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044402</v>
       </c>
       <c r="BB115" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_calcutta_cqe%20(1).pdf</v>
       </c>
       <c r="BC115" t="str">
         <v/>
@@ -26553,7 +26553,7 @@
         <v/>
       </c>
       <c r="AD116" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE116" t="str">
         <v/>
@@ -26607,7 +26607,7 @@
         <v/>
       </c>
       <c r="AV116" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW116" t="str">
         <v/>
@@ -26616,16 +26616,16 @@
         <v/>
       </c>
       <c r="AY116" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ116" t="str">
         <v/>
       </c>
       <c r="BA116" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044419</v>
       </c>
       <c r="BB116" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_calcutta_cqe%20(1).pdf</v>
       </c>
       <c r="BC116" t="str">
         <v/>
@@ -26792,7 +26792,7 @@
         <v/>
       </c>
       <c r="AV117" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW117" t="str">
         <v/>
@@ -26807,10 +26807,10 @@
         <v/>
       </c>
       <c r="BA117" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044426</v>
       </c>
       <c r="BB117" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_ocea_conquest_2022.pdf</v>
       </c>
       <c r="BC117" t="str">
         <v/>
@@ -26977,7 +26977,7 @@
         <v/>
       </c>
       <c r="AV118" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW118" t="str">
         <v/>
@@ -26992,10 +26992,10 @@
         <v/>
       </c>
       <c r="BA118" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044433</v>
       </c>
       <c r="BB118" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_ocea_conquest_2022.pdf</v>
       </c>
       <c r="BC118" t="str">
         <v/>
@@ -27162,7 +27162,7 @@
         <v/>
       </c>
       <c r="AV119" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW119" t="str">
         <v/>
@@ -27177,10 +27177,10 @@
         <v/>
       </c>
       <c r="BA119" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044440</v>
       </c>
       <c r="BB119" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_ocea_conquest_2022.pdf</v>
       </c>
       <c r="BC119" t="str">
         <v/>
@@ -27347,7 +27347,7 @@
         <v/>
       </c>
       <c r="AV120" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW120" t="str">
         <v/>
@@ -27362,10 +27362,10 @@
         <v/>
       </c>
       <c r="BA120" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044457</v>
       </c>
       <c r="BB120" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_ocea_conquest_2022.pdf</v>
       </c>
       <c r="BC120" t="str">
         <v/>
@@ -27532,7 +27532,7 @@
         <v/>
       </c>
       <c r="AV121" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW121" t="str">
         <v/>
@@ -27547,10 +27547,10 @@
         <v/>
       </c>
       <c r="BA121" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044464</v>
       </c>
       <c r="BB121" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_ocea_conquest_2022.pdf</v>
       </c>
       <c r="BC121" t="str">
         <v/>
@@ -27717,7 +27717,7 @@
         <v/>
       </c>
       <c r="AV122" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW122" t="str">
         <v/>
@@ -27732,10 +27732,10 @@
         <v/>
       </c>
       <c r="BA122" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044471</v>
       </c>
       <c r="BB122" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_ocea_conquest_2022.pdf</v>
       </c>
       <c r="BC122" t="str">
         <v/>
@@ -27902,7 +27902,7 @@
         <v/>
       </c>
       <c r="AV123" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW123" t="str">
         <v/>
@@ -27917,10 +27917,10 @@
         <v/>
       </c>
       <c r="BA123" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046260</v>
       </c>
       <c r="BB123" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23oceaconquest200_.pdf</v>
       </c>
       <c r="BC123" t="str">
         <v/>
@@ -28087,7 +28087,7 @@
         <v/>
       </c>
       <c r="AV124" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW124" t="str">
         <v/>
@@ -28102,10 +28102,10 @@
         <v/>
       </c>
       <c r="BA124" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046277</v>
       </c>
       <c r="BB124" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23oceaconquest200_.pdf</v>
       </c>
       <c r="BC124" t="str">
         <v/>
@@ -28272,7 +28272,7 @@
         <v/>
       </c>
       <c r="AV125" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW125" t="str">
         <v/>
@@ -28287,10 +28287,10 @@
         <v/>
       </c>
       <c r="BA125" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046284</v>
       </c>
       <c r="BB125" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23oceaconquest200_.pdf</v>
       </c>
       <c r="BC125" t="str">
         <v/>
@@ -28457,7 +28457,7 @@
         <v/>
       </c>
       <c r="AV126" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW126" t="str">
         <v/>
@@ -28472,10 +28472,10 @@
         <v/>
       </c>
       <c r="BA126" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046291</v>
       </c>
       <c r="BB126" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23oceaconquest200_.pdf</v>
       </c>
       <c r="BC126" t="str">
         <v/>
@@ -28588,7 +28588,7 @@
         <v/>
       </c>
       <c r="AD127" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE127" t="str">
         <v/>
@@ -28642,7 +28642,7 @@
         <v/>
       </c>
       <c r="AV127" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW127" t="str">
         <v/>
@@ -28651,16 +28651,16 @@
         <v/>
       </c>
       <c r="AY127" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ127" t="str">
         <v/>
       </c>
       <c r="BA127" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046734</v>
       </c>
       <c r="BB127" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24CONQUEST_SE_30HG.pdf</v>
       </c>
       <c r="BC127" t="str">
         <v/>
@@ -28773,7 +28773,7 @@
         <v/>
       </c>
       <c r="AD128" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE128" t="str">
         <v/>
@@ -28827,7 +28827,7 @@
         <v/>
       </c>
       <c r="AV128" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW128" t="str">
         <v/>
@@ -28836,16 +28836,16 @@
         <v/>
       </c>
       <c r="AY128" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ128" t="str">
         <v/>
       </c>
       <c r="BA128" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046741</v>
       </c>
       <c r="BB128" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24CONQUEST_SE_31HG.pdf</v>
       </c>
       <c r="BC128" t="str">
         <v/>
@@ -29012,7 +29012,7 @@
         <v/>
       </c>
       <c r="AV129" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW129" t="str">
         <v/>
@@ -29027,10 +29027,10 @@
         <v/>
       </c>
       <c r="BA129" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045683</v>
       </c>
       <c r="BB129" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23CALCUTTA%20CONQUEST%20BFS.pdf</v>
       </c>
       <c r="BC129" t="str">
         <v/>
@@ -29197,7 +29197,7 @@
         <v/>
       </c>
       <c r="AV130" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW130" t="str">
         <v/>
@@ -29212,10 +29212,10 @@
         <v/>
       </c>
       <c r="BA130" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045690</v>
       </c>
       <c r="BB130" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23CALCUTTA%20CONQUEST%20BFS.pdf</v>
       </c>
       <c r="BC130" t="str">
         <v/>
@@ -29382,7 +29382,7 @@
         <v/>
       </c>
       <c r="AV131" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW131" t="str">
         <v/>
@@ -29397,10 +29397,10 @@
         <v/>
       </c>
       <c r="BA131" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045706</v>
       </c>
       <c r="BB131" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23CALCUTTA%20CONQUEST%20BFS.pdf</v>
       </c>
       <c r="BC131" t="str">
         <v/>
@@ -29567,7 +29567,7 @@
         <v/>
       </c>
       <c r="AV132" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW132" t="str">
         <v/>
@@ -29582,10 +29582,10 @@
         <v/>
       </c>
       <c r="BA132" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045713</v>
       </c>
       <c r="BB132" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23CALCUTTA%20CONQUEST%20BFS.pdf</v>
       </c>
       <c r="BC132" t="str">
         <v/>
@@ -29698,7 +29698,7 @@
         <v/>
       </c>
       <c r="AD133" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE133" t="str">
         <v/>
@@ -29752,7 +29752,7 @@
         <v/>
       </c>
       <c r="AV133" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW133" t="str">
         <v/>
@@ -29761,16 +29761,16 @@
         <v/>
       </c>
       <c r="AY133" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ133" t="str">
         <v/>
       </c>
       <c r="BA133" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=049179</v>
       </c>
       <c r="BB133" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_26ocea_conquest_ft_60_q.pdf</v>
       </c>
       <c r="BC133" t="str">
         <v/>
@@ -29883,7 +29883,7 @@
         <v/>
       </c>
       <c r="AD134" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE134" t="str">
         <v/>
@@ -29937,7 +29937,7 @@
         <v/>
       </c>
       <c r="AV134" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW134" t="str">
         <v/>
@@ -29946,7 +29946,7 @@
         <v/>
       </c>
       <c r="AY134" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ134" t="str">
         <v/>
@@ -30068,7 +30068,7 @@
         <v/>
       </c>
       <c r="AD135" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE135" t="str">
         <v/>
@@ -30122,7 +30122,7 @@
         <v/>
       </c>
       <c r="AV135" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW135" t="str">
         <v/>
@@ -30131,16 +30131,16 @@
         <v/>
       </c>
       <c r="AY135" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ135" t="str">
         <v/>
       </c>
       <c r="BA135" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=049193</v>
       </c>
       <c r="BB135" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_26ocea_conquest_ft_60_q.pdf</v>
       </c>
       <c r="BC135" t="str">
         <v/>
@@ -30253,7 +30253,7 @@
         <v/>
       </c>
       <c r="AD136" t="str">
-        <v/>
+        <v>Aluminum</v>
       </c>
       <c r="AE136" t="str">
         <v/>
@@ -30307,7 +30307,7 @@
         <v/>
       </c>
       <c r="AV136" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW136" t="str">
         <v/>
@@ -30316,7 +30316,7 @@
         <v/>
       </c>
       <c r="AY136" t="str">
-        <v/>
+        <v>全加工</v>
       </c>
       <c r="AZ136" t="str">
         <v/>
@@ -30501,16 +30501,16 @@
         <v/>
       </c>
       <c r="AY137" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
       <c r="AZ137" t="str">
         <v/>
       </c>
       <c r="BA137" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047830</v>
       </c>
       <c r="BB137" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25aldebaran_dc%20_q.pdf</v>
       </c>
       <c r="BC137" t="str">
         <v/>
@@ -30686,16 +30686,16 @@
         <v/>
       </c>
       <c r="AY138" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
       <c r="AZ138" t="str">
         <v/>
       </c>
       <c r="BA138" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047847</v>
       </c>
       <c r="BB138" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25aldebaran_dc%20_q.pdf</v>
       </c>
       <c r="BC138" t="str">
         <v/>
@@ -30871,16 +30871,16 @@
         <v/>
       </c>
       <c r="AY139" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
       <c r="AZ139" t="str">
         <v/>
       </c>
       <c r="BA139" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047854</v>
       </c>
       <c r="BB139" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25aldebaran_dc%20_q.pdf</v>
       </c>
       <c r="BC139" t="str">
         <v/>
@@ -31056,16 +31056,16 @@
         <v/>
       </c>
       <c r="AY140" t="str">
-        <v/>
+        <v>HAGANE 机身</v>
       </c>
       <c r="AZ140" t="str">
         <v/>
       </c>
       <c r="BA140" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047861</v>
       </c>
       <c r="BB140" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25aldebaran_dc%20_q.pdf</v>
       </c>
       <c r="BC140" t="str">
         <v/>
@@ -31247,10 +31247,10 @@
         <v/>
       </c>
       <c r="BA141" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048462</v>
       </c>
       <c r="BB141" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25stile_q.pdf</v>
       </c>
       <c r="BC141" t="str">
         <v/>
@@ -31432,10 +31432,10 @@
         <v/>
       </c>
       <c r="BA142" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048479</v>
       </c>
       <c r="BB142" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25stile_q.pdf</v>
       </c>
       <c r="BC142" t="str">
         <v/>
@@ -31617,10 +31617,10 @@
         <v/>
       </c>
       <c r="BA143" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048486</v>
       </c>
       <c r="BB143" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25stile_q.pdf</v>
       </c>
       <c r="BC143" t="str">
         <v/>
@@ -31802,10 +31802,10 @@
         <v/>
       </c>
       <c r="BA144" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048493</v>
       </c>
       <c r="BB144" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25stile_q.pdf</v>
       </c>
       <c r="BC144" t="str">
         <v/>
@@ -31972,7 +31972,7 @@
         <v/>
       </c>
       <c r="AV145" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW145" t="str">
         <v/>
@@ -31987,10 +31987,10 @@
         <v/>
       </c>
       <c r="BA145" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047274</v>
       </c>
       <c r="BB145" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24barchetta_premium_q.pdf</v>
       </c>
       <c r="BC145" t="str">
         <v/>
@@ -32157,7 +32157,7 @@
         <v/>
       </c>
       <c r="AV146" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW146" t="str">
         <v/>
@@ -32172,10 +32172,10 @@
         <v/>
       </c>
       <c r="BA146" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047281</v>
       </c>
       <c r="BB146" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24barchetta_premium_q.pdf</v>
       </c>
       <c r="BC146" t="str">
         <v/>
@@ -32342,7 +32342,7 @@
         <v/>
       </c>
       <c r="AV147" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW147" t="str">
         <v/>
@@ -32357,10 +32357,10 @@
         <v/>
       </c>
       <c r="BA147" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047298</v>
       </c>
       <c r="BB147" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24barchetta_premium_q.pdf</v>
       </c>
       <c r="BC147" t="str">
         <v/>
@@ -32527,7 +32527,7 @@
         <v/>
       </c>
       <c r="AV148" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW148" t="str">
         <v/>
@@ -32542,10 +32542,10 @@
         <v/>
       </c>
       <c r="BA148" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047304</v>
       </c>
       <c r="BB148" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24barchetta_premium_q.pdf</v>
       </c>
       <c r="BC148" t="str">
         <v/>
@@ -32712,7 +32712,7 @@
         <v/>
       </c>
       <c r="AV149" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW149" t="str">
         <v/>
@@ -32727,10 +32727,10 @@
         <v/>
       </c>
       <c r="BA149" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047311</v>
       </c>
       <c r="BB149" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24barchetta_premium_q.pdf</v>
       </c>
       <c r="BC149" t="str">
         <v/>
@@ -32897,7 +32897,7 @@
         <v/>
       </c>
       <c r="AV150" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW150" t="str">
         <v/>
@@ -32912,10 +32912,10 @@
         <v/>
       </c>
       <c r="BA150" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047328</v>
       </c>
       <c r="BB150" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24barchetta_premium_q.pdf</v>
       </c>
       <c r="BC150" t="str">
         <v/>
@@ -33082,7 +33082,7 @@
         <v/>
       </c>
       <c r="AV151" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW151" t="str">
         <v/>
@@ -33097,10 +33097,10 @@
         <v/>
       </c>
       <c r="BA151" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047182</v>
       </c>
       <c r="BB151" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24grappler_premium_JP_q.pdf</v>
       </c>
       <c r="BC151" t="str">
         <v/>
@@ -33267,7 +33267,7 @@
         <v/>
       </c>
       <c r="AV152" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW152" t="str">
         <v/>
@@ -33282,10 +33282,10 @@
         <v/>
       </c>
       <c r="BA152" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047199</v>
       </c>
       <c r="BB152" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24grappler_premium_JP_q.pdf</v>
       </c>
       <c r="BC152" t="str">
         <v/>
@@ -34878,7 +34878,7 @@
         <v/>
       </c>
       <c r="AD161" t="str">
-        <v/>
+        <v>Magnesium</v>
       </c>
       <c r="AE161" t="str">
         <v/>
@@ -34941,16 +34941,16 @@
         <v/>
       </c>
       <c r="AY161" t="str">
-        <v/>
+        <v>CORESOLID BODY</v>
       </c>
       <c r="AZ161" t="str">
         <v/>
       </c>
       <c r="BA161" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044778</v>
       </c>
       <c r="BB161" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_metanium_shallow_edition.pdf</v>
       </c>
       <c r="BC161" t="str">
         <v/>
@@ -35063,7 +35063,7 @@
         <v/>
       </c>
       <c r="AD162" t="str">
-        <v/>
+        <v>Magnesium</v>
       </c>
       <c r="AE162" t="str">
         <v/>
@@ -35126,16 +35126,16 @@
         <v/>
       </c>
       <c r="AY162" t="str">
-        <v/>
+        <v>CORESOLID BODY</v>
       </c>
       <c r="AZ162" t="str">
         <v/>
       </c>
       <c r="BA162" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044785</v>
       </c>
       <c r="BB162" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_metanium_shallow_edition.pdf</v>
       </c>
       <c r="BC162" t="str">
         <v/>
@@ -35248,7 +35248,7 @@
         <v/>
       </c>
       <c r="AD163" t="str">
-        <v/>
+        <v>Magnesium</v>
       </c>
       <c r="AE163" t="str">
         <v/>
@@ -35311,16 +35311,16 @@
         <v/>
       </c>
       <c r="AY163" t="str">
-        <v/>
+        <v>CORESOLID BODY</v>
       </c>
       <c r="AZ163" t="str">
         <v/>
       </c>
       <c r="BA163" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044792</v>
       </c>
       <c r="BB163" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_metanium_shallow_edition.pdf</v>
       </c>
       <c r="BC163" t="str">
         <v/>
@@ -35433,7 +35433,7 @@
         <v/>
       </c>
       <c r="AD164" t="str">
-        <v/>
+        <v>Magnesium</v>
       </c>
       <c r="AE164" t="str">
         <v/>
@@ -35496,16 +35496,16 @@
         <v/>
       </c>
       <c r="AY164" t="str">
-        <v/>
+        <v>CORESOLID BODY</v>
       </c>
       <c r="AZ164" t="str">
         <v/>
       </c>
       <c r="BA164" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044808</v>
       </c>
       <c r="BB164" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_metanium_shallow_edition.pdf</v>
       </c>
       <c r="BC164" t="str">
         <v/>
@@ -35618,7 +35618,7 @@
         <v/>
       </c>
       <c r="AD165" t="str">
-        <v/>
+        <v>Magnesium</v>
       </c>
       <c r="AE165" t="str">
         <v/>
@@ -35681,16 +35681,16 @@
         <v/>
       </c>
       <c r="AY165" t="str">
-        <v/>
+        <v>CORESOLID BODY</v>
       </c>
       <c r="AZ165" t="str">
         <v/>
       </c>
       <c r="BA165" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044815</v>
       </c>
       <c r="BB165" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_metanium_shallow_edition.pdf</v>
       </c>
       <c r="BC165" t="str">
         <v/>
@@ -35803,7 +35803,7 @@
         <v/>
       </c>
       <c r="AD166" t="str">
-        <v/>
+        <v>Magnesium</v>
       </c>
       <c r="AE166" t="str">
         <v/>
@@ -35866,16 +35866,16 @@
         <v/>
       </c>
       <c r="AY166" t="str">
-        <v/>
+        <v>CORESOLID BODY</v>
       </c>
       <c r="AZ166" t="str">
         <v/>
       </c>
       <c r="BA166" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044822</v>
       </c>
       <c r="BB166" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_metanium_shallow_edition.pdf</v>
       </c>
       <c r="BC166" t="str">
         <v/>
@@ -39002,7 +39002,7 @@
         <v/>
       </c>
       <c r="AV183" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW183" t="str">
         <v/>
@@ -39017,10 +39017,10 @@
         <v/>
       </c>
       <c r="BA183" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044365</v>
       </c>
       <c r="BB183" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23SPEEDMASTER%20ISHIDAI.pdf</v>
       </c>
       <c r="BC183" t="str">
         <v/>
@@ -39187,7 +39187,7 @@
         <v/>
       </c>
       <c r="AV184" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW184" t="str">
         <v/>
@@ -39202,10 +39202,10 @@
         <v/>
       </c>
       <c r="BA184" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044372</v>
       </c>
       <c r="BB184" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23SPEEDMASTER%20ISHIDAI.pdf</v>
       </c>
       <c r="BC184" t="str">
         <v/>
@@ -39372,7 +39372,7 @@
         <v/>
       </c>
       <c r="AV185" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW185" t="str">
         <v/>
@@ -39387,10 +39387,10 @@
         <v/>
       </c>
       <c r="BA185" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044389</v>
       </c>
       <c r="BB185" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23SPEEDMASTER%20ISHIDAI.pdf</v>
       </c>
       <c r="BC185" t="str">
         <v/>
@@ -39557,7 +39557,7 @@
         <v/>
       </c>
       <c r="AV186" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW186" t="str">
         <v/>
@@ -39572,10 +39572,10 @@
         <v/>
       </c>
       <c r="BA186" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=023742</v>
       </c>
       <c r="BB186" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_10_tyrnos.pdf</v>
       </c>
       <c r="BC186" t="str">
         <v/>
@@ -39742,7 +39742,7 @@
         <v/>
       </c>
       <c r="AV187" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW187" t="str">
         <v/>
@@ -39757,10 +39757,10 @@
         <v/>
       </c>
       <c r="BA187" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=022523</v>
       </c>
       <c r="BB187" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_10_tyrnos.pdf</v>
       </c>
       <c r="BC187" t="str">
         <v/>
@@ -39927,7 +39927,7 @@
         <v/>
       </c>
       <c r="AV188" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW188" t="str">
         <v/>
@@ -39942,10 +39942,10 @@
         <v/>
       </c>
       <c r="BA188" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=022530</v>
       </c>
       <c r="BB188" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_10_tyrnos.pdf</v>
       </c>
       <c r="BC188" t="str">
         <v/>
@@ -40127,10 +40127,10 @@
         <v/>
       </c>
       <c r="BA189" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041876</v>
       </c>
       <c r="BB189" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20EXSENCE_DC_SS.pdf</v>
       </c>
       <c r="BC189" t="str">
         <v/>
@@ -40312,10 +40312,10 @@
         <v/>
       </c>
       <c r="BA190" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041883</v>
       </c>
       <c r="BB190" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20EXSENCE_DC_SS.pdf</v>
       </c>
       <c r="BC190" t="str">
         <v/>
@@ -40497,10 +40497,10 @@
         <v/>
       </c>
       <c r="BA191" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041890</v>
       </c>
       <c r="BB191" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20EXSENCE_DC_SS.pdf</v>
       </c>
       <c r="BC191" t="str">
         <v/>
@@ -40682,10 +40682,10 @@
         <v/>
       </c>
       <c r="BA192" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041906</v>
       </c>
       <c r="BB192" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20EXSENCE_DC_SS.pdf</v>
       </c>
       <c r="BC192" t="str">
         <v/>
@@ -43442,7 +43442,7 @@
         <v/>
       </c>
       <c r="AV207" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW207" t="str">
         <v/>
@@ -43457,10 +43457,10 @@
         <v/>
       </c>
       <c r="BA207" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=038685</v>
       </c>
       <c r="BB207" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_baygame.pdf</v>
       </c>
       <c r="BC207" t="str">
         <v/>
@@ -43627,7 +43627,7 @@
         <v/>
       </c>
       <c r="AV208" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW208" t="str">
         <v/>
@@ -43642,10 +43642,10 @@
         <v/>
       </c>
       <c r="BA208" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=038692</v>
       </c>
       <c r="BB208" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_baygame.pdf</v>
       </c>
       <c r="BC208" t="str">
         <v/>
@@ -43812,7 +43812,7 @@
         <v/>
       </c>
       <c r="AV209" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW209" t="str">
         <v/>
@@ -43827,10 +43827,10 @@
         <v/>
       </c>
       <c r="BA209" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=038708</v>
       </c>
       <c r="BB209" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_baygame.pdf</v>
       </c>
       <c r="BC209" t="str">
         <v/>
@@ -43997,7 +43997,7 @@
         <v/>
       </c>
       <c r="AV210" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW210" t="str">
         <v/>
@@ -44012,10 +44012,10 @@
         <v/>
       </c>
       <c r="BA210" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=038715</v>
       </c>
       <c r="BB210" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_baygame.pdf</v>
       </c>
       <c r="BC210" t="str">
         <v/>
@@ -44182,7 +44182,7 @@
         <v/>
       </c>
       <c r="AV211" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW211" t="str">
         <v/>
@@ -44197,10 +44197,10 @@
         <v/>
       </c>
       <c r="BA211" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041913</v>
       </c>
       <c r="BB211" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20BAYGAME.pdf</v>
       </c>
       <c r="BC211" t="str">
         <v/>
@@ -44367,7 +44367,7 @@
         <v/>
       </c>
       <c r="AV212" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW212" t="str">
         <v/>
@@ -44382,10 +44382,10 @@
         <v/>
       </c>
       <c r="BA212" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041920</v>
       </c>
       <c r="BB212" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20BAYGAME.pdf</v>
       </c>
       <c r="BC212" t="str">
         <v/>
@@ -44552,7 +44552,7 @@
         <v/>
       </c>
       <c r="AV213" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW213" t="str">
         <v/>
@@ -44567,10 +44567,10 @@
         <v/>
       </c>
       <c r="BA213" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=049735</v>
       </c>
       <c r="BB213" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_26grappler_300_q2.pdf</v>
       </c>
       <c r="BC213" t="str">
         <v/>
@@ -44737,7 +44737,7 @@
         <v/>
       </c>
       <c r="AV214" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW214" t="str">
         <v/>
@@ -44922,7 +44922,7 @@
         <v/>
       </c>
       <c r="AV215" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW215" t="str">
         <v/>
@@ -44937,10 +44937,10 @@
         <v/>
       </c>
       <c r="BA215" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=049759</v>
       </c>
       <c r="BB215" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_26grappler_300_q2.pdf</v>
       </c>
       <c r="BC215" t="str">
         <v/>
@@ -45107,7 +45107,7 @@
         <v/>
       </c>
       <c r="AV216" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW216" t="str">
         <v/>
@@ -45292,7 +45292,7 @@
         <v/>
       </c>
       <c r="AV217" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW217" t="str">
         <v/>
@@ -45307,10 +45307,10 @@
         <v/>
       </c>
       <c r="BA217" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048318</v>
       </c>
       <c r="BB217" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25barchetta_fc_q.pdf</v>
       </c>
       <c r="BC217" t="str">
         <v/>
@@ -45477,7 +45477,7 @@
         <v/>
       </c>
       <c r="AV218" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW218" t="str">
         <v/>
@@ -45492,10 +45492,10 @@
         <v/>
       </c>
       <c r="BA218" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048325</v>
       </c>
       <c r="BB218" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25barchetta_fc_q.pdf</v>
       </c>
       <c r="BC218" t="str">
         <v/>
@@ -45662,7 +45662,7 @@
         <v/>
       </c>
       <c r="AV219" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW219" t="str">
         <v/>
@@ -45677,10 +45677,10 @@
         <v/>
       </c>
       <c r="BA219" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048332</v>
       </c>
       <c r="BB219" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25barchetta_fc_q.pdf</v>
       </c>
       <c r="BC219" t="str">
         <v/>
@@ -45847,7 +45847,7 @@
         <v/>
       </c>
       <c r="AV220" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW220" t="str">
         <v/>
@@ -45862,10 +45862,10 @@
         <v/>
       </c>
       <c r="BA220" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048349</v>
       </c>
       <c r="BB220" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25barchetta_fc_q.pdf</v>
       </c>
       <c r="BC220" t="str">
         <v/>
@@ -46032,7 +46032,7 @@
         <v/>
       </c>
       <c r="AV221" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW221" t="str">
         <v/>
@@ -46047,10 +46047,10 @@
         <v/>
       </c>
       <c r="BA221" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048356</v>
       </c>
       <c r="BB221" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25barchetta_fc_q.pdf</v>
       </c>
       <c r="BC221" t="str">
         <v/>
@@ -46217,7 +46217,7 @@
         <v/>
       </c>
       <c r="AV222" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW222" t="str">
         <v/>
@@ -46232,10 +46232,10 @@
         <v/>
       </c>
       <c r="BA222" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048363</v>
       </c>
       <c r="BB222" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25barchetta_fc_q.pdf</v>
       </c>
       <c r="BC222" t="str">
         <v/>
@@ -46402,7 +46402,7 @@
         <v/>
       </c>
       <c r="AV223" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW223" t="str">
         <v/>
@@ -46417,10 +46417,10 @@
         <v/>
       </c>
       <c r="BA223" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=037435</v>
       </c>
       <c r="BB223" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_grappler.pdf</v>
       </c>
       <c r="BC223" t="str">
         <v/>
@@ -46587,7 +46587,7 @@
         <v/>
       </c>
       <c r="AV224" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW224" t="str">
         <v/>
@@ -46602,10 +46602,10 @@
         <v/>
       </c>
       <c r="BA224" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=037442</v>
       </c>
       <c r="BB224" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_grappler.pdf</v>
       </c>
       <c r="BC224" t="str">
         <v/>
@@ -46718,7 +46718,7 @@
         <v/>
       </c>
       <c r="AD225" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE225" t="str">
         <v/>
@@ -46799,7 +46799,7 @@
         <v/>
       </c>
       <c r="BE225" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="BF225" t="str">
         <v/>
@@ -46903,7 +46903,7 @@
         <v/>
       </c>
       <c r="AD226" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE226" t="str">
         <v/>
@@ -46984,7 +46984,7 @@
         <v/>
       </c>
       <c r="BE226" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="BF226" t="str">
         <v/>
@@ -47142,7 +47142,7 @@
         <v/>
       </c>
       <c r="AV227" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW227" t="str">
         <v/>
@@ -47157,10 +47157,10 @@
         <v/>
       </c>
       <c r="BA227" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044686</v>
       </c>
       <c r="BB227" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/22SLX%20DC%20XT_JP%20211124.pdf</v>
       </c>
       <c r="BC227" t="str">
         <v/>
@@ -47327,7 +47327,7 @@
         <v/>
       </c>
       <c r="AV228" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW228" t="str">
         <v/>
@@ -47342,10 +47342,10 @@
         <v/>
       </c>
       <c r="BA228" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044693</v>
       </c>
       <c r="BB228" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/22SLX%20DC%20XT_JP%20211124.pdf</v>
       </c>
       <c r="BC228" t="str">
         <v/>
@@ -47512,7 +47512,7 @@
         <v/>
       </c>
       <c r="AV229" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW229" t="str">
         <v/>
@@ -47527,10 +47527,10 @@
         <v/>
       </c>
       <c r="BA229" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044709</v>
       </c>
       <c r="BB229" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/22SLX%20DC%20XT_JP%20211124.pdf</v>
       </c>
       <c r="BC229" t="str">
         <v/>
@@ -47697,7 +47697,7 @@
         <v/>
       </c>
       <c r="AV230" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW230" t="str">
         <v/>
@@ -47712,10 +47712,10 @@
         <v/>
       </c>
       <c r="BA230" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044716</v>
       </c>
       <c r="BB230" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/22SLX%20DC%20XT_JP%20211124.pdf</v>
       </c>
       <c r="BC230" t="str">
         <v/>
@@ -47882,7 +47882,7 @@
         <v/>
       </c>
       <c r="AV231" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW231" t="str">
         <v/>
@@ -47897,10 +47897,10 @@
         <v/>
       </c>
       <c r="BA231" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044723</v>
       </c>
       <c r="BB231" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/22SLX%20DC%20XT_JP%20211124.pdf</v>
       </c>
       <c r="BC231" t="str">
         <v/>
@@ -48067,7 +48067,7 @@
         <v/>
       </c>
       <c r="AV232" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW232" t="str">
         <v/>
@@ -48082,10 +48082,10 @@
         <v/>
       </c>
       <c r="BA232" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044730</v>
       </c>
       <c r="BB232" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/22SLX%20DC%20XT_JP%20211124.pdf</v>
       </c>
       <c r="BC232" t="str">
         <v/>
@@ -48198,7 +48198,7 @@
         <v/>
       </c>
       <c r="AD233" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE233" t="str">
         <v/>
@@ -48267,10 +48267,10 @@
         <v/>
       </c>
       <c r="BA233" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043061</v>
       </c>
       <c r="BB233" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_scorpion_dc.pdf</v>
       </c>
       <c r="BC233" t="str">
         <v/>
@@ -48383,7 +48383,7 @@
         <v/>
       </c>
       <c r="AD234" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE234" t="str">
         <v/>
@@ -48452,10 +48452,10 @@
         <v/>
       </c>
       <c r="BA234" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043078</v>
       </c>
       <c r="BB234" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_scorpion_dc.pdf</v>
       </c>
       <c r="BC234" t="str">
         <v/>
@@ -48568,7 +48568,7 @@
         <v/>
       </c>
       <c r="AD235" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE235" t="str">
         <v/>
@@ -48637,10 +48637,10 @@
         <v/>
       </c>
       <c r="BA235" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043085</v>
       </c>
       <c r="BB235" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_scorpion_dc.pdf</v>
       </c>
       <c r="BC235" t="str">
         <v/>
@@ -48753,7 +48753,7 @@
         <v/>
       </c>
       <c r="AD236" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE236" t="str">
         <v/>
@@ -48822,10 +48822,10 @@
         <v/>
       </c>
       <c r="BA236" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043092</v>
       </c>
       <c r="BB236" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_scorpion_dc.pdf</v>
       </c>
       <c r="BC236" t="str">
         <v/>
@@ -48938,7 +48938,7 @@
         <v/>
       </c>
       <c r="AD237" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE237" t="str">
         <v/>
@@ -49007,10 +49007,10 @@
         <v/>
       </c>
       <c r="BA237" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043108</v>
       </c>
       <c r="BB237" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_scorpion_dc.pdf</v>
       </c>
       <c r="BC237" t="str">
         <v/>
@@ -49123,7 +49123,7 @@
         <v/>
       </c>
       <c r="AD238" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE238" t="str">
         <v/>
@@ -49192,10 +49192,10 @@
         <v/>
       </c>
       <c r="BA238" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043115</v>
       </c>
       <c r="BB238" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_scorpion_dc.pdf</v>
       </c>
       <c r="BC238" t="str">
         <v/>
@@ -49308,7 +49308,7 @@
         <v/>
       </c>
       <c r="AD239" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE239" t="str">
         <v/>
@@ -49371,16 +49371,16 @@
         <v/>
       </c>
       <c r="AY239" t="str">
-        <v/>
+        <v>CORESOLID BODY</v>
       </c>
       <c r="AZ239" t="str">
         <v/>
       </c>
       <c r="BA239" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047144</v>
       </c>
       <c r="BB239" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24scorpion_md_300_q2.pdf</v>
       </c>
       <c r="BC239" t="str">
         <v/>
@@ -49493,7 +49493,7 @@
         <v/>
       </c>
       <c r="AD240" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE240" t="str">
         <v/>
@@ -49556,16 +49556,16 @@
         <v/>
       </c>
       <c r="AY240" t="str">
-        <v/>
+        <v>CORESOLID BODY</v>
       </c>
       <c r="AZ240" t="str">
         <v/>
       </c>
       <c r="BA240" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047151</v>
       </c>
       <c r="BB240" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24scorpion_md_300_q2.pdf</v>
       </c>
       <c r="BC240" t="str">
         <v/>
@@ -49678,7 +49678,7 @@
         <v/>
       </c>
       <c r="AD241" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE241" t="str">
         <v/>
@@ -49741,16 +49741,16 @@
         <v/>
       </c>
       <c r="AY241" t="str">
-        <v/>
+        <v>CORESOLID BODY</v>
       </c>
       <c r="AZ241" t="str">
         <v/>
       </c>
       <c r="BA241" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047168</v>
       </c>
       <c r="BB241" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24scorpion_md_300_q2.pdf</v>
       </c>
       <c r="BC241" t="str">
         <v/>
@@ -49863,7 +49863,7 @@
         <v/>
       </c>
       <c r="AD242" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE242" t="str">
         <v/>
@@ -49926,16 +49926,16 @@
         <v/>
       </c>
       <c r="AY242" t="str">
-        <v/>
+        <v>CORESOLID BODY</v>
       </c>
       <c r="AZ242" t="str">
         <v/>
       </c>
       <c r="BA242" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=047175</v>
       </c>
       <c r="BB242" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24scorpion_md_300_q2.pdf</v>
       </c>
       <c r="BC242" t="str">
         <v/>
@@ -50102,7 +50102,7 @@
         <v/>
       </c>
       <c r="AV243" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW243" t="str">
         <v/>
@@ -50117,10 +50117,10 @@
         <v/>
       </c>
       <c r="BA243" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043498</v>
       </c>
       <c r="BB243" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_grappler.pdf</v>
       </c>
       <c r="BC243" t="str">
         <v/>
@@ -50287,7 +50287,7 @@
         <v/>
       </c>
       <c r="AV244" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW244" t="str">
         <v/>
@@ -50302,10 +50302,10 @@
         <v/>
       </c>
       <c r="BA244" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=043504</v>
       </c>
       <c r="BB244" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21_grappler.pdf</v>
       </c>
       <c r="BC244" t="str">
         <v/>
@@ -50472,7 +50472,7 @@
         <v/>
       </c>
       <c r="AV245" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW245" t="str">
         <v/>
@@ -50487,10 +50487,10 @@
         <v/>
       </c>
       <c r="BA245" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048837</v>
       </c>
       <c r="BB245" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25grappler_ct_q.pdf</v>
       </c>
       <c r="BC245" t="str">
         <v/>
@@ -50657,7 +50657,7 @@
         <v/>
       </c>
       <c r="AV246" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW246" t="str">
         <v/>
@@ -50672,10 +50672,10 @@
         <v/>
       </c>
       <c r="BA246" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048844</v>
       </c>
       <c r="BB246" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25grappler_ct_q.pdf</v>
       </c>
       <c r="BC246" t="str">
         <v/>
@@ -50788,7 +50788,7 @@
         <v/>
       </c>
       <c r="AD247" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE247" t="str">
         <v/>
@@ -50973,7 +50973,7 @@
         <v/>
       </c>
       <c r="AD248" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE248" t="str">
         <v/>
@@ -51158,7 +51158,7 @@
         <v/>
       </c>
       <c r="AD249" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE249" t="str">
         <v/>
@@ -51343,7 +51343,7 @@
         <v/>
       </c>
       <c r="AD250" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE250" t="str">
         <v/>
@@ -51582,7 +51582,7 @@
         <v/>
       </c>
       <c r="AV251" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW251" t="str">
         <v/>
@@ -51597,10 +51597,10 @@
         <v/>
       </c>
       <c r="BA251" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=021922</v>
       </c>
       <c r="BB251" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_08chinumatic.pdf</v>
       </c>
       <c r="BC251" t="str">
         <v/>
@@ -51767,7 +51767,7 @@
         <v/>
       </c>
       <c r="AV252" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW252" t="str">
         <v/>
@@ -51782,10 +51782,10 @@
         <v/>
       </c>
       <c r="BA252" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=021939</v>
       </c>
       <c r="BB252" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_08chinumatic.pdf</v>
       </c>
       <c r="BC252" t="str">
         <v/>
@@ -51952,7 +51952,7 @@
         <v/>
       </c>
       <c r="AV253" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW253" t="str">
         <v/>
@@ -51967,10 +51967,10 @@
         <v/>
       </c>
       <c r="BA253" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=021946</v>
       </c>
       <c r="BB253" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_08chinumatic.pdf</v>
       </c>
       <c r="BC253" t="str">
         <v/>
@@ -52137,7 +52137,7 @@
         <v/>
       </c>
       <c r="AV254" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW254" t="str">
         <v/>
@@ -52152,10 +52152,10 @@
         <v/>
       </c>
       <c r="BA254" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=021953</v>
       </c>
       <c r="BB254" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_08chinumatic.pdf</v>
       </c>
       <c r="BC254" t="str">
         <v/>
@@ -52322,7 +52322,7 @@
         <v/>
       </c>
       <c r="AV255" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW255" t="str">
         <v/>
@@ -52337,10 +52337,10 @@
         <v/>
       </c>
       <c r="BA255" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=021960</v>
       </c>
       <c r="BB255" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_08chinumatic.pdf</v>
       </c>
       <c r="BC255" t="str">
         <v/>
@@ -52507,7 +52507,7 @@
         <v/>
       </c>
       <c r="AV256" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW256" t="str">
         <v/>
@@ -52522,10 +52522,10 @@
         <v/>
       </c>
       <c r="BA256" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=021977</v>
       </c>
       <c r="BB256" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_08chinumatic.pdf</v>
       </c>
       <c r="BC256" t="str">
         <v/>
@@ -53802,7 +53802,7 @@
         <v/>
       </c>
       <c r="AV263" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW263" t="str">
         <v/>
@@ -53817,10 +53817,10 @@
         <v/>
       </c>
       <c r="BA263" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=037718</v>
       </c>
       <c r="BB263" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_17_stephano_ss.pdf</v>
       </c>
       <c r="BC263" t="str">
         <v/>
@@ -53987,7 +53987,7 @@
         <v/>
       </c>
       <c r="AV264" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW264" t="str">
         <v/>
@@ -54002,10 +54002,10 @@
         <v/>
       </c>
       <c r="BA264" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=037725</v>
       </c>
       <c r="BB264" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_17_stephano_ss.pdf</v>
       </c>
       <c r="BC264" t="str">
         <v/>
@@ -54187,10 +54187,10 @@
         <v/>
       </c>
       <c r="BA265" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036902</v>
       </c>
       <c r="BB265" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_stile_ss.pdf</v>
       </c>
       <c r="BC265" t="str">
         <v/>
@@ -54372,10 +54372,10 @@
         <v/>
       </c>
       <c r="BA266" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036919</v>
       </c>
       <c r="BB266" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_stile_ss.pdf</v>
       </c>
       <c r="BC266" t="str">
         <v/>
@@ -54557,10 +54557,10 @@
         <v/>
       </c>
       <c r="BA267" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036926</v>
       </c>
       <c r="BB267" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_stile_ss.pdf</v>
       </c>
       <c r="BC267" t="str">
         <v/>
@@ -54742,10 +54742,10 @@
         <v/>
       </c>
       <c r="BA268" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=036933</v>
       </c>
       <c r="BB268" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_stile_ss.pdf</v>
       </c>
       <c r="BC268" t="str">
         <v/>
@@ -54858,7 +54858,7 @@
         <v/>
       </c>
       <c r="AD269" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE269" t="str">
         <v/>
@@ -54927,10 +54927,10 @@
         <v/>
       </c>
       <c r="BA269" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046895</v>
       </c>
       <c r="BB269" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24scorpion_md_200_q.pdf</v>
       </c>
       <c r="BC269" t="str">
         <v/>
@@ -54939,7 +54939,7 @@
         <v/>
       </c>
       <c r="BE269" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="BF269" t="str">
         <v/>
@@ -55043,7 +55043,7 @@
         <v/>
       </c>
       <c r="AD270" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE270" t="str">
         <v/>
@@ -55112,10 +55112,10 @@
         <v/>
       </c>
       <c r="BA270" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046901</v>
       </c>
       <c r="BB270" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24scorpion_md_200_q.pdf</v>
       </c>
       <c r="BC270" t="str">
         <v/>
@@ -55124,7 +55124,7 @@
         <v/>
       </c>
       <c r="BE270" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="BF270" t="str">
         <v/>
@@ -55228,7 +55228,7 @@
         <v/>
       </c>
       <c r="AD271" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE271" t="str">
         <v/>
@@ -55297,10 +55297,10 @@
         <v/>
       </c>
       <c r="BA271" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046918</v>
       </c>
       <c r="BB271" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24scorpion_md_200_q.pdf</v>
       </c>
       <c r="BC271" t="str">
         <v/>
@@ -55309,7 +55309,7 @@
         <v/>
       </c>
       <c r="BE271" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="BF271" t="str">
         <v/>
@@ -55413,7 +55413,7 @@
         <v/>
       </c>
       <c r="AD272" t="str">
-        <v/>
+        <v>Aluminum alloy</v>
       </c>
       <c r="AE272" t="str">
         <v/>
@@ -55482,10 +55482,10 @@
         <v/>
       </c>
       <c r="BA272" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=046925</v>
       </c>
       <c r="BB272" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_24scorpion_md_200_q.pdf</v>
       </c>
       <c r="BC272" t="str">
         <v/>
@@ -55494,7 +55494,7 @@
         <v/>
       </c>
       <c r="BE272" t="str">
-        <v/>
+        <v>Brass</v>
       </c>
       <c r="BF272" t="str">
         <v/>
@@ -55652,7 +55652,7 @@
         <v/>
       </c>
       <c r="AV273" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW273" t="str">
         <v/>
@@ -55667,10 +55667,10 @@
         <v/>
       </c>
       <c r="BA273" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042187</v>
       </c>
       <c r="BB273" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20TORIUM_.pdf</v>
       </c>
       <c r="BC273" t="str">
         <v/>
@@ -55837,7 +55837,7 @@
         <v/>
       </c>
       <c r="AV274" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW274" t="str">
         <v/>
@@ -55852,10 +55852,10 @@
         <v/>
       </c>
       <c r="BA274" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042194</v>
       </c>
       <c r="BB274" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20TORIUM_.pdf</v>
       </c>
       <c r="BC274" t="str">
         <v/>
@@ -56022,7 +56022,7 @@
         <v/>
       </c>
       <c r="AV275" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW275" t="str">
         <v/>
@@ -56037,10 +56037,10 @@
         <v/>
       </c>
       <c r="BA275" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042200</v>
       </c>
       <c r="BB275" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20TORIUM_.pdf</v>
       </c>
       <c r="BC275" t="str">
         <v/>
@@ -57687,7 +57687,7 @@
         <v/>
       </c>
       <c r="AV284" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW284" t="str">
         <v/>
@@ -57702,10 +57702,10 @@
         <v/>
       </c>
       <c r="BA284" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042682</v>
       </c>
       <c r="BB284" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_q.pdf</v>
       </c>
       <c r="BC284" t="str">
         <v/>
@@ -57872,7 +57872,7 @@
         <v/>
       </c>
       <c r="AV285" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW285" t="str">
         <v/>
@@ -57887,10 +57887,10 @@
         <v/>
       </c>
       <c r="BA285" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042699</v>
       </c>
       <c r="BB285" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_q.pdf</v>
       </c>
       <c r="BC285" t="str">
         <v/>
@@ -58057,7 +58057,7 @@
         <v/>
       </c>
       <c r="AV286" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW286" t="str">
         <v/>
@@ -58072,10 +58072,10 @@
         <v/>
       </c>
       <c r="BA286" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042705</v>
       </c>
       <c r="BB286" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_q.pdf</v>
       </c>
       <c r="BC286" t="str">
         <v/>
@@ -58242,7 +58242,7 @@
         <v/>
       </c>
       <c r="AV287" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW287" t="str">
         <v/>
@@ -58257,10 +58257,10 @@
         <v/>
       </c>
       <c r="BA287" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042712</v>
       </c>
       <c r="BB287" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_q.pdf</v>
       </c>
       <c r="BC287" t="str">
         <v/>
@@ -58427,7 +58427,7 @@
         <v/>
       </c>
       <c r="AV288" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW288" t="str">
         <v/>
@@ -58442,10 +58442,10 @@
         <v/>
       </c>
       <c r="BA288" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042729</v>
       </c>
       <c r="BB288" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_q.pdf</v>
       </c>
       <c r="BC288" t="str">
         <v/>
@@ -58612,7 +58612,7 @@
         <v/>
       </c>
       <c r="AV289" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW289" t="str">
         <v/>
@@ -58627,10 +58627,10 @@
         <v/>
       </c>
       <c r="BA289" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042736</v>
       </c>
       <c r="BB289" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_q.pdf</v>
       </c>
       <c r="BC289" t="str">
         <v/>
@@ -58797,7 +58797,7 @@
         <v/>
       </c>
       <c r="AV290" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW290" t="str">
         <v/>
@@ -58812,10 +58812,10 @@
         <v/>
       </c>
       <c r="BA290" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042743</v>
       </c>
       <c r="BB290" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_q.pdf</v>
       </c>
       <c r="BC290" t="str">
         <v/>
@@ -58982,7 +58982,7 @@
         <v/>
       </c>
       <c r="AV291" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW291" t="str">
         <v/>
@@ -58997,10 +58997,10 @@
         <v/>
       </c>
       <c r="BA291" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042750</v>
       </c>
       <c r="BB291" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_q.pdf</v>
       </c>
       <c r="BC291" t="str">
         <v/>
@@ -59167,7 +59167,7 @@
         <v/>
       </c>
       <c r="AV292" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW292" t="str">
         <v/>
@@ -59182,10 +59182,10 @@
         <v/>
       </c>
       <c r="BA292" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042767</v>
       </c>
       <c r="BB292" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_q.pdf</v>
       </c>
       <c r="BC292" t="str">
         <v/>
@@ -59352,7 +59352,7 @@
         <v/>
       </c>
       <c r="AV293" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW293" t="str">
         <v/>
@@ -59367,10 +59367,10 @@
         <v/>
       </c>
       <c r="BA293" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042774</v>
       </c>
       <c r="BB293" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_q.pdf</v>
       </c>
       <c r="BC293" t="str">
         <v/>
@@ -59537,7 +59537,7 @@
         <v/>
       </c>
       <c r="AV294" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW294" t="str">
         <v/>
@@ -59552,10 +59552,10 @@
         <v/>
       </c>
       <c r="BA294" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=039255</v>
       </c>
       <c r="BB294" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_barchtta_sc.pdf</v>
       </c>
       <c r="BC294" t="str">
         <v/>
@@ -59722,7 +59722,7 @@
         <v/>
       </c>
       <c r="AV295" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW295" t="str">
         <v/>
@@ -59737,10 +59737,10 @@
         <v/>
       </c>
       <c r="BA295" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=039262</v>
       </c>
       <c r="BB295" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_barchtta_sc.pdf</v>
       </c>
       <c r="BC295" t="str">
         <v/>
@@ -59907,7 +59907,7 @@
         <v/>
       </c>
       <c r="AV296" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW296" t="str">
         <v/>
@@ -59922,10 +59922,10 @@
         <v/>
       </c>
       <c r="BA296" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=039279</v>
       </c>
       <c r="BB296" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_barchtta_sc.pdf</v>
       </c>
       <c r="BC296" t="str">
         <v/>
@@ -60092,7 +60092,7 @@
         <v/>
       </c>
       <c r="AV297" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW297" t="str">
         <v/>
@@ -60107,10 +60107,10 @@
         <v/>
       </c>
       <c r="BA297" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=039286</v>
       </c>
       <c r="BB297" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_barchtta_sc.pdf</v>
       </c>
       <c r="BC297" t="str">
         <v/>
@@ -60292,10 +60292,10 @@
         <v/>
       </c>
       <c r="BA298" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045607</v>
       </c>
       <c r="BB298" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23SLX%20DC.pdf</v>
       </c>
       <c r="BC298" t="str">
         <v/>
@@ -60477,10 +60477,10 @@
         <v/>
       </c>
       <c r="BA299" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045614</v>
       </c>
       <c r="BB299" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23SLX%20DC.pdf</v>
       </c>
       <c r="BC299" t="str">
         <v/>
@@ -60662,10 +60662,10 @@
         <v/>
       </c>
       <c r="BA300" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045621</v>
       </c>
       <c r="BB300" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23SLX%20DC.pdf</v>
       </c>
       <c r="BC300" t="str">
         <v/>
@@ -60847,10 +60847,10 @@
         <v/>
       </c>
       <c r="BA301" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045638</v>
       </c>
       <c r="BB301" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23SLX%20DC.pdf</v>
       </c>
       <c r="BC301" t="str">
         <v/>
@@ -61032,10 +61032,10 @@
         <v/>
       </c>
       <c r="BA302" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045645</v>
       </c>
       <c r="BB302" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23SLX%20DC.pdf</v>
       </c>
       <c r="BC302" t="str">
         <v/>
@@ -61217,10 +61217,10 @@
         <v/>
       </c>
       <c r="BA303" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=045652</v>
       </c>
       <c r="BB303" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_23SLX%20DC.pdf</v>
       </c>
       <c r="BC303" t="str">
         <v/>
@@ -67677,7 +67677,7 @@
         <v/>
       </c>
       <c r="AV338" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW338" t="str">
         <v/>
@@ -67692,10 +67692,10 @@
         <v/>
       </c>
       <c r="BA338" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044037</v>
       </c>
       <c r="BB338" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_bb_q.pdf</v>
       </c>
       <c r="BC338" t="str">
         <v/>
@@ -67862,7 +67862,7 @@
         <v/>
       </c>
       <c r="AV339" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW339" t="str">
         <v/>
@@ -67877,10 +67877,10 @@
         <v/>
       </c>
       <c r="BA339" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044044</v>
       </c>
       <c r="BB339" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_bb_q.pdf</v>
       </c>
       <c r="BC339" t="str">
         <v/>
@@ -68047,7 +68047,7 @@
         <v/>
       </c>
       <c r="AV340" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW340" t="str">
         <v/>
@@ -68062,10 +68062,10 @@
         <v/>
       </c>
       <c r="BA340" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044051</v>
       </c>
       <c r="BB340" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_bb_q.pdf</v>
       </c>
       <c r="BC340" t="str">
         <v/>
@@ -68232,7 +68232,7 @@
         <v/>
       </c>
       <c r="AV341" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW341" t="str">
         <v/>
@@ -68247,10 +68247,10 @@
         <v/>
       </c>
       <c r="BA341" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044068</v>
       </c>
       <c r="BB341" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_bb_q.pdf</v>
       </c>
       <c r="BC341" t="str">
         <v/>
@@ -68417,7 +68417,7 @@
         <v/>
       </c>
       <c r="AV342" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW342" t="str">
         <v/>
@@ -68432,10 +68432,10 @@
         <v/>
       </c>
       <c r="BA342" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044075</v>
       </c>
       <c r="BB342" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_bb_q.pdf</v>
       </c>
       <c r="BC342" t="str">
         <v/>
@@ -68602,7 +68602,7 @@
         <v/>
       </c>
       <c r="AV343" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW343" t="str">
         <v/>
@@ -68617,10 +68617,10 @@
         <v/>
       </c>
       <c r="BA343" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044082</v>
       </c>
       <c r="BB343" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_bb_q.pdf</v>
       </c>
       <c r="BC343" t="str">
         <v/>
@@ -68787,7 +68787,7 @@
         <v/>
       </c>
       <c r="AV344" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW344" t="str">
         <v/>
@@ -68802,10 +68802,10 @@
         <v/>
       </c>
       <c r="BA344" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044099</v>
       </c>
       <c r="BB344" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_bb_q.pdf</v>
       </c>
       <c r="BC344" t="str">
         <v/>
@@ -68972,7 +68972,7 @@
         <v/>
       </c>
       <c r="AV345" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW345" t="str">
         <v/>
@@ -68987,10 +68987,10 @@
         <v/>
       </c>
       <c r="BA345" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044105</v>
       </c>
       <c r="BB345" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_21barchetta_bb_q.pdf</v>
       </c>
       <c r="BC345" t="str">
         <v/>
@@ -69172,10 +69172,10 @@
         <v/>
       </c>
       <c r="BA346" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048189</v>
       </c>
       <c r="BB346" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25slx_bfs_q.pdf</v>
       </c>
       <c r="BC346" t="str">
         <v/>
@@ -69357,10 +69357,10 @@
         <v/>
       </c>
       <c r="BA347" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=048196</v>
       </c>
       <c r="BB347" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_25slx_bfs_q.pdf</v>
       </c>
       <c r="BC347" t="str">
         <v/>
@@ -69527,7 +69527,7 @@
         <v/>
       </c>
       <c r="AV348" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW348" t="str">
         <v/>
@@ -69542,10 +69542,10 @@
         <v/>
       </c>
       <c r="BA348" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044983</v>
       </c>
       <c r="BB348" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_grappler_bb_2022.pdf</v>
       </c>
       <c r="BC348" t="str">
         <v/>
@@ -69712,7 +69712,7 @@
         <v/>
       </c>
       <c r="AV349" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW349" t="str">
         <v/>
@@ -69727,10 +69727,10 @@
         <v/>
       </c>
       <c r="BA349" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=044990</v>
       </c>
       <c r="BB349" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_22_grappler_bb_2022.pdf</v>
       </c>
       <c r="BC349" t="str">
         <v/>
@@ -72117,7 +72117,7 @@
         <v/>
       </c>
       <c r="AV362" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW362" t="str">
         <v/>
@@ -72132,10 +72132,10 @@
         <v/>
       </c>
       <c r="BA362" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=039293</v>
       </c>
       <c r="BB362" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_kobune.pdf</v>
       </c>
       <c r="BC362" t="str">
         <v/>
@@ -72302,7 +72302,7 @@
         <v/>
       </c>
       <c r="AV363" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW363" t="str">
         <v/>
@@ -72317,10 +72317,10 @@
         <v/>
       </c>
       <c r="BA363" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=039309</v>
       </c>
       <c r="BB363" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_kobune.pdf</v>
       </c>
       <c r="BC363" t="str">
         <v/>
@@ -72487,7 +72487,7 @@
         <v/>
       </c>
       <c r="AV364" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW364" t="str">
         <v/>
@@ -72502,10 +72502,10 @@
         <v/>
       </c>
       <c r="BA364" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=039316</v>
       </c>
       <c r="BB364" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_kobune.pdf</v>
       </c>
       <c r="BC364" t="str">
         <v/>
@@ -72672,7 +72672,7 @@
         <v/>
       </c>
       <c r="AV365" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW365" t="str">
         <v/>
@@ -72687,10 +72687,10 @@
         <v/>
       </c>
       <c r="BA365" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=039323</v>
       </c>
       <c r="BB365" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_18_kobune.pdf</v>
       </c>
       <c r="BC365" t="str">
         <v/>
@@ -72857,7 +72857,7 @@
         <v/>
       </c>
       <c r="AV366" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW366" t="str">
         <v/>
@@ -73042,7 +73042,7 @@
         <v/>
       </c>
       <c r="AV367" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW367" t="str">
         <v/>
@@ -73227,7 +73227,7 @@
         <v/>
       </c>
       <c r="AV368" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW368" t="str">
         <v/>
@@ -73412,7 +73412,7 @@
         <v/>
       </c>
       <c r="AV369" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW369" t="str">
         <v/>
@@ -73597,7 +73597,7 @@
         <v/>
       </c>
       <c r="AV370" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW370" t="str">
         <v/>
@@ -73782,7 +73782,7 @@
         <v/>
       </c>
       <c r="AV371" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW371" t="str">
         <v/>
@@ -73967,7 +73967,7 @@
         <v/>
       </c>
       <c r="AV372" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW372" t="str">
         <v/>
@@ -73982,10 +73982,10 @@
         <v/>
       </c>
       <c r="BA372" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041937</v>
       </c>
       <c r="BB372" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20GENPU_XT.pdf</v>
       </c>
       <c r="BC372" t="str">
         <v/>
@@ -74152,7 +74152,7 @@
         <v/>
       </c>
       <c r="AV373" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW373" t="str">
         <v/>
@@ -74167,10 +74167,10 @@
         <v/>
       </c>
       <c r="BA373" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041944</v>
       </c>
       <c r="BB373" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20GENPU_XT.pdf</v>
       </c>
       <c r="BC373" t="str">
         <v/>
@@ -74337,7 +74337,7 @@
         <v/>
       </c>
       <c r="AV374" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW374" t="str">
         <v/>
@@ -74352,10 +74352,10 @@
         <v/>
       </c>
       <c r="BA374" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041951</v>
       </c>
       <c r="BB374" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20GENPU_XT.pdf</v>
       </c>
       <c r="BC374" t="str">
         <v/>
@@ -74522,7 +74522,7 @@
         <v/>
       </c>
       <c r="AV375" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW375" t="str">
         <v/>
@@ -74537,10 +74537,10 @@
         <v/>
       </c>
       <c r="BA375" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=041968</v>
       </c>
       <c r="BB375" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20GENPU_XT.pdf</v>
       </c>
       <c r="BC375" t="str">
         <v/>
@@ -74707,7 +74707,7 @@
         <v/>
       </c>
       <c r="AV376" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW376" t="str">
         <v/>
@@ -74892,7 +74892,7 @@
         <v/>
       </c>
       <c r="AV377" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW377" t="str">
         <v/>
@@ -75092,10 +75092,10 @@
         <v/>
       </c>
       <c r="BA378" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=037312</v>
       </c>
       <c r="BB378" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_bass_one_xt.pdf</v>
       </c>
       <c r="BC378" t="str">
         <v/>
@@ -75277,10 +75277,10 @@
         <v/>
       </c>
       <c r="BA379" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=037329</v>
       </c>
       <c r="BB379" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_bass_one_xt.pdf</v>
       </c>
       <c r="BC379" t="str">
         <v/>
@@ -75832,10 +75832,10 @@
         <v/>
       </c>
       <c r="BA382" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=038869</v>
       </c>
       <c r="BB382" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/18BASSRISE_180117.pdf</v>
       </c>
       <c r="BC382" t="str">
         <v/>
@@ -76017,10 +76017,10 @@
         <v/>
       </c>
       <c r="BA383" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=038876</v>
       </c>
       <c r="BB383" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/18BASSRISE_180117.pdf</v>
       </c>
       <c r="BC383" t="str">
         <v/>
@@ -76187,7 +76187,7 @@
         <v/>
       </c>
       <c r="AV384" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW384" t="str">
         <v/>
@@ -76202,10 +76202,10 @@
         <v/>
       </c>
       <c r="BA384" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042163</v>
       </c>
       <c r="BB384" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20_genpu.pdf</v>
       </c>
       <c r="BC384" t="str">
         <v/>
@@ -76372,7 +76372,7 @@
         <v/>
       </c>
       <c r="AV385" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW385" t="str">
         <v/>
@@ -76387,10 +76387,10 @@
         <v/>
       </c>
       <c r="BA385" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=042170</v>
       </c>
       <c r="BB385" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_20_genpu.pdf</v>
       </c>
       <c r="BC385" t="str">
         <v/>
@@ -76557,7 +76557,7 @@
         <v/>
       </c>
       <c r="AV386" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW386" t="str">
         <v/>
@@ -76572,10 +76572,10 @@
         <v/>
       </c>
       <c r="BA386" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=011657</v>
       </c>
       <c r="BB386" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_94_chinu-special%20(1).pdf</v>
       </c>
       <c r="BC386" t="str">
         <v/>
@@ -76742,7 +76742,7 @@
         <v/>
       </c>
       <c r="AV387" t="str">
-        <v>baitcasting</v>
+        <v>drum</v>
       </c>
       <c r="AW387" t="str">
         <v/>
@@ -76757,10 +76757,10 @@
         <v/>
       </c>
       <c r="BA387" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/parts_price.php?scode=011664</v>
       </c>
       <c r="BB387" t="str">
-        <v/>
+        <v>https://www.shimanofishingservice.jp/img/product/manual/manual_94_chinu-special%20(1).pdf</v>
       </c>
       <c r="BC387" t="str">
         <v/>

--- a/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/shimano_baitcasting_reels_import.xlsx
@@ -12565,7 +12565,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <dimension ref="A1:BI387"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
@@ -12762,8 +12762,10 @@
       <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
-        <v>630</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="D2" t="s">
         <v>631</v>
@@ -12842,8 +12844,10 @@
       <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" t="s">
-        <v>651</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>20A</t>
+        </is>
       </c>
       <c r="D3" t="s">
         <v>631</v>
@@ -12922,8 +12926,10 @@
       <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
-        <v>667</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>30A</t>
+        </is>
       </c>
       <c r="D4" t="s">
         <v>631</v>
@@ -13002,8 +13008,10 @@
       <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
-        <v>679</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30W LRSA</t>
+        </is>
       </c>
       <c r="D5" t="s">
         <v>631</v>
@@ -13082,8 +13090,10 @@
       <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
-        <v>689</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>50A</t>
+        </is>
       </c>
       <c r="D6" t="s">
         <v>690</v>
@@ -13162,8 +13172,10 @@
       <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
-        <v>701</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>50WA</t>
+        </is>
       </c>
       <c r="D7" t="s">
         <v>690</v>
@@ -13242,8 +13254,10 @@
       <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
-        <v>710</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>50W LRSA</t>
+        </is>
       </c>
       <c r="D8" t="s">
         <v>690</v>
@@ -13322,8 +13336,10 @@
       <c r="B9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" t="s">
-        <v>715</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>80WA</t>
+        </is>
       </c>
       <c r="D9" t="s">
         <v>716</v>
@@ -13402,8 +13418,10 @@
       <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
-        <v>728</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>130A</t>
+        </is>
       </c>
       <c r="D10" t="s">
         <v>729</v>
@@ -13482,8 +13500,10 @@
       <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" t="s">
-        <v>742</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20Ⅱ</t>
+        </is>
       </c>
       <c r="D11" t="s">
         <v>743</v>
@@ -13562,8 +13582,10 @@
       <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
-        <v>757</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>25 II</t>
+        </is>
       </c>
       <c r="D12" t="s">
         <v>743</v>
@@ -13642,8 +13664,10 @@
       <c r="B13" t="s">
         <v>34</v>
       </c>
-      <c r="C13" t="s">
-        <v>767</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>50 II</t>
+        </is>
       </c>
       <c r="D13" t="s">
         <v>768</v>
@@ -13722,8 +13746,10 @@
       <c r="B14" t="s">
         <v>34</v>
       </c>
-      <c r="C14" t="s">
-        <v>782</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12II</t>
+        </is>
       </c>
       <c r="D14" t="s">
         <v>783</v>
@@ -13793,8 +13819,10 @@
       <c r="B15" t="s">
         <v>34</v>
       </c>
-      <c r="C15" t="s">
-        <v>795</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16II</t>
+        </is>
       </c>
       <c r="D15" t="s">
         <v>783</v>
@@ -13864,8 +13892,10 @@
       <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="C16" t="s">
-        <v>803</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20II</t>
+        </is>
       </c>
       <c r="D16" t="s">
         <v>743</v>
@@ -13935,8 +13965,10 @@
       <c r="B17" t="s">
         <v>34</v>
       </c>
-      <c r="C17" t="s">
-        <v>812</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>25II</t>
+        </is>
       </c>
       <c r="D17" t="s">
         <v>743</v>
@@ -14006,8 +14038,10 @@
       <c r="B18" t="s">
         <v>34</v>
       </c>
-      <c r="C18" t="s">
-        <v>818</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>40II</t>
+        </is>
       </c>
       <c r="D18" t="s">
         <v>819</v>
@@ -14077,8 +14111,10 @@
       <c r="B19" t="s">
         <v>34</v>
       </c>
-      <c r="C19" t="s">
-        <v>829</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>50II</t>
+        </is>
       </c>
       <c r="D19" t="s">
         <v>819</v>
@@ -14148,8 +14184,10 @@
       <c r="B20" t="s">
         <v>42</v>
       </c>
-      <c r="C20" t="s">
-        <v>835</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>XG R</t>
+        </is>
       </c>
       <c r="D20" t="s">
         <v>836</v>
@@ -14261,8 +14299,10 @@
       <c r="B21" t="s">
         <v>42</v>
       </c>
-      <c r="C21" t="s">
-        <v>864</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>XG L</t>
+        </is>
       </c>
       <c r="D21" t="s">
         <v>836</v>
@@ -14374,8 +14414,10 @@
       <c r="B22" t="s">
         <v>57</v>
       </c>
-      <c r="C22" t="s">
-        <v>868</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
       </c>
       <c r="D22" t="s">
         <v>869</v>
@@ -14469,8 +14511,10 @@
       <c r="B23" t="s">
         <v>57</v>
       </c>
-      <c r="C23" t="s">
-        <v>881</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="D23" t="s">
         <v>869</v>
@@ -14564,8 +14608,10 @@
       <c r="B24" t="s">
         <v>57</v>
       </c>
-      <c r="C24" t="s">
-        <v>885</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HG R</t>
+        </is>
       </c>
       <c r="D24" t="s">
         <v>886</v>
@@ -14659,8 +14705,10 @@
       <c r="B25" t="s">
         <v>57</v>
       </c>
-      <c r="C25" t="s">
-        <v>891</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HG L</t>
+        </is>
       </c>
       <c r="D25" t="s">
         <v>886</v>
@@ -14754,8 +14802,10 @@
       <c r="B26" t="s">
         <v>57</v>
       </c>
-      <c r="C26" t="s">
-        <v>895</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>XG R</t>
+        </is>
       </c>
       <c r="D26" t="s">
         <v>836</v>
@@ -14849,8 +14899,10 @@
       <c r="B27" t="s">
         <v>57</v>
       </c>
-      <c r="C27" t="s">
-        <v>900</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>XG L</t>
+        </is>
       </c>
       <c r="D27" t="s">
         <v>836</v>
@@ -14944,8 +14996,10 @@
       <c r="B28" t="s">
         <v>68</v>
       </c>
-      <c r="C28" t="s">
-        <v>904</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
       </c>
       <c r="D28" t="s">
         <v>905</v>
@@ -15024,8 +15078,10 @@
       <c r="B29" t="s">
         <v>68</v>
       </c>
-      <c r="C29" t="s">
-        <v>922</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4000HG</t>
+        </is>
       </c>
       <c r="D29" t="s">
         <v>923</v>
@@ -15104,8 +15160,10 @@
       <c r="B30" t="s">
         <v>74</v>
       </c>
-      <c r="C30" t="s">
-        <v>928</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="D30" t="s">
         <v>929</v>
@@ -15199,8 +15257,10 @@
       <c r="B31" t="s">
         <v>74</v>
       </c>
-      <c r="C31" t="s">
-        <v>946</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="D31" t="s">
         <v>929</v>
@@ -15294,8 +15354,10 @@
       <c r="B32" t="s">
         <v>74</v>
       </c>
-      <c r="C32" t="s">
-        <v>950</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="D32" t="s">
         <v>869</v>
@@ -15389,8 +15451,10 @@
       <c r="B33" t="s">
         <v>74</v>
       </c>
-      <c r="C33" t="s">
-        <v>962</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="D33" t="s">
         <v>869</v>
@@ -15484,8 +15548,10 @@
       <c r="B34" t="s">
         <v>74</v>
       </c>
-      <c r="C34" t="s">
-        <v>967</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>100HG</t>
+        </is>
       </c>
       <c r="D34" t="s">
         <v>968</v>
@@ -15579,8 +15645,10 @@
       <c r="B35" t="s">
         <v>74</v>
       </c>
-      <c r="C35" t="s">
-        <v>972</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>101HG</t>
+        </is>
       </c>
       <c r="D35" t="s">
         <v>968</v>
@@ -15674,8 +15742,10 @@
       <c r="B36" t="s">
         <v>74</v>
       </c>
-      <c r="C36" t="s">
-        <v>976</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>200HG</t>
+        </is>
       </c>
       <c r="D36" t="s">
         <v>977</v>
@@ -15769,8 +15839,10 @@
       <c r="B37" t="s">
         <v>74</v>
       </c>
-      <c r="C37" t="s">
-        <v>982</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>201HG</t>
+        </is>
       </c>
       <c r="D37" t="s">
         <v>977</v>
@@ -15864,8 +15936,10 @@
       <c r="B38" t="s">
         <v>74</v>
       </c>
-      <c r="C38" t="s">
-        <v>986</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>100MG</t>
+        </is>
       </c>
       <c r="D38" t="s">
         <v>869</v>
@@ -15959,8 +16033,10 @@
       <c r="B39" t="s">
         <v>74</v>
       </c>
-      <c r="C39" t="s">
-        <v>998</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>101MG</t>
+        </is>
       </c>
       <c r="D39" t="s">
         <v>869</v>
@@ -16054,8 +16130,10 @@
       <c r="B40" t="s">
         <v>74</v>
       </c>
-      <c r="C40" t="s">
-        <v>1002</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>200PG</t>
+        </is>
       </c>
       <c r="D40" t="s">
         <v>929</v>
@@ -16149,8 +16227,10 @@
       <c r="B41" t="s">
         <v>74</v>
       </c>
-      <c r="C41" t="s">
-        <v>1009</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>200XG</t>
+        </is>
       </c>
       <c r="D41" t="s">
         <v>1010</v>
@@ -16244,8 +16324,10 @@
       <c r="B42" t="s">
         <v>82</v>
       </c>
-      <c r="C42" t="s">
-        <v>1014</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2500MG</t>
+        </is>
       </c>
       <c r="D42" t="s">
         <v>783</v>
@@ -16324,8 +16406,10 @@
       <c r="B43" t="s">
         <v>82</v>
       </c>
-      <c r="C43" t="s">
-        <v>1027</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2500HG</t>
+        </is>
       </c>
       <c r="D43" t="s">
         <v>977</v>
@@ -16404,8 +16488,10 @@
       <c r="B44" t="s">
         <v>82</v>
       </c>
-      <c r="C44" t="s">
-        <v>1031</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2501MG</t>
+        </is>
       </c>
       <c r="D44" t="s">
         <v>783</v>
@@ -16484,8 +16570,10 @@
       <c r="B45" t="s">
         <v>82</v>
       </c>
-      <c r="C45" t="s">
-        <v>1036</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2501HG</t>
+        </is>
       </c>
       <c r="D45" t="s">
         <v>977</v>
@@ -16564,8 +16652,10 @@
       <c r="B46" t="s">
         <v>88</v>
       </c>
-      <c r="C46" t="s">
-        <v>1040</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1000HG</t>
+        </is>
       </c>
       <c r="D46" t="s">
         <v>1041</v>
@@ -16644,8 +16734,10 @@
       <c r="B47" t="s">
         <v>88</v>
       </c>
-      <c r="C47" t="s">
-        <v>1054</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1001HG</t>
+        </is>
       </c>
       <c r="D47" t="s">
         <v>1041</v>
@@ -16724,8 +16816,10 @@
       <c r="B48" t="s">
         <v>88</v>
       </c>
-      <c r="C48" t="s">
-        <v>1058</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1500HG</t>
+        </is>
       </c>
       <c r="D48" t="s">
         <v>1041</v>
@@ -16804,8 +16898,10 @@
       <c r="B49" t="s">
         <v>88</v>
       </c>
-      <c r="C49" t="s">
-        <v>1066</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1501HG</t>
+        </is>
       </c>
       <c r="D49" t="s">
         <v>1041</v>
@@ -16884,8 +16980,10 @@
       <c r="B50" t="s">
         <v>88</v>
       </c>
-      <c r="C50" t="s">
-        <v>1070</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2000NRHG</t>
+        </is>
       </c>
       <c r="D50" t="s">
         <v>977</v>
@@ -16964,8 +17062,10 @@
       <c r="B51" t="s">
         <v>88</v>
       </c>
-      <c r="C51" t="s">
-        <v>1081</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2001NRHG</t>
+        </is>
       </c>
       <c r="D51" t="s">
         <v>977</v>
@@ -17044,8 +17144,10 @@
       <c r="B52" t="s">
         <v>88</v>
       </c>
-      <c r="C52" t="s">
-        <v>1085</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3000HG</t>
+        </is>
       </c>
       <c r="D52" t="s">
         <v>977</v>
@@ -17124,8 +17226,10 @@
       <c r="B53" t="s">
         <v>94</v>
       </c>
-      <c r="C53" t="s">
-        <v>1094</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>300XG</t>
+        </is>
       </c>
       <c r="D53" t="s">
         <v>1010</v>
@@ -17207,8 +17311,10 @@
       <c r="B54" t="s">
         <v>94</v>
       </c>
-      <c r="C54" t="s">
-        <v>1108</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>301XG</t>
+        </is>
       </c>
       <c r="D54" t="s">
         <v>1010</v>
@@ -17290,8 +17396,10 @@
       <c r="B55" t="s">
         <v>94</v>
       </c>
-      <c r="C55" t="s">
-        <v>1112</v>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>300PG</t>
+        </is>
       </c>
       <c r="D55" t="s">
         <v>929</v>
@@ -17373,8 +17481,10 @@
       <c r="B56" t="s">
         <v>94</v>
       </c>
-      <c r="C56" t="s">
-        <v>1118</v>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>300MG</t>
+        </is>
       </c>
       <c r="D56" t="s">
         <v>1119</v>
@@ -17456,8 +17566,10 @@
       <c r="B57" t="s">
         <v>94</v>
       </c>
-      <c r="C57" t="s">
-        <v>1124</v>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>301MG</t>
+        </is>
       </c>
       <c r="D57" t="s">
         <v>1119</v>
@@ -17539,8 +17651,10 @@
       <c r="B58" t="s">
         <v>94</v>
       </c>
-      <c r="C58" t="s">
-        <v>1128</v>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>300HG</t>
+        </is>
       </c>
       <c r="D58" t="s">
         <v>977</v>
@@ -17622,8 +17736,10 @@
       <c r="B59" t="s">
         <v>94</v>
       </c>
-      <c r="C59" t="s">
-        <v>1133</v>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>301HG</t>
+        </is>
       </c>
       <c r="D59" t="s">
         <v>977</v>
@@ -17705,8 +17821,10 @@
       <c r="B60" t="s">
         <v>94</v>
       </c>
-      <c r="C60" t="s">
-        <v>1137</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>200PG</t>
+        </is>
       </c>
       <c r="D60" t="s">
         <v>929</v>
@@ -17788,8 +17906,10 @@
       <c r="B61" t="s">
         <v>94</v>
       </c>
-      <c r="C61" t="s">
-        <v>1149</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>201PG</t>
+        </is>
       </c>
       <c r="D61" t="s">
         <v>929</v>
@@ -17871,8 +17991,10 @@
       <c r="B62" t="s">
         <v>94</v>
       </c>
-      <c r="C62" t="s">
-        <v>1153</v>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>200MG</t>
+        </is>
       </c>
       <c r="D62" t="s">
         <v>1119</v>
@@ -17954,8 +18076,10 @@
       <c r="B63" t="s">
         <v>94</v>
       </c>
-      <c r="C63" t="s">
-        <v>1159</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>201MG</t>
+        </is>
       </c>
       <c r="D63" t="s">
         <v>1119</v>
@@ -18037,8 +18161,10 @@
       <c r="B64" t="s">
         <v>94</v>
       </c>
-      <c r="C64" t="s">
-        <v>1163</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>200HG</t>
+        </is>
       </c>
       <c r="D64" t="s">
         <v>1164</v>
@@ -18120,8 +18246,10 @@
       <c r="B65" t="s">
         <v>94</v>
       </c>
-      <c r="C65" t="s">
-        <v>1170</v>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>201HG</t>
+        </is>
       </c>
       <c r="D65" t="s">
         <v>1164</v>
@@ -18203,8 +18331,10 @@
       <c r="B66" t="s">
         <v>100</v>
       </c>
-      <c r="C66" t="s">
-        <v>1174</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2000T</t>
+        </is>
       </c>
       <c r="D66" t="s">
         <v>977</v>
@@ -18286,8 +18416,10 @@
       <c r="B67" t="s">
         <v>100</v>
       </c>
-      <c r="C67" t="s">
-        <v>1188</v>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3000T</t>
+        </is>
       </c>
       <c r="D67" t="s">
         <v>977</v>
@@ -18369,8 +18501,10 @@
       <c r="B68" t="s">
         <v>100</v>
       </c>
-      <c r="C68" t="s">
-        <v>1198</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>4000T</t>
+        </is>
       </c>
       <c r="D68" t="s">
         <v>977</v>
@@ -18452,8 +18586,10 @@
       <c r="B69" t="s">
         <v>106</v>
       </c>
-      <c r="C69" t="s">
-        <v>1209</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>100MG</t>
+        </is>
       </c>
       <c r="D69" t="s">
         <v>869</v>
@@ -18544,8 +18680,10 @@
       <c r="B70" t="s">
         <v>106</v>
       </c>
-      <c r="C70" t="s">
-        <v>1221</v>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>101MG</t>
+        </is>
       </c>
       <c r="D70" t="s">
         <v>869</v>
@@ -18636,8 +18774,10 @@
       <c r="B71" t="s">
         <v>106</v>
       </c>
-      <c r="C71" t="s">
-        <v>1225</v>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>100HG</t>
+        </is>
       </c>
       <c r="D71" t="s">
         <v>886</v>
@@ -18728,8 +18868,10 @@
       <c r="B72" t="s">
         <v>106</v>
       </c>
-      <c r="C72" t="s">
-        <v>1230</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>101HG</t>
+        </is>
       </c>
       <c r="D72" t="s">
         <v>886</v>
@@ -18820,8 +18962,10 @@
       <c r="B73" t="s">
         <v>106</v>
       </c>
-      <c r="C73" t="s">
-        <v>1234</v>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>100XG</t>
+        </is>
       </c>
       <c r="D73" t="s">
         <v>836</v>
@@ -18912,8 +19056,10 @@
       <c r="B74" t="s">
         <v>106</v>
       </c>
-      <c r="C74" t="s">
-        <v>1238</v>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>101XG</t>
+        </is>
       </c>
       <c r="D74" t="s">
         <v>836</v>
@@ -19004,8 +19150,10 @@
       <c r="B75" t="s">
         <v>113</v>
       </c>
-      <c r="C75" t="s">
-        <v>1242</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1500XG</t>
+        </is>
       </c>
       <c r="D75" t="s">
         <v>1243</v>
@@ -19084,8 +19232,10 @@
       <c r="B76" t="s">
         <v>113</v>
       </c>
-      <c r="C76" t="s">
-        <v>1251</v>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1501XG</t>
+        </is>
       </c>
       <c r="D76" t="s">
         <v>1243</v>
@@ -19164,8 +19314,10 @@
       <c r="B77" t="s">
         <v>113</v>
       </c>
-      <c r="C77" t="s">
-        <v>1255</v>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2000NRMG</t>
+        </is>
       </c>
       <c r="D77" t="s">
         <v>783</v>
@@ -19244,8 +19396,10 @@
       <c r="B78" t="s">
         <v>113</v>
       </c>
-      <c r="C78" t="s">
-        <v>1261</v>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2001NRMG</t>
+        </is>
       </c>
       <c r="D78" t="s">
         <v>783</v>
@@ -19324,8 +19478,10 @@
       <c r="B79" t="s">
         <v>113</v>
       </c>
-      <c r="C79" t="s">
-        <v>1265</v>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2000NRXG</t>
+        </is>
       </c>
       <c r="D79" t="s">
         <v>1042</v>
@@ -19404,8 +19560,10 @@
       <c r="B80" t="s">
         <v>113</v>
       </c>
-      <c r="C80" t="s">
-        <v>1270</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2001NRXG</t>
+        </is>
       </c>
       <c r="D80" t="s">
         <v>1042</v>
@@ -19484,8 +19642,10 @@
       <c r="B81" t="s">
         <v>113</v>
       </c>
-      <c r="C81" t="s">
-        <v>1274</v>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1000HG</t>
+        </is>
       </c>
       <c r="D81" t="s">
         <v>1041</v>
@@ -19564,8 +19724,10 @@
       <c r="B82" t="s">
         <v>113</v>
       </c>
-      <c r="C82" t="s">
-        <v>1281</v>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1001HG</t>
+        </is>
       </c>
       <c r="D82" t="s">
         <v>1041</v>
@@ -19644,8 +19806,10 @@
       <c r="B83" t="s">
         <v>113</v>
       </c>
-      <c r="C83" t="s">
-        <v>1285</v>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1500HG</t>
+        </is>
       </c>
       <c r="D83" t="s">
         <v>1041</v>
@@ -19724,8 +19888,10 @@
       <c r="B84" t="s">
         <v>113</v>
       </c>
-      <c r="C84" t="s">
-        <v>1289</v>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1500PG</t>
+        </is>
       </c>
       <c r="D84" t="s">
         <v>923</v>
@@ -19804,8 +19970,10 @@
       <c r="B85" t="s">
         <v>113</v>
       </c>
-      <c r="C85" t="s">
-        <v>1293</v>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1501HG</t>
+        </is>
       </c>
       <c r="D85" t="s">
         <v>1041</v>
@@ -19884,8 +20052,10 @@
       <c r="B86" t="s">
         <v>113</v>
       </c>
-      <c r="C86" t="s">
-        <v>1297</v>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1501PG</t>
+        </is>
       </c>
       <c r="D86" t="s">
         <v>923</v>
@@ -19964,8 +20134,10 @@
       <c r="B87" t="s">
         <v>113</v>
       </c>
-      <c r="C87" t="s">
-        <v>1301</v>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2000NRHG</t>
+        </is>
       </c>
       <c r="D87" t="s">
         <v>977</v>
@@ -20044,8 +20216,10 @@
       <c r="B88" t="s">
         <v>113</v>
       </c>
-      <c r="C88" t="s">
-        <v>1307</v>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2000NRPG</t>
+        </is>
       </c>
       <c r="D88" t="s">
         <v>923</v>
@@ -20124,8 +20298,10 @@
       <c r="B89" t="s">
         <v>113</v>
       </c>
-      <c r="C89" t="s">
-        <v>1311</v>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2001NRHG</t>
+        </is>
       </c>
       <c r="D89" t="s">
         <v>977</v>
@@ -20204,8 +20380,10 @@
       <c r="B90" t="s">
         <v>113</v>
       </c>
-      <c r="C90" t="s">
-        <v>1315</v>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2001NRPG</t>
+        </is>
       </c>
       <c r="D90" t="s">
         <v>923</v>
@@ -20284,8 +20462,10 @@
       <c r="B91" t="s">
         <v>119</v>
       </c>
-      <c r="C91" t="s">
-        <v>1319</v>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>300XG</t>
+        </is>
       </c>
       <c r="D91" t="s">
         <v>1010</v>
@@ -20379,8 +20559,10 @@
       <c r="B92" t="s">
         <v>119</v>
       </c>
-      <c r="C92" t="s">
-        <v>1332</v>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>300XGLH</t>
+        </is>
       </c>
       <c r="D92" t="s">
         <v>1010</v>
@@ -20474,8 +20656,10 @@
       <c r="B93" t="s">
         <v>119</v>
       </c>
-      <c r="C93" t="s">
-        <v>1337</v>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>301XGLH</t>
+        </is>
       </c>
       <c r="D93" t="s">
         <v>1010</v>
@@ -20569,8 +20753,10 @@
       <c r="B94" t="s">
         <v>119</v>
       </c>
-      <c r="C94" t="s">
-        <v>1341</v>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>400XG</t>
+        </is>
       </c>
       <c r="D94" t="s">
         <v>1010</v>
@@ -20664,8 +20850,10 @@
       <c r="B95" t="s">
         <v>119</v>
       </c>
-      <c r="C95" t="s">
-        <v>1351</v>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>400XGLH</t>
+        </is>
       </c>
       <c r="D95" t="s">
         <v>1010</v>
@@ -20759,8 +20947,10 @@
       <c r="B96" t="s">
         <v>119</v>
       </c>
-      <c r="C96" t="s">
-        <v>1356</v>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>401XGLH</t>
+        </is>
       </c>
       <c r="D96" t="s">
         <v>1010</v>
@@ -20854,8 +21044,10 @@
       <c r="B97" t="s">
         <v>125</v>
       </c>
-      <c r="C97" t="s">
-        <v>1360</v>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>HG RIGHT</t>
+        </is>
       </c>
       <c r="D97" t="s">
         <v>836</v>
@@ -20946,8 +21138,10 @@
       <c r="B98" t="s">
         <v>125</v>
       </c>
-      <c r="C98" t="s">
-        <v>1376</v>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>HG LEFT</t>
+        </is>
       </c>
       <c r="D98" t="s">
         <v>836</v>
@@ -21038,8 +21232,10 @@
       <c r="B99" t="s">
         <v>125</v>
       </c>
-      <c r="C99" t="s">
-        <v>1380</v>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>XG RIGHT</t>
+        </is>
       </c>
       <c r="D99" t="s">
         <v>1381</v>
@@ -21130,8 +21326,10 @@
       <c r="B100" t="s">
         <v>125</v>
       </c>
-      <c r="C100" t="s">
-        <v>1387</v>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>XG LEFT</t>
+        </is>
       </c>
       <c r="D100" t="s">
         <v>1381</v>
@@ -21222,8 +21420,10 @@
       <c r="B101" t="s">
         <v>133</v>
       </c>
-      <c r="C101" t="s">
-        <v>1391</v>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="D101" t="s">
         <v>977</v>
@@ -21317,8 +21517,10 @@
       <c r="B102" t="s">
         <v>133</v>
       </c>
-      <c r="C102" t="s">
-        <v>1403</v>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="D102" t="s">
         <v>977</v>
@@ -21412,8 +21614,10 @@
       <c r="B103" t="s">
         <v>133</v>
       </c>
-      <c r="C103" t="s">
-        <v>1408</v>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>70HG</t>
+        </is>
       </c>
       <c r="D103" t="s">
         <v>1409</v>
@@ -21507,8 +21711,10 @@
       <c r="B104" t="s">
         <v>133</v>
       </c>
-      <c r="C104" t="s">
-        <v>1414</v>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>71HG</t>
+        </is>
       </c>
       <c r="D104" t="s">
         <v>1409</v>
@@ -21602,8 +21808,10 @@
       <c r="B105" t="s">
         <v>133</v>
       </c>
-      <c r="C105" t="s">
-        <v>1418</v>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>70XG</t>
+        </is>
       </c>
       <c r="D105" t="s">
         <v>1419</v>
@@ -21697,8 +21905,10 @@
       <c r="B106" t="s">
         <v>133</v>
       </c>
-      <c r="C106" t="s">
-        <v>1424</v>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>71XG</t>
+        </is>
       </c>
       <c r="D106" t="s">
         <v>1419</v>
@@ -21792,8 +22002,10 @@
       <c r="B107" t="s">
         <v>144</v>
       </c>
-      <c r="C107" t="s">
-        <v>1428</v>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="D107" t="s">
         <v>869</v>
@@ -21884,8 +22096,10 @@
       <c r="B108" t="s">
         <v>144</v>
       </c>
-      <c r="C108" t="s">
-        <v>1435</v>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="D108" t="s">
         <v>869</v>
@@ -21976,8 +22190,10 @@
       <c r="B109" t="s">
         <v>144</v>
       </c>
-      <c r="C109" t="s">
-        <v>1439</v>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="D109" t="s">
         <v>929</v>
@@ -22068,8 +22284,10 @@
       <c r="B110" t="s">
         <v>144</v>
       </c>
-      <c r="C110" t="s">
-        <v>1446</v>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="D110" t="s">
         <v>929</v>
@@ -22160,8 +22378,10 @@
       <c r="B111" t="s">
         <v>144</v>
       </c>
-      <c r="C111" t="s">
-        <v>1450</v>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>100HG</t>
+        </is>
       </c>
       <c r="D111" t="s">
         <v>886</v>
@@ -22252,8 +22472,10 @@
       <c r="B112" t="s">
         <v>144</v>
       </c>
-      <c r="C112" t="s">
-        <v>1456</v>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>101HG</t>
+        </is>
       </c>
       <c r="D112" t="s">
         <v>886</v>
@@ -22344,8 +22566,10 @@
       <c r="B113" t="s">
         <v>144</v>
       </c>
-      <c r="C113" t="s">
-        <v>1460</v>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>200HG</t>
+        </is>
       </c>
       <c r="D113" t="s">
         <v>1164</v>
@@ -22436,8 +22660,10 @@
       <c r="B114" t="s">
         <v>144</v>
       </c>
-      <c r="C114" t="s">
-        <v>1464</v>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>201HG</t>
+        </is>
       </c>
       <c r="D114" t="s">
         <v>1164</v>
@@ -22528,8 +22754,10 @@
       <c r="B115" t="s">
         <v>144</v>
       </c>
-      <c r="C115" t="s">
-        <v>1468</v>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>200XG</t>
+        </is>
       </c>
       <c r="D115" t="s">
         <v>1010</v>
@@ -22620,8 +22848,10 @@
       <c r="B116" t="s">
         <v>144</v>
       </c>
-      <c r="C116" t="s">
-        <v>1473</v>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>201XG</t>
+        </is>
       </c>
       <c r="D116" t="s">
         <v>1010</v>
@@ -22712,8 +22942,10 @@
       <c r="B117" t="s">
         <v>153</v>
       </c>
-      <c r="C117" t="s">
-        <v>1477</v>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>300PG</t>
+        </is>
       </c>
       <c r="D117" t="s">
         <v>929</v>
@@ -22795,8 +23027,10 @@
       <c r="B118" t="s">
         <v>153</v>
       </c>
-      <c r="C118" t="s">
-        <v>1484</v>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>301PG</t>
+        </is>
       </c>
       <c r="D118" t="s">
         <v>929</v>
@@ -22878,8 +23112,10 @@
       <c r="B119" t="s">
         <v>153</v>
       </c>
-      <c r="C119" t="s">
-        <v>1488</v>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>300HG</t>
+        </is>
       </c>
       <c r="D119" t="s">
         <v>977</v>
@@ -22961,8 +23197,10 @@
       <c r="B120" t="s">
         <v>153</v>
       </c>
-      <c r="C120" t="s">
-        <v>1493</v>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>301HG</t>
+        </is>
       </c>
       <c r="D120" t="s">
         <v>977</v>
@@ -23044,8 +23282,10 @@
       <c r="B121" t="s">
         <v>153</v>
       </c>
-      <c r="C121" t="s">
-        <v>1497</v>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>300XG</t>
+        </is>
       </c>
       <c r="D121" t="s">
         <v>1010</v>
@@ -23127,8 +23367,10 @@
       <c r="B122" t="s">
         <v>153</v>
       </c>
-      <c r="C122" t="s">
-        <v>1501</v>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>301XG</t>
+        </is>
       </c>
       <c r="D122" t="s">
         <v>1010</v>
@@ -23210,8 +23452,10 @@
       <c r="B123" t="s">
         <v>153</v>
       </c>
-      <c r="C123" t="s">
-        <v>1505</v>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>200PG</t>
+        </is>
       </c>
       <c r="D123" t="s">
         <v>929</v>
@@ -23293,8 +23537,10 @@
       <c r="B124" t="s">
         <v>153</v>
       </c>
-      <c r="C124" t="s">
-        <v>1512</v>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>201PG</t>
+        </is>
       </c>
       <c r="D124" t="s">
         <v>929</v>
@@ -23376,8 +23622,10 @@
       <c r="B125" t="s">
         <v>153</v>
       </c>
-      <c r="C125" t="s">
-        <v>1516</v>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>200HG</t>
+        </is>
       </c>
       <c r="D125" t="s">
         <v>1164</v>
@@ -23459,8 +23707,10 @@
       <c r="B126" t="s">
         <v>153</v>
       </c>
-      <c r="C126" t="s">
-        <v>1521</v>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>201HG</t>
+        </is>
       </c>
       <c r="D126" t="s">
         <v>1164</v>
@@ -23542,8 +23792,10 @@
       <c r="B127" t="s">
         <v>159</v>
       </c>
-      <c r="C127" t="s">
-        <v>1525</v>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>30HG</t>
+        </is>
       </c>
       <c r="D127" t="s">
         <v>886</v>
@@ -23634,8 +23886,10 @@
       <c r="B128" t="s">
         <v>159</v>
       </c>
-      <c r="C128" t="s">
-        <v>1532</v>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>31HG</t>
+        </is>
       </c>
       <c r="D128" t="s">
         <v>886</v>
@@ -23726,8 +23980,10 @@
       <c r="B129" t="s">
         <v>165</v>
       </c>
-      <c r="C129" t="s">
-        <v>1537</v>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>HG RIGHT</t>
+        </is>
       </c>
       <c r="D129" t="s">
         <v>836</v>
@@ -23818,8 +24074,10 @@
       <c r="B130" t="s">
         <v>165</v>
       </c>
-      <c r="C130" t="s">
-        <v>1546</v>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>HG LEFT</t>
+        </is>
       </c>
       <c r="D130" t="s">
         <v>836</v>
@@ -23910,8 +24168,10 @@
       <c r="B131" t="s">
         <v>165</v>
       </c>
-      <c r="C131" t="s">
-        <v>1550</v>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>XG RIGHT</t>
+        </is>
       </c>
       <c r="D131" t="s">
         <v>1381</v>
@@ -24002,8 +24262,10 @@
       <c r="B132" t="s">
         <v>165</v>
       </c>
-      <c r="C132" t="s">
-        <v>1554</v>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>XG LEFT</t>
+        </is>
       </c>
       <c r="D132" t="s">
         <v>1381</v>
@@ -24094,8 +24356,10 @@
       <c r="B133" t="s">
         <v>173</v>
       </c>
-      <c r="C133" t="s">
-        <v>1558</v>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>60MG</t>
+        </is>
       </c>
       <c r="D133" t="s">
         <v>977</v>
@@ -24183,8 +24447,10 @@
       <c r="B134" t="s">
         <v>173</v>
       </c>
-      <c r="C134" t="s">
-        <v>1568</v>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>61MG</t>
+        </is>
       </c>
       <c r="D134" t="s">
         <v>977</v>
@@ -24266,8 +24532,10 @@
       <c r="B135" t="s">
         <v>173</v>
       </c>
-      <c r="C135" t="s">
-        <v>1571</v>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>60HG</t>
+        </is>
       </c>
       <c r="D135" t="s">
         <v>886</v>
@@ -24355,8 +24623,10 @@
       <c r="B136" t="s">
         <v>173</v>
       </c>
-      <c r="C136" t="s">
-        <v>1575</v>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>61HG</t>
+        </is>
       </c>
       <c r="D136" t="s">
         <v>886</v>
@@ -24438,8 +24708,10 @@
       <c r="B137" t="s">
         <v>180</v>
       </c>
-      <c r="C137" t="s">
-        <v>1578</v>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>30HG</t>
+        </is>
       </c>
       <c r="D137" t="s">
         <v>836</v>
@@ -24527,8 +24799,10 @@
       <c r="B138" t="s">
         <v>180</v>
       </c>
-      <c r="C138" t="s">
-        <v>1588</v>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>31HG</t>
+        </is>
       </c>
       <c r="D138" t="s">
         <v>836</v>
@@ -24616,8 +24890,10 @@
       <c r="B139" t="s">
         <v>180</v>
       </c>
-      <c r="C139" t="s">
-        <v>1592</v>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>30XG</t>
+        </is>
       </c>
       <c r="D139" t="s">
         <v>1381</v>
@@ -24705,8 +24981,10 @@
       <c r="B140" t="s">
         <v>180</v>
       </c>
-      <c r="C140" t="s">
-        <v>1596</v>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>31XG</t>
+        </is>
       </c>
       <c r="D140" t="s">
         <v>1381</v>
@@ -24794,8 +25072,10 @@
       <c r="B141" t="s">
         <v>189</v>
       </c>
-      <c r="C141" t="s">
-        <v>1600</v>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>100PG</t>
+        </is>
       </c>
       <c r="D141" t="s">
         <v>1041</v>
@@ -24874,8 +25154,10 @@
       <c r="B142" t="s">
         <v>189</v>
       </c>
-      <c r="C142" t="s">
-        <v>1609</v>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>101PG</t>
+        </is>
       </c>
       <c r="D142" t="s">
         <v>1041</v>
@@ -24954,8 +25236,10 @@
       <c r="B143" t="s">
         <v>189</v>
       </c>
-      <c r="C143" t="s">
-        <v>1613</v>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>100XG</t>
+        </is>
       </c>
       <c r="D143" t="s">
         <v>1381</v>
@@ -25034,8 +25318,10 @@
       <c r="B144" t="s">
         <v>189</v>
       </c>
-      <c r="C144" t="s">
-        <v>1618</v>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>101XG</t>
+        </is>
       </c>
       <c r="D144" t="s">
         <v>1381</v>
@@ -25114,8 +25400,10 @@
       <c r="B145" t="s">
         <v>195</v>
       </c>
-      <c r="C145" t="s">
-        <v>1622</v>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="D145" t="s">
         <v>1623</v>
@@ -25197,8 +25485,10 @@
       <c r="B146" t="s">
         <v>195</v>
       </c>
-      <c r="C146" t="s">
-        <v>1634</v>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="D146" t="s">
         <v>1623</v>
@@ -25280,8 +25570,10 @@
       <c r="B147" t="s">
         <v>195</v>
       </c>
-      <c r="C147" t="s">
-        <v>1638</v>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>150DH</t>
+        </is>
       </c>
       <c r="D147" t="s">
         <v>1623</v>
@@ -25363,8 +25655,10 @@
       <c r="B148" t="s">
         <v>195</v>
       </c>
-      <c r="C148" t="s">
-        <v>1643</v>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>151DH</t>
+        </is>
       </c>
       <c r="D148" t="s">
         <v>1623</v>
@@ -25446,8 +25740,10 @@
       <c r="B149" t="s">
         <v>195</v>
       </c>
-      <c r="C149" t="s">
-        <v>1647</v>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>150DHXG</t>
+        </is>
       </c>
       <c r="D149" t="s">
         <v>1419</v>
@@ -25529,8 +25825,10 @@
       <c r="B150" t="s">
         <v>195</v>
       </c>
-      <c r="C150" t="s">
-        <v>1651</v>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>151DHXG</t>
+        </is>
       </c>
       <c r="D150" t="s">
         <v>1419</v>
@@ -25612,8 +25910,10 @@
       <c r="B151" t="s">
         <v>201</v>
       </c>
-      <c r="C151" t="s">
-        <v>1655</v>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>150XG</t>
+        </is>
       </c>
       <c r="D151" t="s">
         <v>1419</v>
@@ -25692,8 +25992,10 @@
       <c r="B152" t="s">
         <v>201</v>
       </c>
-      <c r="C152" t="s">
-        <v>1662</v>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>151XG</t>
+        </is>
       </c>
       <c r="D152" t="s">
         <v>1419</v>
@@ -25772,8 +26074,10 @@
       <c r="B153" t="s">
         <v>207</v>
       </c>
-      <c r="C153" t="s">
-        <v>1666</v>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>HG R</t>
+        </is>
       </c>
       <c r="D153" t="s">
         <v>836</v>
@@ -25888,8 +26192,10 @@
       <c r="B154" t="s">
         <v>207</v>
       </c>
-      <c r="C154" t="s">
-        <v>1680</v>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>HG L</t>
+        </is>
       </c>
       <c r="D154" t="s">
         <v>836</v>
@@ -26004,8 +26310,10 @@
       <c r="B155" t="s">
         <v>207</v>
       </c>
-      <c r="C155" t="s">
-        <v>1684</v>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>XG R</t>
+        </is>
       </c>
       <c r="D155" t="s">
         <v>1381</v>
@@ -26120,8 +26428,10 @@
       <c r="B156" t="s">
         <v>207</v>
       </c>
-      <c r="C156" t="s">
-        <v>1689</v>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>XG L</t>
+        </is>
       </c>
       <c r="D156" t="s">
         <v>1381</v>
@@ -26236,8 +26546,10 @@
       <c r="B157" t="s">
         <v>221</v>
       </c>
-      <c r="C157" t="s">
-        <v>1693</v>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="D157" t="s">
         <v>1164</v>
@@ -26349,8 +26661,10 @@
       <c r="B158" t="s">
         <v>221</v>
       </c>
-      <c r="C158" t="s">
-        <v>1705</v>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="D158" t="s">
         <v>1164</v>
@@ -26462,8 +26776,10 @@
       <c r="B159" t="s">
         <v>221</v>
       </c>
-      <c r="C159" t="s">
-        <v>1709</v>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>30 HG</t>
+        </is>
       </c>
       <c r="D159" t="s">
         <v>886</v>
@@ -26575,8 +26891,10 @@
       <c r="B160" t="s">
         <v>221</v>
       </c>
-      <c r="C160" t="s">
-        <v>1713</v>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>31 HG</t>
+        </is>
       </c>
       <c r="D160" t="s">
         <v>886</v>
@@ -26688,8 +27006,10 @@
       <c r="B161" t="s">
         <v>234</v>
       </c>
-      <c r="C161" t="s">
-        <v>1717</v>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
       </c>
       <c r="D161" t="s">
         <v>977</v>
@@ -26780,8 +27100,10 @@
       <c r="B162" t="s">
         <v>234</v>
       </c>
-      <c r="C162" t="s">
-        <v>1726</v>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="D162" t="s">
         <v>977</v>
@@ -26872,8 +27194,10 @@
       <c r="B163" t="s">
         <v>234</v>
       </c>
-      <c r="C163" t="s">
-        <v>1730</v>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>HG R</t>
+        </is>
       </c>
       <c r="D163" t="s">
         <v>1409</v>
@@ -26964,8 +27288,10 @@
       <c r="B164" t="s">
         <v>234</v>
       </c>
-      <c r="C164" t="s">
-        <v>1734</v>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>HG L</t>
+        </is>
       </c>
       <c r="D164" t="s">
         <v>1409</v>
@@ -27056,8 +27382,10 @@
       <c r="B165" t="s">
         <v>234</v>
       </c>
-      <c r="C165" t="s">
-        <v>1738</v>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>XG R</t>
+        </is>
       </c>
       <c r="D165" t="s">
         <v>1419</v>
@@ -27148,8 +27476,10 @@
       <c r="B166" t="s">
         <v>234</v>
       </c>
-      <c r="C166" t="s">
-        <v>1742</v>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>XG L</t>
+        </is>
       </c>
       <c r="D166" t="s">
         <v>1419</v>
@@ -27240,8 +27570,10 @@
       <c r="B167" t="s">
         <v>242</v>
       </c>
-      <c r="C167" t="s">
-        <v>1746</v>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="D167" t="s">
         <v>977</v>
@@ -27350,8 +27682,10 @@
       <c r="B168" t="s">
         <v>242</v>
       </c>
-      <c r="C168" t="s">
-        <v>1754</v>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="D168" t="s">
         <v>977</v>
@@ -27460,8 +27794,10 @@
       <c r="B169" t="s">
         <v>242</v>
       </c>
-      <c r="C169" t="s">
-        <v>1756</v>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>150HG</t>
+        </is>
       </c>
       <c r="D169" t="s">
         <v>1409</v>
@@ -27570,8 +27906,10 @@
       <c r="B170" t="s">
         <v>242</v>
       </c>
-      <c r="C170" t="s">
-        <v>1758</v>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>151HG</t>
+        </is>
       </c>
       <c r="D170" t="s">
         <v>1409</v>
@@ -27680,8 +28018,10 @@
       <c r="B171" t="s">
         <v>242</v>
       </c>
-      <c r="C171" t="s">
-        <v>1760</v>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>150XG</t>
+        </is>
       </c>
       <c r="D171" t="s">
         <v>1419</v>
@@ -27790,8 +28130,10 @@
       <c r="B172" t="s">
         <v>242</v>
       </c>
-      <c r="C172" t="s">
-        <v>1764</v>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>151XG</t>
+        </is>
       </c>
       <c r="D172" t="s">
         <v>1419</v>
@@ -27900,8 +28242,10 @@
       <c r="B173" t="s">
         <v>242</v>
       </c>
-      <c r="C173" t="s">
-        <v>1766</v>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="D173" t="s">
         <v>977</v>
@@ -28016,8 +28360,10 @@
       <c r="B174" t="s">
         <v>242</v>
       </c>
-      <c r="C174" t="s">
-        <v>1771</v>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="D174" t="s">
         <v>977</v>
@@ -28132,8 +28478,10 @@
       <c r="B175" t="s">
         <v>242</v>
       </c>
-      <c r="C175" t="s">
-        <v>1775</v>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>70HG</t>
+        </is>
       </c>
       <c r="D175" t="s">
         <v>1409</v>
@@ -28248,8 +28596,10 @@
       <c r="B176" t="s">
         <v>242</v>
       </c>
-      <c r="C176" t="s">
-        <v>1779</v>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>71HG</t>
+        </is>
       </c>
       <c r="D176" t="s">
         <v>1409</v>
@@ -28364,8 +28714,10 @@
       <c r="B177" t="s">
         <v>242</v>
       </c>
-      <c r="C177" t="s">
-        <v>1783</v>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>70XG</t>
+        </is>
       </c>
       <c r="D177" t="s">
         <v>1419</v>
@@ -28480,8 +28832,10 @@
       <c r="B178" t="s">
         <v>242</v>
       </c>
-      <c r="C178" t="s">
-        <v>1787</v>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>71XG</t>
+        </is>
       </c>
       <c r="D178" t="s">
         <v>1419</v>
@@ -28596,8 +28950,10 @@
       <c r="B179" t="s">
         <v>242</v>
       </c>
-      <c r="C179" t="s">
-        <v>1791</v>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>100HG</t>
+        </is>
       </c>
       <c r="D179" t="s">
         <v>1409</v>
@@ -28712,8 +29068,10 @@
       <c r="B180" t="s">
         <v>242</v>
       </c>
-      <c r="C180" t="s">
-        <v>1796</v>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>101HG</t>
+        </is>
       </c>
       <c r="D180" t="s">
         <v>1409</v>
@@ -28828,8 +29186,10 @@
       <c r="B181" t="s">
         <v>242</v>
       </c>
-      <c r="C181" t="s">
-        <v>1800</v>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>100XG</t>
+        </is>
       </c>
       <c r="D181" t="s">
         <v>1419</v>
@@ -28944,8 +29304,10 @@
       <c r="B182" t="s">
         <v>242</v>
       </c>
-      <c r="C182" t="s">
-        <v>1804</v>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>101XG</t>
+        </is>
       </c>
       <c r="D182" t="s">
         <v>1419</v>
@@ -29060,8 +29422,10 @@
       <c r="B183" t="s">
         <v>253</v>
       </c>
-      <c r="C183" t="s">
-        <v>1808</v>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2000T</t>
+        </is>
       </c>
       <c r="D183" t="s">
         <v>977</v>
@@ -29143,8 +29507,10 @@
       <c r="B184" t="s">
         <v>253</v>
       </c>
-      <c r="C184" t="s">
-        <v>1816</v>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>3000T</t>
+        </is>
       </c>
       <c r="D184" t="s">
         <v>977</v>
@@ -29226,8 +29592,10 @@
       <c r="B185" t="s">
         <v>253</v>
       </c>
-      <c r="C185" t="s">
-        <v>1822</v>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>4000T</t>
+        </is>
       </c>
       <c r="D185" t="s">
         <v>977</v>
@@ -29309,8 +29677,10 @@
       <c r="B186" t="s">
         <v>259</v>
       </c>
-      <c r="C186" t="s">
-        <v>1828</v>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="D186" t="s">
         <v>837</v>
@@ -29392,8 +29762,10 @@
       <c r="B187" t="s">
         <v>259</v>
       </c>
-      <c r="C187" t="s">
-        <v>1841</v>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="D187" t="s">
         <v>837</v>
@@ -29475,8 +29847,10 @@
       <c r="B188" t="s">
         <v>259</v>
       </c>
-      <c r="C188" t="s">
-        <v>1851</v>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="D188" t="s">
         <v>837</v>
@@ -29558,8 +29932,10 @@
       <c r="B189" t="s">
         <v>265</v>
       </c>
-      <c r="C189" t="s">
-        <v>1861</v>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>HG R</t>
+        </is>
       </c>
       <c r="D189" t="s">
         <v>886</v>
@@ -29647,8 +30023,10 @@
       <c r="B190" t="s">
         <v>265</v>
       </c>
-      <c r="C190" t="s">
-        <v>1869</v>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>HG L</t>
+        </is>
       </c>
       <c r="D190" t="s">
         <v>886</v>
@@ -29736,8 +30114,10 @@
       <c r="B191" t="s">
         <v>265</v>
       </c>
-      <c r="C191" t="s">
-        <v>1873</v>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>XG R</t>
+        </is>
       </c>
       <c r="D191" t="s">
         <v>1874</v>
@@ -29825,8 +30205,10 @@
       <c r="B192" t="s">
         <v>265</v>
       </c>
-      <c r="C192" t="s">
-        <v>1878</v>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>XG L</t>
+        </is>
       </c>
       <c r="D192" t="s">
         <v>1874</v>
@@ -29914,8 +30296,10 @@
       <c r="B193" t="s">
         <v>272</v>
       </c>
-      <c r="C193" t="s">
-        <v>1882</v>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="D193" t="s">
         <v>1883</v>
@@ -29991,8 +30375,10 @@
       <c r="B194" t="s">
         <v>272</v>
       </c>
-      <c r="C194" t="s">
-        <v>1892</v>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
       </c>
       <c r="D194" t="s">
         <v>1883</v>
@@ -30068,8 +30454,10 @@
       <c r="B195" t="s">
         <v>272</v>
       </c>
-      <c r="C195" t="s">
-        <v>1894</v>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>400HG</t>
+        </is>
       </c>
       <c r="D195" t="s">
         <v>1895</v>
@@ -30145,8 +30533,10 @@
       <c r="B196" t="s">
         <v>272</v>
       </c>
-      <c r="C196" t="s">
-        <v>1899</v>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>401HG</t>
+        </is>
       </c>
       <c r="D196" t="s">
         <v>1895</v>
@@ -30222,8 +30612,10 @@
       <c r="B197" t="s">
         <v>279</v>
       </c>
-      <c r="C197" t="s">
-        <v>1901</v>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
       </c>
       <c r="D197" t="s">
         <v>977</v>
@@ -30332,8 +30724,10 @@
       <c r="B198" t="s">
         <v>279</v>
       </c>
-      <c r="C198" t="s">
-        <v>1915</v>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="D198" t="s">
         <v>977</v>
@@ -30442,8 +30836,10 @@
       <c r="B199" t="s">
         <v>279</v>
       </c>
-      <c r="C199" t="s">
-        <v>1919</v>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>HG R</t>
+        </is>
       </c>
       <c r="D199" t="s">
         <v>1409</v>
@@ -30552,8 +30948,10 @@
       <c r="B200" t="s">
         <v>279</v>
       </c>
-      <c r="C200" t="s">
-        <v>1923</v>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>HG L</t>
+        </is>
       </c>
       <c r="D200" t="s">
         <v>1409</v>
@@ -30662,8 +31060,10 @@
       <c r="B201" t="s">
         <v>279</v>
       </c>
-      <c r="C201" t="s">
-        <v>1927</v>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>XG R</t>
+        </is>
       </c>
       <c r="D201" t="s">
         <v>1419</v>
@@ -30772,8 +31172,10 @@
       <c r="B202" t="s">
         <v>279</v>
       </c>
-      <c r="C202" t="s">
-        <v>1931</v>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>XG L</t>
+        </is>
       </c>
       <c r="D202" t="s">
         <v>1419</v>
@@ -30882,8 +31284,10 @@
       <c r="B203" t="s">
         <v>293</v>
       </c>
-      <c r="C203" t="s">
-        <v>1935</v>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="D203" t="s">
         <v>1883</v>
@@ -30959,8 +31363,10 @@
       <c r="B204" t="s">
         <v>293</v>
       </c>
-      <c r="C204" t="s">
-        <v>1940</v>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
       </c>
       <c r="D204" t="s">
         <v>1883</v>
@@ -31036,8 +31442,10 @@
       <c r="B205" t="s">
         <v>293</v>
       </c>
-      <c r="C205" t="s">
-        <v>1942</v>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>300HG</t>
+        </is>
       </c>
       <c r="D205" t="s">
         <v>1895</v>
@@ -31113,8 +31521,10 @@
       <c r="B206" t="s">
         <v>293</v>
       </c>
-      <c r="C206" t="s">
-        <v>1944</v>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>301HG</t>
+        </is>
       </c>
       <c r="D206" t="s">
         <v>1895</v>
@@ -31190,8 +31600,10 @@
       <c r="B207" t="s">
         <v>300</v>
       </c>
-      <c r="C207" t="s">
-        <v>1946</v>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="D207" t="s">
         <v>1623</v>
@@ -31273,8 +31685,10 @@
       <c r="B208" t="s">
         <v>300</v>
       </c>
-      <c r="C208" t="s">
-        <v>1955</v>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="D208" t="s">
         <v>1623</v>
@@ -31356,8 +31770,10 @@
       <c r="B209" t="s">
         <v>300</v>
       </c>
-      <c r="C209" t="s">
-        <v>1959</v>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>150DH</t>
+        </is>
       </c>
       <c r="D209" t="s">
         <v>1623</v>
@@ -31439,8 +31855,10 @@
       <c r="B210" t="s">
         <v>300</v>
       </c>
-      <c r="C210" t="s">
-        <v>1963</v>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>151DH</t>
+        </is>
       </c>
       <c r="D210" t="s">
         <v>1623</v>
@@ -31522,8 +31940,10 @@
       <c r="B211" t="s">
         <v>300</v>
       </c>
-      <c r="C211" t="s">
-        <v>1967</v>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>300PG</t>
+        </is>
       </c>
       <c r="D211" t="s">
         <v>929</v>
@@ -31605,8 +32025,10 @@
       <c r="B212" t="s">
         <v>300</v>
       </c>
-      <c r="C212" t="s">
-        <v>1978</v>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>301PG</t>
+        </is>
       </c>
       <c r="D212" t="s">
         <v>929</v>
@@ -31688,8 +32110,10 @@
       <c r="B213" t="s">
         <v>306</v>
       </c>
-      <c r="C213" t="s">
-        <v>1982</v>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>300HG</t>
+        </is>
       </c>
       <c r="D213" t="s">
         <v>1983</v>
@@ -31771,8 +32195,10 @@
       <c r="B214" t="s">
         <v>306</v>
       </c>
-      <c r="C214" t="s">
-        <v>1989</v>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>301HG</t>
+        </is>
       </c>
       <c r="D214" t="s">
         <v>1983</v>
@@ -31848,8 +32274,10 @@
       <c r="B215" t="s">
         <v>306</v>
       </c>
-      <c r="C215" t="s">
-        <v>1992</v>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>300XG</t>
+        </is>
       </c>
       <c r="D215" t="s">
         <v>1895</v>
@@ -31931,8 +32359,10 @@
       <c r="B216" t="s">
         <v>306</v>
       </c>
-      <c r="C216" t="s">
-        <v>1996</v>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>301XG</t>
+        </is>
       </c>
       <c r="D216" t="s">
         <v>1895</v>
@@ -32008,8 +32438,10 @@
       <c r="B217" t="s">
         <v>312</v>
       </c>
-      <c r="C217" t="s">
-        <v>1999</v>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="D217" t="s">
         <v>1623</v>
@@ -32091,8 +32523,10 @@
       <c r="B218" t="s">
         <v>312</v>
       </c>
-      <c r="C218" t="s">
-        <v>2006</v>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="D218" t="s">
         <v>1623</v>
@@ -32174,8 +32608,10 @@
       <c r="B219" t="s">
         <v>312</v>
       </c>
-      <c r="C219" t="s">
-        <v>2010</v>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>150DH</t>
+        </is>
       </c>
       <c r="D219" t="s">
         <v>1623</v>
@@ -32257,8 +32693,10 @@
       <c r="B220" t="s">
         <v>312</v>
       </c>
-      <c r="C220" t="s">
-        <v>2014</v>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>151DH</t>
+        </is>
       </c>
       <c r="D220" t="s">
         <v>1623</v>
@@ -32340,8 +32778,10 @@
       <c r="B221" t="s">
         <v>312</v>
       </c>
-      <c r="C221" t="s">
-        <v>2018</v>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>150DHXG</t>
+        </is>
       </c>
       <c r="D221" t="s">
         <v>1419</v>
@@ -32423,8 +32863,10 @@
       <c r="B222" t="s">
         <v>312</v>
       </c>
-      <c r="C222" t="s">
-        <v>2022</v>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>151DHXG</t>
+        </is>
       </c>
       <c r="D222" t="s">
         <v>1419</v>
@@ -32672,8 +33114,10 @@
       <c r="B225" t="s">
         <v>324</v>
       </c>
-      <c r="C225" t="s">
-        <v>2035</v>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>200HG</t>
+        </is>
       </c>
       <c r="D225" t="s">
         <v>886</v>
@@ -32755,8 +33199,10 @@
       <c r="B226" t="s">
         <v>324</v>
       </c>
-      <c r="C226" t="s">
-        <v>2040</v>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>200XG</t>
+        </is>
       </c>
       <c r="D226" t="s">
         <v>1874</v>
@@ -32838,8 +33284,10 @@
       <c r="B227" t="s">
         <v>332</v>
       </c>
-      <c r="C227" t="s">
-        <v>2043</v>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="D227" t="s">
         <v>977</v>
@@ -32921,8 +33369,10 @@
       <c r="B228" t="s">
         <v>332</v>
       </c>
-      <c r="C228" t="s">
-        <v>2050</v>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="D228" t="s">
         <v>977</v>
@@ -33004,8 +33454,10 @@
       <c r="B229" t="s">
         <v>332</v>
       </c>
-      <c r="C229" t="s">
-        <v>2054</v>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>70HG</t>
+        </is>
       </c>
       <c r="D229" t="s">
         <v>886</v>
@@ -33087,8 +33539,10 @@
       <c r="B230" t="s">
         <v>332</v>
       </c>
-      <c r="C230" t="s">
-        <v>2058</v>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>71HG</t>
+        </is>
       </c>
       <c r="D230" t="s">
         <v>886</v>
@@ -33170,8 +33624,10 @@
       <c r="B231" t="s">
         <v>332</v>
       </c>
-      <c r="C231" t="s">
-        <v>2062</v>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>70XG</t>
+        </is>
       </c>
       <c r="D231" t="s">
         <v>1419</v>
@@ -33253,8 +33709,10 @@
       <c r="B232" t="s">
         <v>332</v>
       </c>
-      <c r="C232" t="s">
-        <v>2066</v>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>71XG</t>
+        </is>
       </c>
       <c r="D232" t="s">
         <v>1419</v>
@@ -33336,8 +33794,10 @@
       <c r="B233" t="s">
         <v>338</v>
       </c>
-      <c r="C233" t="s">
-        <v>2070</v>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="D233" t="s">
         <v>977</v>
@@ -33422,8 +33882,10 @@
       <c r="B234" t="s">
         <v>338</v>
       </c>
-      <c r="C234" t="s">
-        <v>2078</v>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="D234" t="s">
         <v>977</v>
@@ -33508,8 +33970,10 @@
       <c r="B235" t="s">
         <v>338</v>
       </c>
-      <c r="C235" t="s">
-        <v>2082</v>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>150HG</t>
+        </is>
       </c>
       <c r="D235" t="s">
         <v>886</v>
@@ -33594,8 +34058,10 @@
       <c r="B236" t="s">
         <v>338</v>
       </c>
-      <c r="C236" t="s">
-        <v>2086</v>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>151HG</t>
+        </is>
       </c>
       <c r="D236" t="s">
         <v>886</v>
@@ -33680,8 +34146,10 @@
       <c r="B237" t="s">
         <v>338</v>
       </c>
-      <c r="C237" t="s">
-        <v>2090</v>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>150XG</t>
+        </is>
       </c>
       <c r="D237" t="s">
         <v>1874</v>
@@ -33766,8 +34234,10 @@
       <c r="B238" t="s">
         <v>338</v>
       </c>
-      <c r="C238" t="s">
-        <v>2094</v>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>151XG</t>
+        </is>
       </c>
       <c r="D238" t="s">
         <v>1874</v>
@@ -33852,8 +34322,10 @@
       <c r="B239" t="s">
         <v>345</v>
       </c>
-      <c r="C239" t="s">
-        <v>2098</v>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>300XG</t>
+        </is>
       </c>
       <c r="D239" t="s">
         <v>1895</v>
@@ -33950,8 +34422,10 @@
       <c r="B240" t="s">
         <v>345</v>
       </c>
-      <c r="C240" t="s">
-        <v>2105</v>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>301XG</t>
+        </is>
       </c>
       <c r="D240" t="s">
         <v>1895</v>
@@ -34048,8 +34522,10 @@
       <c r="B241" t="s">
         <v>345</v>
       </c>
-      <c r="C241" t="s">
-        <v>2109</v>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>300XGLH</t>
+        </is>
       </c>
       <c r="D241" t="s">
         <v>1895</v>
@@ -34146,8 +34622,10 @@
       <c r="B242" t="s">
         <v>345</v>
       </c>
-      <c r="C242" t="s">
-        <v>2113</v>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>301XGLH</t>
+        </is>
       </c>
       <c r="D242" t="s">
         <v>1895</v>
@@ -34410,8 +34888,10 @@
       <c r="B245" t="s">
         <v>360</v>
       </c>
-      <c r="C245" t="s">
-        <v>2127</v>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>150XG</t>
+        </is>
       </c>
       <c r="D245" t="s">
         <v>1419</v>
@@ -34490,8 +34970,10 @@
       <c r="B246" t="s">
         <v>360</v>
       </c>
-      <c r="C246" t="s">
-        <v>2133</v>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>151XG</t>
+        </is>
       </c>
       <c r="D246" t="s">
         <v>1419</v>
@@ -34878,8 +35360,10 @@
       <c r="B251" t="s">
         <v>374</v>
       </c>
-      <c r="C251" t="s">
-        <v>2148</v>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>1000SP</t>
+        </is>
       </c>
       <c r="D251" t="s">
         <v>1409</v>
@@ -34958,8 +35442,10 @@
       <c r="B252" t="s">
         <v>374</v>
       </c>
-      <c r="C252" t="s">
-        <v>2157</v>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>1001SP</t>
+        </is>
       </c>
       <c r="D252" t="s">
         <v>1409</v>
@@ -35038,8 +35524,10 @@
       <c r="B253" t="s">
         <v>374</v>
       </c>
-      <c r="C253" t="s">
-        <v>2161</v>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>1000XT</t>
+        </is>
       </c>
       <c r="D253" t="s">
         <v>977</v>
@@ -35118,8 +35606,10 @@
       <c r="B254" t="s">
         <v>374</v>
       </c>
-      <c r="C254" t="s">
-        <v>2168</v>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>1001XT</t>
+        </is>
       </c>
       <c r="D254" t="s">
         <v>977</v>
@@ -35198,8 +35688,10 @@
       <c r="B255" t="s">
         <v>374</v>
       </c>
-      <c r="C255" t="s">
-        <v>2172</v>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="D255" t="s">
         <v>977</v>
@@ -35278,8 +35770,10 @@
       <c r="B256" t="s">
         <v>374</v>
       </c>
-      <c r="C256" t="s">
-        <v>2178</v>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
       </c>
       <c r="D256" t="s">
         <v>977</v>
@@ -35802,8 +36296,10 @@
       <c r="B263" t="s">
         <v>386</v>
       </c>
-      <c r="C263" t="s">
-        <v>2195</v>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>100HG</t>
+        </is>
       </c>
       <c r="D263" t="s">
         <v>2196</v>
@@ -35888,8 +36384,10 @@
       <c r="B264" t="s">
         <v>386</v>
       </c>
-      <c r="C264" t="s">
-        <v>2206</v>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>101HG</t>
+        </is>
       </c>
       <c r="D264" t="s">
         <v>2196</v>
@@ -35974,8 +36472,10 @@
       <c r="B265" t="s">
         <v>392</v>
       </c>
-      <c r="C265" t="s">
-        <v>2210</v>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>150PG</t>
+        </is>
       </c>
       <c r="D265" t="s">
         <v>1119</v>
@@ -36057,8 +36557,10 @@
       <c r="B266" t="s">
         <v>392</v>
       </c>
-      <c r="C266" t="s">
-        <v>2215</v>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>151PG</t>
+        </is>
       </c>
       <c r="D266" t="s">
         <v>1119</v>
@@ -36140,8 +36642,10 @@
       <c r="B267" t="s">
         <v>392</v>
       </c>
-      <c r="C267" t="s">
-        <v>2219</v>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>150HG</t>
+        </is>
       </c>
       <c r="D267" t="s">
         <v>2196</v>
@@ -36223,8 +36727,10 @@
       <c r="B268" t="s">
         <v>392</v>
       </c>
-      <c r="C268" t="s">
-        <v>2223</v>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>151HG</t>
+        </is>
       </c>
       <c r="D268" t="s">
         <v>2196</v>
@@ -36306,8 +36812,10 @@
       <c r="B269" t="s">
         <v>397</v>
       </c>
-      <c r="C269" t="s">
-        <v>2227</v>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>200HG</t>
+        </is>
       </c>
       <c r="D269" t="s">
         <v>886</v>
@@ -36395,8 +36903,10 @@
       <c r="B270" t="s">
         <v>397</v>
       </c>
-      <c r="C270" t="s">
-        <v>2235</v>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>201HG</t>
+        </is>
       </c>
       <c r="D270" t="s">
         <v>886</v>
@@ -36484,8 +36994,10 @@
       <c r="B271" t="s">
         <v>397</v>
       </c>
-      <c r="C271" t="s">
-        <v>2239</v>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>200XG</t>
+        </is>
       </c>
       <c r="D271" t="s">
         <v>1874</v>
@@ -36573,8 +37085,10 @@
       <c r="B272" t="s">
         <v>397</v>
       </c>
-      <c r="C272" t="s">
-        <v>2243</v>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>201XG</t>
+        </is>
       </c>
       <c r="D272" t="s">
         <v>1874</v>
@@ -36662,8 +37176,10 @@
       <c r="B273" t="s">
         <v>405</v>
       </c>
-      <c r="C273" t="s">
-        <v>2247</v>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>1500HG</t>
+        </is>
       </c>
       <c r="D273" t="s">
         <v>1983</v>
@@ -36742,8 +37258,10 @@
       <c r="B274" t="s">
         <v>405</v>
       </c>
-      <c r="C274" t="s">
-        <v>2255</v>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2000PG</t>
+        </is>
       </c>
       <c r="D274" t="s">
         <v>2256</v>
@@ -36822,8 +37340,10 @@
       <c r="B275" t="s">
         <v>405</v>
       </c>
-      <c r="C275" t="s">
-        <v>2262</v>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2000HG</t>
+        </is>
       </c>
       <c r="D275" t="s">
         <v>977</v>
@@ -36902,8 +37422,10 @@
       <c r="B276" t="s">
         <v>410</v>
       </c>
-      <c r="C276" t="s">
-        <v>2268</v>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="D276" t="s">
         <v>977</v>
@@ -36976,8 +37498,10 @@
       <c r="B277" t="s">
         <v>410</v>
       </c>
-      <c r="C277" t="s">
-        <v>2270</v>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>200HG</t>
+        </is>
       </c>
       <c r="D277" t="s">
         <v>2196</v>
@@ -37050,8 +37574,10 @@
       <c r="B278" t="s">
         <v>410</v>
       </c>
-      <c r="C278" t="s">
-        <v>2272</v>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>201HG</t>
+        </is>
       </c>
       <c r="D278" t="s">
         <v>2196</v>
@@ -37124,8 +37650,10 @@
       <c r="B279" t="s">
         <v>410</v>
       </c>
-      <c r="C279" t="s">
-        <v>2274</v>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>200XG</t>
+        </is>
       </c>
       <c r="D279" t="s">
         <v>1874</v>
@@ -37198,8 +37726,10 @@
       <c r="B280" t="s">
         <v>415</v>
       </c>
-      <c r="C280" t="s">
-        <v>2276</v>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="D280" t="s">
         <v>1983</v>
@@ -37266,8 +37796,10 @@
       <c r="B281" t="s">
         <v>415</v>
       </c>
-      <c r="C281" t="s">
-        <v>2282</v>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>150HG</t>
+        </is>
       </c>
       <c r="D281" t="s">
         <v>2196</v>
@@ -37334,8 +37866,10 @@
       <c r="B282" t="s">
         <v>415</v>
       </c>
-      <c r="C282" t="s">
-        <v>2284</v>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>151HG</t>
+        </is>
       </c>
       <c r="D282" t="s">
         <v>2196</v>
@@ -37402,8 +37936,10 @@
       <c r="B283" t="s">
         <v>415</v>
       </c>
-      <c r="C283" t="s">
-        <v>2286</v>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>150XG</t>
+        </is>
       </c>
       <c r="D283" t="s">
         <v>2287</v>
@@ -37470,8 +38006,10 @@
       <c r="B284" t="s">
         <v>421</v>
       </c>
-      <c r="C284" t="s">
-        <v>2290</v>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>100DHHG</t>
+        </is>
       </c>
       <c r="D284" t="s">
         <v>1042</v>
@@ -37553,8 +38091,10 @@
       <c r="B285" t="s">
         <v>421</v>
       </c>
-      <c r="C285" t="s">
-        <v>2298</v>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>101DHHG</t>
+        </is>
       </c>
       <c r="D285" t="s">
         <v>1042</v>
@@ -37636,8 +38176,10 @@
       <c r="B286" t="s">
         <v>421</v>
       </c>
-      <c r="C286" t="s">
-        <v>2302</v>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>150DHPG</t>
+        </is>
       </c>
       <c r="D286" t="s">
         <v>1883</v>
@@ -37719,8 +38261,10 @@
       <c r="B287" t="s">
         <v>421</v>
       </c>
-      <c r="C287" t="s">
-        <v>2308</v>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>151DHPG</t>
+        </is>
       </c>
       <c r="D287" t="s">
         <v>1883</v>
@@ -37802,8 +38346,10 @@
       <c r="B288" t="s">
         <v>421</v>
       </c>
-      <c r="C288" t="s">
-        <v>2312</v>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>150HG</t>
+        </is>
       </c>
       <c r="D288" t="s">
         <v>1042</v>
@@ -37885,8 +38431,10 @@
       <c r="B289" t="s">
         <v>421</v>
       </c>
-      <c r="C289" t="s">
-        <v>2316</v>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>151HG</t>
+        </is>
       </c>
       <c r="D289" t="s">
         <v>1042</v>
@@ -37968,8 +38516,10 @@
       <c r="B290" t="s">
         <v>421</v>
       </c>
-      <c r="C290" t="s">
-        <v>2320</v>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>150DHHG</t>
+        </is>
       </c>
       <c r="D290" t="s">
         <v>1042</v>
@@ -38051,8 +38601,10 @@
       <c r="B291" t="s">
         <v>421</v>
       </c>
-      <c r="C291" t="s">
-        <v>2324</v>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>151DHHG</t>
+        </is>
       </c>
       <c r="D291" t="s">
         <v>1042</v>
@@ -38134,8 +38686,10 @@
       <c r="B292" t="s">
         <v>421</v>
       </c>
-      <c r="C292" t="s">
-        <v>2328</v>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>300PG</t>
+        </is>
       </c>
       <c r="D292" t="s">
         <v>1883</v>
@@ -38217,8 +38771,10 @@
       <c r="B293" t="s">
         <v>421</v>
       </c>
-      <c r="C293" t="s">
-        <v>2337</v>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>300HG</t>
+        </is>
       </c>
       <c r="D293" t="s">
         <v>1042</v>
@@ -38300,8 +38856,10 @@
       <c r="B294" t="s">
         <v>427</v>
       </c>
-      <c r="C294" t="s">
-        <v>2341</v>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
       </c>
       <c r="D294" t="s">
         <v>923</v>
@@ -38383,8 +38941,10 @@
       <c r="B295" t="s">
         <v>427</v>
       </c>
-      <c r="C295" t="s">
-        <v>2354</v>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="D295" t="s">
         <v>923</v>
@@ -38466,8 +39026,10 @@
       <c r="B296" t="s">
         <v>427</v>
       </c>
-      <c r="C296" t="s">
-        <v>2363</v>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="D296" t="s">
         <v>923</v>
@@ -38549,8 +39111,10 @@
       <c r="B297" t="s">
         <v>427</v>
       </c>
-      <c r="C297" t="s">
-        <v>2372</v>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
       </c>
       <c r="D297" t="s">
         <v>2256</v>
@@ -38632,8 +39196,10 @@
       <c r="B298" t="s">
         <v>433</v>
       </c>
-      <c r="C298" t="s">
-        <v>2382</v>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="D298" t="s">
         <v>1983</v>
@@ -38715,8 +39281,10 @@
       <c r="B299" t="s">
         <v>433</v>
       </c>
-      <c r="C299" t="s">
-        <v>2388</v>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="D299" t="s">
         <v>1983</v>
@@ -38798,8 +39366,10 @@
       <c r="B300" t="s">
         <v>433</v>
       </c>
-      <c r="C300" t="s">
-        <v>2392</v>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>70HG</t>
+        </is>
       </c>
       <c r="D300" t="s">
         <v>2196</v>
@@ -38881,8 +39451,10 @@
       <c r="B301" t="s">
         <v>433</v>
       </c>
-      <c r="C301" t="s">
-        <v>2396</v>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>71HG</t>
+        </is>
       </c>
       <c r="D301" t="s">
         <v>2196</v>
@@ -38964,8 +39536,10 @@
       <c r="B302" t="s">
         <v>433</v>
       </c>
-      <c r="C302" t="s">
-        <v>2400</v>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>70XG</t>
+        </is>
       </c>
       <c r="D302" t="s">
         <v>2287</v>
@@ -39047,8 +39621,10 @@
       <c r="B303" t="s">
         <v>433</v>
       </c>
-      <c r="C303" t="s">
-        <v>2404</v>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>71XG</t>
+        </is>
       </c>
       <c r="D303" t="s">
         <v>2287</v>
@@ -39718,8 +40294,10 @@
       <c r="B310" t="s">
         <v>445</v>
       </c>
-      <c r="C310" t="s">
-        <v>2425</v>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>150MG</t>
+        </is>
       </c>
       <c r="D310" t="s">
         <v>977</v>
@@ -39792,8 +40370,10 @@
       <c r="B311" t="s">
         <v>445</v>
       </c>
-      <c r="C311" t="s">
-        <v>2429</v>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>151MG</t>
+        </is>
       </c>
       <c r="D311" t="s">
         <v>977</v>
@@ -39866,8 +40446,10 @@
       <c r="B312" t="s">
         <v>445</v>
       </c>
-      <c r="C312" t="s">
-        <v>2431</v>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>150HG</t>
+        </is>
       </c>
       <c r="D312" t="s">
         <v>886</v>
@@ -39940,8 +40522,10 @@
       <c r="B313" t="s">
         <v>445</v>
       </c>
-      <c r="C313" t="s">
-        <v>2433</v>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>151HG</t>
+        </is>
       </c>
       <c r="D313" t="s">
         <v>886</v>
@@ -40014,8 +40598,10 @@
       <c r="B314" t="s">
         <v>445</v>
       </c>
-      <c r="C314" t="s">
-        <v>2435</v>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>150XG</t>
+        </is>
       </c>
       <c r="D314" t="s">
         <v>1419</v>
@@ -40088,8 +40674,10 @@
       <c r="B315" t="s">
         <v>445</v>
       </c>
-      <c r="C315" t="s">
-        <v>2437</v>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>151XG</t>
+        </is>
       </c>
       <c r="D315" t="s">
         <v>1419</v>
@@ -40162,8 +40750,10 @@
       <c r="B316" t="s">
         <v>451</v>
       </c>
-      <c r="C316" t="s">
-        <v>2439</v>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="D316" t="s">
         <v>2440</v>
@@ -40266,8 +40856,10 @@
       <c r="B317" t="s">
         <v>451</v>
       </c>
-      <c r="C317" t="s">
-        <v>2448</v>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
       </c>
       <c r="D317" t="s">
         <v>2440</v>
@@ -40370,8 +40962,10 @@
       <c r="B318" t="s">
         <v>451</v>
       </c>
-      <c r="C318" t="s">
-        <v>2450</v>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>300HG</t>
+        </is>
       </c>
       <c r="D318" t="s">
         <v>2451</v>
@@ -40474,8 +41068,10 @@
       <c r="B319" t="s">
         <v>451</v>
       </c>
-      <c r="C319" t="s">
-        <v>2454</v>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>301HG</t>
+        </is>
       </c>
       <c r="D319" t="s">
         <v>2451</v>
@@ -41318,8 +41914,10 @@
       <c r="B330" t="s">
         <v>474</v>
       </c>
-      <c r="C330" t="s">
-        <v>2477</v>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>XG R</t>
+        </is>
       </c>
       <c r="D330" t="s">
         <v>2287</v>
@@ -41392,8 +41990,10 @@
       <c r="B331" t="s">
         <v>474</v>
       </c>
-      <c r="C331" t="s">
-        <v>2483</v>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>XG L</t>
+        </is>
       </c>
       <c r="D331" t="s">
         <v>2287</v>
@@ -41466,8 +42066,10 @@
       <c r="B332" t="s">
         <v>481</v>
       </c>
-      <c r="C332" t="s">
-        <v>2485</v>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="D332" t="s">
         <v>1983</v>
@@ -41561,8 +42163,10 @@
       <c r="B333" t="s">
         <v>481</v>
       </c>
-      <c r="C333" t="s">
-        <v>2493</v>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="D333" t="s">
         <v>1983</v>
@@ -41656,8 +42260,10 @@
       <c r="B334" t="s">
         <v>481</v>
       </c>
-      <c r="C334" t="s">
-        <v>2497</v>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>70HG</t>
+        </is>
       </c>
       <c r="D334" t="s">
         <v>2196</v>
@@ -41751,8 +42357,10 @@
       <c r="B335" t="s">
         <v>481</v>
       </c>
-      <c r="C335" t="s">
-        <v>2501</v>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>71HG</t>
+        </is>
       </c>
       <c r="D335" t="s">
         <v>2196</v>
@@ -41846,8 +42454,10 @@
       <c r="B336" t="s">
         <v>481</v>
       </c>
-      <c r="C336" t="s">
-        <v>2505</v>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>70XG</t>
+        </is>
       </c>
       <c r="D336" t="s">
         <v>2287</v>
@@ -41941,8 +42551,10 @@
       <c r="B337" t="s">
         <v>481</v>
       </c>
-      <c r="C337" t="s">
-        <v>2509</v>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>71XG</t>
+        </is>
       </c>
       <c r="D337" t="s">
         <v>2287</v>
@@ -42036,8 +42648,10 @@
       <c r="B338" t="s">
         <v>492</v>
       </c>
-      <c r="C338" t="s">
-        <v>2513</v>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>150HG</t>
+        </is>
       </c>
       <c r="D338" t="s">
         <v>1042</v>
@@ -42119,8 +42733,10 @@
       <c r="B339" t="s">
         <v>492</v>
       </c>
-      <c r="C339" t="s">
-        <v>2519</v>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>151HG</t>
+        </is>
       </c>
       <c r="D339" t="s">
         <v>1042</v>
@@ -42202,8 +42818,10 @@
       <c r="B340" t="s">
         <v>492</v>
       </c>
-      <c r="C340" t="s">
-        <v>2523</v>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>150DHPG</t>
+        </is>
       </c>
       <c r="D340" t="s">
         <v>1883</v>
@@ -42285,8 +42903,10 @@
       <c r="B341" t="s">
         <v>492</v>
       </c>
-      <c r="C341" t="s">
-        <v>2527</v>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>151DHPG</t>
+        </is>
       </c>
       <c r="D341" t="s">
         <v>1883</v>
@@ -42368,8 +42988,10 @@
       <c r="B342" t="s">
         <v>492</v>
       </c>
-      <c r="C342" t="s">
-        <v>2531</v>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>150DHHG</t>
+        </is>
       </c>
       <c r="D342" t="s">
         <v>1042</v>
@@ -42451,8 +43073,10 @@
       <c r="B343" t="s">
         <v>492</v>
       </c>
-      <c r="C343" t="s">
-        <v>2535</v>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>151DHHG</t>
+        </is>
       </c>
       <c r="D343" t="s">
         <v>1042</v>
@@ -42534,8 +43158,10 @@
       <c r="B344" t="s">
         <v>492</v>
       </c>
-      <c r="C344" t="s">
-        <v>2539</v>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>300PG</t>
+        </is>
       </c>
       <c r="D344" t="s">
         <v>1883</v>
@@ -42617,8 +43243,10 @@
       <c r="B345" t="s">
         <v>492</v>
       </c>
-      <c r="C345" t="s">
-        <v>2544</v>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>300HG</t>
+        </is>
       </c>
       <c r="D345" t="s">
         <v>1042</v>
@@ -42700,8 +43328,10 @@
       <c r="B346" t="s">
         <v>498</v>
       </c>
-      <c r="C346" t="s">
-        <v>2548</v>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>XG RIGHT</t>
+        </is>
       </c>
       <c r="D346" t="s">
         <v>2287</v>
@@ -42786,8 +43416,10 @@
       <c r="B347" t="s">
         <v>498</v>
       </c>
-      <c r="C347" t="s">
-        <v>2555</v>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>XG LEFT</t>
+        </is>
       </c>
       <c r="D347" t="s">
         <v>2287</v>
@@ -42872,8 +43504,10 @@
       <c r="B348" t="s">
         <v>505</v>
       </c>
-      <c r="C348" t="s">
-        <v>2559</v>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>150HG</t>
+        </is>
       </c>
       <c r="D348" t="s">
         <v>2196</v>
@@ -42952,8 +43586,10 @@
       <c r="B349" t="s">
         <v>505</v>
       </c>
-      <c r="C349" t="s">
-        <v>2565</v>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>151HG</t>
+        </is>
       </c>
       <c r="D349" t="s">
         <v>2196</v>
@@ -43032,8 +43668,10 @@
       <c r="B350" t="s">
         <v>511</v>
       </c>
-      <c r="C350" t="s">
-        <v>2569</v>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="D350" t="s">
         <v>1983</v>
@@ -43115,8 +43753,10 @@
       <c r="B351" t="s">
         <v>511</v>
       </c>
-      <c r="C351" t="s">
-        <v>2572</v>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="D351" t="s">
         <v>1983</v>
@@ -43198,8 +43838,10 @@
       <c r="B352" t="s">
         <v>511</v>
       </c>
-      <c r="C352" t="s">
-        <v>2574</v>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>150HG</t>
+        </is>
       </c>
       <c r="D352" t="s">
         <v>2196</v>
@@ -43281,8 +43923,10 @@
       <c r="B353" t="s">
         <v>511</v>
       </c>
-      <c r="C353" t="s">
-        <v>2576</v>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>151HG</t>
+        </is>
       </c>
       <c r="D353" t="s">
         <v>2196</v>
@@ -43364,8 +44008,10 @@
       <c r="B354" t="s">
         <v>511</v>
       </c>
-      <c r="C354" t="s">
-        <v>2578</v>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>150XG</t>
+        </is>
       </c>
       <c r="D354" t="s">
         <v>2287</v>
@@ -43447,8 +44093,10 @@
       <c r="B355" t="s">
         <v>511</v>
       </c>
-      <c r="C355" t="s">
-        <v>2580</v>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>151XG</t>
+        </is>
       </c>
       <c r="D355" t="s">
         <v>2287</v>
@@ -43974,8 +44622,10 @@
       <c r="B362" t="s">
         <v>520</v>
       </c>
-      <c r="C362" t="s">
-        <v>2596</v>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
       </c>
       <c r="D362" t="s">
         <v>923</v>
@@ -44057,8 +44707,10 @@
       <c r="B363" t="s">
         <v>520</v>
       </c>
-      <c r="C363" t="s">
-        <v>2603</v>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="D363" t="s">
         <v>923</v>
@@ -44140,8 +44792,10 @@
       <c r="B364" t="s">
         <v>520</v>
       </c>
-      <c r="C364" t="s">
-        <v>2608</v>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="D364" t="s">
         <v>923</v>
@@ -44223,8 +44877,10 @@
       <c r="B365" t="s">
         <v>520</v>
       </c>
-      <c r="C365" t="s">
-        <v>2613</v>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
       </c>
       <c r="D365" t="s">
         <v>2256</v>
@@ -44306,8 +44962,10 @@
       <c r="B366" t="s">
         <v>526</v>
       </c>
-      <c r="C366" t="s">
-        <v>2618</v>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="D366" t="s">
         <v>1883</v>
@@ -44365,8 +45023,10 @@
       <c r="B367" t="s">
         <v>526</v>
       </c>
-      <c r="C367" t="s">
-        <v>2623</v>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="D367" t="s">
         <v>1883</v>
@@ -44424,8 +45084,10 @@
       <c r="B368" t="s">
         <v>526</v>
       </c>
-      <c r="C368" t="s">
-        <v>2625</v>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
       </c>
       <c r="D368" t="s">
         <v>1883</v>
@@ -44483,8 +45145,10 @@
       <c r="B369" t="s">
         <v>526</v>
       </c>
-      <c r="C369" t="s">
-        <v>2628</v>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
       </c>
       <c r="D369" t="s">
         <v>1883</v>
@@ -44542,8 +45206,10 @@
       <c r="B370" t="s">
         <v>526</v>
       </c>
-      <c r="C370" t="s">
-        <v>2630</v>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="D370" t="s">
         <v>743</v>
@@ -44601,8 +45267,10 @@
       <c r="B371" t="s">
         <v>526</v>
       </c>
-      <c r="C371" t="s">
-        <v>2635</v>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
       </c>
       <c r="D371" t="s">
         <v>743</v>
@@ -44660,8 +45328,10 @@
       <c r="B372" t="s">
         <v>532</v>
       </c>
-      <c r="C372" t="s">
-        <v>2637</v>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="D372" t="s">
         <v>1983</v>
@@ -44743,8 +45413,10 @@
       <c r="B373" t="s">
         <v>532</v>
       </c>
-      <c r="C373" t="s">
-        <v>2644</v>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="D373" t="s">
         <v>1983</v>
@@ -44826,8 +45498,10 @@
       <c r="B374" t="s">
         <v>532</v>
       </c>
-      <c r="C374" t="s">
-        <v>2648</v>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>200PG</t>
+        </is>
       </c>
       <c r="D374" t="s">
         <v>1119</v>
@@ -44909,8 +45583,10 @@
       <c r="B375" t="s">
         <v>532</v>
       </c>
-      <c r="C375" t="s">
-        <v>2655</v>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>201PG</t>
+        </is>
       </c>
       <c r="D375" t="s">
         <v>1119</v>
@@ -44992,8 +45668,10 @@
       <c r="B376" t="s">
         <v>538</v>
       </c>
-      <c r="C376" t="s">
-        <v>2659</v>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>GT2000</t>
+        </is>
       </c>
       <c r="D376" t="s">
         <v>2660</v>
@@ -45066,8 +45744,10 @@
       <c r="B377" t="s">
         <v>538</v>
       </c>
-      <c r="C377" t="s">
-        <v>2668</v>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>GT3000</t>
+        </is>
       </c>
       <c r="D377" t="s">
         <v>2660</v>
@@ -45140,8 +45820,10 @@
       <c r="B378" t="s">
         <v>544</v>
       </c>
-      <c r="C378" t="s">
-        <v>2675</v>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="D378" t="s">
         <v>2196</v>
@@ -45223,8 +45905,10 @@
       <c r="B379" t="s">
         <v>544</v>
       </c>
-      <c r="C379" t="s">
-        <v>2681</v>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="D379" t="s">
         <v>2196</v>
@@ -45306,8 +45990,10 @@
       <c r="B380" t="s">
         <v>550</v>
       </c>
-      <c r="C380" t="s">
-        <v>2685</v>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>150HG</t>
+        </is>
       </c>
       <c r="D380" t="s">
         <v>2196</v>
@@ -45380,8 +46066,10 @@
       <c r="B381" t="s">
         <v>550</v>
       </c>
-      <c r="C381" t="s">
-        <v>2688</v>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>151HG</t>
+        </is>
       </c>
       <c r="D381" t="s">
         <v>2196</v>
@@ -45454,8 +46142,10 @@
       <c r="B382" t="s">
         <v>557</v>
       </c>
-      <c r="C382" t="s">
-        <v>2690</v>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
       </c>
       <c r="D382" t="s">
         <v>2196</v>
@@ -45537,8 +46227,10 @@
       <c r="B383" t="s">
         <v>557</v>
       </c>
-      <c r="C383" t="s">
-        <v>2696</v>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>R 带线</t>
+        </is>
       </c>
       <c r="D383" t="s">
         <v>2196</v>
@@ -45620,8 +46312,10 @@
       <c r="B384" t="s">
         <v>563</v>
       </c>
-      <c r="C384" t="s">
-        <v>2701</v>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>200PG</t>
+        </is>
       </c>
       <c r="D384" t="s">
         <v>1119</v>
@@ -45703,8 +46397,10 @@
       <c r="B385" t="s">
         <v>563</v>
       </c>
-      <c r="C385" t="s">
-        <v>2707</v>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>201PG</t>
+        </is>
       </c>
       <c r="D385" t="s">
         <v>1119</v>
@@ -45786,8 +46482,10 @@
       <c r="B386" t="s">
         <v>569</v>
       </c>
-      <c r="C386" t="s">
-        <v>2711</v>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="D386" t="s">
         <v>951</v>
@@ -45860,8 +46558,10 @@
       <c r="B387" t="s">
         <v>569</v>
       </c>
-      <c r="C387" t="s">
-        <v>2719</v>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="D387" t="s">
         <v>951</v>
